--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -70,15 +70,6 @@
     <x:t>SUPPORT</x:t>
   </x:si>
   <x:si>
-    <x:t>H2IL13153</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BUDZINSKI, NIKKI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13</x:t>
-  </x:si>
-  <x:si>
     <x:t>C00835959</x:t>
   </x:si>
   <x:si>
@@ -145,15 +136,6 @@
     <x:t>KRISHNAMOORTHI, S</x:t>
   </x:si>
   <x:si>
-    <x:t>H6TX18232</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MENEFEE, CHRISTIAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18</x:t>
-  </x:si>
-  <x:si>
     <x:t>S6AL00476</x:t>
   </x:si>
   <x:si>
@@ -185,12 +167,6 @@
   </x:si>
   <x:si>
     <x:t>22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6IL02298</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PETERS, ROBERT JAMES</x:t>
   </x:si>
   <x:si>
     <x:t>H6TX08209</x:t>
@@ -273,8 +249,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J16" totalsRowShown="0">
-  <x:autoFilter ref="A1:J16"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J13" totalsRowShown="0">
+  <x:autoFilter ref="A1:J13"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -579,7 +555,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J16"/>
+  <x:dimension ref="A1:J13"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -650,7 +626,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="H2" s="1">
-        <x:v>557012</x:v>
+        <x:v>41493</x:v>
       </x:c>
       <x:c r="I2" s="1">
         <x:v>2026</x:v>
@@ -661,92 +637,92 @@
     </x:row>
     <x:row r="3" spans="1:10">
       <x:c r="A3" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F3" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="G3" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="H3" s="1">
-        <x:v>83860</x:v>
+        <x:v>672092</x:v>
       </x:c>
       <x:c r="I3" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J3" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:10">
       <x:c r="A4" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F4" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G4" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="H4" s="1">
-        <x:v>2475788</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="I4" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J4" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:10">
       <x:c r="A5" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F5" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="G5" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="H5" s="1">
-        <x:v>91656</x:v>
+        <x:v>418060</x:v>
       </x:c>
       <x:c r="I5" s="1">
         <x:v>2026</x:v>
@@ -757,28 +733,28 @@
     </x:row>
     <x:row r="6" spans="1:10">
       <x:c r="A6" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F6" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="G6" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H6" s="1">
-        <x:v>418060</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="I6" s="1">
         <x:v>2026</x:v>
@@ -795,22 +771,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="D7" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="E7" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="F7" s="1" t="s">
         <x:v>37</x:v>
-      </x:c>
-      <x:c r="D7" s="1" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="E7" s="1" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="F7" s="1" t="s">
-        <x:v>40</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="H7" s="1">
-        <x:v>285008</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="I7" s="1">
         <x:v>2026</x:v>
@@ -821,28 +797,28 @@
     </x:row>
     <x:row r="8" spans="1:10">
       <x:c r="A8" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="D8" s="1" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="D8" s="1" t="s">
+      <x:c r="E8" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="F8" s="1" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="E8" s="1" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="F8" s="1" t="s">
-        <x:v>40</x:v>
-      </x:c>
       <x:c r="G8" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="H8" s="1">
-        <x:v>30183</x:v>
+        <x:v>5031161</x:v>
       </x:c>
       <x:c r="I8" s="1">
         <x:v>2026</x:v>
@@ -853,28 +829,28 @@
     </x:row>
     <x:row r="9" spans="1:10">
       <x:c r="A9" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F9" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="H9" s="1">
-        <x:v>1564215</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="I9" s="1">
         <x:v>2026</x:v>
@@ -885,28 +861,28 @@
     </x:row>
     <x:row r="10" spans="1:10">
       <x:c r="A10" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F10" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="H10" s="1">
-        <x:v>5031161</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="I10" s="1">
         <x:v>2026</x:v>
@@ -917,28 +893,28 @@
     </x:row>
     <x:row r="11" spans="1:10">
       <x:c r="A11" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F11" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="H11" s="1">
-        <x:v>80948</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="I11" s="1">
         <x:v>2026</x:v>
@@ -949,162 +925,66 @@
     </x:row>
     <x:row r="12" spans="1:10">
       <x:c r="A12" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D12" s="1" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="D12" s="1" t="s">
-        <x:v>55</x:v>
-      </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F12" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H12" s="1">
-        <x:v>141263</x:v>
+        <x:v>4697360</x:v>
       </x:c>
       <x:c r="I12" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J12" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:10">
       <x:c r="A13" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="H13" s="1">
-        <x:v>817065</x:v>
+        <x:v>119644</x:v>
       </x:c>
       <x:c r="I13" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J13" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:10">
-      <x:c r="A14" s="1" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="B14" s="1" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C14" s="1" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="D14" s="1" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="E14" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F14" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G14" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="H14" s="1">
-        <x:v>771658</x:v>
-      </x:c>
-      <x:c r="I14" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J14" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:10">
-      <x:c r="A15" s="1" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="B15" s="1" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C15" s="1" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="D15" s="1" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="E15" s="1" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="F15" s="1" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="G15" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="H15" s="1">
-        <x:v>9866096</x:v>
-      </x:c>
-      <x:c r="I15" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J15" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:10">
-      <x:c r="A16" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B16" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C16" s="1" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="D16" s="1" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="E16" s="1" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="F16" s="1" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="G16" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="H16" s="1">
-        <x:v>119644</x:v>
-      </x:c>
-      <x:c r="I16" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J16" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -88,6 +88,24 @@
     <x:t>OPPOSE</x:t>
   </x:si>
   <x:si>
+    <x:t>C00915181</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FELLOWSHIP PAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H0GA14030</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FULLER, CLAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GA</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00836221</x:t>
   </x:si>
   <x:si>
@@ -152,9 +170,6 @@
   </x:si>
   <x:si>
     <x:t>MOORE, TIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14</x:t>
   </x:si>
   <x:si>
     <x:t>NC</x:t>
@@ -249,8 +264,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J13" totalsRowShown="0">
-  <x:autoFilter ref="A1:J13"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J14" totalsRowShown="0">
+  <x:autoFilter ref="A1:J14"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -555,7 +570,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J13"/>
+  <x:dimension ref="A1:J14"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -690,7 +705,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="H4" s="1">
-        <x:v>91656</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="I4" s="1">
         <x:v>2026</x:v>
@@ -701,28 +716,28 @@
     </x:row>
     <x:row r="5" spans="1:10">
       <x:c r="A5" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F5" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G5" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H5" s="1">
-        <x:v>418060</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="I5" s="1">
         <x:v>2026</x:v>
@@ -733,28 +748,28 @@
     </x:row>
     <x:row r="6" spans="1:10">
       <x:c r="A6" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F6" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G6" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H6" s="1">
-        <x:v>285008</x:v>
+        <x:v>418060</x:v>
       </x:c>
       <x:c r="I6" s="1">
         <x:v>2026</x:v>
@@ -771,22 +786,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F7" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="H7" s="1">
-        <x:v>30183</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="I7" s="1">
         <x:v>2026</x:v>
@@ -797,28 +812,28 @@
     </x:row>
     <x:row r="8" spans="1:10">
       <x:c r="A8" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F8" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H8" s="1">
-        <x:v>5031161</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="I8" s="1">
         <x:v>2026</x:v>
@@ -829,28 +844,28 @@
     </x:row>
     <x:row r="9" spans="1:10">
       <x:c r="A9" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F9" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="H9" s="1">
-        <x:v>80948</x:v>
+        <x:v>5031161</x:v>
       </x:c>
       <x:c r="I9" s="1">
         <x:v>2026</x:v>
@@ -861,28 +876,28 @@
     </x:row>
     <x:row r="10" spans="1:10">
       <x:c r="A10" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F10" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="H10" s="1">
-        <x:v>141263</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="I10" s="1">
         <x:v>2026</x:v>
@@ -893,28 +908,28 @@
     </x:row>
     <x:row r="11" spans="1:10">
       <x:c r="A11" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F11" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H11" s="1">
-        <x:v>771658</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="I11" s="1">
         <x:v>2026</x:v>
@@ -925,65 +940,97 @@
     </x:row>
     <x:row r="12" spans="1:10">
       <x:c r="A12" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F12" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H12" s="1">
-        <x:v>4697360</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="I12" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J12" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:10">
       <x:c r="A13" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="H13" s="1">
+        <x:v>4697360</x:v>
+      </x:c>
+      <x:c r="I13" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J13" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:10">
+      <x:c r="A14" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B14" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C14" s="1" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="D14" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="E14" s="1" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F14" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="G14" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="H14" s="1">
         <x:v>119644</x:v>
       </x:c>
-      <x:c r="I13" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J13" s="1" t="s">
+      <x:c r="I14" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J14" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -70,6 +70,18 @@
     <x:t>SUPPORT</x:t>
   </x:si>
   <x:si>
+    <x:t>H6GA13070</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CLARK, JASMINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GA</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00835959</x:t>
   </x:si>
   <x:si>
@@ -103,9 +115,6 @@
     <x:t>14</x:t>
   </x:si>
   <x:si>
-    <x:t>GA</x:t>
-  </x:si>
-  <x:si>
     <x:t>C00836221</x:t>
   </x:si>
   <x:si>
@@ -175,6 +184,15 @@
     <x:t>NC</x:t>
   </x:si>
   <x:si>
+    <x:t>S6KY00302</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MORRIS, NATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KY</x:t>
+  </x:si>
+  <x:si>
     <x:t>H6TX22283</x:t>
   </x:si>
   <x:si>
@@ -182,6 +200,15 @@
   </x:si>
   <x:si>
     <x:t>22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>S6NE00129</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RICKETTS, PETE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NE</x:t>
   </x:si>
   <x:si>
     <x:t>H6TX08209</x:t>
@@ -264,8 +291,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J14" totalsRowShown="0">
-  <x:autoFilter ref="A1:J14"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J17" totalsRowShown="0">
+  <x:autoFilter ref="A1:J17"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -570,7 +597,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J14"/>
+  <x:dimension ref="A1:J17"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -652,92 +679,92 @@
     </x:row>
     <x:row r="3" spans="1:10">
       <x:c r="A3" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B3" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C3" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="B3" s="1" t="s">
+      <x:c r="D3" s="1" t="s">
         <x:v>19</x:v>
-      </x:c>
-      <x:c r="C3" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D3" s="1" t="s">
-        <x:v>21</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F3" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G3" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="H3" s="1">
-        <x:v>672092</x:v>
+        <x:v>102144</x:v>
       </x:c>
       <x:c r="I3" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J3" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:10">
       <x:c r="A4" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B4" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C4" s="1" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="B4" s="1" t="s">
+      <x:c r="D4" s="1" t="s">
         <x:v>25</x:v>
-      </x:c>
-      <x:c r="C4" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D4" s="1" t="s">
-        <x:v>27</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F4" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G4" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H4" s="1">
-        <x:v>300000</x:v>
+        <x:v>672092</x:v>
       </x:c>
       <x:c r="I4" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J4" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:10">
       <x:c r="A5" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B5" s="1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C5" s="1" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="B5" s="1" t="s">
+      <x:c r="D5" s="1" t="s">
         <x:v>31</x:v>
-      </x:c>
-      <x:c r="C5" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="D5" s="1" t="s">
-        <x:v>33</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F5" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="G5" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="H5" s="1">
-        <x:v>91656</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="I5" s="1">
         <x:v>2026</x:v>
@@ -748,28 +775,28 @@
     </x:row>
     <x:row r="6" spans="1:10">
       <x:c r="A6" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D6" s="1" t="s">
         <x:v>36</x:v>
-      </x:c>
-      <x:c r="D6" s="1" t="s">
-        <x:v>37</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F6" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G6" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="G6" s="1" t="s">
-        <x:v>39</x:v>
-      </x:c>
       <x:c r="H6" s="1">
-        <x:v>418060</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="I6" s="1">
         <x:v>2026</x:v>
@@ -780,28 +807,28 @@
     </x:row>
     <x:row r="7" spans="1:10">
       <x:c r="A7" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D7" s="1" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D7" s="1" t="s">
+      <x:c r="E7" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F7" s="1" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="E7" s="1" t="s">
+      <x:c r="G7" s="1" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F7" s="1" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="G7" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
       <x:c r="H7" s="1">
-        <x:v>285008</x:v>
+        <x:v>418060</x:v>
       </x:c>
       <x:c r="I7" s="1">
         <x:v>2026</x:v>
@@ -818,22 +845,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="D8" s="1" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="D8" s="1" t="s">
+      <x:c r="E8" s="1" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="E8" s="1" t="s">
-        <x:v>42</x:v>
-      </x:c>
       <x:c r="F8" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="H8" s="1">
-        <x:v>30183</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="I8" s="1">
         <x:v>2026</x:v>
@@ -844,28 +871,28 @@
     </x:row>
     <x:row r="9" spans="1:10">
       <x:c r="A9" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="D9" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="E9" s="1" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F9" s="1" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="D9" s="1" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="E9" s="1" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="F9" s="1" t="s">
-        <x:v>48</x:v>
-      </x:c>
       <x:c r="G9" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H9" s="1">
-        <x:v>5031161</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="I9" s="1">
         <x:v>2026</x:v>
@@ -876,28 +903,28 @@
     </x:row>
     <x:row r="10" spans="1:10">
       <x:c r="A10" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D10" s="1" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="D10" s="1" t="s">
+      <x:c r="E10" s="1" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F10" s="1" t="s">
         <x:v>51</x:v>
-      </x:c>
-      <x:c r="E10" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F10" s="1" t="s">
-        <x:v>28</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
         <x:v>52</x:v>
       </x:c>
       <x:c r="H10" s="1">
-        <x:v>80948</x:v>
+        <x:v>5031161</x:v>
       </x:c>
       <x:c r="I10" s="1">
         <x:v>2026</x:v>
@@ -908,10 +935,10 @@
     </x:row>
     <x:row r="11" spans="1:10">
       <x:c r="A11" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
         <x:v>53</x:v>
@@ -923,13 +950,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F11" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G11" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="G11" s="1" t="s">
-        <x:v>35</x:v>
-      </x:c>
       <x:c r="H11" s="1">
-        <x:v>141263</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="I11" s="1">
         <x:v>2026</x:v>
@@ -940,10 +967,10 @@
     </x:row>
     <x:row r="12" spans="1:10">
       <x:c r="A12" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
         <x:v>56</x:v>
@@ -952,16 +979,16 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F12" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="H12" s="1">
-        <x:v>771658</x:v>
+        <x:v>850000</x:v>
       </x:c>
       <x:c r="I12" s="1">
         <x:v>2026</x:v>
@@ -972,66 +999,162 @@
     </x:row>
     <x:row r="13" spans="1:10">
       <x:c r="A13" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H13" s="1">
-        <x:v>4697360</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="I13" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J13" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:10">
       <x:c r="A14" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B14" s="1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C14" s="1" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="D14" s="1" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="E14" s="1" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F14" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="G14" s="1" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="H14" s="1">
+        <x:v>350000</x:v>
+      </x:c>
+      <x:c r="I14" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J14" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:10">
+      <x:c r="A15" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B15" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C15" s="1" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="D15" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E15" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F15" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G15" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="H15" s="1">
+        <x:v>771658</x:v>
+      </x:c>
+      <x:c r="I15" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J15" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:10">
+      <x:c r="A16" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B16" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C16" s="1" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="D16" s="1" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="E16" s="1" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F16" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="G16" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="H16" s="1">
+        <x:v>4697360</x:v>
+      </x:c>
+      <x:c r="I16" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J16" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:10">
+      <x:c r="A17" s="1" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B14" s="1" t="s">
+      <x:c r="B17" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="C14" s="1" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="D14" s="1" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="E14" s="1" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="F14" s="1" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="G14" s="1" t="s">
+      <x:c r="C17" s="1" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="D17" s="1" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="E17" s="1" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F17" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="G17" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="H14" s="1">
+      <x:c r="H17" s="1">
         <x:v>119644</x:v>
       </x:c>
-      <x:c r="I14" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J14" s="1" t="s">
-        <x:v>23</x:v>
+      <x:c r="I17" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J17" s="1" t="s">
+        <x:v>27</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -700,7 +700,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="H3" s="1">
-        <x:v>102144</x:v>
+        <x:v>161489</x:v>
       </x:c>
       <x:c r="I3" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -700,7 +700,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="H3" s="1">
-        <x:v>161489</x:v>
+        <x:v>882245</x:v>
       </x:c>
       <x:c r="I3" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -700,7 +700,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="H3" s="1">
-        <x:v>882245</x:v>
+        <x:v>996447</x:v>
       </x:c>
       <x:c r="I3" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -700,7 +700,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="H3" s="1">
-        <x:v>996447</x:v>
+        <x:v>1052492</x:v>
       </x:c>
       <x:c r="I3" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -82,6 +82,24 @@
     <x:t>GA</x:t>
   </x:si>
   <x:si>
+    <x:t>C00915181</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FELLOWSHIP PAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>S6GA00390</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COLLINS, MICHAEL A JR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Senate</x:t>
+  </x:si>
+  <x:si>
+    <x:t>00</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00835959</x:t>
   </x:si>
   <x:si>
@@ -100,12 +118,6 @@
     <x:t>OPPOSE</x:t>
   </x:si>
   <x:si>
-    <x:t>C00915181</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FELLOWSHIP PAC</x:t>
-  </x:si>
-  <x:si>
     <x:t>H0GA14030</x:t>
   </x:si>
   <x:si>
@@ -151,9 +163,6 @@
     <x:t>KELLY, ROBIN</x:t>
   </x:si>
   <x:si>
-    <x:t>Senate</x:t>
-  </x:si>
-  <x:si>
     <x:t/>
   </x:si>
   <x:si>
@@ -163,15 +172,27 @@
     <x:t>KRISHNAMOORTHI, S</x:t>
   </x:si>
   <x:si>
+    <x:t>S6LA00664</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LETLOW, JULIA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>S6LA00540</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIGUEZ, BLAKE</x:t>
+  </x:si>
+  <x:si>
     <x:t>S6AL00476</x:t>
   </x:si>
   <x:si>
     <x:t>MOORE, FELIX BARRY</x:t>
   </x:si>
   <x:si>
-    <x:t>00</x:t>
-  </x:si>
-  <x:si>
     <x:t>AL</x:t>
   </x:si>
   <x:si>
@@ -200,6 +221,12 @@
   </x:si>
   <x:si>
     <x:t>22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>S6TX00388</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAXTON, WARREN KENNETH JR.</x:t>
   </x:si>
   <x:si>
     <x:t>S6NE00129</x:t>
@@ -291,8 +318,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J17" totalsRowShown="0">
-  <x:autoFilter ref="A1:J17"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J22" totalsRowShown="0">
+  <x:autoFilter ref="A1:J22"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -597,14 +624,14 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J17"/>
+  <x:dimension ref="A1:J22"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
     <x:col min="1" max="1" width="15.710625" style="1" customWidth="1"/>
     <x:col min="2" max="2" width="23.424911" style="1" customWidth="1"/>
     <x:col min="3" max="3" width="14.853482" style="1" customWidth="1"/>
-    <x:col min="4" max="4" width="25.139196" style="1" customWidth="1"/>
+    <x:col min="4" max="4" width="29.424911" style="1" customWidth="1"/>
     <x:col min="5" max="5" width="17.853482" style="1" customWidth="1"/>
     <x:col min="6" max="6" width="25.282054" style="1" customWidth="1"/>
     <x:col min="7" max="7" width="23.424911" style="1" customWidth="1"/>
@@ -723,22 +750,22 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F4" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G4" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="H4" s="1">
-        <x:v>672092</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I4" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J4" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:10">
@@ -761,42 +788,42 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="G5" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H5" s="1">
-        <x:v>300000</x:v>
+        <x:v>672092</x:v>
       </x:c>
       <x:c r="I5" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J5" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:10">
       <x:c r="A6" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C6" s="1" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C6" s="1" t="s">
+      <x:c r="D6" s="1" t="s">
         <x:v>35</x:v>
-      </x:c>
-      <x:c r="D6" s="1" t="s">
-        <x:v>36</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F6" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="G6" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="H6" s="1">
-        <x:v>91656</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="I6" s="1">
         <x:v>2026</x:v>
@@ -807,10 +834,10 @@
     </x:row>
     <x:row r="7" spans="1:10">
       <x:c r="A7" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
         <x:v>39</x:v>
@@ -828,7 +855,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="H7" s="1">
-        <x:v>418060</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="I7" s="1">
         <x:v>2026</x:v>
@@ -839,10 +866,10 @@
     </x:row>
     <x:row r="8" spans="1:10">
       <x:c r="A8" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
         <x:v>43</x:v>
@@ -851,16 +878,16 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F8" s="1" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="F8" s="1" t="s">
+      <x:c r="G8" s="1" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="G8" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
       <x:c r="H8" s="1">
-        <x:v>285008</x:v>
+        <x:v>418060</x:v>
       </x:c>
       <x:c r="I8" s="1">
         <x:v>2026</x:v>
@@ -883,16 +910,16 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F9" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="H9" s="1">
-        <x:v>30183</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="I9" s="1">
         <x:v>2026</x:v>
@@ -903,28 +930,28 @@
     </x:row>
     <x:row r="10" spans="1:10">
       <x:c r="A10" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D10" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E10" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="F10" s="1" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="D10" s="1" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="E10" s="1" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="F10" s="1" t="s">
-        <x:v>51</x:v>
-      </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H10" s="1">
-        <x:v>5031161</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="I10" s="1">
         <x:v>2026</x:v>
@@ -935,28 +962,28 @@
     </x:row>
     <x:row r="11" spans="1:10">
       <x:c r="A11" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="D11" s="1" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="D11" s="1" t="s">
+      <x:c r="E11" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="F11" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="G11" s="1" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="E11" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F11" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="G11" s="1" t="s">
-        <x:v>55</x:v>
-      </x:c>
       <x:c r="H11" s="1">
-        <x:v>80948</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I11" s="1">
         <x:v>2026</x:v>
@@ -967,28 +994,28 @@
     </x:row>
     <x:row r="12" spans="1:10">
       <x:c r="A12" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="D12" s="1" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="D12" s="1" t="s">
-        <x:v>57</x:v>
-      </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F12" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="H12" s="1">
-        <x:v>850000</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="I12" s="1">
         <x:v>2026</x:v>
@@ -999,28 +1026,28 @@
     </x:row>
     <x:row r="13" spans="1:10">
       <x:c r="A13" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="D13" s="1" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="E13" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="F13" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="G13" s="1" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="D13" s="1" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="E13" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F13" s="1" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="G13" s="1" t="s">
-        <x:v>38</x:v>
-      </x:c>
       <x:c r="H13" s="1">
-        <x:v>141263</x:v>
+        <x:v>5031161</x:v>
       </x:c>
       <x:c r="I13" s="1">
         <x:v>2026</x:v>
@@ -1031,25 +1058,25 @@
     </x:row>
     <x:row r="14" spans="1:10">
       <x:c r="A14" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F14" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="H14" s="1">
         <x:v>350000</x:v>
@@ -1063,28 +1090,28 @@
     </x:row>
     <x:row r="15" spans="1:10">
       <x:c r="A15" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F15" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="H15" s="1">
-        <x:v>771658</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="I15" s="1">
         <x:v>2026</x:v>
@@ -1101,60 +1128,220 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F16" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="H16" s="1">
-        <x:v>4697360</x:v>
+        <x:v>850000</x:v>
       </x:c>
       <x:c r="I16" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J16" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:10">
       <x:c r="A17" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B17" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C17" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="D17" s="1" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="E17" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F17" s="1" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="G17" s="1" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="H17" s="1">
+        <x:v>141263</x:v>
+      </x:c>
+      <x:c r="I17" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J17" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:10">
+      <x:c r="A18" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B18" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C18" s="1" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="D18" s="1" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="E18" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="F18" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="G18" s="1" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="H18" s="1">
+        <x:v>1750000</x:v>
+      </x:c>
+      <x:c r="I18" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J18" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:10">
+      <x:c r="A19" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B19" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C19" s="1" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="D19" s="1" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="E19" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="F19" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="G19" s="1" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="H19" s="1">
+        <x:v>350000</x:v>
+      </x:c>
+      <x:c r="I19" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J19" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:10">
+      <x:c r="A20" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B20" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C20" s="1" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="D20" s="1" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="E20" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F20" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G20" s="1" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="H20" s="1">
+        <x:v>771658</x:v>
+      </x:c>
+      <x:c r="I20" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J20" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:10">
+      <x:c r="A21" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B21" s="1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C21" s="1" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="D21" s="1" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="E21" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="F21" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="G21" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="H21" s="1">
+        <x:v>4697360</x:v>
+      </x:c>
+      <x:c r="I21" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J21" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:10">
+      <x:c r="A22" s="1" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B17" s="1" t="s">
+      <x:c r="B22" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="C17" s="1" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="D17" s="1" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="E17" s="1" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="F17" s="1" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="G17" s="1" t="s">
+      <x:c r="C22" s="1" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="D22" s="1" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="E22" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="F22" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="G22" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="H17" s="1">
+      <x:c r="H22" s="1">
         <x:v>119644</x:v>
       </x:c>
-      <x:c r="I17" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J17" s="1" t="s">
-        <x:v>27</x:v>
+      <x:c r="I22" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J22" s="1" t="s">
+        <x:v>33</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -236,6 +236,12 @@
   </x:si>
   <x:si>
     <x:t>NE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H2GA13012</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SCOTT, DAVID ALBERT</x:t>
   </x:si>
   <x:si>
     <x:t>H6TX08209</x:t>
@@ -318,8 +324,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J22" totalsRowShown="0">
-  <x:autoFilter ref="A1:J22"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J23" totalsRowShown="0">
+  <x:autoFilter ref="A1:J23"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -624,7 +630,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J22"/>
+  <x:dimension ref="A1:J23"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1250,10 +1256,10 @@
     </x:row>
     <x:row r="20" spans="1:10">
       <x:c r="A20" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
         <x:v>74</x:v>
@@ -1265,27 +1271,27 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F20" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="H20" s="1">
-        <x:v>771658</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="I20" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J20" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:10">
       <x:c r="A21" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
         <x:v>76</x:v>
@@ -1294,36 +1300,36 @@
         <x:v>77</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F21" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H21" s="1">
-        <x:v>4697360</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="I21" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J21" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:10">
       <x:c r="A22" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
         <x:v>26</x:v>
@@ -1335,12 +1341,44 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="H22" s="1">
+        <x:v>4697360</x:v>
+      </x:c>
+      <x:c r="I22" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J22" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:10">
+      <x:c r="A23" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B23" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C23" s="1" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="D23" s="1" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="E23" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="F23" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="G23" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="H23" s="1">
         <x:v>119644</x:v>
       </x:c>
-      <x:c r="I22" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J22" s="1" t="s">
+      <x:c r="I23" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J23" s="1" t="s">
         <x:v>33</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -733,7 +733,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="H3" s="1">
-        <x:v>1052492</x:v>
+        <x:v>2010471</x:v>
       </x:c>
       <x:c r="I3" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -733,7 +733,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="H3" s="1">
-        <x:v>2010471</x:v>
+        <x:v>2067216</x:v>
       </x:c>
       <x:c r="I3" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -179,6 +179,15 @@
   </x:si>
   <x:si>
     <x:t>LA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H6TX18232</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MENEFEE, CHRISTIAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18</x:t>
   </x:si>
   <x:si>
     <x:t>S6LA00540</x:t>
@@ -324,8 +333,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J23" totalsRowShown="0">
-  <x:autoFilter ref="A1:J23"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J24" totalsRowShown="0">
+  <x:autoFilter ref="A1:J24"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -630,7 +639,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J23"/>
+  <x:dimension ref="A1:J24"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1000,10 +1009,10 @@
     </x:row>
     <x:row r="12" spans="1:10">
       <x:c r="A12" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
         <x:v>55</x:v>
@@ -1012,16 +1021,16 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F12" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H12" s="1">
-        <x:v>250000</x:v>
+        <x:v>47162</x:v>
       </x:c>
       <x:c r="I12" s="1">
         <x:v>2026</x:v>
@@ -1032,16 +1041,16 @@
     </x:row>
     <x:row r="13" spans="1:10">
       <x:c r="A13" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
         <x:v>26</x:v>
@@ -1050,10 +1059,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="H13" s="1">
-        <x:v>5031161</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="I13" s="1">
         <x:v>2026</x:v>
@@ -1064,16 +1073,16 @@
     </x:row>
     <x:row r="14" spans="1:10">
       <x:c r="A14" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
         <x:v>26</x:v>
@@ -1082,10 +1091,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="H14" s="1">
-        <x:v>350000</x:v>
+        <x:v>5031161</x:v>
       </x:c>
       <x:c r="I14" s="1">
         <x:v>2026</x:v>
@@ -1096,10 +1105,10 @@
     </x:row>
     <x:row r="15" spans="1:10">
       <x:c r="A15" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
         <x:v>60</x:v>
@@ -1108,16 +1117,16 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F15" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="H15" s="1">
-        <x:v>80948</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I15" s="1">
         <x:v>2026</x:v>
@@ -1128,10 +1137,10 @@
     </x:row>
     <x:row r="16" spans="1:10">
       <x:c r="A16" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
         <x:v>63</x:v>
@@ -1140,16 +1149,16 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F16" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
         <x:v>65</x:v>
       </x:c>
       <x:c r="H16" s="1">
-        <x:v>850000</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="I16" s="1">
         <x:v>2026</x:v>
@@ -1160,10 +1169,10 @@
     </x:row>
     <x:row r="17" spans="1:10">
       <x:c r="A17" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
         <x:v>66</x:v>
@@ -1172,16 +1181,16 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F17" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="G17" s="1" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="G17" s="1" t="s">
-        <x:v>42</x:v>
-      </x:c>
       <x:c r="H17" s="1">
-        <x:v>141263</x:v>
+        <x:v>850000</x:v>
       </x:c>
       <x:c r="I17" s="1">
         <x:v>2026</x:v>
@@ -1192,10 +1201,10 @@
     </x:row>
     <x:row r="18" spans="1:10">
       <x:c r="A18" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
         <x:v>69</x:v>
@@ -1204,16 +1213,16 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F18" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
         <x:v>42</x:v>
       </x:c>
       <x:c r="H18" s="1">
-        <x:v>1750000</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="I18" s="1">
         <x:v>2026</x:v>
@@ -1230,10 +1239,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
         <x:v>26</x:v>
@@ -1242,10 +1251,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H19" s="1">
-        <x:v>350000</x:v>
+        <x:v>1750000</x:v>
       </x:c>
       <x:c r="I19" s="1">
         <x:v>2026</x:v>
@@ -1256,10 +1265,10 @@
     </x:row>
     <x:row r="20" spans="1:10">
       <x:c r="A20" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
         <x:v>74</x:v>
@@ -1268,100 +1277,100 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F20" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="H20" s="1">
-        <x:v>56045</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I20" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J20" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:10">
       <x:c r="A21" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F21" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="H21" s="1">
-        <x:v>771658</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="I21" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J21" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:10">
       <x:c r="A22" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F22" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H22" s="1">
-        <x:v>4697360</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="I22" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J22" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:10">
       <x:c r="A23" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
         <x:v>26</x:v>
@@ -1373,12 +1382,44 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="H23" s="1">
+        <x:v>4697360</x:v>
+      </x:c>
+      <x:c r="I23" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J23" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:10">
+      <x:c r="A24" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B24" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C24" s="1" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="D24" s="1" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="E24" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="F24" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="G24" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="H24" s="1">
         <x:v>119644</x:v>
       </x:c>
-      <x:c r="I23" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J23" s="1" t="s">
+      <x:c r="I24" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J24" s="1" t="s">
         <x:v>33</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -742,7 +742,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="H3" s="1">
-        <x:v>2067216</x:v>
+        <x:v>2123261</x:v>
       </x:c>
       <x:c r="I3" s="1">
         <x:v>2026</x:v>
@@ -1030,7 +1030,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="H12" s="1">
-        <x:v>47162</x:v>
+        <x:v>94324</x:v>
       </x:c>
       <x:c r="I12" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -742,7 +742,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="H3" s="1">
-        <x:v>2123261</x:v>
+        <x:v>2648216</x:v>
       </x:c>
       <x:c r="I3" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -263,6 +263,18 @@
   </x:si>
   <x:si>
     <x:t>STRATTON, JULIANA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H0NY15160</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TORRES, RITCHIE JOHN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NY</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -333,8 +345,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J24" totalsRowShown="0">
-  <x:autoFilter ref="A1:J24"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J25" totalsRowShown="0">
+  <x:autoFilter ref="A1:J25"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -639,7 +651,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J24"/>
+  <x:dimension ref="A1:J25"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -742,7 +754,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="H3" s="1">
-        <x:v>2648216</x:v>
+        <x:v>2704261</x:v>
       </x:c>
       <x:c r="I3" s="1">
         <x:v>2026</x:v>
@@ -1030,7 +1042,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="H12" s="1">
-        <x:v>94324</x:v>
+        <x:v>141486</x:v>
       </x:c>
       <x:c r="I12" s="1">
         <x:v>2026</x:v>
@@ -1421,6 +1433,38 @@
       </x:c>
       <x:c r="J24" s="1" t="s">
         <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:10">
+      <x:c r="A25" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B25" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C25" s="1" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="D25" s="1" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="E25" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F25" s="1" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="G25" s="1" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="H25" s="1">
+        <x:v>50875</x:v>
+      </x:c>
+      <x:c r="I25" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J25" s="1" t="s">
+        <x:v>17</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -46,6 +46,30 @@
     <x:t>expenditure_description</x:t>
   </x:si>
   <x:si>
+    <x:t>C00836221</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DEFEND AMERICAN JOBS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H8IN04199</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAIRD, JAMES R DR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>House</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUPPORT</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00848440</x:t>
   </x:si>
   <x:si>
@@ -58,18 +82,12 @@
     <x:t>BEAN, MELISSA LUBURICH</x:t>
   </x:si>
   <x:si>
-    <x:t>House</x:t>
-  </x:si>
-  <x:si>
     <x:t>08</x:t>
   </x:si>
   <x:si>
     <x:t>IL</x:t>
   </x:si>
   <x:si>
-    <x:t>SUPPORT</x:t>
-  </x:si>
-  <x:si>
     <x:t>H6GA13070</x:t>
   </x:si>
   <x:si>
@@ -125,12 +143,6 @@
   </x:si>
   <x:si>
     <x:t>14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00836221</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DEFEND AMERICAN JOBS</x:t>
   </x:si>
   <x:si>
     <x:t>H6TX10221</x:t>
@@ -345,8 +357,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J25" totalsRowShown="0">
-  <x:autoFilter ref="A1:J25"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J26" totalsRowShown="0">
+  <x:autoFilter ref="A1:J26"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -651,7 +663,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J25"/>
+  <x:dimension ref="A1:J26"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -722,7 +734,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="H2" s="1">
-        <x:v>41493</x:v>
+        <x:v>513868</x:v>
       </x:c>
       <x:c r="I2" s="1">
         <x:v>2026</x:v>
@@ -733,28 +745,28 @@
     </x:row>
     <x:row r="3" spans="1:10">
       <x:c r="A3" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F3" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="G3" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="H3" s="1">
-        <x:v>2704261</x:v>
+        <x:v>41493</x:v>
       </x:c>
       <x:c r="I3" s="1">
         <x:v>2026</x:v>
@@ -765,10 +777,10 @@
     </x:row>
     <x:row r="4" spans="1:10">
       <x:c r="A4" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
         <x:v>24</x:v>
@@ -777,16 +789,16 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F4" s="1" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="F4" s="1" t="s">
+      <x:c r="G4" s="1" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="G4" s="1" t="s">
-        <x:v>21</x:v>
-      </x:c>
       <x:c r="H4" s="1">
-        <x:v>350000</x:v>
+        <x:v>2704261</x:v>
       </x:c>
       <x:c r="I4" s="1">
         <x:v>2026</x:v>
@@ -809,80 +821,80 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F5" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G5" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="H5" s="1">
-        <x:v>672092</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I5" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J5" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:10">
       <x:c r="A6" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F6" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G6" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="H6" s="1">
-        <x:v>300000</x:v>
+        <x:v>672092</x:v>
       </x:c>
       <x:c r="I6" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J6" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:10">
       <x:c r="A7" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F7" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="H7" s="1">
-        <x:v>91656</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="I7" s="1">
         <x:v>2026</x:v>
@@ -893,10 +905,10 @@
     </x:row>
     <x:row r="8" spans="1:10">
       <x:c r="A8" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
         <x:v>43</x:v>
@@ -914,7 +926,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="H8" s="1">
-        <x:v>418060</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="I8" s="1">
         <x:v>2026</x:v>
@@ -937,16 +949,16 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F9" s="1" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H9" s="1">
-        <x:v>285008</x:v>
+        <x:v>418060</x:v>
       </x:c>
       <x:c r="I9" s="1">
         <x:v>2026</x:v>
@@ -957,28 +969,28 @@
     </x:row>
     <x:row r="10" spans="1:10">
       <x:c r="A10" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F10" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="H10" s="1">
-        <x:v>30183</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="I10" s="1">
         <x:v>2026</x:v>
@@ -989,28 +1001,28 @@
     </x:row>
     <x:row r="11" spans="1:10">
       <x:c r="A11" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C11" s="1" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="D11" s="1" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E11" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F11" s="1" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="G11" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C11" s="1" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="D11" s="1" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E11" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="F11" s="1" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="G11" s="1" t="s">
-        <x:v>54</x:v>
-      </x:c>
       <x:c r="H11" s="1">
-        <x:v>350000</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="I11" s="1">
         <x:v>2026</x:v>
@@ -1021,28 +1033,28 @@
     </x:row>
     <x:row r="12" spans="1:10">
       <x:c r="A12" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F12" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="H12" s="1">
-        <x:v>141486</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I12" s="1">
         <x:v>2026</x:v>
@@ -1053,28 +1065,28 @@
     </x:row>
     <x:row r="13" spans="1:10">
       <x:c r="A13" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H13" s="1">
-        <x:v>250000</x:v>
+        <x:v>141486</x:v>
       </x:c>
       <x:c r="I13" s="1">
         <x:v>2026</x:v>
@@ -1085,28 +1097,28 @@
     </x:row>
     <x:row r="14" spans="1:10">
       <x:c r="A14" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F14" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="H14" s="1">
-        <x:v>5031161</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="I14" s="1">
         <x:v>2026</x:v>
@@ -1117,28 +1129,28 @@
     </x:row>
     <x:row r="15" spans="1:10">
       <x:c r="A15" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F15" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="H15" s="1">
-        <x:v>350000</x:v>
+        <x:v>5031161</x:v>
       </x:c>
       <x:c r="I15" s="1">
         <x:v>2026</x:v>
@@ -1149,28 +1161,28 @@
     </x:row>
     <x:row r="16" spans="1:10">
       <x:c r="A16" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F16" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="H16" s="1">
-        <x:v>80948</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I16" s="1">
         <x:v>2026</x:v>
@@ -1181,28 +1193,28 @@
     </x:row>
     <x:row r="17" spans="1:10">
       <x:c r="A17" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F17" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="H17" s="1">
-        <x:v>850000</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="I17" s="1">
         <x:v>2026</x:v>
@@ -1213,28 +1225,28 @@
     </x:row>
     <x:row r="18" spans="1:10">
       <x:c r="A18" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F18" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="H18" s="1">
-        <x:v>141263</x:v>
+        <x:v>850000</x:v>
       </x:c>
       <x:c r="I18" s="1">
         <x:v>2026</x:v>
@@ -1245,28 +1257,28 @@
     </x:row>
     <x:row r="19" spans="1:10">
       <x:c r="A19" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F19" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H19" s="1">
-        <x:v>1750000</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="I19" s="1">
         <x:v>2026</x:v>
@@ -1277,28 +1289,28 @@
     </x:row>
     <x:row r="20" spans="1:10">
       <x:c r="A20" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F20" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H20" s="1">
-        <x:v>350000</x:v>
+        <x:v>1750000</x:v>
       </x:c>
       <x:c r="I20" s="1">
         <x:v>2026</x:v>
@@ -1309,161 +1321,193 @@
     </x:row>
     <x:row r="21" spans="1:10">
       <x:c r="A21" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F21" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="H21" s="1">
-        <x:v>56045</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I21" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J21" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:10">
       <x:c r="A22" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F22" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="H22" s="1">
-        <x:v>771658</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="I22" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J22" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:10">
       <x:c r="A23" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F23" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H23" s="1">
-        <x:v>4697360</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="I23" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J23" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:10">
       <x:c r="A24" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F24" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="H24" s="1">
-        <x:v>119644</x:v>
+        <x:v>4697360</x:v>
       </x:c>
       <x:c r="I24" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J24" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:10">
       <x:c r="A25" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F25" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G25" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="H25" s="1">
+        <x:v>119644</x:v>
+      </x:c>
+      <x:c r="I25" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J25" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:10">
+      <x:c r="A26" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B26" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C26" s="1" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="D26" s="1" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="E26" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="F25" s="1" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="G25" s="1" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="H25" s="1">
+      <x:c r="F26" s="1" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="G26" s="1" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="H26" s="1">
         <x:v>50875</x:v>
       </x:c>
-      <x:c r="I25" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J25" s="1" t="s">
+      <x:c r="I26" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J26" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -1086,7 +1086,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="H13" s="1">
-        <x:v>141486</x:v>
+        <x:v>188648</x:v>
       </x:c>
       <x:c r="I13" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -145,15 +145,21 @@
     <x:t>14</x:t>
   </x:si>
   <x:si>
+    <x:t>H6GA10175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GAINES, HOUSTON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10</x:t>
+  </x:si>
+  <x:si>
     <x:t>H6TX10221</x:t>
   </x:si>
   <x:si>
     <x:t>GOBER, CHRIS</x:t>
   </x:si>
   <x:si>
-    <x:t>10</x:t>
-  </x:si>
-  <x:si>
     <x:t>TX</x:t>
   </x:si>
   <x:si>
@@ -176,6 +182,15 @@
   </x:si>
   <x:si>
     <x:t/>
+  </x:si>
+  <x:si>
+    <x:t>H2GA01157</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KINGSTON, JACK REP.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01</x:t>
   </x:si>
   <x:si>
     <x:t>S6IL00482</x:t>
@@ -357,8 +372,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J26" totalsRowShown="0">
-  <x:autoFilter ref="A1:J26"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J29" totalsRowShown="0">
+  <x:autoFilter ref="A1:J29"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -663,7 +678,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J26"/>
+  <x:dimension ref="A1:J29"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -798,7 +813,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="H4" s="1">
-        <x:v>2704261</x:v>
+        <x:v>2761006</x:v>
       </x:c>
       <x:c r="I4" s="1">
         <x:v>2026</x:v>
@@ -873,10 +888,10 @@
     </x:row>
     <x:row r="7" spans="1:10">
       <x:c r="A7" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
         <x:v>40</x:v>
@@ -894,7 +909,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="H7" s="1">
-        <x:v>300000</x:v>
+        <x:v>63285</x:v>
       </x:c>
       <x:c r="I7" s="1">
         <x:v>2026</x:v>
@@ -905,28 +920,28 @@
     </x:row>
     <x:row r="8" spans="1:10">
       <x:c r="A8" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F8" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="H8" s="1">
-        <x:v>91656</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="I8" s="1">
         <x:v>2026</x:v>
@@ -943,22 +958,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F9" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="H9" s="1">
-        <x:v>418060</x:v>
+        <x:v>64338</x:v>
       </x:c>
       <x:c r="I9" s="1">
         <x:v>2026</x:v>
@@ -969,28 +984,28 @@
     </x:row>
     <x:row r="10" spans="1:10">
       <x:c r="A10" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F10" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="H10" s="1">
-        <x:v>285008</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="I10" s="1">
         <x:v>2026</x:v>
@@ -1001,28 +1016,28 @@
     </x:row>
     <x:row r="11" spans="1:10">
       <x:c r="A11" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F11" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="H11" s="1">
-        <x:v>30183</x:v>
+        <x:v>418060</x:v>
       </x:c>
       <x:c r="I11" s="1">
         <x:v>2026</x:v>
@@ -1033,28 +1048,28 @@
     </x:row>
     <x:row r="12" spans="1:10">
       <x:c r="A12" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="F12" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="H12" s="1">
-        <x:v>350000</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="I12" s="1">
         <x:v>2026</x:v>
@@ -1065,28 +1080,28 @@
     </x:row>
     <x:row r="13" spans="1:10">
       <x:c r="A13" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="H13" s="1">
-        <x:v>188648</x:v>
+        <x:v>54935</x:v>
       </x:c>
       <x:c r="I13" s="1">
         <x:v>2026</x:v>
@@ -1097,28 +1112,28 @@
     </x:row>
     <x:row r="14" spans="1:10">
       <x:c r="A14" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="F14" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="H14" s="1">
-        <x:v>250000</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="I14" s="1">
         <x:v>2026</x:v>
@@ -1129,16 +1144,16 @@
     </x:row>
     <x:row r="15" spans="1:10">
       <x:c r="A15" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
         <x:v>32</x:v>
@@ -1147,10 +1162,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H15" s="1">
-        <x:v>5031161</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I15" s="1">
         <x:v>2026</x:v>
@@ -1161,10 +1176,10 @@
     </x:row>
     <x:row r="16" spans="1:10">
       <x:c r="A16" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
         <x:v>64</x:v>
@@ -1173,16 +1188,16 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F16" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="H16" s="1">
-        <x:v>350000</x:v>
+        <x:v>188648</x:v>
       </x:c>
       <x:c r="I16" s="1">
         <x:v>2026</x:v>
@@ -1193,10 +1208,10 @@
     </x:row>
     <x:row r="17" spans="1:10">
       <x:c r="A17" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
         <x:v>67</x:v>
@@ -1205,16 +1220,16 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F17" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H17" s="1">
-        <x:v>80948</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="I17" s="1">
         <x:v>2026</x:v>
@@ -1225,16 +1240,16 @@
     </x:row>
     <x:row r="18" spans="1:10">
       <x:c r="A18" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="D18" s="1" t="s">
         <x:v>70</x:v>
-      </x:c>
-      <x:c r="D18" s="1" t="s">
-        <x:v>71</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
         <x:v>32</x:v>
@@ -1243,10 +1258,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="H18" s="1">
-        <x:v>850000</x:v>
+        <x:v>5031161</x:v>
       </x:c>
       <x:c r="I18" s="1">
         <x:v>2026</x:v>
@@ -1257,28 +1272,28 @@
     </x:row>
     <x:row r="19" spans="1:10">
       <x:c r="A19" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F19" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="H19" s="1">
-        <x:v>141263</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I19" s="1">
         <x:v>2026</x:v>
@@ -1289,28 +1304,28 @@
     </x:row>
     <x:row r="20" spans="1:10">
       <x:c r="A20" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F20" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="H20" s="1">
-        <x:v>1750000</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="I20" s="1">
         <x:v>2026</x:v>
@@ -1327,10 +1342,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
         <x:v>32</x:v>
@@ -1339,10 +1354,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="H21" s="1">
-        <x:v>350000</x:v>
+        <x:v>850000</x:v>
       </x:c>
       <x:c r="I21" s="1">
         <x:v>2026</x:v>
@@ -1353,60 +1368,60 @@
     </x:row>
     <x:row r="22" spans="1:10">
       <x:c r="A22" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F22" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="H22" s="1">
-        <x:v>56045</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="I22" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J22" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:10">
       <x:c r="A23" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F23" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="H23" s="1">
-        <x:v>771658</x:v>
+        <x:v>1750000</x:v>
       </x:c>
       <x:c r="I23" s="1">
         <x:v>2026</x:v>
@@ -1417,16 +1432,16 @@
     </x:row>
     <x:row r="24" spans="1:10">
       <x:c r="A24" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
         <x:v>32</x:v>
@@ -1435,16 +1450,16 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="H24" s="1">
-        <x:v>4697360</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I24" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J24" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:10">
@@ -1455,22 +1470,22 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F25" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="H25" s="1">
-        <x:v>119644</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="I25" s="1">
         <x:v>2026</x:v>
@@ -1481,33 +1496,129 @@
     </x:row>
     <x:row r="26" spans="1:10">
       <x:c r="A26" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F26" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="H26" s="1">
+        <x:v>771658</x:v>
+      </x:c>
+      <x:c r="I26" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J26" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:10">
+      <x:c r="A27" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B27" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C27" s="1" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="H26" s="1">
+      <x:c r="D27" s="1" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="E27" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F27" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G27" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="H27" s="1">
+        <x:v>4697360</x:v>
+      </x:c>
+      <x:c r="I27" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J27" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:10">
+      <x:c r="A28" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B28" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C28" s="1" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D28" s="1" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="E28" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F28" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G28" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="H28" s="1">
+        <x:v>119644</x:v>
+      </x:c>
+      <x:c r="I28" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J28" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:10">
+      <x:c r="A29" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B29" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C29" s="1" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D29" s="1" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="E29" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F29" s="1" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="G29" s="1" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="H29" s="1">
         <x:v>50875</x:v>
       </x:c>
-      <x:c r="I26" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J26" s="1" t="s">
+      <x:c r="I29" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J29" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -70,6 +70,18 @@
     <x:t>SUPPORT</x:t>
   </x:si>
   <x:si>
+    <x:t>H0KY06104</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BARR, GARLAND ANDY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KY</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00848440</x:t>
   </x:si>
   <x:si>
@@ -247,9 +259,6 @@
     <x:t>MORRIS, NATE</x:t>
   </x:si>
   <x:si>
-    <x:t>KY</x:t>
-  </x:si>
-  <x:si>
     <x:t>H6TX22283</x:t>
   </x:si>
   <x:si>
@@ -278,6 +287,15 @@
   </x:si>
   <x:si>
     <x:t>SCOTT, DAVID ALBERT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H6NE03115</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SMITH, ADRIAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03</x:t>
   </x:si>
   <x:si>
     <x:t>H6TX08209</x:t>
@@ -372,8 +390,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J29" totalsRowShown="0">
-  <x:autoFilter ref="A1:J29"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J31" totalsRowShown="0">
+  <x:autoFilter ref="A1:J31"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -678,7 +696,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J29"/>
+  <x:dimension ref="A1:J31"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -760,28 +778,28 @@
     </x:row>
     <x:row r="3" spans="1:10">
       <x:c r="A3" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B3" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C3" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="B3" s="1" t="s">
+      <x:c r="D3" s="1" t="s">
         <x:v>19</x:v>
-      </x:c>
-      <x:c r="C3" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D3" s="1" t="s">
-        <x:v>21</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F3" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G3" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="H3" s="1">
-        <x:v>41493</x:v>
+        <x:v>3590517</x:v>
       </x:c>
       <x:c r="I3" s="1">
         <x:v>2026</x:v>
@@ -792,10 +810,10 @@
     </x:row>
     <x:row r="4" spans="1:10">
       <x:c r="A4" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
         <x:v>24</x:v>
@@ -813,7 +831,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="H4" s="1">
-        <x:v>2761006</x:v>
+        <x:v>41493</x:v>
       </x:c>
       <x:c r="I4" s="1">
         <x:v>2026</x:v>
@@ -824,28 +842,28 @@
     </x:row>
     <x:row r="5" spans="1:10">
       <x:c r="A5" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B5" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C5" s="1" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="B5" s="1" t="s">
+      <x:c r="D5" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C5" s="1" t="s">
+      <x:c r="E5" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F5" s="1" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="D5" s="1" t="s">
+      <x:c r="G5" s="1" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="E5" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="F5" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="G5" s="1" t="s">
-        <x:v>27</x:v>
-      </x:c>
       <x:c r="H5" s="1">
-        <x:v>350000</x:v>
+        <x:v>3343831</x:v>
       </x:c>
       <x:c r="I5" s="1">
         <x:v>2026</x:v>
@@ -856,42 +874,42 @@
     </x:row>
     <x:row r="6" spans="1:10">
       <x:c r="A6" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B6" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C6" s="1" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="B6" s="1" t="s">
+      <x:c r="D6" s="1" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="C6" s="1" t="s">
+      <x:c r="E6" s="1" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D6" s="1" t="s">
+      <x:c r="F6" s="1" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="E6" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F6" s="1" t="s">
-        <x:v>38</x:v>
-      </x:c>
       <x:c r="G6" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="H6" s="1">
-        <x:v>672092</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I6" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J6" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:10">
       <x:c r="A7" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
         <x:v>40</x:v>
@@ -909,39 +927,39 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="H7" s="1">
-        <x:v>63285</x:v>
+        <x:v>672092</x:v>
       </x:c>
       <x:c r="I7" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J7" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:10">
       <x:c r="A8" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F8" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="H8" s="1">
-        <x:v>300000</x:v>
+        <x:v>63285</x:v>
       </x:c>
       <x:c r="I8" s="1">
         <x:v>2026</x:v>
@@ -952,28 +970,28 @@
     </x:row>
     <x:row r="9" spans="1:10">
       <x:c r="A9" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F9" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="H9" s="1">
-        <x:v>64338</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="I9" s="1">
         <x:v>2026</x:v>
@@ -990,22 +1008,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F10" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="H10" s="1">
-        <x:v>91656</x:v>
+        <x:v>64338</x:v>
       </x:c>
       <x:c r="I10" s="1">
         <x:v>2026</x:v>
@@ -1022,22 +1040,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F11" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
         <x:v>52</x:v>
       </x:c>
       <x:c r="H11" s="1">
-        <x:v>418060</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="I11" s="1">
         <x:v>2026</x:v>
@@ -1048,10 +1066,10 @@
     </x:row>
     <x:row r="12" spans="1:10">
       <x:c r="A12" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
         <x:v>53</x:v>
@@ -1060,16 +1078,16 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F12" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="H12" s="1">
-        <x:v>285008</x:v>
+        <x:v>418060</x:v>
       </x:c>
       <x:c r="I12" s="1">
         <x:v>2026</x:v>
@@ -1080,28 +1098,28 @@
     </x:row>
     <x:row r="13" spans="1:10">
       <x:c r="A13" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
         <x:v>27</x:v>
       </x:c>
       <x:c r="H13" s="1">
-        <x:v>54935</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="I13" s="1">
         <x:v>2026</x:v>
@@ -1112,28 +1130,28 @@
     </x:row>
     <x:row r="14" spans="1:10">
       <x:c r="A14" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F14" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="H14" s="1">
-        <x:v>30183</x:v>
+        <x:v>54935</x:v>
       </x:c>
       <x:c r="I14" s="1">
         <x:v>2026</x:v>
@@ -1144,28 +1162,28 @@
     </x:row>
     <x:row r="15" spans="1:10">
       <x:c r="A15" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F15" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="H15" s="1">
-        <x:v>350000</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="I15" s="1">
         <x:v>2026</x:v>
@@ -1176,28 +1194,28 @@
     </x:row>
     <x:row r="16" spans="1:10">
       <x:c r="A16" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F16" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H16" s="1">
-        <x:v>188648</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I16" s="1">
         <x:v>2026</x:v>
@@ -1208,28 +1226,28 @@
     </x:row>
     <x:row r="17" spans="1:10">
       <x:c r="A17" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F17" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="H17" s="1">
-        <x:v>250000</x:v>
+        <x:v>1215641</x:v>
       </x:c>
       <x:c r="I17" s="1">
         <x:v>2026</x:v>
@@ -1240,28 +1258,28 @@
     </x:row>
     <x:row r="18" spans="1:10">
       <x:c r="A18" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F18" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H18" s="1">
-        <x:v>5031161</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="I18" s="1">
         <x:v>2026</x:v>
@@ -1272,28 +1290,28 @@
     </x:row>
     <x:row r="19" spans="1:10">
       <x:c r="A19" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F19" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="H19" s="1">
-        <x:v>350000</x:v>
+        <x:v>6576247</x:v>
       </x:c>
       <x:c r="I19" s="1">
         <x:v>2026</x:v>
@@ -1304,28 +1322,28 @@
     </x:row>
     <x:row r="20" spans="1:10">
       <x:c r="A20" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F20" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="H20" s="1">
-        <x:v>80948</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I20" s="1">
         <x:v>2026</x:v>
@@ -1336,28 +1354,28 @@
     </x:row>
     <x:row r="21" spans="1:10">
       <x:c r="A21" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F21" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="H21" s="1">
-        <x:v>850000</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="I21" s="1">
         <x:v>2026</x:v>
@@ -1368,28 +1386,28 @@
     </x:row>
     <x:row r="22" spans="1:10">
       <x:c r="A22" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F22" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="H22" s="1">
-        <x:v>141263</x:v>
+        <x:v>850000</x:v>
       </x:c>
       <x:c r="I22" s="1">
         <x:v>2026</x:v>
@@ -1400,10 +1418,10 @@
     </x:row>
     <x:row r="23" spans="1:10">
       <x:c r="A23" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
         <x:v>81</x:v>
@@ -1412,16 +1430,16 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F23" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="H23" s="1">
-        <x:v>1750000</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="I23" s="1">
         <x:v>2026</x:v>
@@ -1432,28 +1450,28 @@
     </x:row>
     <x:row r="24" spans="1:10">
       <x:c r="A24" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F24" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="H24" s="1">
-        <x:v>350000</x:v>
+        <x:v>1750000</x:v>
       </x:c>
       <x:c r="I24" s="1">
         <x:v>2026</x:v>
@@ -1464,10 +1482,10 @@
     </x:row>
     <x:row r="25" spans="1:10">
       <x:c r="A25" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
         <x:v>86</x:v>
@@ -1476,149 +1494,213 @@
         <x:v>87</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F25" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="H25" s="1">
-        <x:v>56045</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I25" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J25" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:10">
       <x:c r="A26" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F26" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="H26" s="1">
-        <x:v>771658</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="I26" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J26" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:10">
       <x:c r="A27" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F27" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="H27" s="1">
-        <x:v>4697360</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="I27" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J27" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:10">
       <x:c r="A28" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F28" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="H28" s="1">
-        <x:v>119644</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="I28" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J28" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:10">
       <x:c r="A29" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="F29" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G29" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="H29" s="1">
+        <x:v>4697360</x:v>
+      </x:c>
+      <x:c r="I29" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J29" s="1" t="s">
+        <x:v>43</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:10">
+      <x:c r="A30" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B30" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C30" s="1" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D30" s="1" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="E30" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="F30" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G30" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="H30" s="1">
+        <x:v>119644</x:v>
+      </x:c>
+      <x:c r="I30" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J30" s="1" t="s">
+        <x:v>43</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:10">
+      <x:c r="A31" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B31" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C31" s="1" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D31" s="1" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="E31" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="F29" s="1" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="G29" s="1" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="H29" s="1">
+      <x:c r="F31" s="1" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G31" s="1" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="H31" s="1">
         <x:v>50875</x:v>
       </x:c>
-      <x:c r="I29" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J29" s="1" t="s">
+      <x:c r="I31" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J31" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -98,6 +98,18 @@
   </x:si>
   <x:si>
     <x:t>IL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H6MD05321</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOAFO, ADRIAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MD</x:t>
   </x:si>
   <x:si>
     <x:t>H6GA13070</x:t>
@@ -390,8 +402,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J31" totalsRowShown="0">
-  <x:autoFilter ref="A1:J31"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J32" totalsRowShown="0">
+  <x:autoFilter ref="A1:J32"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -696,7 +708,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J31"/>
+  <x:dimension ref="A1:J32"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -863,7 +875,7 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="H5" s="1">
-        <x:v>3343831</x:v>
+        <x:v>243968</x:v>
       </x:c>
       <x:c r="I5" s="1">
         <x:v>2026</x:v>
@@ -874,28 +886,28 @@
     </x:row>
     <x:row r="6" spans="1:10">
       <x:c r="A6" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B6" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C6" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="B6" s="1" t="s">
+      <x:c r="D6" s="1" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C6" s="1" t="s">
+      <x:c r="E6" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F6" s="1" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="D6" s="1" t="s">
+      <x:c r="G6" s="1" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="E6" s="1" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="F6" s="1" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="G6" s="1" t="s">
-        <x:v>31</x:v>
-      </x:c>
       <x:c r="H6" s="1">
-        <x:v>350000</x:v>
+        <x:v>3399876</x:v>
       </x:c>
       <x:c r="I6" s="1">
         <x:v>2026</x:v>
@@ -906,42 +918,42 @@
     </x:row>
     <x:row r="7" spans="1:10">
       <x:c r="A7" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B7" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C7" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="B7" s="1" t="s">
+      <x:c r="D7" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="C7" s="1" t="s">
+      <x:c r="E7" s="1" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D7" s="1" t="s">
+      <x:c r="F7" s="1" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="E7" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F7" s="1" t="s">
-        <x:v>42</x:v>
-      </x:c>
       <x:c r="G7" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H7" s="1">
-        <x:v>672092</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I7" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J7" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:10">
       <x:c r="A8" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
         <x:v>44</x:v>
@@ -956,42 +968,42 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="H8" s="1">
-        <x:v>63285</x:v>
+        <x:v>672092</x:v>
       </x:c>
       <x:c r="I8" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J8" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:10">
       <x:c r="A9" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F9" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H9" s="1">
-        <x:v>300000</x:v>
+        <x:v>63285</x:v>
       </x:c>
       <x:c r="I9" s="1">
         <x:v>2026</x:v>
@@ -1002,28 +1014,28 @@
     </x:row>
     <x:row r="10" spans="1:10">
       <x:c r="A10" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F10" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H10" s="1">
-        <x:v>64338</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="I10" s="1">
         <x:v>2026</x:v>
@@ -1040,22 +1052,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F11" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H11" s="1">
-        <x:v>91656</x:v>
+        <x:v>64338</x:v>
       </x:c>
       <x:c r="I11" s="1">
         <x:v>2026</x:v>
@@ -1072,22 +1084,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="D12" s="1" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E12" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F12" s="1" t="s">
         <x:v>53</x:v>
-      </x:c>
-      <x:c r="D12" s="1" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E12" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F12" s="1" t="s">
-        <x:v>55</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
         <x:v>56</x:v>
       </x:c>
       <x:c r="H12" s="1">
-        <x:v>418060</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="I12" s="1">
         <x:v>2026</x:v>
@@ -1098,10 +1110,10 @@
     </x:row>
     <x:row r="13" spans="1:10">
       <x:c r="A13" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
         <x:v>57</x:v>
@@ -1110,16 +1122,16 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s">
         <x:v>59</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H13" s="1">
-        <x:v>285008</x:v>
+        <x:v>418060</x:v>
       </x:c>
       <x:c r="I13" s="1">
         <x:v>2026</x:v>
@@ -1130,28 +1142,28 @@
     </x:row>
     <x:row r="14" spans="1:10">
       <x:c r="A14" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F14" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="H14" s="1">
-        <x:v>54935</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="I14" s="1">
         <x:v>2026</x:v>
@@ -1162,28 +1174,28 @@
     </x:row>
     <x:row r="15" spans="1:10">
       <x:c r="A15" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F15" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H15" s="1">
-        <x:v>30183</x:v>
+        <x:v>54935</x:v>
       </x:c>
       <x:c r="I15" s="1">
         <x:v>2026</x:v>
@@ -1194,28 +1206,28 @@
     </x:row>
     <x:row r="16" spans="1:10">
       <x:c r="A16" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F16" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="H16" s="1">
-        <x:v>350000</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="I16" s="1">
         <x:v>2026</x:v>
@@ -1226,28 +1238,28 @@
     </x:row>
     <x:row r="17" spans="1:10">
       <x:c r="A17" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F17" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="H17" s="1">
-        <x:v>1215641</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I17" s="1">
         <x:v>2026</x:v>
@@ -1258,28 +1270,28 @@
     </x:row>
     <x:row r="18" spans="1:10">
       <x:c r="A18" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F18" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="H18" s="1">
-        <x:v>250000</x:v>
+        <x:v>1215641</x:v>
       </x:c>
       <x:c r="I18" s="1">
         <x:v>2026</x:v>
@@ -1290,28 +1302,28 @@
     </x:row>
     <x:row r="19" spans="1:10">
       <x:c r="A19" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F19" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="H19" s="1">
-        <x:v>6576247</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="I19" s="1">
         <x:v>2026</x:v>
@@ -1322,28 +1334,28 @@
     </x:row>
     <x:row r="20" spans="1:10">
       <x:c r="A20" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F20" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="H20" s="1">
-        <x:v>350000</x:v>
+        <x:v>6576247</x:v>
       </x:c>
       <x:c r="I20" s="1">
         <x:v>2026</x:v>
@@ -1354,28 +1366,28 @@
     </x:row>
     <x:row r="21" spans="1:10">
       <x:c r="A21" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F21" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="H21" s="1">
-        <x:v>80948</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I21" s="1">
         <x:v>2026</x:v>
@@ -1386,28 +1398,28 @@
     </x:row>
     <x:row r="22" spans="1:10">
       <x:c r="A22" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F22" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="H22" s="1">
-        <x:v>850000</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="I22" s="1">
         <x:v>2026</x:v>
@@ -1418,28 +1430,28 @@
     </x:row>
     <x:row r="23" spans="1:10">
       <x:c r="A23" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F23" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="H23" s="1">
-        <x:v>141263</x:v>
+        <x:v>850000</x:v>
       </x:c>
       <x:c r="I23" s="1">
         <x:v>2026</x:v>
@@ -1450,28 +1462,28 @@
     </x:row>
     <x:row r="24" spans="1:10">
       <x:c r="A24" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F24" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="H24" s="1">
-        <x:v>1750000</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="I24" s="1">
         <x:v>2026</x:v>
@@ -1482,28 +1494,28 @@
     </x:row>
     <x:row r="25" spans="1:10">
       <x:c r="A25" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F25" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="H25" s="1">
-        <x:v>350000</x:v>
+        <x:v>1750000</x:v>
       </x:c>
       <x:c r="I25" s="1">
         <x:v>2026</x:v>
@@ -1514,66 +1526,66 @@
     </x:row>
     <x:row r="26" spans="1:10">
       <x:c r="A26" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F26" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="H26" s="1">
-        <x:v>56045</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I26" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J26" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:10">
       <x:c r="A27" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F27" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H27" s="1">
-        <x:v>282975</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="I27" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J27" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:10">
@@ -1584,22 +1596,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F28" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="H28" s="1">
-        <x:v>771658</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="I28" s="1">
         <x:v>2026</x:v>
@@ -1610,66 +1622,66 @@
     </x:row>
     <x:row r="29" spans="1:10">
       <x:c r="A29" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F29" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="H29" s="1">
-        <x:v>4697360</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="I29" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J29" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:10">
       <x:c r="A30" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F30" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
         <x:v>27</x:v>
       </x:c>
       <x:c r="H30" s="1">
-        <x:v>119644</x:v>
+        <x:v>4697360</x:v>
       </x:c>
       <x:c r="I30" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J30" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:10">
@@ -1680,27 +1692,59 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F31" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="H31" s="1">
+        <x:v>119644</x:v>
+      </x:c>
+      <x:c r="I31" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J31" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:10">
+      <x:c r="A32" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B32" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C32" s="1" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="D32" s="1" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="E32" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F32" s="1" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="G32" s="1" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="H32" s="1">
         <x:v>50875</x:v>
       </x:c>
-      <x:c r="I31" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J31" s="1" t="s">
+      <x:c r="I32" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J32" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -82,6 +82,21 @@
     <x:t>KY</x:t>
   </x:si>
   <x:si>
+    <x:t>C00915181</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FELLOWSHIP PAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>S6KY00286</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Senate</x:t>
+  </x:si>
+  <x:si>
+    <x:t>00</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00848440</x:t>
   </x:si>
   <x:si>
@@ -124,22 +139,10 @@
     <x:t>GA</x:t>
   </x:si>
   <x:si>
-    <x:t>C00915181</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FELLOWSHIP PAC</x:t>
-  </x:si>
-  <x:si>
     <x:t>S6GA00390</x:t>
   </x:si>
   <x:si>
     <x:t>COLLINS, MICHAEL A JR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Senate</x:t>
-  </x:si>
-  <x:si>
-    <x:t>00</x:t>
   </x:si>
   <x:si>
     <x:t>C00835959</x:t>
@@ -402,8 +405,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J32" totalsRowShown="0">
-  <x:autoFilter ref="A1:J32"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J33" totalsRowShown="0">
+  <x:autoFilter ref="A1:J33"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -708,7 +711,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J32"/>
+  <x:dimension ref="A1:J33"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -831,19 +834,19 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="E4" s="1" t="s">
         <x:v>25</x:v>
-      </x:c>
-      <x:c r="E4" s="1" t="s">
-        <x:v>14</x:v>
       </x:c>
       <x:c r="F4" s="1" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="G4" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="H4" s="1">
-        <x:v>41493</x:v>
+        <x:v>628597</x:v>
       </x:c>
       <x:c r="I4" s="1">
         <x:v>2026</x:v>
@@ -854,28 +857,28 @@
     </x:row>
     <x:row r="5" spans="1:10">
       <x:c r="A5" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F5" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="G5" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H5" s="1">
-        <x:v>243968</x:v>
+        <x:v>41493</x:v>
       </x:c>
       <x:c r="I5" s="1">
         <x:v>2026</x:v>
@@ -886,28 +889,28 @@
     </x:row>
     <x:row r="6" spans="1:10">
       <x:c r="A6" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F6" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="G6" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="H6" s="1">
-        <x:v>3399876</x:v>
+        <x:v>243968</x:v>
       </x:c>
       <x:c r="I6" s="1">
         <x:v>2026</x:v>
@@ -918,28 +921,28 @@
     </x:row>
     <x:row r="7" spans="1:10">
       <x:c r="A7" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C7" s="1" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="C7" s="1" t="s">
+      <x:c r="D7" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="D7" s="1" t="s">
+      <x:c r="E7" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F7" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="E7" s="1" t="s">
+      <x:c r="G7" s="1" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="F7" s="1" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="G7" s="1" t="s">
-        <x:v>35</x:v>
-      </x:c>
       <x:c r="H7" s="1">
-        <x:v>350000</x:v>
+        <x:v>3399876</x:v>
       </x:c>
       <x:c r="I7" s="1">
         <x:v>2026</x:v>
@@ -950,92 +953,92 @@
     </x:row>
     <x:row r="8" spans="1:10">
       <x:c r="A8" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B8" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C8" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D8" s="1" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="B8" s="1" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="C8" s="1" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="D8" s="1" t="s">
-        <x:v>45</x:v>
-      </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F8" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H8" s="1">
-        <x:v>672092</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I8" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J8" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:10">
       <x:c r="A9" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D9" s="1" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="E9" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F9" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="G9" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H9" s="1">
+        <x:v>672092</x:v>
+      </x:c>
+      <x:c r="I9" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J9" s="1" t="s">
         <x:v>48</x:v>
-      </x:c>
-      <x:c r="D9" s="1" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="E9" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F9" s="1" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="G9" s="1" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="H9" s="1">
-        <x:v>63285</x:v>
-      </x:c>
-      <x:c r="I9" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J9" s="1" t="s">
-        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:10">
       <x:c r="A10" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F10" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H10" s="1">
-        <x:v>300000</x:v>
+        <x:v>328576</x:v>
       </x:c>
       <x:c r="I10" s="1">
         <x:v>2026</x:v>
@@ -1046,28 +1049,28 @@
     </x:row>
     <x:row r="11" spans="1:10">
       <x:c r="A11" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D11" s="1" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E11" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F11" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="D11" s="1" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E11" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F11" s="1" t="s">
-        <x:v>53</x:v>
-      </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H11" s="1">
-        <x:v>64338</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="I11" s="1">
         <x:v>2026</x:v>
@@ -1084,22 +1087,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="D12" s="1" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E12" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F12" s="1" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="D12" s="1" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="E12" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F12" s="1" t="s">
-        <x:v>53</x:v>
-      </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H12" s="1">
-        <x:v>91656</x:v>
+        <x:v>580151</x:v>
       </x:c>
       <x:c r="I12" s="1">
         <x:v>2026</x:v>
@@ -1116,22 +1119,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="D13" s="1" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="E13" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F13" s="1" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="G13" s="1" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="D13" s="1" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="E13" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F13" s="1" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="G13" s="1" t="s">
-        <x:v>60</x:v>
-      </x:c>
       <x:c r="H13" s="1">
-        <x:v>418060</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="I13" s="1">
         <x:v>2026</x:v>
@@ -1142,28 +1145,28 @@
     </x:row>
     <x:row r="14" spans="1:10">
       <x:c r="A14" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="D14" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="E14" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F14" s="1" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="G14" s="1" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="D14" s="1" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="E14" s="1" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="F14" s="1" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="G14" s="1" t="s">
-        <x:v>27</x:v>
-      </x:c>
       <x:c r="H14" s="1">
-        <x:v>285008</x:v>
+        <x:v>418060</x:v>
       </x:c>
       <x:c r="I14" s="1">
         <x:v>2026</x:v>
@@ -1174,28 +1177,28 @@
     </x:row>
     <x:row r="15" spans="1:10">
       <x:c r="A15" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="D15" s="1" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="E15" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F15" s="1" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="D15" s="1" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="E15" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F15" s="1" t="s">
-        <x:v>66</x:v>
-      </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H15" s="1">
-        <x:v>54935</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="I15" s="1">
         <x:v>2026</x:v>
@@ -1206,28 +1209,28 @@
     </x:row>
     <x:row r="16" spans="1:10">
       <x:c r="A16" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="D16" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E16" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F16" s="1" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="D16" s="1" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="E16" s="1" t="s">
+      <x:c r="G16" s="1" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="F16" s="1" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="G16" s="1" t="s">
-        <x:v>27</x:v>
-      </x:c>
       <x:c r="H16" s="1">
-        <x:v>30183</x:v>
+        <x:v>320996</x:v>
       </x:c>
       <x:c r="I16" s="1">
         <x:v>2026</x:v>
@@ -1238,28 +1241,28 @@
     </x:row>
     <x:row r="17" spans="1:10">
       <x:c r="A17" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="D17" s="1" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="D17" s="1" t="s">
-        <x:v>70</x:v>
-      </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F17" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H17" s="1">
-        <x:v>350000</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="I17" s="1">
         <x:v>2026</x:v>
@@ -1276,22 +1279,22 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="D18" s="1" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="E18" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F18" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G18" s="1" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="D18" s="1" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="E18" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F18" s="1" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="G18" s="1" t="s">
-        <x:v>56</x:v>
-      </x:c>
       <x:c r="H18" s="1">
-        <x:v>1215641</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I18" s="1">
         <x:v>2026</x:v>
@@ -1302,28 +1305,28 @@
     </x:row>
     <x:row r="19" spans="1:10">
       <x:c r="A19" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="D19" s="1" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="E19" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F19" s="1" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="D19" s="1" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="E19" s="1" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="F19" s="1" t="s">
-        <x:v>41</x:v>
-      </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H19" s="1">
-        <x:v>250000</x:v>
+        <x:v>1262803</x:v>
       </x:c>
       <x:c r="I19" s="1">
         <x:v>2026</x:v>
@@ -1334,28 +1337,28 @@
     </x:row>
     <x:row r="20" spans="1:10">
       <x:c r="A20" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="D20" s="1" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="D20" s="1" t="s">
-        <x:v>78</x:v>
-      </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F20" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="H20" s="1">
-        <x:v>6576247</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="I20" s="1">
         <x:v>2026</x:v>
@@ -1366,28 +1369,28 @@
     </x:row>
     <x:row r="21" spans="1:10">
       <x:c r="A21" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F21" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="H21" s="1">
-        <x:v>350000</x:v>
+        <x:v>6576247</x:v>
       </x:c>
       <x:c r="I21" s="1">
         <x:v>2026</x:v>
@@ -1398,28 +1401,28 @@
     </x:row>
     <x:row r="22" spans="1:10">
       <x:c r="A22" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="D22" s="1" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="E22" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F22" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G22" s="1" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="D22" s="1" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="E22" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F22" s="1" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="G22" s="1" t="s">
-        <x:v>82</x:v>
-      </x:c>
       <x:c r="H22" s="1">
-        <x:v>80948</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I22" s="1">
         <x:v>2026</x:v>
@@ -1430,28 +1433,28 @@
     </x:row>
     <x:row r="23" spans="1:10">
       <x:c r="A23" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="D23" s="1" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="E23" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F23" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="G23" s="1" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="D23" s="1" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="E23" s="1" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="F23" s="1" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="G23" s="1" t="s">
-        <x:v>21</x:v>
-      </x:c>
       <x:c r="H23" s="1">
-        <x:v>850000</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="I23" s="1">
         <x:v>2026</x:v>
@@ -1462,28 +1465,28 @@
     </x:row>
     <x:row r="24" spans="1:10">
       <x:c r="A24" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="D24" s="1" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="D24" s="1" t="s">
-        <x:v>86</x:v>
-      </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F24" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="H24" s="1">
-        <x:v>141263</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="I24" s="1">
         <x:v>2026</x:v>
@@ -1494,28 +1497,28 @@
     </x:row>
     <x:row r="25" spans="1:10">
       <x:c r="A25" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="D25" s="1" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="E25" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F25" s="1" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="D25" s="1" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="E25" s="1" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="F25" s="1" t="s">
-        <x:v>41</x:v>
-      </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H25" s="1">
-        <x:v>1750000</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="I25" s="1">
         <x:v>2026</x:v>
@@ -1526,28 +1529,28 @@
     </x:row>
     <x:row r="26" spans="1:10">
       <x:c r="A26" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D26" s="1" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="D26" s="1" t="s">
-        <x:v>91</x:v>
-      </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F26" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H26" s="1">
-        <x:v>350000</x:v>
+        <x:v>1750000</x:v>
       </x:c>
       <x:c r="I26" s="1">
         <x:v>2026</x:v>
@@ -1564,60 +1567,60 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="D27" s="1" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="E27" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F27" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G27" s="1" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="D27" s="1" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="E27" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F27" s="1" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="G27" s="1" t="s">
-        <x:v>35</x:v>
-      </x:c>
       <x:c r="H27" s="1">
-        <x:v>56045</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I27" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J27" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:10">
       <x:c r="A28" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="D28" s="1" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="D28" s="1" t="s">
-        <x:v>96</x:v>
-      </x:c>
       <x:c r="E28" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F28" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H28" s="1">
-        <x:v>282975</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="I28" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J28" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:10">
@@ -1628,22 +1631,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D29" s="1" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="E29" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F29" s="1" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="D29" s="1" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="E29" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F29" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="H29" s="1">
-        <x:v>771658</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="I29" s="1">
         <x:v>2026</x:v>
@@ -1654,97 +1657,129 @@
     </x:row>
     <x:row r="30" spans="1:10">
       <x:c r="A30" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D30" s="1" t="s">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="D30" s="1" t="s">
-        <x:v>101</x:v>
-      </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F30" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H30" s="1">
-        <x:v>4697360</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="I30" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J30" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:10">
       <x:c r="A31" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F31" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H31" s="1">
-        <x:v>119644</x:v>
+        <x:v>4697360</x:v>
       </x:c>
       <x:c r="I31" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J31" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:10">
       <x:c r="A32" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="D32" s="1" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="D32" s="1" t="s">
+      <x:c r="E32" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F32" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G32" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H32" s="1">
+        <x:v>119644</x:v>
+      </x:c>
+      <x:c r="I32" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J32" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:10">
+      <x:c r="A33" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B33" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C33" s="1" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="E32" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F32" s="1" t="s">
+      <x:c r="D33" s="1" t="s">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="G32" s="1" t="s">
+      <x:c r="E33" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F33" s="1" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="H32" s="1">
-        <x:v>50875</x:v>
-      </x:c>
-      <x:c r="I32" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J32" s="1" t="s">
+      <x:c r="G33" s="1" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="H33" s="1">
+        <x:v>101750</x:v>
+      </x:c>
+      <x:c r="I33" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J33" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -942,7 +942,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="H7" s="1">
-        <x:v>3399876</x:v>
+        <x:v>3455921</x:v>
       </x:c>
       <x:c r="I7" s="1">
         <x:v>2026</x:v>
@@ -1326,7 +1326,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="H19" s="1">
-        <x:v>1262803</x:v>
+        <x:v>1309965</x:v>
       </x:c>
       <x:c r="I19" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -127,15 +127,21 @@
     <x:t>MD</x:t>
   </x:si>
   <x:si>
+    <x:t>H2IL13153</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BUDZINSKI, NIKKI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13</x:t>
+  </x:si>
+  <x:si>
     <x:t>H6GA13070</x:t>
   </x:si>
   <x:si>
     <x:t>CLARK, JASMINE</x:t>
   </x:si>
   <x:si>
-    <x:t>13</x:t>
-  </x:si>
-  <x:si>
     <x:t>GA</x:t>
   </x:si>
   <x:si>
@@ -287,6 +293,12 @@
   </x:si>
   <x:si>
     <x:t>PAXTON, WARREN KENNETH JR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H6IL02298</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PETERS, ROBERT JAMES</x:t>
   </x:si>
   <x:si>
     <x:t>S6NE00129</x:t>
@@ -405,8 +417,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J33" totalsRowShown="0">
-  <x:autoFilter ref="A1:J33"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J35" totalsRowShown="0">
+  <x:autoFilter ref="A1:J35"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -711,7 +723,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J33"/>
+  <x:dimension ref="A1:J35"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -878,7 +890,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="H5" s="1">
-        <x:v>41493</x:v>
+        <x:v>557012</x:v>
       </x:c>
       <x:c r="I5" s="1">
         <x:v>2026</x:v>
@@ -910,7 +922,7 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="H6" s="1">
-        <x:v>243968</x:v>
+        <x:v>303642</x:v>
       </x:c>
       <x:c r="I6" s="1">
         <x:v>2026</x:v>
@@ -939,10 +951,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H7" s="1">
-        <x:v>3455921</x:v>
+        <x:v>83860</x:v>
       </x:c>
       <x:c r="I7" s="1">
         <x:v>2026</x:v>
@@ -953,28 +965,28 @@
     </x:row>
     <x:row r="8" spans="1:10">
       <x:c r="A8" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="D8" s="1" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="D8" s="1" t="s">
+      <x:c r="E8" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F8" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="G8" s="1" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="E8" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F8" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="G8" s="1" t="s">
-        <x:v>40</x:v>
-      </x:c>
       <x:c r="H8" s="1">
-        <x:v>350000</x:v>
+        <x:v>3455921</x:v>
       </x:c>
       <x:c r="I8" s="1">
         <x:v>2026</x:v>
@@ -985,92 +997,92 @@
     </x:row>
     <x:row r="9" spans="1:10">
       <x:c r="A9" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B9" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C9" s="1" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="B9" s="1" t="s">
+      <x:c r="D9" s="1" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="C9" s="1" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="D9" s="1" t="s">
-        <x:v>46</x:v>
-      </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F9" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H9" s="1">
-        <x:v>672092</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I9" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J9" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:10">
       <x:c r="A10" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="D10" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="E10" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F10" s="1" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="D10" s="1" t="s">
+      <x:c r="G10" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H10" s="1">
+        <x:v>2475788</x:v>
+      </x:c>
+      <x:c r="I10" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J10" s="1" t="s">
         <x:v>50</x:v>
-      </x:c>
-      <x:c r="E10" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F10" s="1" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="G10" s="1" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="H10" s="1">
-        <x:v>328576</x:v>
-      </x:c>
-      <x:c r="I10" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J10" s="1" t="s">
-        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:10">
       <x:c r="A11" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F11" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H11" s="1">
-        <x:v>300000</x:v>
+        <x:v>328576</x:v>
       </x:c>
       <x:c r="I11" s="1">
         <x:v>2026</x:v>
@@ -1081,28 +1093,28 @@
     </x:row>
     <x:row r="12" spans="1:10">
       <x:c r="A12" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="D12" s="1" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="D12" s="1" t="s">
+      <x:c r="E12" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F12" s="1" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="E12" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F12" s="1" t="s">
-        <x:v>54</x:v>
-      </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H12" s="1">
-        <x:v>580151</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="I12" s="1">
         <x:v>2026</x:v>
@@ -1119,22 +1131,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="D13" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="D13" s="1" t="s">
+      <x:c r="E13" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F13" s="1" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="E13" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F13" s="1" t="s">
-        <x:v>54</x:v>
-      </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H13" s="1">
-        <x:v>91656</x:v>
+        <x:v>580151</x:v>
       </x:c>
       <x:c r="I13" s="1">
         <x:v>2026</x:v>
@@ -1151,22 +1163,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="D14" s="1" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="D14" s="1" t="s">
+      <x:c r="E14" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F14" s="1" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="G14" s="1" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="E14" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F14" s="1" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="G14" s="1" t="s">
-        <x:v>61</x:v>
-      </x:c>
       <x:c r="H14" s="1">
-        <x:v>418060</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="I14" s="1">
         <x:v>2026</x:v>
@@ -1177,28 +1189,28 @@
     </x:row>
     <x:row r="15" spans="1:10">
       <x:c r="A15" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="D15" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E15" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F15" s="1" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="D15" s="1" t="s">
+      <x:c r="G15" s="1" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="E15" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F15" s="1" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="G15" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
       <x:c r="H15" s="1">
-        <x:v>285008</x:v>
+        <x:v>418060</x:v>
       </x:c>
       <x:c r="I15" s="1">
         <x:v>2026</x:v>
@@ -1209,28 +1221,28 @@
     </x:row>
     <x:row r="16" spans="1:10">
       <x:c r="A16" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="D16" s="1" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="D16" s="1" t="s">
+      <x:c r="E16" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F16" s="1" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="E16" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F16" s="1" t="s">
-        <x:v>67</x:v>
-      </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H16" s="1">
-        <x:v>320996</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="I16" s="1">
         <x:v>2026</x:v>
@@ -1241,28 +1253,28 @@
     </x:row>
     <x:row r="17" spans="1:10">
       <x:c r="A17" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="D17" s="1" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="D17" s="1" t="s">
+      <x:c r="E17" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F17" s="1" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="E17" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F17" s="1" t="s">
-        <x:v>64</x:v>
-      </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H17" s="1">
-        <x:v>30183</x:v>
+        <x:v>320996</x:v>
       </x:c>
       <x:c r="I17" s="1">
         <x:v>2026</x:v>
@@ -1273,10 +1285,10 @@
     </x:row>
     <x:row r="18" spans="1:10">
       <x:c r="A18" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
         <x:v>70</x:v>
@@ -1288,13 +1300,13 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="F18" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H18" s="1">
-        <x:v>350000</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="I18" s="1">
         <x:v>2026</x:v>
@@ -1305,28 +1317,28 @@
     </x:row>
     <x:row r="19" spans="1:10">
       <x:c r="A19" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="D19" s="1" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="D19" s="1" t="s">
+      <x:c r="E19" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F19" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G19" s="1" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="E19" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F19" s="1" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="G19" s="1" t="s">
-        <x:v>57</x:v>
-      </x:c>
       <x:c r="H19" s="1">
-        <x:v>1309965</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I19" s="1">
         <x:v>2026</x:v>
@@ -1337,28 +1349,28 @@
     </x:row>
     <x:row r="20" spans="1:10">
       <x:c r="A20" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="D20" s="1" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="D20" s="1" t="s">
+      <x:c r="E20" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F20" s="1" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="E20" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F20" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="H20" s="1">
-        <x:v>250000</x:v>
+        <x:v>2874180</x:v>
       </x:c>
       <x:c r="I20" s="1">
         <x:v>2026</x:v>
@@ -1369,10 +1381,10 @@
     </x:row>
     <x:row r="21" spans="1:10">
       <x:c r="A21" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
         <x:v>78</x:v>
@@ -1387,10 +1399,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="H21" s="1">
-        <x:v>6576247</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="I21" s="1">
         <x:v>2026</x:v>
@@ -1401,16 +1413,16 @@
     </x:row>
     <x:row r="22" spans="1:10">
       <x:c r="A22" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
         <x:v>25</x:v>
@@ -1419,10 +1431,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="H22" s="1">
-        <x:v>350000</x:v>
+        <x:v>6576247</x:v>
       </x:c>
       <x:c r="I22" s="1">
         <x:v>2026</x:v>
@@ -1433,28 +1445,28 @@
     </x:row>
     <x:row r="23" spans="1:10">
       <x:c r="A23" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D23" s="1" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="D23" s="1" t="s">
+      <x:c r="E23" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F23" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G23" s="1" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="E23" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F23" s="1" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="G23" s="1" t="s">
-        <x:v>83</x:v>
-      </x:c>
       <x:c r="H23" s="1">
-        <x:v>80948</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I23" s="1">
         <x:v>2026</x:v>
@@ -1465,28 +1477,28 @@
     </x:row>
     <x:row r="24" spans="1:10">
       <x:c r="A24" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="D24" s="1" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="D24" s="1" t="s">
+      <x:c r="E24" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F24" s="1" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="G24" s="1" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="E24" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F24" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="G24" s="1" t="s">
-        <x:v>21</x:v>
-      </x:c>
       <x:c r="H24" s="1">
-        <x:v>221403</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="I24" s="1">
         <x:v>2026</x:v>
@@ -1497,10 +1509,10 @@
     </x:row>
     <x:row r="25" spans="1:10">
       <x:c r="A25" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
         <x:v>86</x:v>
@@ -1509,16 +1521,16 @@
         <x:v>87</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F25" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="H25" s="1">
-        <x:v>141263</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="I25" s="1">
         <x:v>2026</x:v>
@@ -1529,28 +1541,28 @@
     </x:row>
     <x:row r="26" spans="1:10">
       <x:c r="A26" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="D26" s="1" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="D26" s="1" t="s">
+      <x:c r="E26" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F26" s="1" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="E26" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F26" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="H26" s="1">
-        <x:v>1750000</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="I26" s="1">
         <x:v>2026</x:v>
@@ -1579,10 +1591,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="H27" s="1">
-        <x:v>350000</x:v>
+        <x:v>1750000</x:v>
       </x:c>
       <x:c r="I27" s="1">
         <x:v>2026</x:v>
@@ -1593,60 +1605,60 @@
     </x:row>
     <x:row r="28" spans="1:10">
       <x:c r="A28" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="D28" s="1" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="D28" s="1" t="s">
-        <x:v>95</x:v>
-      </x:c>
       <x:c r="E28" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F28" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H28" s="1">
-        <x:v>56045</x:v>
+        <x:v>817065</x:v>
       </x:c>
       <x:c r="I28" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J28" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:10">
       <x:c r="A29" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="D29" s="1" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="D29" s="1" t="s">
+      <x:c r="E29" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F29" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G29" s="1" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="E29" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F29" s="1" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="G29" s="1" t="s">
-        <x:v>93</x:v>
-      </x:c>
       <x:c r="H29" s="1">
-        <x:v>282975</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I29" s="1">
         <x:v>2026</x:v>
@@ -1657,129 +1669,193 @@
     </x:row>
     <x:row r="30" spans="1:10">
       <x:c r="A30" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D30" s="1" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="D30" s="1" t="s">
-        <x:v>100</x:v>
-      </x:c>
       <x:c r="E30" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F30" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H30" s="1">
-        <x:v>771658</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="I30" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J30" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:10">
       <x:c r="A31" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D31" s="1" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="D31" s="1" t="s">
+      <x:c r="E31" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F31" s="1" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="E31" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F31" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H31" s="1">
-        <x:v>4697360</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="I31" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J31" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:10">
       <x:c r="A32" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F32" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="H32" s="1">
-        <x:v>119644</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="I32" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J32" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:10">
       <x:c r="A33" s="1" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B33" s="1" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C33" s="1" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="D33" s="1" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="E33" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F33" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G33" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H33" s="1">
+        <x:v>9866096</x:v>
+      </x:c>
+      <x:c r="I33" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J33" s="1" t="s">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:10">
+      <x:c r="A34" s="1" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="B33" s="1" t="s">
+      <x:c r="B34" s="1" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C33" s="1" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="D33" s="1" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="E33" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F33" s="1" t="s">
+      <x:c r="C34" s="1" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="G33" s="1" t="s">
+      <x:c r="D34" s="1" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="H33" s="1">
+      <x:c r="E34" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F34" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G34" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H34" s="1">
+        <x:v>119644</x:v>
+      </x:c>
+      <x:c r="I34" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J34" s="1" t="s">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:10">
+      <x:c r="A35" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B35" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C35" s="1" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="D35" s="1" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="E35" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F35" s="1" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="G35" s="1" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="H35" s="1">
         <x:v>101750</x:v>
       </x:c>
-      <x:c r="I33" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J33" s="1" t="s">
+      <x:c r="I35" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J35" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -1370,7 +1370,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="H20" s="1">
-        <x:v>2874180</x:v>
+        <x:v>3442924</x:v>
       </x:c>
       <x:c r="I20" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -986,7 +986,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="H8" s="1">
-        <x:v>3455921</x:v>
+        <x:v>4210393</x:v>
       </x:c>
       <x:c r="I8" s="1">
         <x:v>2026</x:v>
@@ -1082,7 +1082,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="H11" s="1">
-        <x:v>328576</x:v>
+        <x:v>391861</x:v>
       </x:c>
       <x:c r="I11" s="1">
         <x:v>2026</x:v>
@@ -1146,7 +1146,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="H13" s="1">
-        <x:v>580151</x:v>
+        <x:v>644489</x:v>
       </x:c>
       <x:c r="I13" s="1">
         <x:v>2026</x:v>
@@ -1274,7 +1274,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="H17" s="1">
-        <x:v>320996</x:v>
+        <x:v>375931</x:v>
       </x:c>
       <x:c r="I17" s="1">
         <x:v>2026</x:v>
@@ -1434,7 +1434,7 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="H22" s="1">
-        <x:v>6576247</x:v>
+        <x:v>6774919</x:v>
       </x:c>
       <x:c r="I22" s="1">
         <x:v>2026</x:v>
@@ -1850,7 +1850,7 @@
         <x:v>110</x:v>
       </x:c>
       <x:c r="H35" s="1">
-        <x:v>101750</x:v>
+        <x:v>144600</x:v>
       </x:c>
       <x:c r="I35" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -826,7 +826,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="H3" s="1">
-        <x:v>3590517</x:v>
+        <x:v>7170138</x:v>
       </x:c>
       <x:c r="I3" s="1">
         <x:v>2026</x:v>
@@ -922,7 +922,7 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="H6" s="1">
-        <x:v>303642</x:v>
+        <x:v>535135</x:v>
       </x:c>
       <x:c r="I6" s="1">
         <x:v>2026</x:v>
@@ -1082,7 +1082,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="H11" s="1">
-        <x:v>391861</x:v>
+        <x:v>455146</x:v>
       </x:c>
       <x:c r="I11" s="1">
         <x:v>2026</x:v>
@@ -1146,7 +1146,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="H13" s="1">
-        <x:v>644489</x:v>
+        <x:v>708827</x:v>
       </x:c>
       <x:c r="I13" s="1">
         <x:v>2026</x:v>
@@ -1274,7 +1274,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="H17" s="1">
-        <x:v>375931</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="I17" s="1">
         <x:v>2026</x:v>
@@ -1370,7 +1370,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="H20" s="1">
-        <x:v>3442924</x:v>
+        <x:v>3490086</x:v>
       </x:c>
       <x:c r="I20" s="1">
         <x:v>2026</x:v>
@@ -1434,7 +1434,7 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="H22" s="1">
-        <x:v>6774919</x:v>
+        <x:v>7217154</x:v>
       </x:c>
       <x:c r="I22" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -127,6 +127,18 @@
     <x:t>MD</x:t>
   </x:si>
   <x:si>
+    <x:t>H6TX02244</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BONCK, JON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>38</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TX</x:t>
+  </x:si>
+  <x:si>
     <x:t>H2IL13153</x:t>
   </x:si>
   <x:si>
@@ -193,9 +205,6 @@
     <x:t>GOBER, CHRIS</x:t>
   </x:si>
   <x:si>
-    <x:t>TX</x:t>
-  </x:si>
-  <x:si>
     <x:t>H4AR02141</x:t>
   </x:si>
   <x:si>
@@ -250,6 +259,15 @@
     <x:t>18</x:t>
   </x:si>
   <x:si>
+    <x:t>H2NJ08232</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MENENDEZ, ROBERT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NJ</x:t>
+  </x:si>
+  <x:si>
     <x:t>S6LA00540</x:t>
   </x:si>
   <x:si>
@@ -316,6 +334,15 @@
     <x:t>SCOTT, DAVID ALBERT</x:t>
   </x:si>
   <x:si>
+    <x:t>H6TX19206</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SELL, TOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19</x:t>
+  </x:si>
+  <x:si>
     <x:t>H6NE03115</x:t>
   </x:si>
   <x:si>
@@ -335,6 +362,15 @@
   </x:si>
   <x:si>
     <x:t>STRATTON, JULIANA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H8SC04250</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TIMMONS, WILLIAM R IV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SC</x:t>
   </x:si>
   <x:si>
     <x:t>H0NY15160</x:t>
@@ -417,8 +453,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J35" totalsRowShown="0">
-  <x:autoFilter ref="A1:J35"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J39" totalsRowShown="0">
+  <x:autoFilter ref="A1:J39"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -723,7 +759,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J35"/>
+  <x:dimension ref="A1:J39"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -922,7 +958,7 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="H6" s="1">
-        <x:v>535135</x:v>
+        <x:v>1069843</x:v>
       </x:c>
       <x:c r="I6" s="1">
         <x:v>2026</x:v>
@@ -933,10 +969,10 @@
     </x:row>
     <x:row r="7" spans="1:10">
       <x:c r="A7" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
         <x:v>37</x:v>
@@ -951,10 +987,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H7" s="1">
-        <x:v>83860</x:v>
+        <x:v>42720</x:v>
       </x:c>
       <x:c r="I7" s="1">
         <x:v>2026</x:v>
@@ -971,22 +1007,22 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F8" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H8" s="1">
-        <x:v>4210393</x:v>
+        <x:v>83860</x:v>
       </x:c>
       <x:c r="I8" s="1">
         <x:v>2026</x:v>
@@ -997,28 +1033,28 @@
     </x:row>
     <x:row r="9" spans="1:10">
       <x:c r="A9" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="D9" s="1" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E9" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F9" s="1" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="D9" s="1" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="E9" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F9" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
       <x:c r="G9" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H9" s="1">
-        <x:v>350000</x:v>
+        <x:v>4210393</x:v>
       </x:c>
       <x:c r="I9" s="1">
         <x:v>2026</x:v>
@@ -1029,10 +1065,10 @@
     </x:row>
     <x:row r="10" spans="1:10">
       <x:c r="A10" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
         <x:v>47</x:v>
@@ -1041,30 +1077,30 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F10" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H10" s="1">
-        <x:v>2475788</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I10" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J10" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:10">
       <x:c r="A11" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
         <x:v>51</x:v>
@@ -1079,42 +1115,42 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H11" s="1">
-        <x:v>455146</x:v>
+        <x:v>2475788</x:v>
       </x:c>
       <x:c r="I11" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J11" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:10">
       <x:c r="A12" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F12" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H12" s="1">
-        <x:v>300000</x:v>
+        <x:v>455146</x:v>
       </x:c>
       <x:c r="I12" s="1">
         <x:v>2026</x:v>
@@ -1125,28 +1161,28 @@
     </x:row>
     <x:row r="13" spans="1:10">
       <x:c r="A13" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H13" s="1">
-        <x:v>708827</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="I13" s="1">
         <x:v>2026</x:v>
@@ -1163,22 +1199,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F14" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H14" s="1">
-        <x:v>91656</x:v>
+        <x:v>708827</x:v>
       </x:c>
       <x:c r="I14" s="1">
         <x:v>2026</x:v>
@@ -1195,22 +1231,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="D15" s="1" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="E15" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F15" s="1" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="D15" s="1" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="E15" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F15" s="1" t="s">
-        <x:v>62</x:v>
-      </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H15" s="1">
-        <x:v>418060</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="I15" s="1">
         <x:v>2026</x:v>
@@ -1221,28 +1257,28 @@
     </x:row>
     <x:row r="16" spans="1:10">
       <x:c r="A16" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="D16" s="1" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="D16" s="1" t="s">
+      <x:c r="E16" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F16" s="1" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="E16" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F16" s="1" t="s">
+      <x:c r="G16" s="1" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="G16" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
       <x:c r="H16" s="1">
-        <x:v>285008</x:v>
+        <x:v>418060</x:v>
       </x:c>
       <x:c r="I16" s="1">
         <x:v>2026</x:v>
@@ -1253,10 +1289,10 @@
     </x:row>
     <x:row r="17" spans="1:10">
       <x:c r="A17" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
         <x:v>67</x:v>
@@ -1265,16 +1301,16 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F17" s="1" t="s">
         <x:v>69</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H17" s="1">
-        <x:v>430866</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="I17" s="1">
         <x:v>2026</x:v>
@@ -1285,10 +1321,10 @@
     </x:row>
     <x:row r="18" spans="1:10">
       <x:c r="A18" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
         <x:v>70</x:v>
@@ -1297,16 +1333,16 @@
         <x:v>71</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F18" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H18" s="1">
-        <x:v>30183</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="I18" s="1">
         <x:v>2026</x:v>
@@ -1317,28 +1353,28 @@
     </x:row>
     <x:row r="19" spans="1:10">
       <x:c r="A19" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="F19" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H19" s="1">
-        <x:v>350000</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="I19" s="1">
         <x:v>2026</x:v>
@@ -1349,10 +1385,10 @@
     </x:row>
     <x:row r="20" spans="1:10">
       <x:c r="A20" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
         <x:v>75</x:v>
@@ -1361,16 +1397,16 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F20" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G20" s="1" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="G20" s="1" t="s">
-        <x:v>59</x:v>
-      </x:c>
       <x:c r="H20" s="1">
-        <x:v>3490086</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I20" s="1">
         <x:v>2026</x:v>
@@ -1381,10 +1417,10 @@
     </x:row>
     <x:row r="21" spans="1:10">
       <x:c r="A21" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
         <x:v>78</x:v>
@@ -1393,16 +1429,16 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F21" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H21" s="1">
-        <x:v>250000</x:v>
+        <x:v>4345153</x:v>
       </x:c>
       <x:c r="I21" s="1">
         <x:v>2026</x:v>
@@ -1413,28 +1449,28 @@
     </x:row>
     <x:row r="22" spans="1:10">
       <x:c r="A22" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F22" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="H22" s="1">
-        <x:v>7217154</x:v>
+        <x:v>64395</x:v>
       </x:c>
       <x:c r="I22" s="1">
         <x:v>2026</x:v>
@@ -1451,10 +1487,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
         <x:v>25</x:v>
@@ -1463,10 +1499,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="H23" s="1">
-        <x:v>350000</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="I23" s="1">
         <x:v>2026</x:v>
@@ -1483,22 +1519,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F24" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="H24" s="1">
-        <x:v>80948</x:v>
+        <x:v>7415826</x:v>
       </x:c>
       <x:c r="I24" s="1">
         <x:v>2026</x:v>
@@ -1527,10 +1563,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="H25" s="1">
-        <x:v>221403</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I25" s="1">
         <x:v>2026</x:v>
@@ -1547,22 +1583,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F26" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="H26" s="1">
-        <x:v>141263</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="I26" s="1">
         <x:v>2026</x:v>
@@ -1579,10 +1615,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
         <x:v>25</x:v>
@@ -1591,10 +1627,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="H27" s="1">
-        <x:v>1750000</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="I27" s="1">
         <x:v>2026</x:v>
@@ -1605,34 +1641,34 @@
     </x:row>
     <x:row r="28" spans="1:10">
       <x:c r="A28" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F28" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H28" s="1">
-        <x:v>817065</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="I28" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J28" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:10">
@@ -1643,10 +1679,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
         <x:v>25</x:v>
@@ -1655,10 +1691,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H29" s="1">
-        <x:v>350000</x:v>
+        <x:v>1750000</x:v>
       </x:c>
       <x:c r="I29" s="1">
         <x:v>2026</x:v>
@@ -1669,60 +1705,60 @@
     </x:row>
     <x:row r="30" spans="1:10">
       <x:c r="A30" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F30" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H30" s="1">
-        <x:v>56045</x:v>
+        <x:v>817065</x:v>
       </x:c>
       <x:c r="I30" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J30" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:10">
       <x:c r="A31" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F31" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="H31" s="1">
-        <x:v>282975</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I31" s="1">
         <x:v>2026</x:v>
@@ -1733,129 +1769,257 @@
     </x:row>
     <x:row r="32" spans="1:10">
       <x:c r="A32" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F32" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H32" s="1">
-        <x:v>771658</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="I32" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J32" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:10">
       <x:c r="A33" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F33" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H33" s="1">
-        <x:v>9866096</x:v>
+        <x:v>54372</x:v>
       </x:c>
       <x:c r="I33" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J33" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:10">
       <x:c r="A34" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F34" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="H34" s="1">
-        <x:v>119644</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="I34" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J34" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:10">
       <x:c r="A35" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B35" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C35" s="1" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="D35" s="1" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="E35" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F35" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="G35" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="H35" s="1">
+        <x:v>771658</x:v>
+      </x:c>
+      <x:c r="I35" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J35" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:10">
+      <x:c r="A36" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B36" s="1" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C36" s="1" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="D36" s="1" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="E36" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F36" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G36" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H36" s="1">
+        <x:v>9866096</x:v>
+      </x:c>
+      <x:c r="I36" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J36" s="1" t="s">
+        <x:v>54</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:10">
+      <x:c r="A37" s="1" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="B35" s="1" t="s">
+      <x:c r="B37" s="1" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C35" s="1" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="D35" s="1" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="E35" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F35" s="1" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="G35" s="1" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="H35" s="1">
+      <x:c r="C37" s="1" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="D37" s="1" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="E37" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F37" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G37" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H37" s="1">
+        <x:v>119644</x:v>
+      </x:c>
+      <x:c r="I37" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J37" s="1" t="s">
+        <x:v>54</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:10">
+      <x:c r="A38" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B38" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C38" s="1" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="D38" s="1" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="E38" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F38" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G38" s="1" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="H38" s="1">
+        <x:v>56118</x:v>
+      </x:c>
+      <x:c r="I38" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J38" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:10">
+      <x:c r="A39" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B39" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C39" s="1" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="D39" s="1" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="E39" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F39" s="1" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="G39" s="1" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="H39" s="1">
         <x:v>144600</x:v>
       </x:c>
-      <x:c r="I35" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J35" s="1" t="s">
+      <x:c r="I39" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J39" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -163,6 +163,15 @@
     <x:t>COLLINS, MICHAEL A JR</x:t>
   </x:si>
   <x:si>
+    <x:t>H6TX35087</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DE LA CRUZ, CARLOS JR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00835959</x:t>
   </x:si>
   <x:si>
@@ -205,6 +214,15 @@
     <x:t>GOBER, CHRIS</x:t>
   </x:si>
   <x:si>
+    <x:t>H4TX09095</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GREEN, ALEXANDER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18</x:t>
+  </x:si>
+  <x:si>
     <x:t>H4AR02141</x:t>
   </x:si>
   <x:si>
@@ -254,9 +272,6 @@
   </x:si>
   <x:si>
     <x:t>MENEFEE, CHRISTIAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18</x:t>
   </x:si>
   <x:si>
     <x:t>H2NJ08232</x:t>
@@ -453,8 +468,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J39" totalsRowShown="0">
-  <x:autoFilter ref="A1:J39"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J41" totalsRowShown="0">
+  <x:autoFilter ref="A1:J41"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -759,7 +774,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J39"/>
+  <x:dimension ref="A1:J41"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -990,7 +1005,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="H7" s="1">
-        <x:v>42720</x:v>
+        <x:v>85440</x:v>
       </x:c>
       <x:c r="I7" s="1">
         <x:v>2026</x:v>
@@ -1097,92 +1112,92 @@
     </x:row>
     <x:row r="11" spans="1:10">
       <x:c r="A11" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B11" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C11" s="1" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="B11" s="1" t="s">
+      <x:c r="D11" s="1" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="C11" s="1" t="s">
+      <x:c r="E11" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F11" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="D11" s="1" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E11" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F11" s="1" t="s">
-        <x:v>53</x:v>
-      </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H11" s="1">
-        <x:v>2475788</x:v>
+        <x:v>35211</x:v>
       </x:c>
       <x:c r="I11" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J11" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:10">
       <x:c r="A12" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="D12" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="D12" s="1" t="s">
+      <x:c r="E12" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F12" s="1" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="E12" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F12" s="1" t="s">
+      <x:c r="G12" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H12" s="1">
+        <x:v>2475788</x:v>
+      </x:c>
+      <x:c r="I12" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J12" s="1" t="s">
         <x:v>57</x:v>
-      </x:c>
-      <x:c r="G12" s="1" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="H12" s="1">
-        <x:v>455146</x:v>
-      </x:c>
-      <x:c r="I12" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J12" s="1" t="s">
-        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:10">
       <x:c r="A13" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
         <x:v>46</x:v>
       </x:c>
       <x:c r="H13" s="1">
-        <x:v>300000</x:v>
+        <x:v>455146</x:v>
       </x:c>
       <x:c r="I13" s="1">
         <x:v>2026</x:v>
@@ -1193,10 +1208,10 @@
     </x:row>
     <x:row r="14" spans="1:10">
       <x:c r="A14" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
         <x:v>58</x:v>
@@ -1214,7 +1229,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="H14" s="1">
-        <x:v>708827</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="I14" s="1">
         <x:v>2026</x:v>
@@ -1240,13 +1255,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F15" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H15" s="1">
-        <x:v>91656</x:v>
+        <x:v>708827</x:v>
       </x:c>
       <x:c r="I15" s="1">
         <x:v>2026</x:v>
@@ -1263,22 +1278,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="D16" s="1" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E16" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F16" s="1" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="D16" s="1" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="E16" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F16" s="1" t="s">
-        <x:v>65</x:v>
-      </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H16" s="1">
-        <x:v>418060</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="I16" s="1">
         <x:v>2026</x:v>
@@ -1295,28 +1310,28 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="D17" s="1" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="D17" s="1" t="s">
+      <x:c r="E17" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F17" s="1" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="E17" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F17" s="1" t="s">
-        <x:v>69</x:v>
-      </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H17" s="1">
-        <x:v>285008</x:v>
+        <x:v>47162</x:v>
       </x:c>
       <x:c r="I17" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J17" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:10">
@@ -1327,22 +1342,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="D18" s="1" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="D18" s="1" t="s">
+      <x:c r="E18" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F18" s="1" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="E18" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F18" s="1" t="s">
+      <x:c r="G18" s="1" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="G18" s="1" t="s">
-        <x:v>46</x:v>
-      </x:c>
       <x:c r="H18" s="1">
-        <x:v>430866</x:v>
+        <x:v>418060</x:v>
       </x:c>
       <x:c r="I18" s="1">
         <x:v>2026</x:v>
@@ -1368,13 +1383,13 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="F19" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="H19" s="1">
-        <x:v>30183</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="I19" s="1">
         <x:v>2026</x:v>
@@ -1385,28 +1400,28 @@
     </x:row>
     <x:row r="20" spans="1:10">
       <x:c r="A20" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F20" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H20" s="1">
-        <x:v>350000</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="I20" s="1">
         <x:v>2026</x:v>
@@ -1423,22 +1438,22 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F21" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H21" s="1">
-        <x:v>4345153</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="I21" s="1">
         <x:v>2026</x:v>
@@ -1449,10 +1464,10 @@
     </x:row>
     <x:row r="22" spans="1:10">
       <x:c r="A22" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
         <x:v>81</x:v>
@@ -1461,16 +1476,16 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F22" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
         <x:v>83</x:v>
       </x:c>
       <x:c r="H22" s="1">
-        <x:v>64395</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I22" s="1">
         <x:v>2026</x:v>
@@ -1481,10 +1496,10 @@
     </x:row>
     <x:row r="23" spans="1:10">
       <x:c r="A23" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
         <x:v>84</x:v>
@@ -1493,16 +1508,16 @@
         <x:v>85</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F23" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H23" s="1">
-        <x:v>250000</x:v>
+        <x:v>4345153</x:v>
       </x:c>
       <x:c r="I23" s="1">
         <x:v>2026</x:v>
@@ -1513,10 +1528,10 @@
     </x:row>
     <x:row r="24" spans="1:10">
       <x:c r="A24" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
         <x:v>86</x:v>
@@ -1525,16 +1540,16 @@
         <x:v>87</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F24" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
         <x:v>88</x:v>
       </x:c>
       <x:c r="H24" s="1">
-        <x:v>7415826</x:v>
+        <x:v>64395</x:v>
       </x:c>
       <x:c r="I24" s="1">
         <x:v>2026</x:v>
@@ -1551,10 +1566,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
         <x:v>25</x:v>
@@ -1563,10 +1578,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="H25" s="1">
-        <x:v>350000</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="I25" s="1">
         <x:v>2026</x:v>
@@ -1583,22 +1598,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F26" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="H26" s="1">
-        <x:v>80948</x:v>
+        <x:v>7415826</x:v>
       </x:c>
       <x:c r="I26" s="1">
         <x:v>2026</x:v>
@@ -1615,10 +1630,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="D27" s="1" t="s">
         <x:v>92</x:v>
-      </x:c>
-      <x:c r="D27" s="1" t="s">
-        <x:v>93</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
         <x:v>25</x:v>
@@ -1627,10 +1642,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="H27" s="1">
-        <x:v>221403</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I27" s="1">
         <x:v>2026</x:v>
@@ -1656,13 +1671,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F28" s="1" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="G28" s="1" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="G28" s="1" t="s">
-        <x:v>40</x:v>
-      </x:c>
       <x:c r="H28" s="1">
-        <x:v>141263</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="I28" s="1">
         <x:v>2026</x:v>
@@ -1691,10 +1706,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="H29" s="1">
-        <x:v>1750000</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="I29" s="1">
         <x:v>2026</x:v>
@@ -1705,10 +1720,10 @@
     </x:row>
     <x:row r="30" spans="1:10">
       <x:c r="A30" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
         <x:v>99</x:v>
@@ -1720,19 +1735,19 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F30" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H30" s="1">
-        <x:v>817065</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="I30" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J30" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:10">
@@ -1743,10 +1758,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
         <x:v>25</x:v>
@@ -1755,10 +1770,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H31" s="1">
-        <x:v>350000</x:v>
+        <x:v>1750000</x:v>
       </x:c>
       <x:c r="I31" s="1">
         <x:v>2026</x:v>
@@ -1769,10 +1784,10 @@
     </x:row>
     <x:row r="32" spans="1:10">
       <x:c r="A32" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
         <x:v>104</x:v>
@@ -1784,27 +1799,27 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F32" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H32" s="1">
-        <x:v>56045</x:v>
+        <x:v>817065</x:v>
       </x:c>
       <x:c r="I32" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J32" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:10">
       <x:c r="A33" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
         <x:v>106</x:v>
@@ -1813,16 +1828,16 @@
         <x:v>107</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F33" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G33" s="1" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="G33" s="1" t="s">
-        <x:v>40</x:v>
-      </x:c>
       <x:c r="H33" s="1">
-        <x:v>54372</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I33" s="1">
         <x:v>2026</x:v>
@@ -1833,10 +1848,10 @@
     </x:row>
     <x:row r="34" spans="1:10">
       <x:c r="A34" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
         <x:v>109</x:v>
@@ -1848,19 +1863,19 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F34" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H34" s="1">
-        <x:v>282975</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="I34" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J34" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:10">
@@ -1871,22 +1886,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="D35" s="1" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="D35" s="1" t="s">
+      <x:c r="E35" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F35" s="1" t="s">
         <x:v>113</x:v>
-      </x:c>
-      <x:c r="E35" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F35" s="1" t="s">
-        <x:v>31</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
         <x:v>40</x:v>
       </x:c>
       <x:c r="H35" s="1">
-        <x:v>771658</x:v>
+        <x:v>108744</x:v>
       </x:c>
       <x:c r="I35" s="1">
         <x:v>2026</x:v>
@@ -1897,10 +1912,10 @@
     </x:row>
     <x:row r="36" spans="1:10">
       <x:c r="A36" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
         <x:v>114</x:v>
@@ -1909,86 +1924,86 @@
         <x:v>115</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F36" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="H36" s="1">
-        <x:v>9866096</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="I36" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J36" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:10">
       <x:c r="A37" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F37" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H37" s="1">
-        <x:v>119644</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="I37" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J37" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:10">
       <x:c r="A38" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F38" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H38" s="1">
-        <x:v>56118</x:v>
+        <x:v>9866096</x:v>
       </x:c>
       <x:c r="I38" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J38" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:10">
@@ -2005,21 +2020,85 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F39" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G39" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H39" s="1">
+        <x:v>119644</x:v>
+      </x:c>
+      <x:c r="I39" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J39" s="1" t="s">
+        <x:v>57</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:10">
+      <x:c r="A40" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B40" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C40" s="1" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="G39" s="1" t="s">
+      <x:c r="D40" s="1" t="s">
         <x:v>122</x:v>
       </x:c>
-      <x:c r="H39" s="1">
+      <x:c r="E40" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F40" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G40" s="1" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="H40" s="1">
+        <x:v>56118</x:v>
+      </x:c>
+      <x:c r="I40" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J40" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:10">
+      <x:c r="A41" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B41" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C41" s="1" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="D41" s="1" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="E41" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F41" s="1" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="G41" s="1" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="H41" s="1">
         <x:v>144600</x:v>
       </x:c>
-      <x:c r="I39" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J39" s="1" t="s">
+      <x:c r="I41" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J41" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -139,21 +139,15 @@
     <x:t>TX</x:t>
   </x:si>
   <x:si>
-    <x:t>H2IL13153</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BUDZINSKI, NIKKI</x:t>
+    <x:t>H6GA13070</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CLARK, JASMINE</x:t>
   </x:si>
   <x:si>
     <x:t>13</x:t>
   </x:si>
   <x:si>
-    <x:t>H6GA13070</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CLARK, JASMINE</x:t>
-  </x:si>
-  <x:si>
     <x:t>GA</x:t>
   </x:si>
   <x:si>
@@ -326,12 +320,6 @@
   </x:si>
   <x:si>
     <x:t>PAXTON, WARREN KENNETH JR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6IL02298</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PETERS, ROBERT JAMES</x:t>
   </x:si>
   <x:si>
     <x:t>S6NE00129</x:t>
@@ -468,8 +456,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J41" totalsRowShown="0">
-  <x:autoFilter ref="A1:J41"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J39" totalsRowShown="0">
+  <x:autoFilter ref="A1:J39"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -774,7 +762,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J41"/>
+  <x:dimension ref="A1:J39"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -941,7 +929,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="H5" s="1">
-        <x:v>557012</x:v>
+        <x:v>41493</x:v>
       </x:c>
       <x:c r="I5" s="1">
         <x:v>2026</x:v>
@@ -1034,10 +1022,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="H8" s="1">
-        <x:v>83860</x:v>
+        <x:v>4210393</x:v>
       </x:c>
       <x:c r="I8" s="1">
         <x:v>2026</x:v>
@@ -1048,28 +1036,28 @@
     </x:row>
     <x:row r="9" spans="1:10">
       <x:c r="A9" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D9" s="1" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="E9" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F9" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G9" s="1" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="D9" s="1" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="E9" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F9" s="1" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="G9" s="1" t="s">
-        <x:v>46</x:v>
-      </x:c>
       <x:c r="H9" s="1">
-        <x:v>4210393</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I9" s="1">
         <x:v>2026</x:v>
@@ -1080,10 +1068,10 @@
     </x:row>
     <x:row r="10" spans="1:10">
       <x:c r="A10" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
         <x:v>47</x:v>
@@ -1092,16 +1080,16 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F10" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H10" s="1">
-        <x:v>350000</x:v>
+        <x:v>35211</x:v>
       </x:c>
       <x:c r="I10" s="1">
         <x:v>2026</x:v>
@@ -1112,92 +1100,92 @@
     </x:row>
     <x:row r="11" spans="1:10">
       <x:c r="A11" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F11" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H11" s="1">
-        <x:v>35211</x:v>
+        <x:v>672092</x:v>
       </x:c>
       <x:c r="I11" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J11" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:10">
       <x:c r="A12" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F12" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="H12" s="1">
-        <x:v>2475788</x:v>
+        <x:v>455146</x:v>
       </x:c>
       <x:c r="I12" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J12" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:10">
       <x:c r="A13" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="D13" s="1" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E13" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F13" s="1" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="D13" s="1" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="E13" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F13" s="1" t="s">
-        <x:v>60</x:v>
-      </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="H13" s="1">
-        <x:v>455146</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="I13" s="1">
         <x:v>2026</x:v>
@@ -1208,28 +1196,28 @@
     </x:row>
     <x:row r="14" spans="1:10">
       <x:c r="A14" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F14" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="H14" s="1">
-        <x:v>300000</x:v>
+        <x:v>708827</x:v>
       </x:c>
       <x:c r="I14" s="1">
         <x:v>2026</x:v>
@@ -1246,22 +1234,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="D15" s="1" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="E15" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F15" s="1" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="D15" s="1" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="E15" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F15" s="1" t="s">
-        <x:v>63</x:v>
-      </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H15" s="1">
-        <x:v>708827</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="I15" s="1">
         <x:v>2026</x:v>
@@ -1272,10 +1260,10 @@
     </x:row>
     <x:row r="16" spans="1:10">
       <x:c r="A16" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
         <x:v>64</x:v>
@@ -1287,77 +1275,77 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F16" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
         <x:v>40</x:v>
       </x:c>
       <x:c r="H16" s="1">
-        <x:v>91656</x:v>
+        <x:v>47162</x:v>
       </x:c>
       <x:c r="I16" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J16" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:10">
       <x:c r="A17" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F17" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="H17" s="1">
-        <x:v>47162</x:v>
+        <x:v>418060</x:v>
       </x:c>
       <x:c r="I17" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J17" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:10">
       <x:c r="A18" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F18" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H18" s="1">
-        <x:v>418060</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="I18" s="1">
         <x:v>2026</x:v>
@@ -1368,28 +1356,28 @@
     </x:row>
     <x:row r="19" spans="1:10">
       <x:c r="A19" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F19" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="H19" s="1">
-        <x:v>285008</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="I19" s="1">
         <x:v>2026</x:v>
@@ -1400,28 +1388,28 @@
     </x:row>
     <x:row r="20" spans="1:10">
       <x:c r="A20" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F20" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H20" s="1">
-        <x:v>430866</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="I20" s="1">
         <x:v>2026</x:v>
@@ -1432,10 +1420,10 @@
     </x:row>
     <x:row r="21" spans="1:10">
       <x:c r="A21" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
         <x:v>79</x:v>
@@ -1447,13 +1435,13 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="F21" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="H21" s="1">
-        <x:v>30183</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I21" s="1">
         <x:v>2026</x:v>
@@ -1464,28 +1452,28 @@
     </x:row>
     <x:row r="22" spans="1:10">
       <x:c r="A22" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F22" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H22" s="1">
-        <x:v>350000</x:v>
+        <x:v>2780938</x:v>
       </x:c>
       <x:c r="I22" s="1">
         <x:v>2026</x:v>
@@ -1511,13 +1499,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F23" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="H23" s="1">
-        <x:v>4345153</x:v>
+        <x:v>64395</x:v>
       </x:c>
       <x:c r="I23" s="1">
         <x:v>2026</x:v>
@@ -1528,28 +1516,28 @@
     </x:row>
     <x:row r="24" spans="1:10">
       <x:c r="A24" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F24" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="H24" s="1">
-        <x:v>64395</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="I24" s="1">
         <x:v>2026</x:v>
@@ -1560,10 +1548,10 @@
     </x:row>
     <x:row r="25" spans="1:10">
       <x:c r="A25" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
         <x:v>89</x:v>
@@ -1578,10 +1566,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="H25" s="1">
-        <x:v>250000</x:v>
+        <x:v>7415826</x:v>
       </x:c>
       <x:c r="I25" s="1">
         <x:v>2026</x:v>
@@ -1592,16 +1580,16 @@
     </x:row>
     <x:row r="26" spans="1:10">
       <x:c r="A26" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
         <x:v>25</x:v>
@@ -1610,10 +1598,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="H26" s="1">
-        <x:v>7415826</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I26" s="1">
         <x:v>2026</x:v>
@@ -1624,28 +1612,28 @@
     </x:row>
     <x:row r="27" spans="1:10">
       <x:c r="A27" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F27" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="H27" s="1">
-        <x:v>350000</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="I27" s="1">
         <x:v>2026</x:v>
@@ -1656,28 +1644,28 @@
     </x:row>
     <x:row r="28" spans="1:10">
       <x:c r="A28" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F28" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="H28" s="1">
-        <x:v>80948</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="I28" s="1">
         <x:v>2026</x:v>
@@ -1688,10 +1676,10 @@
     </x:row>
     <x:row r="29" spans="1:10">
       <x:c r="A29" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
         <x:v>97</x:v>
@@ -1700,16 +1688,16 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F29" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H29" s="1">
-        <x:v>221403</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="I29" s="1">
         <x:v>2026</x:v>
@@ -1720,28 +1708,28 @@
     </x:row>
     <x:row r="30" spans="1:10">
       <x:c r="A30" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F30" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
         <x:v>40</x:v>
       </x:c>
       <x:c r="H30" s="1">
-        <x:v>141263</x:v>
+        <x:v>1750000</x:v>
       </x:c>
       <x:c r="I30" s="1">
         <x:v>2026</x:v>
@@ -1770,10 +1758,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="H31" s="1">
-        <x:v>1750000</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I31" s="1">
         <x:v>2026</x:v>
@@ -1784,60 +1772,60 @@
     </x:row>
     <x:row r="32" spans="1:10">
       <x:c r="A32" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F32" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="H32" s="1">
-        <x:v>817065</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="I32" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J32" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:10">
       <x:c r="A33" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F33" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H33" s="1">
-        <x:v>350000</x:v>
+        <x:v>108744</x:v>
       </x:c>
       <x:c r="I33" s="1">
         <x:v>2026</x:v>
@@ -1848,34 +1836,34 @@
     </x:row>
     <x:row r="34" spans="1:10">
       <x:c r="A34" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F34" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="H34" s="1">
-        <x:v>56045</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="I34" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J34" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:10">
@@ -1886,22 +1874,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F35" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
         <x:v>40</x:v>
       </x:c>
       <x:c r="H35" s="1">
-        <x:v>108744</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="I35" s="1">
         <x:v>2026</x:v>
@@ -1912,98 +1900,98 @@
     </x:row>
     <x:row r="36" spans="1:10">
       <x:c r="A36" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F36" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H36" s="1">
-        <x:v>282975</x:v>
+        <x:v>4697360</x:v>
       </x:c>
       <x:c r="I36" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J36" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:10">
       <x:c r="A37" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F37" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H37" s="1">
-        <x:v>771658</x:v>
+        <x:v>119644</x:v>
       </x:c>
       <x:c r="I37" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J37" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:10">
       <x:c r="A38" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="D38" s="1" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="E38" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F38" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G38" s="1" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="D38" s="1" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="E38" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F38" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="G38" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
       <x:c r="H38" s="1">
-        <x:v>9866096</x:v>
+        <x:v>56118</x:v>
       </x:c>
       <x:c r="I38" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J38" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:10">
@@ -2014,91 +2002,27 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F39" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H39" s="1">
-        <x:v>119644</x:v>
+        <x:v>187450</x:v>
       </x:c>
       <x:c r="I39" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J39" s="1" t="s">
-        <x:v>57</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:10">
-      <x:c r="A40" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B40" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C40" s="1" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="D40" s="1" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="E40" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F40" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G40" s="1" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="H40" s="1">
-        <x:v>56118</x:v>
-      </x:c>
-      <x:c r="I40" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J40" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:10">
-      <x:c r="A41" s="1" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="B41" s="1" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C41" s="1" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="D41" s="1" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="E41" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F41" s="1" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="G41" s="1" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="H41" s="1">
-        <x:v>144600</x:v>
-      </x:c>
-      <x:c r="I41" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J41" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -208,6 +208,15 @@
     <x:t>GOBER, CHRIS</x:t>
   </x:si>
   <x:si>
+    <x:t>S0SC00149</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRAHAM, LINDSEY O.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SC</x:t>
+  </x:si>
+  <x:si>
     <x:t>H4TX09095</x:t>
   </x:si>
   <x:si>
@@ -247,6 +256,12 @@
     <x:t>01</x:t>
   </x:si>
   <x:si>
+    <x:t>H6GA01109</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KINGSTON, JAMES MORRIS</x:t>
+  </x:si>
+  <x:si>
     <x:t>S6IL00482</x:t>
   </x:si>
   <x:si>
@@ -262,6 +277,15 @@
     <x:t>LA</x:t>
   </x:si>
   <x:si>
+    <x:t>H6TX09140</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEALER, ALEXANDRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09</x:t>
+  </x:si>
+  <x:si>
     <x:t>H6TX18232</x:t>
   </x:si>
   <x:si>
@@ -277,6 +301,9 @@
     <x:t>NJ</x:t>
   </x:si>
   <x:si>
+    <x:t>H2NJ13075</x:t>
+  </x:si>
+  <x:si>
     <x:t>S6LA00540</x:t>
   </x:si>
   <x:si>
@@ -371,9 +398,6 @@
   </x:si>
   <x:si>
     <x:t>TIMMONS, WILLIAM R IV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SC</x:t>
   </x:si>
   <x:si>
     <x:t>H0NY15160</x:t>
@@ -456,8 +480,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J39" totalsRowShown="0">
-  <x:autoFilter ref="A1:J39"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J43" totalsRowShown="0">
+  <x:autoFilter ref="A1:J43"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -762,7 +786,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J39"/>
+  <x:dimension ref="A1:J43"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1089,7 +1113,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="H10" s="1">
-        <x:v>35211</x:v>
+        <x:v>70422</x:v>
       </x:c>
       <x:c r="I10" s="1">
         <x:v>2026</x:v>
@@ -1260,10 +1284,10 @@
     </x:row>
     <x:row r="16" spans="1:10">
       <x:c r="A16" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
         <x:v>64</x:v>
@@ -1272,30 +1296,30 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F16" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G16" s="1" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="G16" s="1" t="s">
-        <x:v>40</x:v>
-      </x:c>
       <x:c r="H16" s="1">
-        <x:v>47162</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="I16" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J16" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:10">
       <x:c r="A17" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
         <x:v>67</x:v>
@@ -1310,42 +1334,42 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H17" s="1">
-        <x:v>418060</x:v>
+        <x:v>47162</x:v>
       </x:c>
       <x:c r="I17" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J17" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:10">
       <x:c r="A18" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="D18" s="1" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="D18" s="1" t="s">
+      <x:c r="E18" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F18" s="1" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="E18" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F18" s="1" t="s">
+      <x:c r="G18" s="1" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="G18" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
       <x:c r="H18" s="1">
-        <x:v>285008</x:v>
+        <x:v>418060</x:v>
       </x:c>
       <x:c r="I18" s="1">
         <x:v>2026</x:v>
@@ -1356,10 +1380,10 @@
     </x:row>
     <x:row r="19" spans="1:10">
       <x:c r="A19" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
         <x:v>74</x:v>
@@ -1368,16 +1392,16 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F19" s="1" t="s">
         <x:v>76</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H19" s="1">
-        <x:v>430866</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="I19" s="1">
         <x:v>2026</x:v>
@@ -1388,10 +1412,10 @@
     </x:row>
     <x:row r="20" spans="1:10">
       <x:c r="A20" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
         <x:v>77</x:v>
@@ -1400,16 +1424,16 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F20" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="H20" s="1">
-        <x:v>30183</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="I20" s="1">
         <x:v>2026</x:v>
@@ -1420,28 +1444,28 @@
     </x:row>
     <x:row r="21" spans="1:10">
       <x:c r="A21" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D21" s="1" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="E21" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F21" s="1" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="D21" s="1" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="E21" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F21" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="H21" s="1">
-        <x:v>350000</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="I21" s="1">
         <x:v>2026</x:v>
@@ -1464,16 +1488,16 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F22" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H22" s="1">
-        <x:v>2780938</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="I22" s="1">
         <x:v>2026</x:v>
@@ -1484,10 +1508,10 @@
     </x:row>
     <x:row r="23" spans="1:10">
       <x:c r="A23" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
         <x:v>84</x:v>
@@ -1496,16 +1520,16 @@
         <x:v>85</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F23" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
         <x:v>86</x:v>
       </x:c>
       <x:c r="H23" s="1">
-        <x:v>64395</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I23" s="1">
         <x:v>2026</x:v>
@@ -1516,10 +1540,10 @@
     </x:row>
     <x:row r="24" spans="1:10">
       <x:c r="A24" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
         <x:v>87</x:v>
@@ -1528,16 +1552,16 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F24" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H24" s="1">
-        <x:v>250000</x:v>
+        <x:v>25663</x:v>
       </x:c>
       <x:c r="I24" s="1">
         <x:v>2026</x:v>
@@ -1548,28 +1572,28 @@
     </x:row>
     <x:row r="25" spans="1:10">
       <x:c r="A25" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F25" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H25" s="1">
-        <x:v>7415826</x:v>
+        <x:v>4085945</x:v>
       </x:c>
       <x:c r="I25" s="1">
         <x:v>2026</x:v>
@@ -1580,28 +1604,28 @@
     </x:row>
     <x:row r="26" spans="1:10">
       <x:c r="A26" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F26" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="H26" s="1">
-        <x:v>350000</x:v>
+        <x:v>64395</x:v>
       </x:c>
       <x:c r="I26" s="1">
         <x:v>2026</x:v>
@@ -1612,13 +1636,13 @@
     </x:row>
     <x:row r="27" spans="1:10">
       <x:c r="A27" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
         <x:v>93</x:v>
@@ -1627,13 +1651,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F27" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
         <x:v>94</x:v>
       </x:c>
       <x:c r="H27" s="1">
-        <x:v>80948</x:v>
+        <x:v>34890</x:v>
       </x:c>
       <x:c r="I27" s="1">
         <x:v>2026</x:v>
@@ -1650,10 +1674,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
         <x:v>25</x:v>
@@ -1662,10 +1686,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="H28" s="1">
-        <x:v>221403</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="I28" s="1">
         <x:v>2026</x:v>
@@ -1682,22 +1706,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F29" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="H29" s="1">
-        <x:v>141263</x:v>
+        <x:v>7415826</x:v>
       </x:c>
       <x:c r="I29" s="1">
         <x:v>2026</x:v>
@@ -1714,10 +1738,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
         <x:v>25</x:v>
@@ -1726,10 +1750,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="H30" s="1">
-        <x:v>1750000</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I30" s="1">
         <x:v>2026</x:v>
@@ -1740,28 +1764,28 @@
     </x:row>
     <x:row r="31" spans="1:10">
       <x:c r="A31" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="D31" s="1" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="D31" s="1" t="s">
+      <x:c r="E31" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F31" s="1" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="G31" s="1" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="E31" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F31" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="G31" s="1" t="s">
-        <x:v>104</x:v>
-      </x:c>
       <x:c r="H31" s="1">
-        <x:v>350000</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="I31" s="1">
         <x:v>2026</x:v>
@@ -1772,34 +1796,34 @@
     </x:row>
     <x:row r="32" spans="1:10">
       <x:c r="A32" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="D32" s="1" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="D32" s="1" t="s">
-        <x:v>106</x:v>
-      </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F32" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="H32" s="1">
-        <x:v>56045</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="I32" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J32" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:10">
@@ -1810,22 +1834,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="D33" s="1" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="D33" s="1" t="s">
+      <x:c r="E33" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F33" s="1" t="s">
         <x:v>108</x:v>
-      </x:c>
-      <x:c r="E33" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F33" s="1" t="s">
-        <x:v>109</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
         <x:v>40</x:v>
       </x:c>
       <x:c r="H33" s="1">
-        <x:v>108744</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="I33" s="1">
         <x:v>2026</x:v>
@@ -1836,28 +1860,28 @@
     </x:row>
     <x:row r="34" spans="1:10">
       <x:c r="A34" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="D34" s="1" t="s">
         <x:v>110</x:v>
       </x:c>
-      <x:c r="D34" s="1" t="s">
-        <x:v>111</x:v>
-      </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F34" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H34" s="1">
-        <x:v>282975</x:v>
+        <x:v>1750000</x:v>
       </x:c>
       <x:c r="I34" s="1">
         <x:v>2026</x:v>
@@ -1868,28 +1892,28 @@
     </x:row>
     <x:row r="35" spans="1:10">
       <x:c r="A35" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="D35" s="1" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="E35" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F35" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G35" s="1" t="s">
         <x:v>113</x:v>
       </x:c>
-      <x:c r="D35" s="1" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="E35" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F35" s="1" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="G35" s="1" t="s">
-        <x:v>40</x:v>
-      </x:c>
       <x:c r="H35" s="1">
-        <x:v>771658</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I35" s="1">
         <x:v>2026</x:v>
@@ -1900,28 +1924,28 @@
     </x:row>
     <x:row r="36" spans="1:10">
       <x:c r="A36" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="D36" s="1" t="s">
         <x:v>115</x:v>
       </x:c>
-      <x:c r="D36" s="1" t="s">
-        <x:v>116</x:v>
-      </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F36" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="H36" s="1">
-        <x:v>4697360</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="I36" s="1">
         <x:v>2026</x:v>
@@ -1932,34 +1956,34 @@
     </x:row>
     <x:row r="37" spans="1:10">
       <x:c r="A37" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F37" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H37" s="1">
-        <x:v>119644</x:v>
+        <x:v>108744</x:v>
       </x:c>
       <x:c r="I37" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J37" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:10">
@@ -1970,22 +1994,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F38" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="H38" s="1">
-        <x:v>56118</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="I38" s="1">
         <x:v>2026</x:v>
@@ -1996,33 +2020,161 @@
     </x:row>
     <x:row r="39" spans="1:10">
       <x:c r="A39" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B39" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C39" s="1" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="D39" s="1" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="E39" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F39" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="G39" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="H39" s="1">
+        <x:v>771658</x:v>
+      </x:c>
+      <x:c r="I39" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J39" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:10">
+      <x:c r="A40" s="1" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B40" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C40" s="1" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="D40" s="1" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="E40" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F40" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G40" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H40" s="1">
+        <x:v>4697360</x:v>
+      </x:c>
+      <x:c r="I40" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J40" s="1" t="s">
+        <x:v>55</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:10">
+      <x:c r="A41" s="1" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="B39" s="1" t="s">
+      <x:c r="B41" s="1" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C39" s="1" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="D39" s="1" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="E39" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F39" s="1" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="G39" s="1" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="H39" s="1">
+      <x:c r="C41" s="1" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="D41" s="1" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="E41" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F41" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G41" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H41" s="1">
+        <x:v>119644</x:v>
+      </x:c>
+      <x:c r="I41" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J41" s="1" t="s">
+        <x:v>55</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:10">
+      <x:c r="A42" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B42" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C42" s="1" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="D42" s="1" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E42" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F42" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G42" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="H42" s="1">
+        <x:v>56118</x:v>
+      </x:c>
+      <x:c r="I42" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J42" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:10">
+      <x:c r="A43" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B43" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C43" s="1" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="D43" s="1" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="E43" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F43" s="1" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="G43" s="1" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="H43" s="1">
         <x:v>187450</x:v>
       </x:c>
-      <x:c r="I39" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J39" s="1" t="s">
+      <x:c r="I43" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J43" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -985,7 +985,7 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="H6" s="1">
-        <x:v>1069843</x:v>
+        <x:v>2062516</x:v>
       </x:c>
       <x:c r="I6" s="1">
         <x:v>2026</x:v>
@@ -1017,7 +1017,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="H7" s="1">
-        <x:v>85440</x:v>
+        <x:v>348433</x:v>
       </x:c>
       <x:c r="I7" s="1">
         <x:v>2026</x:v>
@@ -1113,7 +1113,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="H10" s="1">
-        <x:v>70422</x:v>
+        <x:v>581175</x:v>
       </x:c>
       <x:c r="I10" s="1">
         <x:v>2026</x:v>
@@ -1561,7 +1561,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="H24" s="1">
-        <x:v>25663</x:v>
+        <x:v>436280</x:v>
       </x:c>
       <x:c r="I24" s="1">
         <x:v>2026</x:v>
@@ -1593,7 +1593,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="H25" s="1">
-        <x:v>4085945</x:v>
+        <x:v>4103505</x:v>
       </x:c>
       <x:c r="I25" s="1">
         <x:v>2026</x:v>
@@ -1881,7 +1881,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="H34" s="1">
-        <x:v>1750000</x:v>
+        <x:v>2250000</x:v>
       </x:c>
       <x:c r="I34" s="1">
         <x:v>2026</x:v>
@@ -1977,7 +1977,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="H37" s="1">
-        <x:v>108744</x:v>
+        <x:v>426280</x:v>
       </x:c>
       <x:c r="I37" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -157,6 +157,18 @@
     <x:t>COLLINS, MICHAEL A JR</x:t>
   </x:si>
   <x:si>
+    <x:t>H6CA46116</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CORREA, LOU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>46</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CA</x:t>
+  </x:si>
+  <x:si>
     <x:t>H6TX35087</x:t>
   </x:si>
   <x:si>
@@ -277,6 +289,21 @@
     <x:t>LA</x:t>
   </x:si>
   <x:si>
+    <x:t>H4CA33119</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LIEU, TED</x:t>
+  </x:si>
+  <x:si>
+    <x:t>36</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H4CA16049</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LOFGREN, ZOE</x:t>
+  </x:si>
+  <x:si>
     <x:t>H6TX09140</x:t>
   </x:si>
   <x:si>
@@ -310,6 +337,15 @@
     <x:t>MIGUEZ, BLAKE</x:t>
   </x:si>
   <x:si>
+    <x:t>H4CA47085</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIN, DAVE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>47</x:t>
+  </x:si>
+  <x:si>
     <x:t>S6AL00476</x:t>
   </x:si>
   <x:si>
@@ -371,6 +407,15 @@
   </x:si>
   <x:si>
     <x:t>19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H4CA12154</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SIMON, LATEEFAH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12</x:t>
   </x:si>
   <x:si>
     <x:t>H6NE03115</x:t>
@@ -480,8 +525,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J43" totalsRowShown="0">
-  <x:autoFilter ref="A1:J43"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J48" totalsRowShown="0">
+  <x:autoFilter ref="A1:J48"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -786,7 +831,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J43"/>
+  <x:dimension ref="A1:J48"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1092,10 +1137,10 @@
     </x:row>
     <x:row r="10" spans="1:10">
       <x:c r="A10" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
         <x:v>47</x:v>
@@ -1110,10 +1155,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H10" s="1">
-        <x:v>581175</x:v>
+        <x:v>53694</x:v>
       </x:c>
       <x:c r="I10" s="1">
         <x:v>2026</x:v>
@@ -1124,42 +1169,42 @@
     </x:row>
     <x:row r="11" spans="1:10">
       <x:c r="A11" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C11" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="C11" s="1" t="s">
+      <x:c r="D11" s="1" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="D11" s="1" t="s">
+      <x:c r="E11" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F11" s="1" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="E11" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F11" s="1" t="s">
-        <x:v>54</x:v>
-      </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H11" s="1">
-        <x:v>672092</x:v>
+        <x:v>616386</x:v>
       </x:c>
       <x:c r="I11" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J11" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:10">
       <x:c r="A12" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
         <x:v>56</x:v>
@@ -1174,42 +1219,42 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H12" s="1">
-        <x:v>455146</x:v>
+        <x:v>672092</x:v>
       </x:c>
       <x:c r="I12" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J12" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:10">
       <x:c r="A13" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
         <x:v>44</x:v>
       </x:c>
       <x:c r="H13" s="1">
-        <x:v>300000</x:v>
+        <x:v>455146</x:v>
       </x:c>
       <x:c r="I13" s="1">
         <x:v>2026</x:v>
@@ -1220,28 +1265,28 @@
     </x:row>
     <x:row r="14" spans="1:10">
       <x:c r="A14" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F14" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
         <x:v>44</x:v>
       </x:c>
       <x:c r="H14" s="1">
-        <x:v>708827</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="I14" s="1">
         <x:v>2026</x:v>
@@ -1258,22 +1303,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F15" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="H15" s="1">
-        <x:v>91656</x:v>
+        <x:v>708827</x:v>
       </x:c>
       <x:c r="I15" s="1">
         <x:v>2026</x:v>
@@ -1284,28 +1329,28 @@
     </x:row>
     <x:row r="16" spans="1:10">
       <x:c r="A16" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="E16" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F16" s="1" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="E16" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F16" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H16" s="1">
-        <x:v>550000</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="I16" s="1">
         <x:v>2026</x:v>
@@ -1316,74 +1361,74 @@
     </x:row>
     <x:row r="17" spans="1:10">
       <x:c r="A17" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F17" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="H17" s="1">
-        <x:v>47162</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="I17" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J17" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:10">
       <x:c r="A18" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F18" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H18" s="1">
-        <x:v>418060</x:v>
+        <x:v>47162</x:v>
       </x:c>
       <x:c r="I18" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J18" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:10">
       <x:c r="A19" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
         <x:v>74</x:v>
@@ -1392,16 +1437,16 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F19" s="1" t="s">
         <x:v>76</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="H19" s="1">
-        <x:v>285008</x:v>
+        <x:v>418060</x:v>
       </x:c>
       <x:c r="I19" s="1">
         <x:v>2026</x:v>
@@ -1412,28 +1457,28 @@
     </x:row>
     <x:row r="20" spans="1:10">
       <x:c r="A20" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F20" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H20" s="1">
-        <x:v>430866</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="I20" s="1">
         <x:v>2026</x:v>
@@ -1450,16 +1495,16 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F21" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
         <x:v>44</x:v>
@@ -1476,28 +1521,28 @@
     </x:row>
     <x:row r="22" spans="1:10">
       <x:c r="A22" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="E22" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F22" s="1" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="E22" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F22" s="1" t="s">
-        <x:v>76</x:v>
-      </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="H22" s="1">
-        <x:v>30183</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="I22" s="1">
         <x:v>2026</x:v>
@@ -1508,28 +1553,28 @@
     </x:row>
     <x:row r="23" spans="1:10">
       <x:c r="A23" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="F23" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H23" s="1">
-        <x:v>350000</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="I23" s="1">
         <x:v>2026</x:v>
@@ -1540,28 +1585,28 @@
     </x:row>
     <x:row r="24" spans="1:10">
       <x:c r="A24" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F24" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H24" s="1">
-        <x:v>436280</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I24" s="1">
         <x:v>2026</x:v>
@@ -1578,22 +1623,22 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F25" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H25" s="1">
-        <x:v>4103505</x:v>
+        <x:v>53174</x:v>
       </x:c>
       <x:c r="I25" s="1">
         <x:v>2026</x:v>
@@ -1610,22 +1655,22 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F26" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H26" s="1">
-        <x:v>64395</x:v>
+        <x:v>54637</x:v>
       </x:c>
       <x:c r="I26" s="1">
         <x:v>2026</x:v>
@@ -1636,28 +1681,28 @@
     </x:row>
     <x:row r="27" spans="1:10">
       <x:c r="A27" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F27" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H27" s="1">
-        <x:v>34890</x:v>
+        <x:v>461943</x:v>
       </x:c>
       <x:c r="I27" s="1">
         <x:v>2026</x:v>
@@ -1668,28 +1713,28 @@
     </x:row>
     <x:row r="28" spans="1:10">
       <x:c r="A28" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F28" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H28" s="1">
-        <x:v>250000</x:v>
+        <x:v>4150667</x:v>
       </x:c>
       <x:c r="I28" s="1">
         <x:v>2026</x:v>
@@ -1700,28 +1745,28 @@
     </x:row>
     <x:row r="29" spans="1:10">
       <x:c r="A29" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F29" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="H29" s="1">
-        <x:v>7415826</x:v>
+        <x:v>128790</x:v>
       </x:c>
       <x:c r="I29" s="1">
         <x:v>2026</x:v>
@@ -1732,28 +1777,28 @@
     </x:row>
     <x:row r="30" spans="1:10">
       <x:c r="A30" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F30" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="H30" s="1">
-        <x:v>350000</x:v>
+        <x:v>34890</x:v>
       </x:c>
       <x:c r="I30" s="1">
         <x:v>2026</x:v>
@@ -1764,28 +1809,28 @@
     </x:row>
     <x:row r="31" spans="1:10">
       <x:c r="A31" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F31" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H31" s="1">
-        <x:v>80948</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="I31" s="1">
         <x:v>2026</x:v>
@@ -1796,28 +1841,28 @@
     </x:row>
     <x:row r="32" spans="1:10">
       <x:c r="A32" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F32" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H32" s="1">
-        <x:v>221403</x:v>
+        <x:v>53970</x:v>
       </x:c>
       <x:c r="I32" s="1">
         <x:v>2026</x:v>
@@ -1834,22 +1879,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F33" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="H33" s="1">
-        <x:v>141263</x:v>
+        <x:v>7415826</x:v>
       </x:c>
       <x:c r="I33" s="1">
         <x:v>2026</x:v>
@@ -1866,10 +1911,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
         <x:v>25</x:v>
@@ -1878,10 +1923,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="H34" s="1">
-        <x:v>2250000</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I34" s="1">
         <x:v>2026</x:v>
@@ -1892,28 +1937,28 @@
     </x:row>
     <x:row r="35" spans="1:10">
       <x:c r="A35" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F35" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="H35" s="1">
-        <x:v>350000</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="I35" s="1">
         <x:v>2026</x:v>
@@ -1924,34 +1969,34 @@
     </x:row>
     <x:row r="36" spans="1:10">
       <x:c r="A36" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F36" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="H36" s="1">
-        <x:v>56045</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="I36" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J36" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:10">
@@ -1962,22 +2007,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F37" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
         <x:v>40</x:v>
       </x:c>
       <x:c r="H37" s="1">
-        <x:v>426280</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="I37" s="1">
         <x:v>2026</x:v>
@@ -1988,28 +2033,28 @@
     </x:row>
     <x:row r="38" spans="1:10">
       <x:c r="A38" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F38" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H38" s="1">
-        <x:v>282975</x:v>
+        <x:v>2250000</x:v>
       </x:c>
       <x:c r="I38" s="1">
         <x:v>2026</x:v>
@@ -2020,28 +2065,28 @@
     </x:row>
     <x:row r="39" spans="1:10">
       <x:c r="A39" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F39" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="H39" s="1">
-        <x:v>771658</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I39" s="1">
         <x:v>2026</x:v>
@@ -2052,92 +2097,92 @@
     </x:row>
     <x:row r="40" spans="1:10">
       <x:c r="A40" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F40" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="H40" s="1">
-        <x:v>4697360</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="I40" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J40" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:10">
       <x:c r="A41" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F41" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H41" s="1">
-        <x:v>119644</x:v>
+        <x:v>426280</x:v>
       </x:c>
       <x:c r="I41" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J41" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:10">
       <x:c r="A42" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F42" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H42" s="1">
-        <x:v>56118</x:v>
+        <x:v>55799</x:v>
       </x:c>
       <x:c r="I42" s="1">
         <x:v>2026</x:v>
@@ -2148,33 +2193,193 @@
     </x:row>
     <x:row r="43" spans="1:10">
       <x:c r="A43" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B43" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C43" s="1" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="D43" s="1" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="E43" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F43" s="1" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="G43" s="1" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="H43" s="1">
+        <x:v>282975</x:v>
+      </x:c>
+      <x:c r="I43" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J43" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:10">
+      <x:c r="A44" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B44" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C44" s="1" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="D44" s="1" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="E44" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F44" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="G44" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="H44" s="1">
+        <x:v>771658</x:v>
+      </x:c>
+      <x:c r="I44" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J44" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:10">
+      <x:c r="A45" s="1" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B45" s="1" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="C45" s="1" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="D45" s="1" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="E45" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F45" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G45" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H45" s="1">
+        <x:v>4697360</x:v>
+      </x:c>
+      <x:c r="I45" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J45" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:10">
+      <x:c r="A46" s="1" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="B43" s="1" t="s">
+      <x:c r="B46" s="1" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C43" s="1" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="D43" s="1" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="E43" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F43" s="1" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="G43" s="1" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="H43" s="1">
+      <x:c r="C46" s="1" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="D46" s="1" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="E46" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F46" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G46" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H46" s="1">
+        <x:v>119644</x:v>
+      </x:c>
+      <x:c r="I46" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J46" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:10">
+      <x:c r="A47" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B47" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C47" s="1" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="D47" s="1" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="E47" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F47" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G47" s="1" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="H47" s="1">
+        <x:v>56118</x:v>
+      </x:c>
+      <x:c r="I47" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J47" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:10">
+      <x:c r="A48" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B48" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C48" s="1" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="D48" s="1" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="E48" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F48" s="1" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="G48" s="1" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="H48" s="1">
         <x:v>187450</x:v>
       </x:c>
-      <x:c r="I43" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J43" s="1" t="s">
+      <x:c r="I48" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J48" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -2374,7 +2374,7 @@
         <x:v>146</x:v>
       </x:c>
       <x:c r="H48" s="1">
-        <x:v>187450</x:v>
+        <x:v>231242</x:v>
       </x:c>
       <x:c r="I48" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -302,6 +302,12 @@
   </x:si>
   <x:si>
     <x:t>LOFGREN, ZOE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H6CA01269</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCGUIRE, MIKE</x:t>
   </x:si>
   <x:si>
     <x:t>H6TX09140</x:t>
@@ -525,8 +531,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J48" totalsRowShown="0">
-  <x:autoFilter ref="A1:J48"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J49" totalsRowShown="0">
+  <x:autoFilter ref="A1:J49"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -831,7 +837,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J48"/>
+  <x:dimension ref="A1:J49"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1030,7 +1036,7 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="H6" s="1">
-        <x:v>2062516</x:v>
+        <x:v>2122190</x:v>
       </x:c>
       <x:c r="I6" s="1">
         <x:v>2026</x:v>
@@ -1681,10 +1687,10 @@
     </x:row>
     <x:row r="27" spans="1:10">
       <x:c r="A27" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
         <x:v>96</x:v>
@@ -1696,13 +1702,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F27" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H27" s="1">
-        <x:v>461943</x:v>
+        <x:v>55720</x:v>
       </x:c>
       <x:c r="I27" s="1">
         <x:v>2026</x:v>
@@ -1713,28 +1719,28 @@
     </x:row>
     <x:row r="28" spans="1:10">
       <x:c r="A28" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D28" s="1" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="D28" s="1" t="s">
+      <x:c r="E28" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F28" s="1" t="s">
         <x:v>100</x:v>
-      </x:c>
-      <x:c r="E28" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F28" s="1" t="s">
-        <x:v>73</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
         <x:v>40</x:v>
       </x:c>
       <x:c r="H28" s="1">
-        <x:v>4150667</x:v>
+        <x:v>461943</x:v>
       </x:c>
       <x:c r="I28" s="1">
         <x:v>2026</x:v>
@@ -1760,13 +1766,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F29" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H29" s="1">
-        <x:v>128790</x:v>
+        <x:v>4150667</x:v>
       </x:c>
       <x:c r="I29" s="1">
         <x:v>2026</x:v>
@@ -1783,10 +1789,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="D30" s="1" t="s">
         <x:v>104</x:v>
-      </x:c>
-      <x:c r="D30" s="1" t="s">
-        <x:v>102</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
         <x:v>14</x:v>
@@ -1795,10 +1801,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="H30" s="1">
-        <x:v>34890</x:v>
+        <x:v>128790</x:v>
       </x:c>
       <x:c r="I30" s="1">
         <x:v>2026</x:v>
@@ -1809,28 +1815,28 @@
     </x:row>
     <x:row r="31" spans="1:10">
       <x:c r="A31" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="D31" s="1" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="E31" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F31" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="G31" s="1" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="D31" s="1" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="E31" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F31" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="G31" s="1" t="s">
-        <x:v>90</x:v>
-      </x:c>
       <x:c r="H31" s="1">
-        <x:v>250000</x:v>
+        <x:v>34890</x:v>
       </x:c>
       <x:c r="I31" s="1">
         <x:v>2026</x:v>
@@ -1841,10 +1847,10 @@
     </x:row>
     <x:row r="32" spans="1:10">
       <x:c r="A32" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
         <x:v>107</x:v>
@@ -1853,16 +1859,16 @@
         <x:v>108</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F32" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H32" s="1">
-        <x:v>53970</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="I32" s="1">
         <x:v>2026</x:v>
@@ -1873,28 +1879,28 @@
     </x:row>
     <x:row r="33" spans="1:10">
       <x:c r="A33" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="D33" s="1" t="s">
         <x:v>110</x:v>
       </x:c>
-      <x:c r="D33" s="1" t="s">
+      <x:c r="E33" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F33" s="1" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="E33" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F33" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H33" s="1">
-        <x:v>7415826</x:v>
+        <x:v>53970</x:v>
       </x:c>
       <x:c r="I33" s="1">
         <x:v>2026</x:v>
@@ -1905,16 +1911,16 @@
     </x:row>
     <x:row r="34" spans="1:10">
       <x:c r="A34" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
         <x:v>25</x:v>
@@ -1923,10 +1929,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="H34" s="1">
-        <x:v>350000</x:v>
+        <x:v>7415826</x:v>
       </x:c>
       <x:c r="I34" s="1">
         <x:v>2026</x:v>
@@ -1937,28 +1943,28 @@
     </x:row>
     <x:row r="35" spans="1:10">
       <x:c r="A35" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="D35" s="1" t="s">
         <x:v>113</x:v>
       </x:c>
-      <x:c r="D35" s="1" t="s">
+      <x:c r="E35" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F35" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G35" s="1" t="s">
         <x:v>114</x:v>
       </x:c>
-      <x:c r="E35" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F35" s="1" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="G35" s="1" t="s">
-        <x:v>115</x:v>
-      </x:c>
       <x:c r="H35" s="1">
-        <x:v>80948</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I35" s="1">
         <x:v>2026</x:v>
@@ -1969,28 +1975,28 @@
     </x:row>
     <x:row r="36" spans="1:10">
       <x:c r="A36" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="D36" s="1" t="s">
         <x:v>116</x:v>
       </x:c>
-      <x:c r="D36" s="1" t="s">
+      <x:c r="E36" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F36" s="1" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="G36" s="1" t="s">
         <x:v>117</x:v>
       </x:c>
-      <x:c r="E36" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F36" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="G36" s="1" t="s">
-        <x:v>21</x:v>
-      </x:c>
       <x:c r="H36" s="1">
-        <x:v>221403</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="I36" s="1">
         <x:v>2026</x:v>
@@ -2001,10 +2007,10 @@
     </x:row>
     <x:row r="37" spans="1:10">
       <x:c r="A37" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
         <x:v>118</x:v>
@@ -2013,16 +2019,16 @@
         <x:v>119</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F37" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="H37" s="1">
-        <x:v>141263</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="I37" s="1">
         <x:v>2026</x:v>
@@ -2033,28 +2039,28 @@
     </x:row>
     <x:row r="38" spans="1:10">
       <x:c r="A38" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="D38" s="1" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="D38" s="1" t="s">
+      <x:c r="E38" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F38" s="1" t="s">
         <x:v>122</x:v>
-      </x:c>
-      <x:c r="E38" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F38" s="1" t="s">
-        <x:v>26</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
         <x:v>40</x:v>
       </x:c>
       <x:c r="H38" s="1">
-        <x:v>2250000</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="I38" s="1">
         <x:v>2026</x:v>
@@ -2083,10 +2089,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H39" s="1">
-        <x:v>350000</x:v>
+        <x:v>2250000</x:v>
       </x:c>
       <x:c r="I39" s="1">
         <x:v>2026</x:v>
@@ -2097,42 +2103,42 @@
     </x:row>
     <x:row r="40" spans="1:10">
       <x:c r="A40" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="D40" s="1" t="s">
         <x:v>126</x:v>
       </x:c>
-      <x:c r="D40" s="1" t="s">
+      <x:c r="E40" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F40" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G40" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
-      <x:c r="E40" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F40" s="1" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="G40" s="1" t="s">
-        <x:v>44</x:v>
-      </x:c>
       <x:c r="H40" s="1">
-        <x:v>56045</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I40" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J40" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:10">
       <x:c r="A41" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
         <x:v>128</x:v>
@@ -2144,45 +2150,45 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F41" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="H41" s="1">
-        <x:v>426280</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="I41" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J41" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:10">
       <x:c r="A42" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="D42" s="1" t="s">
         <x:v>131</x:v>
       </x:c>
-      <x:c r="D42" s="1" t="s">
+      <x:c r="E42" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F42" s="1" t="s">
         <x:v>132</x:v>
       </x:c>
-      <x:c r="E42" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F42" s="1" t="s">
-        <x:v>133</x:v>
-      </x:c>
       <x:c r="G42" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H42" s="1">
-        <x:v>55799</x:v>
+        <x:v>426280</x:v>
       </x:c>
       <x:c r="I42" s="1">
         <x:v>2026</x:v>
@@ -2193,28 +2199,28 @@
     </x:row>
     <x:row r="43" spans="1:10">
       <x:c r="A43" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="D43" s="1" t="s">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="D43" s="1" t="s">
+      <x:c r="E43" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F43" s="1" t="s">
         <x:v>135</x:v>
       </x:c>
-      <x:c r="E43" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F43" s="1" t="s">
-        <x:v>136</x:v>
-      </x:c>
       <x:c r="G43" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H43" s="1">
-        <x:v>282975</x:v>
+        <x:v>55799</x:v>
       </x:c>
       <x:c r="I43" s="1">
         <x:v>2026</x:v>
@@ -2231,22 +2237,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="D44" s="1" t="s">
         <x:v>137</x:v>
       </x:c>
-      <x:c r="D44" s="1" t="s">
+      <x:c r="E44" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F44" s="1" t="s">
         <x:v>138</x:v>
       </x:c>
-      <x:c r="E44" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F44" s="1" t="s">
-        <x:v>31</x:v>
-      </x:c>
       <x:c r="G44" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="H44" s="1">
-        <x:v>771658</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="I44" s="1">
         <x:v>2026</x:v>
@@ -2257,10 +2263,10 @@
     </x:row>
     <x:row r="45" spans="1:10">
       <x:c r="A45" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
         <x:v>139</x:v>
@@ -2269,36 +2275,36 @@
         <x:v>140</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F45" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H45" s="1">
-        <x:v>4697360</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="I45" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J45" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:10">
       <x:c r="A46" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>139</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>140</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
         <x:v>25</x:v>
@@ -2310,7 +2316,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="H46" s="1">
-        <x:v>119644</x:v>
+        <x:v>4697360</x:v>
       </x:c>
       <x:c r="I46" s="1">
         <x:v>2026</x:v>
@@ -2321,10 +2327,10 @@
     </x:row>
     <x:row r="47" spans="1:10">
       <x:c r="A47" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
         <x:v>141</x:v>
@@ -2333,30 +2339,30 @@
         <x:v>142</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F47" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H47" s="1">
-        <x:v>56118</x:v>
+        <x:v>119644</x:v>
       </x:c>
       <x:c r="I47" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J47" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:10">
       <x:c r="A48" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
         <x:v>143</x:v>
@@ -2368,18 +2374,50 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F48" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G48" s="1" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="H48" s="1">
+        <x:v>56118</x:v>
+      </x:c>
+      <x:c r="I48" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J48" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:10">
+      <x:c r="A49" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B49" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C49" s="1" t="s">
         <x:v>145</x:v>
       </x:c>
-      <x:c r="G48" s="1" t="s">
+      <x:c r="D49" s="1" t="s">
         <x:v>146</x:v>
       </x:c>
-      <x:c r="H48" s="1">
+      <x:c r="E49" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F49" s="1" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="G49" s="1" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="H49" s="1">
         <x:v>231242</x:v>
       </x:c>
-      <x:c r="I48" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J48" s="1" t="s">
+      <x:c r="I49" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J49" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -1772,7 +1772,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="H29" s="1">
-        <x:v>4150667</x:v>
+        <x:v>4903859</x:v>
       </x:c>
       <x:c r="I29" s="1">
         <x:v>2026</x:v>
@@ -1932,7 +1932,7 @@
         <x:v>114</x:v>
       </x:c>
       <x:c r="H34" s="1">
-        <x:v>7415826</x:v>
+        <x:v>8423195</x:v>
       </x:c>
       <x:c r="I34" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -250,6 +250,15 @@
     <x:t>AR</x:t>
   </x:si>
   <x:si>
+    <x:t>H6CA26266</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IRWIN, JACQUI V</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26</x:t>
+  </x:si>
+  <x:si>
     <x:t>S6IL00474</x:t>
   </x:si>
   <x:si>
@@ -431,6 +440,12 @@
   </x:si>
   <x:si>
     <x:t>03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H6CA38139</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SOLIS, HILDA</x:t>
   </x:si>
   <x:si>
     <x:t>H6TX08209</x:t>
@@ -531,8 +546,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J49" totalsRowShown="0">
-  <x:autoFilter ref="A1:J49"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J51" totalsRowShown="0">
+  <x:autoFilter ref="A1:J51"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -837,7 +852,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J49"/>
+  <x:dimension ref="A1:J51"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1036,7 +1051,7 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="H6" s="1">
-        <x:v>2122190</x:v>
+        <x:v>3114863</x:v>
       </x:c>
       <x:c r="I6" s="1">
         <x:v>2026</x:v>
@@ -1164,7 +1179,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="H10" s="1">
-        <x:v>53694</x:v>
+        <x:v>107388</x:v>
       </x:c>
       <x:c r="I10" s="1">
         <x:v>2026</x:v>
@@ -1475,16 +1490,16 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F20" s="1" t="s">
         <x:v>80</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H20" s="1">
-        <x:v>285008</x:v>
+        <x:v>54932</x:v>
       </x:c>
       <x:c r="I20" s="1">
         <x:v>2026</x:v>
@@ -1495,10 +1510,10 @@
     </x:row>
     <x:row r="21" spans="1:10">
       <x:c r="A21" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
         <x:v>81</x:v>
@@ -1507,16 +1522,16 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F21" s="1" t="s">
         <x:v>83</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H21" s="1">
-        <x:v>430866</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="I21" s="1">
         <x:v>2026</x:v>
@@ -1542,7 +1557,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F22" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
         <x:v>44</x:v>
@@ -1559,28 +1574,28 @@
     </x:row>
     <x:row r="23" spans="1:10">
       <x:c r="A23" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="D23" s="1" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="E23" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F23" s="1" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="D23" s="1" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="E23" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F23" s="1" t="s">
-        <x:v>80</x:v>
-      </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="H23" s="1">
-        <x:v>30183</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="I23" s="1">
         <x:v>2026</x:v>
@@ -1591,28 +1606,28 @@
     </x:row>
     <x:row r="24" spans="1:10">
       <x:c r="A24" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="F24" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H24" s="1">
-        <x:v>350000</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="I24" s="1">
         <x:v>2026</x:v>
@@ -1623,10 +1638,10 @@
     </x:row>
     <x:row r="25" spans="1:10">
       <x:c r="A25" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
         <x:v>91</x:v>
@@ -1635,16 +1650,16 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F25" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G25" s="1" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="G25" s="1" t="s">
-        <x:v>50</x:v>
-      </x:c>
       <x:c r="H25" s="1">
-        <x:v>53174</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I25" s="1">
         <x:v>2026</x:v>
@@ -1670,13 +1685,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F26" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
         <x:v>50</x:v>
       </x:c>
       <x:c r="H26" s="1">
-        <x:v>54637</x:v>
+        <x:v>106348</x:v>
       </x:c>
       <x:c r="I26" s="1">
         <x:v>2026</x:v>
@@ -1693,22 +1708,22 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F27" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
         <x:v>50</x:v>
       </x:c>
       <x:c r="H27" s="1">
-        <x:v>55720</x:v>
+        <x:v>109274</x:v>
       </x:c>
       <x:c r="I27" s="1">
         <x:v>2026</x:v>
@@ -1719,28 +1734,28 @@
     </x:row>
     <x:row r="28" spans="1:10">
       <x:c r="A28" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F28" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H28" s="1">
-        <x:v>461943</x:v>
+        <x:v>111440</x:v>
       </x:c>
       <x:c r="I28" s="1">
         <x:v>2026</x:v>
@@ -1751,10 +1766,10 @@
     </x:row>
     <x:row r="29" spans="1:10">
       <x:c r="A29" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
         <x:v>101</x:v>
@@ -1766,13 +1781,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F29" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
         <x:v>40</x:v>
       </x:c>
       <x:c r="H29" s="1">
-        <x:v>4903859</x:v>
+        <x:v>461943</x:v>
       </x:c>
       <x:c r="I29" s="1">
         <x:v>2026</x:v>
@@ -1789,22 +1804,22 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F30" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H30" s="1">
-        <x:v>128790</x:v>
+        <x:v>4903859</x:v>
       </x:c>
       <x:c r="I30" s="1">
         <x:v>2026</x:v>
@@ -1824,7 +1839,7 @@
         <x:v>106</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
         <x:v>14</x:v>
@@ -1833,10 +1848,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="H31" s="1">
-        <x:v>34890</x:v>
+        <x:v>163680</x:v>
       </x:c>
       <x:c r="I31" s="1">
         <x:v>2026</x:v>
@@ -1847,28 +1862,28 @@
     </x:row>
     <x:row r="32" spans="1:10">
       <x:c r="A32" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="D32" s="1" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="D32" s="1" t="s">
+      <x:c r="E32" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F32" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="G32" s="1" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="E32" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F32" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="G32" s="1" t="s">
-        <x:v>90</x:v>
-      </x:c>
       <x:c r="H32" s="1">
-        <x:v>250000</x:v>
+        <x:v>34890</x:v>
       </x:c>
       <x:c r="I32" s="1">
         <x:v>2026</x:v>
@@ -1879,28 +1894,28 @@
     </x:row>
     <x:row r="33" spans="1:10">
       <x:c r="A33" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F33" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="H33" s="1">
-        <x:v>53970</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="I33" s="1">
         <x:v>2026</x:v>
@@ -1911,10 +1926,10 @@
     </x:row>
     <x:row r="34" spans="1:10">
       <x:c r="A34" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
         <x:v>112</x:v>
@@ -1923,16 +1938,16 @@
         <x:v>113</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F34" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H34" s="1">
-        <x:v>8423195</x:v>
+        <x:v>107940</x:v>
       </x:c>
       <x:c r="I34" s="1">
         <x:v>2026</x:v>
@@ -1943,16 +1958,16 @@
     </x:row>
     <x:row r="35" spans="1:10">
       <x:c r="A35" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
         <x:v>25</x:v>
@@ -1961,10 +1976,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="H35" s="1">
-        <x:v>350000</x:v>
+        <x:v>8423195</x:v>
       </x:c>
       <x:c r="I35" s="1">
         <x:v>2026</x:v>
@@ -1975,10 +1990,10 @@
     </x:row>
     <x:row r="36" spans="1:10">
       <x:c r="A36" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
         <x:v>115</x:v>
@@ -1987,16 +2002,16 @@
         <x:v>116</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F36" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
         <x:v>117</x:v>
       </x:c>
       <x:c r="H36" s="1">
-        <x:v>80948</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I36" s="1">
         <x:v>2026</x:v>
@@ -2007,10 +2022,10 @@
     </x:row>
     <x:row r="37" spans="1:10">
       <x:c r="A37" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
         <x:v>118</x:v>
@@ -2019,16 +2034,16 @@
         <x:v>119</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F37" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="H37" s="1">
-        <x:v>221403</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="I37" s="1">
         <x:v>2026</x:v>
@@ -2039,28 +2054,28 @@
     </x:row>
     <x:row r="38" spans="1:10">
       <x:c r="A38" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F38" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="H38" s="1">
-        <x:v>141263</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="I38" s="1">
         <x:v>2026</x:v>
@@ -2071,10 +2086,10 @@
     </x:row>
     <x:row r="39" spans="1:10">
       <x:c r="A39" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
         <x:v>123</x:v>
@@ -2083,16 +2098,16 @@
         <x:v>124</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F39" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
         <x:v>40</x:v>
       </x:c>
       <x:c r="H39" s="1">
-        <x:v>2250000</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="I39" s="1">
         <x:v>2026</x:v>
@@ -2109,10 +2124,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
         <x:v>25</x:v>
@@ -2121,10 +2136,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H40" s="1">
-        <x:v>350000</x:v>
+        <x:v>2250000</x:v>
       </x:c>
       <x:c r="I40" s="1">
         <x:v>2026</x:v>
@@ -2135,10 +2150,10 @@
     </x:row>
     <x:row r="41" spans="1:10">
       <x:c r="A41" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
         <x:v>128</x:v>
@@ -2147,62 +2162,62 @@
         <x:v>129</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F41" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="H41" s="1">
-        <x:v>56045</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I41" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J41" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:10">
       <x:c r="A42" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F42" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="H42" s="1">
-        <x:v>426280</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="I42" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J42" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:10">
       <x:c r="A43" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
         <x:v>133</x:v>
@@ -2217,10 +2232,10 @@
         <x:v>135</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H43" s="1">
-        <x:v>55799</x:v>
+        <x:v>426280</x:v>
       </x:c>
       <x:c r="I43" s="1">
         <x:v>2026</x:v>
@@ -2231,10 +2246,10 @@
     </x:row>
     <x:row r="44" spans="1:10">
       <x:c r="A44" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
         <x:v>136</x:v>
@@ -2249,10 +2264,10 @@
         <x:v>138</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H44" s="1">
-        <x:v>282975</x:v>
+        <x:v>111598</x:v>
       </x:c>
       <x:c r="I44" s="1">
         <x:v>2026</x:v>
@@ -2278,13 +2293,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F45" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="H45" s="1">
-        <x:v>771658</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="I45" s="1">
         <x:v>2026</x:v>
@@ -2295,98 +2310,98 @@
     </x:row>
     <x:row r="46" spans="1:10">
       <x:c r="A46" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F46" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H46" s="1">
-        <x:v>4697360</x:v>
+        <x:v>54685</x:v>
       </x:c>
       <x:c r="I46" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J46" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:10">
       <x:c r="A47" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>141</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F47" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H47" s="1">
-        <x:v>119644</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="I47" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J47" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:10">
       <x:c r="A48" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>143</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>144</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F48" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H48" s="1">
-        <x:v>56118</x:v>
+        <x:v>4697360</x:v>
       </x:c>
       <x:c r="I48" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J48" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:10">
@@ -2397,27 +2412,91 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>145</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F49" s="1" t="s">
-        <x:v>147</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H49" s="1">
+        <x:v>119644</x:v>
+      </x:c>
+      <x:c r="I49" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J49" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:10">
+      <x:c r="A50" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B50" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C50" s="1" t="s">
         <x:v>148</x:v>
       </x:c>
-      <x:c r="H49" s="1">
-        <x:v>231242</x:v>
-      </x:c>
-      <x:c r="I49" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J49" s="1" t="s">
+      <x:c r="D50" s="1" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="E50" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F50" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G50" s="1" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="H50" s="1">
+        <x:v>56118</x:v>
+      </x:c>
+      <x:c r="I50" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J50" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:10">
+      <x:c r="A51" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B51" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C51" s="1" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="D51" s="1" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="E51" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F51" s="1" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="G51" s="1" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="H51" s="1">
+        <x:v>275034</x:v>
+      </x:c>
+      <x:c r="I51" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J51" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -476,6 +476,15 @@
   </x:si>
   <x:si>
     <x:t>NY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H4CA27111</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WHITESIDES, GEORGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -546,8 +555,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J51" totalsRowShown="0">
-  <x:autoFilter ref="A1:J51"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J52" totalsRowShown="0">
+  <x:autoFilter ref="A1:J52"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -852,7 +861,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J51"/>
+  <x:dimension ref="A1:J52"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1499,7 +1508,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="H20" s="1">
-        <x:v>54932</x:v>
+        <x:v>366028</x:v>
       </x:c>
       <x:c r="I20" s="1">
         <x:v>2026</x:v>
@@ -1755,7 +1764,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="H28" s="1">
-        <x:v>111440</x:v>
+        <x:v>372060</x:v>
       </x:c>
       <x:c r="I28" s="1">
         <x:v>2026</x:v>
@@ -1851,7 +1860,7 @@
         <x:v>108</x:v>
       </x:c>
       <x:c r="H31" s="1">
-        <x:v>163680</x:v>
+        <x:v>228075</x:v>
       </x:c>
       <x:c r="I31" s="1">
         <x:v>2026</x:v>
@@ -2331,7 +2340,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="H46" s="1">
-        <x:v>54685</x:v>
+        <x:v>367531</x:v>
       </x:c>
       <x:c r="I46" s="1">
         <x:v>2026</x:v>
@@ -2497,6 +2506,38 @@
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J51" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:10">
+      <x:c r="A52" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B52" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C52" s="1" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="D52" s="1" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="E52" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F52" s="1" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="G52" s="1" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="H52" s="1">
+        <x:v>476254</x:v>
+      </x:c>
+      <x:c r="I52" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J52" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -407,6 +407,15 @@
   </x:si>
   <x:si>
     <x:t>NE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>S4SD00049</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROUNDS, MIKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SD</x:t>
   </x:si>
   <x:si>
     <x:t>H2GA13012</x:t>
@@ -555,8 +564,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J52" totalsRowShown="0">
-  <x:autoFilter ref="A1:J52"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J53" totalsRowShown="0">
+  <x:autoFilter ref="A1:J53"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -861,7 +870,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J52"/>
+  <x:dimension ref="A1:J53"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2191,10 +2200,10 @@
     </x:row>
     <x:row r="42" spans="1:10">
       <x:c r="A42" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
         <x:v>131</x:v>
@@ -2203,62 +2212,62 @@
         <x:v>132</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F42" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="H42" s="1">
-        <x:v>56045</x:v>
+        <x:v>411748</x:v>
       </x:c>
       <x:c r="I42" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J42" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:10">
       <x:c r="A43" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F43" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="H43" s="1">
-        <x:v>426280</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="I43" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J43" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:10">
       <x:c r="A44" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
         <x:v>136</x:v>
@@ -2273,10 +2282,10 @@
         <x:v>138</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H44" s="1">
-        <x:v>111598</x:v>
+        <x:v>426280</x:v>
       </x:c>
       <x:c r="I44" s="1">
         <x:v>2026</x:v>
@@ -2287,10 +2296,10 @@
     </x:row>
     <x:row r="45" spans="1:10">
       <x:c r="A45" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
         <x:v>139</x:v>
@@ -2305,10 +2314,10 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H45" s="1">
-        <x:v>282975</x:v>
+        <x:v>111598</x:v>
       </x:c>
       <x:c r="I45" s="1">
         <x:v>2026</x:v>
@@ -2319,10 +2328,10 @@
     </x:row>
     <x:row r="46" spans="1:10">
       <x:c r="A46" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
         <x:v>142</x:v>
@@ -2334,13 +2343,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F46" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="H46" s="1">
-        <x:v>367531</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="I46" s="1">
         <x:v>2026</x:v>
@@ -2351,28 +2360,28 @@
     </x:row>
     <x:row r="47" spans="1:10">
       <x:c r="A47" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>144</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>145</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F47" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H47" s="1">
-        <x:v>771658</x:v>
+        <x:v>367531</x:v>
       </x:c>
       <x:c r="I47" s="1">
         <x:v>2026</x:v>
@@ -2383,48 +2392,48 @@
     </x:row>
     <x:row r="48" spans="1:10">
       <x:c r="A48" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>147</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F48" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H48" s="1">
-        <x:v>4697360</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="I48" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J48" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:10">
       <x:c r="A49" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>147</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
         <x:v>25</x:v>
@@ -2436,7 +2445,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="H49" s="1">
-        <x:v>119644</x:v>
+        <x:v>4697360</x:v>
       </x:c>
       <x:c r="I49" s="1">
         <x:v>2026</x:v>
@@ -2447,60 +2456,60 @@
     </x:row>
     <x:row r="50" spans="1:10">
       <x:c r="A50" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>148</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F50" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H50" s="1">
-        <x:v>56118</x:v>
+        <x:v>119644</x:v>
       </x:c>
       <x:c r="I50" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J50" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:10">
       <x:c r="A51" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>150</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F51" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="H51" s="1">
-        <x:v>275034</x:v>
+        <x:v>56118</x:v>
       </x:c>
       <x:c r="I51" s="1">
         <x:v>2026</x:v>
@@ -2517,27 +2526,59 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="D52" s="1" t="s">
         <x:v>154</x:v>
       </x:c>
-      <x:c r="D52" s="1" t="s">
+      <x:c r="E52" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F52" s="1" t="s">
         <x:v>155</x:v>
       </x:c>
-      <x:c r="E52" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F52" s="1" t="s">
+      <x:c r="G52" s="1" t="s">
         <x:v>156</x:v>
       </x:c>
-      <x:c r="G52" s="1" t="s">
+      <x:c r="H52" s="1">
+        <x:v>275034</x:v>
+      </x:c>
+      <x:c r="I52" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J52" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:10">
+      <x:c r="A53" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B53" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C53" s="1" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="D53" s="1" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="E53" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F53" s="1" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="G53" s="1" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="H52" s="1">
+      <x:c r="H53" s="1">
         <x:v>476254</x:v>
       </x:c>
-      <x:c r="I52" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J52" s="1" t="s">
+      <x:c r="I53" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J53" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -1069,7 +1069,7 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="H6" s="1">
-        <x:v>3114863</x:v>
+        <x:v>3174537</x:v>
       </x:c>
       <x:c r="I6" s="1">
         <x:v>2026</x:v>
@@ -2509,7 +2509,7 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="H51" s="1">
-        <x:v>56118</x:v>
+        <x:v>112236</x:v>
       </x:c>
       <x:c r="I51" s="1">
         <x:v>2026</x:v>
@@ -2541,7 +2541,7 @@
         <x:v>156</x:v>
       </x:c>
       <x:c r="H52" s="1">
-        <x:v>275034</x:v>
+        <x:v>318826</x:v>
       </x:c>
       <x:c r="I52" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -2509,7 +2509,7 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="H51" s="1">
-        <x:v>112236</x:v>
+        <x:v>168354</x:v>
       </x:c>
       <x:c r="I51" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -1069,7 +1069,7 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="H6" s="1">
-        <x:v>3174537</x:v>
+        <x:v>3234211</x:v>
       </x:c>
       <x:c r="I6" s="1">
         <x:v>2026</x:v>
@@ -1997,7 +1997,7 @@
         <x:v>117</x:v>
       </x:c>
       <x:c r="H35" s="1">
-        <x:v>8423195</x:v>
+        <x:v>9673851</x:v>
       </x:c>
       <x:c r="I35" s="1">
         <x:v>2026</x:v>
@@ -2509,7 +2509,7 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="H51" s="1">
-        <x:v>168354</x:v>
+        <x:v>487317</x:v>
       </x:c>
       <x:c r="I51" s="1">
         <x:v>2026</x:v>
@@ -2541,7 +2541,7 @@
         <x:v>156</x:v>
       </x:c>
       <x:c r="H52" s="1">
-        <x:v>318826</x:v>
+        <x:v>362618</x:v>
       </x:c>
       <x:c r="I52" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -2541,7 +2541,7 @@
         <x:v>156</x:v>
       </x:c>
       <x:c r="H52" s="1">
-        <x:v>362618</x:v>
+        <x:v>384929</x:v>
       </x:c>
       <x:c r="I52" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -1069,7 +1069,7 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="H6" s="1">
-        <x:v>3234211</x:v>
+        <x:v>3293885</x:v>
       </x:c>
       <x:c r="I6" s="1">
         <x:v>2026</x:v>
@@ -1997,7 +1997,7 @@
         <x:v>117</x:v>
       </x:c>
       <x:c r="H35" s="1">
-        <x:v>9673851</x:v>
+        <x:v>9917138</x:v>
       </x:c>
       <x:c r="I35" s="1">
         <x:v>2026</x:v>
@@ -2541,7 +2541,7 @@
         <x:v>156</x:v>
       </x:c>
       <x:c r="H52" s="1">
-        <x:v>384929</x:v>
+        <x:v>428721</x:v>
       </x:c>
       <x:c r="I52" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -103,243 +103,204 @@
     <x:t>PROTECT PROGRESS</x:t>
   </x:si>
   <x:si>
-    <x:t>H6IL08329</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BEAN, MELISSA LUBURICH</x:t>
+    <x:t>H6MD05321</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOAFO, ADRIAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H6TX02244</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BONCK, JON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>38</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TX</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H6GA13070</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CLARK, JASMINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>S6GA00390</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COLLINS, MICHAEL A JR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H6CA46116</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CORREA, LOU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>46</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H6TX35087</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DE LA CRUZ, CARLOS JR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H0GA14030</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FULLER, CLAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H6GA10175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GAINES, HOUSTON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H6TX10221</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOBER, CHRIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>S0SC00149</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRAHAM, LINDSEY O.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H4TX09095</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GREEN, ALEXANDER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OPPOSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H4AR02141</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HILL, JAMES FRENCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H6CA26266</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IRWIN, JACQUI V</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H2GA01157</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KINGSTON, JACK REP.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H6GA01109</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KINGSTON, JAMES MORRIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>S6LA00664</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LETLOW, JULIA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H4CA33119</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LIEU, TED</x:t>
+  </x:si>
+  <x:si>
+    <x:t>36</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H4CA16049</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LOFGREN, ZOE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H6CA01269</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCGUIRE, MIKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H6TX09140</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEALER, ALEXANDRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H6TX18232</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MENEFEE, CHRISTIAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H2NJ08232</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MENENDEZ, ROBERT</x:t>
   </x:si>
   <x:si>
     <x:t>08</x:t>
   </x:si>
   <x:si>
-    <x:t>IL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6MD05321</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOAFO, ADRIAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6TX02244</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BONCK, JON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>38</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TX</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6GA13070</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CLARK, JASMINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>S6GA00390</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COLLINS, MICHAEL A JR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6CA46116</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CORREA, LOU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>46</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6TX35087</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DE LA CRUZ, CARLOS JR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>35</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00835959</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FAIRSHAKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6IL07354</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FORD, LA SHAWN K</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OPPOSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H0GA14030</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FULLER, CLAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6GA10175</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GAINES, HOUSTON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6TX10221</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOBER, CHRIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>S0SC00149</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRAHAM, LINDSEY O.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H4TX09095</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GREEN, ALEXANDER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H4AR02141</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HILL, JAMES FRENCH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6CA26266</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IRWIN, JACQUI V</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>S6IL00474</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KELLY, ROBIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t/>
-  </x:si>
-  <x:si>
-    <x:t>H2GA01157</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KINGSTON, JACK REP.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6GA01109</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KINGSTON, JAMES MORRIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>S6IL00482</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRISHNAMOORTHI, S</x:t>
-  </x:si>
-  <x:si>
-    <x:t>S6LA00664</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LETLOW, JULIA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H4CA33119</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LIEU, TED</x:t>
-  </x:si>
-  <x:si>
-    <x:t>36</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H4CA16049</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LOFGREN, ZOE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6CA01269</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MCGUIRE, MIKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6TX09140</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEALER, ALEXANDRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6TX18232</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MENEFEE, CHRISTIAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H2NJ08232</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MENENDEZ, ROBERT</x:t>
-  </x:si>
-  <x:si>
     <x:t>NJ</x:t>
   </x:si>
   <x:si>
@@ -461,12 +422,6 @@
   </x:si>
   <x:si>
     <x:t>STEINMANN, JESSICA HART</x:t>
-  </x:si>
-  <x:si>
-    <x:t>S6IL00458</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STRATTON, JULIANA</x:t>
   </x:si>
   <x:si>
     <x:t>H8SC04250</x:t>
@@ -564,8 +519,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J53" totalsRowShown="0">
-  <x:autoFilter ref="A1:J53"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J47" totalsRowShown="0">
+  <x:autoFilter ref="A1:J47"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -870,7 +825,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J53"/>
+  <x:dimension ref="A1:J47"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1037,7 +992,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="H5" s="1">
-        <x:v>41493</x:v>
+        <x:v>3293885</x:v>
       </x:c>
       <x:c r="I5" s="1">
         <x:v>2026</x:v>
@@ -1048,10 +1003,10 @@
     </x:row>
     <x:row r="6" spans="1:10">
       <x:c r="A6" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
         <x:v>33</x:v>
@@ -1069,7 +1024,7 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="H6" s="1">
-        <x:v>3293885</x:v>
+        <x:v>348433</x:v>
       </x:c>
       <x:c r="I6" s="1">
         <x:v>2026</x:v>
@@ -1080,10 +1035,10 @@
     </x:row>
     <x:row r="7" spans="1:10">
       <x:c r="A7" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
         <x:v>37</x:v>
@@ -1101,7 +1056,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="H7" s="1">
-        <x:v>348433</x:v>
+        <x:v>4210393</x:v>
       </x:c>
       <x:c r="I7" s="1">
         <x:v>2026</x:v>
@@ -1112,10 +1067,10 @@
     </x:row>
     <x:row r="8" spans="1:10">
       <x:c r="A8" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
         <x:v>41</x:v>
@@ -1124,16 +1079,16 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F8" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H8" s="1">
-        <x:v>4210393</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I8" s="1">
         <x:v>2026</x:v>
@@ -1144,28 +1099,28 @@
     </x:row>
     <x:row r="9" spans="1:10">
       <x:c r="A9" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="D9" s="1" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="E9" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F9" s="1" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="D9" s="1" t="s">
+      <x:c r="G9" s="1" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="E9" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F9" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="G9" s="1" t="s">
-        <x:v>44</x:v>
-      </x:c>
       <x:c r="H9" s="1">
-        <x:v>350000</x:v>
+        <x:v>107388</x:v>
       </x:c>
       <x:c r="I9" s="1">
         <x:v>2026</x:v>
@@ -1176,10 +1131,10 @@
     </x:row>
     <x:row r="10" spans="1:10">
       <x:c r="A10" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
         <x:v>47</x:v>
@@ -1194,10 +1149,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="H10" s="1">
-        <x:v>107388</x:v>
+        <x:v>616386</x:v>
       </x:c>
       <x:c r="I10" s="1">
         <x:v>2026</x:v>
@@ -1214,22 +1169,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D11" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="D11" s="1" t="s">
+      <x:c r="E11" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F11" s="1" t="s">
         <x:v>52</x:v>
-      </x:c>
-      <x:c r="E11" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F11" s="1" t="s">
-        <x:v>53</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
         <x:v>40</x:v>
       </x:c>
       <x:c r="H11" s="1">
-        <x:v>616386</x:v>
+        <x:v>455146</x:v>
       </x:c>
       <x:c r="I11" s="1">
         <x:v>2026</x:v>
@@ -1240,34 +1195,34 @@
     </x:row>
     <x:row r="12" spans="1:10">
       <x:c r="A12" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F12" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H12" s="1">
-        <x:v>672092</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="I12" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J12" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:10">
@@ -1278,22 +1233,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H13" s="1">
-        <x:v>455146</x:v>
+        <x:v>708827</x:v>
       </x:c>
       <x:c r="I13" s="1">
         <x:v>2026</x:v>
@@ -1304,28 +1259,28 @@
     </x:row>
     <x:row r="14" spans="1:10">
       <x:c r="A14" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F14" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="H14" s="1">
-        <x:v>300000</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="I14" s="1">
         <x:v>2026</x:v>
@@ -1336,28 +1291,28 @@
     </x:row>
     <x:row r="15" spans="1:10">
       <x:c r="A15" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F15" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H15" s="1">
-        <x:v>708827</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="I15" s="1">
         <x:v>2026</x:v>
@@ -1368,60 +1323,60 @@
     </x:row>
     <x:row r="16" spans="1:10">
       <x:c r="A16" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F16" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="H16" s="1">
-        <x:v>91656</x:v>
+        <x:v>47162</x:v>
       </x:c>
       <x:c r="I16" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J16" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:10">
       <x:c r="A17" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="D17" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E17" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F17" s="1" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="G17" s="1" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="D17" s="1" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="E17" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F17" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="G17" s="1" t="s">
-        <x:v>70</x:v>
-      </x:c>
       <x:c r="H17" s="1">
-        <x:v>550000</x:v>
+        <x:v>418060</x:v>
       </x:c>
       <x:c r="I17" s="1">
         <x:v>2026</x:v>
@@ -1438,28 +1393,28 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="D18" s="1" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="E18" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F18" s="1" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="D18" s="1" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="E18" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F18" s="1" t="s">
-        <x:v>73</x:v>
-      </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H18" s="1">
-        <x:v>47162</x:v>
+        <x:v>366028</x:v>
       </x:c>
       <x:c r="I18" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J18" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:10">
@@ -1470,22 +1425,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="D19" s="1" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="E19" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F19" s="1" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="D19" s="1" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="E19" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F19" s="1" t="s">
-        <x:v>76</x:v>
-      </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H19" s="1">
-        <x:v>418060</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="I19" s="1">
         <x:v>2026</x:v>
@@ -1496,28 +1451,28 @@
     </x:row>
     <x:row r="20" spans="1:10">
       <x:c r="A20" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F20" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H20" s="1">
-        <x:v>366028</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="I20" s="1">
         <x:v>2026</x:v>
@@ -1528,28 +1483,28 @@
     </x:row>
     <x:row r="21" spans="1:10">
       <x:c r="A21" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="F21" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="H21" s="1">
-        <x:v>285008</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I21" s="1">
         <x:v>2026</x:v>
@@ -1560,28 +1515,28 @@
     </x:row>
     <x:row r="22" spans="1:10">
       <x:c r="A22" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F22" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H22" s="1">
-        <x:v>430866</x:v>
+        <x:v>106348</x:v>
       </x:c>
       <x:c r="I22" s="1">
         <x:v>2026</x:v>
@@ -1592,28 +1547,28 @@
     </x:row>
     <x:row r="23" spans="1:10">
       <x:c r="A23" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F23" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H23" s="1">
-        <x:v>430866</x:v>
+        <x:v>109274</x:v>
       </x:c>
       <x:c r="I23" s="1">
         <x:v>2026</x:v>
@@ -1630,22 +1585,22 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F24" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H24" s="1">
-        <x:v>30183</x:v>
+        <x:v>372060</x:v>
       </x:c>
       <x:c r="I24" s="1">
         <x:v>2026</x:v>
@@ -1656,28 +1611,28 @@
     </x:row>
     <x:row r="25" spans="1:10">
       <x:c r="A25" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F25" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="H25" s="1">
-        <x:v>350000</x:v>
+        <x:v>461943</x:v>
       </x:c>
       <x:c r="I25" s="1">
         <x:v>2026</x:v>
@@ -1694,22 +1649,22 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F26" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="H26" s="1">
-        <x:v>106348</x:v>
+        <x:v>4903859</x:v>
       </x:c>
       <x:c r="I26" s="1">
         <x:v>2026</x:v>
@@ -1726,22 +1681,22 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F27" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="H27" s="1">
-        <x:v>109274</x:v>
+        <x:v>228075</x:v>
       </x:c>
       <x:c r="I27" s="1">
         <x:v>2026</x:v>
@@ -1758,22 +1713,22 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F28" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="H28" s="1">
-        <x:v>372060</x:v>
+        <x:v>34890</x:v>
       </x:c>
       <x:c r="I28" s="1">
         <x:v>2026</x:v>
@@ -1784,28 +1739,28 @@
     </x:row>
     <x:row r="29" spans="1:10">
       <x:c r="A29" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F29" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="H29" s="1">
-        <x:v>461943</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="I29" s="1">
         <x:v>2026</x:v>
@@ -1822,22 +1777,22 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F30" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H30" s="1">
-        <x:v>4903859</x:v>
+        <x:v>107940</x:v>
       </x:c>
       <x:c r="I30" s="1">
         <x:v>2026</x:v>
@@ -1848,28 +1803,28 @@
     </x:row>
     <x:row r="31" spans="1:10">
       <x:c r="A31" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F31" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="H31" s="1">
-        <x:v>228075</x:v>
+        <x:v>9917138</x:v>
       </x:c>
       <x:c r="I31" s="1">
         <x:v>2026</x:v>
@@ -1880,28 +1835,28 @@
     </x:row>
     <x:row r="32" spans="1:10">
       <x:c r="A32" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F32" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="H32" s="1">
-        <x:v>34890</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I32" s="1">
         <x:v>2026</x:v>
@@ -1912,28 +1867,28 @@
     </x:row>
     <x:row r="33" spans="1:10">
       <x:c r="A33" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F33" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="H33" s="1">
-        <x:v>250000</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="I33" s="1">
         <x:v>2026</x:v>
@@ -1944,28 +1899,28 @@
     </x:row>
     <x:row r="34" spans="1:10">
       <x:c r="A34" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F34" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="H34" s="1">
-        <x:v>107940</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="I34" s="1">
         <x:v>2026</x:v>
@@ -1982,22 +1937,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F35" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="H35" s="1">
-        <x:v>9917138</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="I35" s="1">
         <x:v>2026</x:v>
@@ -2014,10 +1969,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
         <x:v>25</x:v>
@@ -2026,10 +1981,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="H36" s="1">
-        <x:v>350000</x:v>
+        <x:v>2250000</x:v>
       </x:c>
       <x:c r="I36" s="1">
         <x:v>2026</x:v>
@@ -2040,28 +1995,28 @@
     </x:row>
     <x:row r="37" spans="1:10">
       <x:c r="A37" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F37" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="H37" s="1">
-        <x:v>80948</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I37" s="1">
         <x:v>2026</x:v>
@@ -2072,16 +2027,16 @@
     </x:row>
     <x:row r="38" spans="1:10">
       <x:c r="A38" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
         <x:v>25</x:v>
@@ -2090,10 +2045,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="H38" s="1">
-        <x:v>221403</x:v>
+        <x:v>411748</x:v>
       </x:c>
       <x:c r="I38" s="1">
         <x:v>2026</x:v>
@@ -2104,60 +2059,60 @@
     </x:row>
     <x:row r="39" spans="1:10">
       <x:c r="A39" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F39" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
         <x:v>40</x:v>
       </x:c>
       <x:c r="H39" s="1">
-        <x:v>141263</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="I39" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J39" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:10">
       <x:c r="A40" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F40" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="H40" s="1">
-        <x:v>2250000</x:v>
+        <x:v>426280</x:v>
       </x:c>
       <x:c r="I40" s="1">
         <x:v>2026</x:v>
@@ -2168,28 +2123,28 @@
     </x:row>
     <x:row r="41" spans="1:10">
       <x:c r="A41" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="D41" s="1" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E41" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F41" s="1" t="s">
         <x:v>128</x:v>
       </x:c>
-      <x:c r="D41" s="1" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="E41" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F41" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
       <x:c r="G41" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H41" s="1">
-        <x:v>350000</x:v>
+        <x:v>111598</x:v>
       </x:c>
       <x:c r="I41" s="1">
         <x:v>2026</x:v>
@@ -2206,22 +2161,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="D42" s="1" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="E42" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F42" s="1" t="s">
         <x:v>131</x:v>
       </x:c>
-      <x:c r="D42" s="1" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="E42" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F42" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
       <x:c r="G42" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="H42" s="1">
-        <x:v>411748</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="I42" s="1">
         <x:v>2026</x:v>
@@ -2238,28 +2193,28 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F43" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H43" s="1">
-        <x:v>56045</x:v>
+        <x:v>367531</x:v>
       </x:c>
       <x:c r="I43" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J43" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:10">
@@ -2270,22 +2225,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F44" s="1" t="s">
-        <x:v>138</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="H44" s="1">
-        <x:v>426280</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="I44" s="1">
         <x:v>2026</x:v>
@@ -2296,28 +2251,28 @@
     </x:row>
     <x:row r="45" spans="1:10">
       <x:c r="A45" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>139</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>140</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F45" s="1" t="s">
-        <x:v>141</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H45" s="1">
-        <x:v>111598</x:v>
+        <x:v>487317</x:v>
       </x:c>
       <x:c r="I45" s="1">
         <x:v>2026</x:v>
@@ -2328,28 +2283,28 @@
     </x:row>
     <x:row r="46" spans="1:10">
       <x:c r="A46" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>143</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F46" s="1" t="s">
-        <x:v>144</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="H46" s="1">
-        <x:v>282975</x:v>
+        <x:v>428721</x:v>
       </x:c>
       <x:c r="I46" s="1">
         <x:v>2026</x:v>
@@ -2366,219 +2321,27 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>145</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F47" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H47" s="1">
-        <x:v>367531</x:v>
+        <x:v>476254</x:v>
       </x:c>
       <x:c r="I47" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J47" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48" spans="1:10">
-      <x:c r="A48" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B48" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C48" s="1" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="D48" s="1" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="E48" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F48" s="1" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="G48" s="1" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="H48" s="1">
-        <x:v>771658</x:v>
-      </x:c>
-      <x:c r="I48" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J48" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" spans="1:10">
-      <x:c r="A49" s="1" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="B49" s="1" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="C49" s="1" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="D49" s="1" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="E49" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F49" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="G49" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="H49" s="1">
-        <x:v>4697360</x:v>
-      </x:c>
-      <x:c r="I49" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J49" s="1" t="s">
-        <x:v>59</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50" spans="1:10">
-      <x:c r="A50" s="1" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="B50" s="1" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C50" s="1" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="D50" s="1" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="E50" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F50" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="G50" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="H50" s="1">
-        <x:v>119644</x:v>
-      </x:c>
-      <x:c r="I50" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J50" s="1" t="s">
-        <x:v>59</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51" spans="1:10">
-      <x:c r="A51" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B51" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C51" s="1" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="D51" s="1" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="E51" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F51" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G51" s="1" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="H51" s="1">
-        <x:v>487317</x:v>
-      </x:c>
-      <x:c r="I51" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J51" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="52" spans="1:10">
-      <x:c r="A52" s="1" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="B52" s="1" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C52" s="1" t="s">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c r="D52" s="1" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="E52" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F52" s="1" t="s">
-        <x:v>155</x:v>
-      </x:c>
-      <x:c r="G52" s="1" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="H52" s="1">
-        <x:v>428721</x:v>
-      </x:c>
-      <x:c r="I52" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J52" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="53" spans="1:10">
-      <x:c r="A53" s="1" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="B53" s="1" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C53" s="1" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="D53" s="1" t="s">
-        <x:v>158</x:v>
-      </x:c>
-      <x:c r="E53" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F53" s="1" t="s">
-        <x:v>159</x:v>
-      </x:c>
-      <x:c r="G53" s="1" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="H53" s="1">
-        <x:v>476254</x:v>
-      </x:c>
-      <x:c r="I53" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J53" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -1824,7 +1824,7 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="H31" s="1">
-        <x:v>9917138</x:v>
+        <x:v>10918495</x:v>
       </x:c>
       <x:c r="I31" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -209,6 +209,15 @@
   </x:si>
   <x:si>
     <x:t>OPPOSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>S6OK04247</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HERN, KEVIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OK</x:t>
   </x:si>
   <x:si>
     <x:t>H4AR02141</x:t>
@@ -519,8 +528,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J47" totalsRowShown="0">
-  <x:autoFilter ref="A1:J47"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J48" totalsRowShown="0">
+  <x:autoFilter ref="A1:J48"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -825,7 +834,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J47"/>
+  <x:dimension ref="A1:J48"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -992,7 +1001,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="H5" s="1">
-        <x:v>3293885</x:v>
+        <x:v>3353559</x:v>
       </x:c>
       <x:c r="I5" s="1">
         <x:v>2026</x:v>
@@ -1355,10 +1364,10 @@
     </x:row>
     <x:row r="17" spans="1:10">
       <x:c r="A17" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
         <x:v>65</x:v>
@@ -1367,16 +1376,16 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F17" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G17" s="1" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="G17" s="1" t="s">
-        <x:v>68</x:v>
-      </x:c>
       <x:c r="H17" s="1">
-        <x:v>418060</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="I17" s="1">
         <x:v>2026</x:v>
@@ -1387,28 +1396,28 @@
     </x:row>
     <x:row r="18" spans="1:10">
       <x:c r="A18" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="D18" s="1" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="D18" s="1" t="s">
+      <x:c r="E18" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F18" s="1" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="E18" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F18" s="1" t="s">
+      <x:c r="G18" s="1" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="G18" s="1" t="s">
-        <x:v>46</x:v>
-      </x:c>
       <x:c r="H18" s="1">
-        <x:v>366028</x:v>
+        <x:v>418060</x:v>
       </x:c>
       <x:c r="I18" s="1">
         <x:v>2026</x:v>
@@ -1419,10 +1428,10 @@
     </x:row>
     <x:row r="19" spans="1:10">
       <x:c r="A19" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
         <x:v>72</x:v>
@@ -1437,10 +1446,10 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H19" s="1">
-        <x:v>430866</x:v>
+        <x:v>366028</x:v>
       </x:c>
       <x:c r="I19" s="1">
         <x:v>2026</x:v>
@@ -1466,7 +1475,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F20" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
         <x:v>40</x:v>
@@ -1483,28 +1492,28 @@
     </x:row>
     <x:row r="21" spans="1:10">
       <x:c r="A21" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="D21" s="1" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="E21" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F21" s="1" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="D21" s="1" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="E21" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F21" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H21" s="1">
-        <x:v>350000</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="I21" s="1">
         <x:v>2026</x:v>
@@ -1515,10 +1524,10 @@
     </x:row>
     <x:row r="22" spans="1:10">
       <x:c r="A22" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
         <x:v>80</x:v>
@@ -1527,16 +1536,16 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F22" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G22" s="1" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="G22" s="1" t="s">
-        <x:v>46</x:v>
-      </x:c>
       <x:c r="H22" s="1">
-        <x:v>106348</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I22" s="1">
         <x:v>2026</x:v>
@@ -1562,13 +1571,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F23" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
         <x:v>46</x:v>
       </x:c>
       <x:c r="H23" s="1">
-        <x:v>109274</x:v>
+        <x:v>106348</x:v>
       </x:c>
       <x:c r="I23" s="1">
         <x:v>2026</x:v>
@@ -1585,22 +1594,22 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F24" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
         <x:v>46</x:v>
       </x:c>
       <x:c r="H24" s="1">
-        <x:v>372060</x:v>
+        <x:v>109274</x:v>
       </x:c>
       <x:c r="I24" s="1">
         <x:v>2026</x:v>
@@ -1611,28 +1620,28 @@
     </x:row>
     <x:row r="25" spans="1:10">
       <x:c r="A25" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F25" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H25" s="1">
-        <x:v>461943</x:v>
+        <x:v>372060</x:v>
       </x:c>
       <x:c r="I25" s="1">
         <x:v>2026</x:v>
@@ -1643,10 +1652,10 @@
     </x:row>
     <x:row r="26" spans="1:10">
       <x:c r="A26" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
         <x:v>90</x:v>
@@ -1658,13 +1667,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F26" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
         <x:v>36</x:v>
       </x:c>
       <x:c r="H26" s="1">
-        <x:v>4903859</x:v>
+        <x:v>461943</x:v>
       </x:c>
       <x:c r="I26" s="1">
         <x:v>2026</x:v>
@@ -1681,22 +1690,22 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F27" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="H27" s="1">
-        <x:v>228075</x:v>
+        <x:v>4903859</x:v>
       </x:c>
       <x:c r="I27" s="1">
         <x:v>2026</x:v>
@@ -1713,22 +1722,22 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="D28" s="1" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="D28" s="1" t="s">
-        <x:v>93</x:v>
-      </x:c>
       <x:c r="E28" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F28" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="H28" s="1">
-        <x:v>34890</x:v>
+        <x:v>228075</x:v>
       </x:c>
       <x:c r="I28" s="1">
         <x:v>2026</x:v>
@@ -1739,28 +1748,28 @@
     </x:row>
     <x:row r="29" spans="1:10">
       <x:c r="A29" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D29" s="1" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="E29" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F29" s="1" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="D29" s="1" t="s">
+      <x:c r="G29" s="1" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="E29" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F29" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="G29" s="1" t="s">
-        <x:v>79</x:v>
-      </x:c>
       <x:c r="H29" s="1">
-        <x:v>250000</x:v>
+        <x:v>34890</x:v>
       </x:c>
       <x:c r="I29" s="1">
         <x:v>2026</x:v>
@@ -1771,28 +1780,28 @@
     </x:row>
     <x:row r="30" spans="1:10">
       <x:c r="A30" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F30" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="H30" s="1">
-        <x:v>107940</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="I30" s="1">
         <x:v>2026</x:v>
@@ -1803,10 +1812,10 @@
     </x:row>
     <x:row r="31" spans="1:10">
       <x:c r="A31" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
         <x:v>102</x:v>
@@ -1815,16 +1824,16 @@
         <x:v>103</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F31" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H31" s="1">
-        <x:v>10918495</x:v>
+        <x:v>107940</x:v>
       </x:c>
       <x:c r="I31" s="1">
         <x:v>2026</x:v>
@@ -1835,16 +1844,16 @@
     </x:row>
     <x:row r="32" spans="1:10">
       <x:c r="A32" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
         <x:v>25</x:v>
@@ -1853,10 +1862,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="H32" s="1">
-        <x:v>350000</x:v>
+        <x:v>10918495</x:v>
       </x:c>
       <x:c r="I32" s="1">
         <x:v>2026</x:v>
@@ -1867,10 +1876,10 @@
     </x:row>
     <x:row r="33" spans="1:10">
       <x:c r="A33" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
         <x:v>105</x:v>
@@ -1879,16 +1888,16 @@
         <x:v>106</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F33" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
         <x:v>107</x:v>
       </x:c>
       <x:c r="H33" s="1">
-        <x:v>80948</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I33" s="1">
         <x:v>2026</x:v>
@@ -1899,10 +1908,10 @@
     </x:row>
     <x:row r="34" spans="1:10">
       <x:c r="A34" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
         <x:v>108</x:v>
@@ -1911,16 +1920,16 @@
         <x:v>109</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F34" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="H34" s="1">
-        <x:v>221403</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="I34" s="1">
         <x:v>2026</x:v>
@@ -1931,28 +1940,28 @@
     </x:row>
     <x:row r="35" spans="1:10">
       <x:c r="A35" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F35" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="H35" s="1">
-        <x:v>141263</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="I35" s="1">
         <x:v>2026</x:v>
@@ -1963,10 +1972,10 @@
     </x:row>
     <x:row r="36" spans="1:10">
       <x:c r="A36" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
         <x:v>113</x:v>
@@ -1975,16 +1984,16 @@
         <x:v>114</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F36" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
         <x:v>36</x:v>
       </x:c>
       <x:c r="H36" s="1">
-        <x:v>2250000</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="I36" s="1">
         <x:v>2026</x:v>
@@ -2001,10 +2010,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
         <x:v>25</x:v>
@@ -2013,10 +2022,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="H37" s="1">
-        <x:v>350000</x:v>
+        <x:v>2250000</x:v>
       </x:c>
       <x:c r="I37" s="1">
         <x:v>2026</x:v>
@@ -2027,10 +2036,10 @@
     </x:row>
     <x:row r="38" spans="1:10">
       <x:c r="A38" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
         <x:v>118</x:v>
@@ -2048,7 +2057,7 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="H38" s="1">
-        <x:v>411748</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I38" s="1">
         <x:v>2026</x:v>
@@ -2059,10 +2068,10 @@
     </x:row>
     <x:row r="39" spans="1:10">
       <x:c r="A39" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
         <x:v>121</x:v>
@@ -2071,62 +2080,62 @@
         <x:v>122</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F39" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H39" s="1">
-        <x:v>56045</x:v>
+        <x:v>411748</x:v>
       </x:c>
       <x:c r="I39" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J39" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:10">
       <x:c r="A40" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F40" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H40" s="1">
-        <x:v>426280</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="I40" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J40" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:10">
       <x:c r="A41" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
         <x:v>126</x:v>
@@ -2141,10 +2150,10 @@
         <x:v>128</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="H41" s="1">
-        <x:v>111598</x:v>
+        <x:v>426280</x:v>
       </x:c>
       <x:c r="I41" s="1">
         <x:v>2026</x:v>
@@ -2155,10 +2164,10 @@
     </x:row>
     <x:row r="42" spans="1:10">
       <x:c r="A42" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
         <x:v>129</x:v>
@@ -2173,10 +2182,10 @@
         <x:v>131</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H42" s="1">
-        <x:v>282975</x:v>
+        <x:v>111598</x:v>
       </x:c>
       <x:c r="I42" s="1">
         <x:v>2026</x:v>
@@ -2187,10 +2196,10 @@
     </x:row>
     <x:row r="43" spans="1:10">
       <x:c r="A43" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
         <x:v>132</x:v>
@@ -2202,13 +2211,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F43" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="H43" s="1">
-        <x:v>367531</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="I43" s="1">
         <x:v>2026</x:v>
@@ -2219,28 +2228,28 @@
     </x:row>
     <x:row r="44" spans="1:10">
       <x:c r="A44" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F44" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H44" s="1">
-        <x:v>771658</x:v>
+        <x:v>367531</x:v>
       </x:c>
       <x:c r="I44" s="1">
         <x:v>2026</x:v>
@@ -2257,22 +2266,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F45" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="H45" s="1">
-        <x:v>487317</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="I45" s="1">
         <x:v>2026</x:v>
@@ -2283,28 +2292,28 @@
     </x:row>
     <x:row r="46" spans="1:10">
       <x:c r="A46" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>138</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F46" s="1" t="s">
-        <x:v>140</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
-        <x:v>141</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H46" s="1">
-        <x:v>428721</x:v>
+        <x:v>487317</x:v>
       </x:c>
       <x:c r="I46" s="1">
         <x:v>2026</x:v>
@@ -2321,27 +2330,59 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="D47" s="1" t="s">
         <x:v>142</x:v>
       </x:c>
-      <x:c r="D47" s="1" t="s">
+      <x:c r="E47" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F47" s="1" t="s">
         <x:v>143</x:v>
       </x:c>
-      <x:c r="E47" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F47" s="1" t="s">
+      <x:c r="G47" s="1" t="s">
         <x:v>144</x:v>
       </x:c>
-      <x:c r="G47" s="1" t="s">
+      <x:c r="H47" s="1">
+        <x:v>485970</x:v>
+      </x:c>
+      <x:c r="I47" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J47" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:10">
+      <x:c r="A48" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B48" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C48" s="1" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="D48" s="1" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="E48" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F48" s="1" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="G48" s="1" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="H47" s="1">
+      <x:c r="H48" s="1">
         <x:v>476254</x:v>
       </x:c>
-      <x:c r="I47" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J47" s="1" t="s">
+      <x:c r="I48" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J48" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -528,8 +528,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J48" totalsRowShown="0">
-  <x:autoFilter ref="A1:J48"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J49" totalsRowShown="0">
+  <x:autoFilter ref="A1:J49"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -834,7 +834,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J48"/>
+  <x:dimension ref="A1:J49"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1364,10 +1364,10 @@
     </x:row>
     <x:row r="17" spans="1:10">
       <x:c r="A17" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
         <x:v>65</x:v>
@@ -1385,7 +1385,7 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="H17" s="1">
-        <x:v>300000</x:v>
+        <x:v>735613</x:v>
       </x:c>
       <x:c r="I17" s="1">
         <x:v>2026</x:v>
@@ -1396,28 +1396,28 @@
     </x:row>
     <x:row r="18" spans="1:10">
       <x:c r="A18" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F18" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H18" s="1">
-        <x:v>418060</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="I18" s="1">
         <x:v>2026</x:v>
@@ -1428,28 +1428,28 @@
     </x:row>
     <x:row r="19" spans="1:10">
       <x:c r="A19" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F19" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="H19" s="1">
-        <x:v>366028</x:v>
+        <x:v>418060</x:v>
       </x:c>
       <x:c r="I19" s="1">
         <x:v>2026</x:v>
@@ -1460,28 +1460,28 @@
     </x:row>
     <x:row r="20" spans="1:10">
       <x:c r="A20" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F20" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H20" s="1">
-        <x:v>430866</x:v>
+        <x:v>366028</x:v>
       </x:c>
       <x:c r="I20" s="1">
         <x:v>2026</x:v>
@@ -1498,10 +1498,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
         <x:v>14</x:v>
@@ -1524,28 +1524,28 @@
     </x:row>
     <x:row r="22" spans="1:10">
       <x:c r="A22" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F22" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H22" s="1">
-        <x:v>350000</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="I22" s="1">
         <x:v>2026</x:v>
@@ -1556,28 +1556,28 @@
     </x:row>
     <x:row r="23" spans="1:10">
       <x:c r="A23" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F23" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="H23" s="1">
-        <x:v>106348</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I23" s="1">
         <x:v>2026</x:v>
@@ -1594,22 +1594,22 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F24" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
         <x:v>46</x:v>
       </x:c>
       <x:c r="H24" s="1">
-        <x:v>109274</x:v>
+        <x:v>106348</x:v>
       </x:c>
       <x:c r="I24" s="1">
         <x:v>2026</x:v>
@@ -1626,22 +1626,22 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F25" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
         <x:v>46</x:v>
       </x:c>
       <x:c r="H25" s="1">
-        <x:v>372060</x:v>
+        <x:v>109274</x:v>
       </x:c>
       <x:c r="I25" s="1">
         <x:v>2026</x:v>
@@ -1652,28 +1652,28 @@
     </x:row>
     <x:row r="26" spans="1:10">
       <x:c r="A26" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F26" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H26" s="1">
-        <x:v>461943</x:v>
+        <x:v>372060</x:v>
       </x:c>
       <x:c r="I26" s="1">
         <x:v>2026</x:v>
@@ -1684,28 +1684,28 @@
     </x:row>
     <x:row r="27" spans="1:10">
       <x:c r="A27" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F27" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
         <x:v>36</x:v>
       </x:c>
       <x:c r="H27" s="1">
-        <x:v>4903859</x:v>
+        <x:v>461943</x:v>
       </x:c>
       <x:c r="I27" s="1">
         <x:v>2026</x:v>
@@ -1722,22 +1722,22 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F28" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="H28" s="1">
-        <x:v>228075</x:v>
+        <x:v>4903859</x:v>
       </x:c>
       <x:c r="I28" s="1">
         <x:v>2026</x:v>
@@ -1754,7 +1754,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
         <x:v>96</x:v>
@@ -1769,7 +1769,7 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="H29" s="1">
-        <x:v>34890</x:v>
+        <x:v>228075</x:v>
       </x:c>
       <x:c r="I29" s="1">
         <x:v>2026</x:v>
@@ -1780,28 +1780,28 @@
     </x:row>
     <x:row r="30" spans="1:10">
       <x:c r="A30" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F30" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="H30" s="1">
-        <x:v>250000</x:v>
+        <x:v>34890</x:v>
       </x:c>
       <x:c r="I30" s="1">
         <x:v>2026</x:v>
@@ -1812,28 +1812,28 @@
     </x:row>
     <x:row r="31" spans="1:10">
       <x:c r="A31" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F31" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="H31" s="1">
-        <x:v>107940</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="I31" s="1">
         <x:v>2026</x:v>
@@ -1844,28 +1844,28 @@
     </x:row>
     <x:row r="32" spans="1:10">
       <x:c r="A32" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F32" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H32" s="1">
-        <x:v>10918495</x:v>
+        <x:v>107940</x:v>
       </x:c>
       <x:c r="I32" s="1">
         <x:v>2026</x:v>
@@ -1876,10 +1876,10 @@
     </x:row>
     <x:row r="33" spans="1:10">
       <x:c r="A33" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
         <x:v>105</x:v>
@@ -1897,7 +1897,7 @@
         <x:v>107</x:v>
       </x:c>
       <x:c r="H33" s="1">
-        <x:v>350000</x:v>
+        <x:v>12183751</x:v>
       </x:c>
       <x:c r="I33" s="1">
         <x:v>2026</x:v>
@@ -1908,28 +1908,28 @@
     </x:row>
     <x:row r="34" spans="1:10">
       <x:c r="A34" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F34" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="H34" s="1">
-        <x:v>80948</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I34" s="1">
         <x:v>2026</x:v>
@@ -1940,28 +1940,28 @@
     </x:row>
     <x:row r="35" spans="1:10">
       <x:c r="A35" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F35" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="H35" s="1">
-        <x:v>221403</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="I35" s="1">
         <x:v>2026</x:v>
@@ -1972,28 +1972,28 @@
     </x:row>
     <x:row r="36" spans="1:10">
       <x:c r="A36" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F36" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="H36" s="1">
-        <x:v>141263</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="I36" s="1">
         <x:v>2026</x:v>
@@ -2004,28 +2004,28 @@
     </x:row>
     <x:row r="37" spans="1:10">
       <x:c r="A37" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F37" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
         <x:v>36</x:v>
       </x:c>
       <x:c r="H37" s="1">
-        <x:v>2250000</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="I37" s="1">
         <x:v>2026</x:v>
@@ -2042,10 +2042,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
         <x:v>25</x:v>
@@ -2054,10 +2054,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="H38" s="1">
-        <x:v>350000</x:v>
+        <x:v>2250000</x:v>
       </x:c>
       <x:c r="I38" s="1">
         <x:v>2026</x:v>
@@ -2068,16 +2068,16 @@
     </x:row>
     <x:row r="39" spans="1:10">
       <x:c r="A39" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
         <x:v>25</x:v>
@@ -2086,10 +2086,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="H39" s="1">
-        <x:v>411748</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I39" s="1">
         <x:v>2026</x:v>
@@ -2100,92 +2100,92 @@
     </x:row>
     <x:row r="40" spans="1:10">
       <x:c r="A40" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F40" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H40" s="1">
-        <x:v>56045</x:v>
+        <x:v>411748</x:v>
       </x:c>
       <x:c r="I40" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J40" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:10">
       <x:c r="A41" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F41" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H41" s="1">
-        <x:v>426280</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="I41" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J41" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:10">
       <x:c r="A42" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F42" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="H42" s="1">
-        <x:v>111598</x:v>
+        <x:v>426280</x:v>
       </x:c>
       <x:c r="I42" s="1">
         <x:v>2026</x:v>
@@ -2196,28 +2196,28 @@
     </x:row>
     <x:row r="43" spans="1:10">
       <x:c r="A43" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F43" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H43" s="1">
-        <x:v>282975</x:v>
+        <x:v>111598</x:v>
       </x:c>
       <x:c r="I43" s="1">
         <x:v>2026</x:v>
@@ -2228,28 +2228,28 @@
     </x:row>
     <x:row r="44" spans="1:10">
       <x:c r="A44" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F44" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="H44" s="1">
-        <x:v>367531</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="I44" s="1">
         <x:v>2026</x:v>
@@ -2260,28 +2260,28 @@
     </x:row>
     <x:row r="45" spans="1:10">
       <x:c r="A45" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>138</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F45" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H45" s="1">
-        <x:v>771658</x:v>
+        <x:v>367531</x:v>
       </x:c>
       <x:c r="I45" s="1">
         <x:v>2026</x:v>
@@ -2298,22 +2298,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>139</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>140</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F46" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="H46" s="1">
-        <x:v>487317</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="I46" s="1">
         <x:v>2026</x:v>
@@ -2324,28 +2324,28 @@
     </x:row>
     <x:row r="47" spans="1:10">
       <x:c r="A47" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>141</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F47" s="1" t="s">
-        <x:v>143</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
-        <x:v>144</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H47" s="1">
-        <x:v>485970</x:v>
+        <x:v>487317</x:v>
       </x:c>
       <x:c r="I47" s="1">
         <x:v>2026</x:v>
@@ -2362,27 +2362,59 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="D48" s="1" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="E48" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F48" s="1" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="G48" s="1" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="H48" s="1">
+        <x:v>485970</x:v>
+      </x:c>
+      <x:c r="I48" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J48" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:10">
+      <x:c r="A49" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B49" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C49" s="1" t="s">
         <x:v>145</x:v>
       </x:c>
-      <x:c r="D48" s="1" t="s">
+      <x:c r="D49" s="1" t="s">
         <x:v>146</x:v>
       </x:c>
-      <x:c r="E48" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F48" s="1" t="s">
+      <x:c r="E49" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F49" s="1" t="s">
         <x:v>147</x:v>
       </x:c>
-      <x:c r="G48" s="1" t="s">
+      <x:c r="G49" s="1" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="H48" s="1">
+      <x:c r="H49" s="1">
         <x:v>476254</x:v>
       </x:c>
-      <x:c r="I48" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J48" s="1" t="s">
+      <x:c r="I49" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J49" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -1001,7 +1001,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="H5" s="1">
-        <x:v>3353559</x:v>
+        <x:v>4868351</x:v>
       </x:c>
       <x:c r="I5" s="1">
         <x:v>2026</x:v>
@@ -2377,7 +2377,7 @@
         <x:v>144</x:v>
       </x:c>
       <x:c r="H48" s="1">
-        <x:v>485970</x:v>
+        <x:v>508281</x:v>
       </x:c>
       <x:c r="I48" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -1001,7 +1001,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="H5" s="1">
-        <x:v>4868351</x:v>
+        <x:v>4928025</x:v>
       </x:c>
       <x:c r="I5" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -2377,7 +2377,7 @@
         <x:v>144</x:v>
       </x:c>
       <x:c r="H48" s="1">
-        <x:v>508281</x:v>
+        <x:v>565530</x:v>
       </x:c>
       <x:c r="I48" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -386,12 +386,6 @@
   </x:si>
   <x:si>
     <x:t>SD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H2GA13012</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SCOTT, DAVID ALBERT</x:t>
   </x:si>
   <x:si>
     <x:t>H6TX19206</x:t>
@@ -528,8 +522,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J49" totalsRowShown="0">
-  <x:autoFilter ref="A1:J49"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J48" totalsRowShown="0">
+  <x:autoFilter ref="A1:J48"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -834,7 +828,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J49"/>
+  <x:dimension ref="A1:J48"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1065,7 +1059,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="H7" s="1">
-        <x:v>4210393</x:v>
+        <x:v>1281252</x:v>
       </x:c>
       <x:c r="I7" s="1">
         <x:v>2026</x:v>
@@ -1737,7 +1731,7 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="H28" s="1">
-        <x:v>4903859</x:v>
+        <x:v>4715211</x:v>
       </x:c>
       <x:c r="I28" s="1">
         <x:v>2026</x:v>
@@ -2132,10 +2126,10 @@
     </x:row>
     <x:row r="41" spans="1:10">
       <x:c r="A41" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
         <x:v>124</x:v>
@@ -2147,45 +2141,45 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F41" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="H41" s="1">
-        <x:v>56045</x:v>
+        <x:v>426280</x:v>
       </x:c>
       <x:c r="I41" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J41" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:10">
       <x:c r="A42" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F42" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H42" s="1">
-        <x:v>426280</x:v>
+        <x:v>111598</x:v>
       </x:c>
       <x:c r="I42" s="1">
         <x:v>2026</x:v>
@@ -2196,28 +2190,28 @@
     </x:row>
     <x:row r="43" spans="1:10">
       <x:c r="A43" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F43" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="H43" s="1">
-        <x:v>111598</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="I43" s="1">
         <x:v>2026</x:v>
@@ -2228,28 +2222,28 @@
     </x:row>
     <x:row r="44" spans="1:10">
       <x:c r="A44" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F44" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H44" s="1">
-        <x:v>282975</x:v>
+        <x:v>367531</x:v>
       </x:c>
       <x:c r="I44" s="1">
         <x:v>2026</x:v>
@@ -2260,10 +2254,10 @@
     </x:row>
     <x:row r="45" spans="1:10">
       <x:c r="A45" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
         <x:v>135</x:v>
@@ -2275,13 +2269,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F45" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="H45" s="1">
-        <x:v>367531</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="I45" s="1">
         <x:v>2026</x:v>
@@ -2307,13 +2301,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F46" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H46" s="1">
-        <x:v>771658</x:v>
+        <x:v>487317</x:v>
       </x:c>
       <x:c r="I46" s="1">
         <x:v>2026</x:v>
@@ -2324,10 +2318,10 @@
     </x:row>
     <x:row r="47" spans="1:10">
       <x:c r="A47" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
         <x:v>139</x:v>
@@ -2339,13 +2333,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F47" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="H47" s="1">
-        <x:v>487317</x:v>
+        <x:v>463780</x:v>
       </x:c>
       <x:c r="I47" s="1">
         <x:v>2026</x:v>
@@ -2362,59 +2356,27 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>141</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F48" s="1" t="s">
-        <x:v>143</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
-        <x:v>144</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H48" s="1">
-        <x:v>565530</x:v>
+        <x:v>476254</x:v>
       </x:c>
       <x:c r="I48" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J48" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" spans="1:10">
-      <x:c r="A49" s="1" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="B49" s="1" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C49" s="1" t="s">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="D49" s="1" t="s">
-        <x:v>146</x:v>
-      </x:c>
-      <x:c r="E49" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F49" s="1" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="G49" s="1" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="H49" s="1">
-        <x:v>476254</x:v>
-      </x:c>
-      <x:c r="I49" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J49" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -522,8 +522,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J48" totalsRowShown="0">
-  <x:autoFilter ref="A1:J48"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J49" totalsRowShown="0">
+  <x:autoFilter ref="A1:J49"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -828,7 +828,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J48"/>
+  <x:dimension ref="A1:J49"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1891,7 +1891,7 @@
         <x:v>107</x:v>
       </x:c>
       <x:c r="H33" s="1">
-        <x:v>12183751</x:v>
+        <x:v>12203100</x:v>
       </x:c>
       <x:c r="I33" s="1">
         <x:v>2026</x:v>
@@ -2318,10 +2318,10 @@
     </x:row>
     <x:row r="47" spans="1:10">
       <x:c r="A47" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
         <x:v>139</x:v>
@@ -2339,7 +2339,7 @@
         <x:v>142</x:v>
       </x:c>
       <x:c r="H47" s="1">
-        <x:v>463780</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="I47" s="1">
         <x:v>2026</x:v>
@@ -2356,27 +2356,59 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="D48" s="1" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="E48" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F48" s="1" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="G48" s="1" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="H48" s="1">
+        <x:v>463780</x:v>
+      </x:c>
+      <x:c r="I48" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J48" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:10">
+      <x:c r="A49" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B49" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C49" s="1" t="s">
         <x:v>143</x:v>
       </x:c>
-      <x:c r="D48" s="1" t="s">
+      <x:c r="D49" s="1" t="s">
         <x:v>144</x:v>
       </x:c>
-      <x:c r="E48" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F48" s="1" t="s">
+      <x:c r="E49" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F49" s="1" t="s">
         <x:v>145</x:v>
       </x:c>
-      <x:c r="G48" s="1" t="s">
+      <x:c r="G49" s="1" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="H48" s="1">
+      <x:c r="H49" s="1">
         <x:v>476254</x:v>
       </x:c>
-      <x:c r="I48" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J48" s="1" t="s">
+      <x:c r="I49" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J49" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -166,6 +166,15 @@
     <x:t>35</x:t>
   </x:si>
   <x:si>
+    <x:t>H4MD03263</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DUNN, HARRY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OPPOSE</x:t>
+  </x:si>
+  <x:si>
     <x:t>H0GA14030</x:t>
   </x:si>
   <x:si>
@@ -206,9 +215,6 @@
   </x:si>
   <x:si>
     <x:t>18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OPPOSE</x:t>
   </x:si>
   <x:si>
     <x:t>S6OK04247</x:t>
@@ -522,8 +528,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J49" totalsRowShown="0">
-  <x:autoFilter ref="A1:J49"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J50" totalsRowShown="0">
+  <x:autoFilter ref="A1:J50"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -828,7 +834,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J49"/>
+  <x:dimension ref="A1:J50"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -995,7 +1001,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="H5" s="1">
-        <x:v>4928025</x:v>
+        <x:v>5175229</x:v>
       </x:c>
       <x:c r="I5" s="1">
         <x:v>2026</x:v>
@@ -1166,10 +1172,10 @@
     </x:row>
     <x:row r="11" spans="1:10">
       <x:c r="A11" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
         <x:v>50</x:v>
@@ -1181,45 +1187,45 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F11" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="G11" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H11" s="1">
+        <x:v>73841</x:v>
+      </x:c>
+      <x:c r="I11" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J11" s="1" t="s">
         <x:v>52</x:v>
-      </x:c>
-      <x:c r="G11" s="1" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="H11" s="1">
-        <x:v>455146</x:v>
-      </x:c>
-      <x:c r="I11" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J11" s="1" t="s">
-        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:10">
       <x:c r="A12" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F12" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
         <x:v>40</x:v>
       </x:c>
       <x:c r="H12" s="1">
-        <x:v>300000</x:v>
+        <x:v>455146</x:v>
       </x:c>
       <x:c r="I12" s="1">
         <x:v>2026</x:v>
@@ -1230,10 +1236,10 @@
     </x:row>
     <x:row r="13" spans="1:10">
       <x:c r="A13" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
         <x:v>53</x:v>
@@ -1251,7 +1257,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="H13" s="1">
-        <x:v>708827</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="I13" s="1">
         <x:v>2026</x:v>
@@ -1277,13 +1283,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F14" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H14" s="1">
-        <x:v>91656</x:v>
+        <x:v>708827</x:v>
       </x:c>
       <x:c r="I14" s="1">
         <x:v>2026</x:v>
@@ -1294,28 +1300,28 @@
     </x:row>
     <x:row r="15" spans="1:10">
       <x:c r="A15" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="D15" s="1" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E15" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F15" s="1" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="D15" s="1" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="E15" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F15" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="H15" s="1">
-        <x:v>550000</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="I15" s="1">
         <x:v>2026</x:v>
@@ -1326,10 +1332,10 @@
     </x:row>
     <x:row r="16" spans="1:10">
       <x:c r="A16" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
         <x:v>61</x:v>
@@ -1338,68 +1344,68 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F16" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G16" s="1" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="G16" s="1" t="s">
-        <x:v>36</x:v>
-      </x:c>
       <x:c r="H16" s="1">
-        <x:v>47162</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="I16" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J16" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:10">
       <x:c r="A17" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="D17" s="1" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="D17" s="1" t="s">
+      <x:c r="E17" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F17" s="1" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="E17" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F17" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="H17" s="1">
-        <x:v>735613</x:v>
+        <x:v>47162</x:v>
       </x:c>
       <x:c r="I17" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J17" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:10">
       <x:c r="A18" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
         <x:v>25</x:v>
@@ -1408,10 +1414,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="H18" s="1">
-        <x:v>300000</x:v>
+        <x:v>735613</x:v>
       </x:c>
       <x:c r="I18" s="1">
         <x:v>2026</x:v>
@@ -1422,28 +1428,28 @@
     </x:row>
     <x:row r="19" spans="1:10">
       <x:c r="A19" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="D19" s="1" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="D19" s="1" t="s">
+      <x:c r="E19" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F19" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G19" s="1" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="E19" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F19" s="1" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="G19" s="1" t="s">
-        <x:v>71</x:v>
-      </x:c>
       <x:c r="H19" s="1">
-        <x:v>418060</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="I19" s="1">
         <x:v>2026</x:v>
@@ -1454,28 +1460,28 @@
     </x:row>
     <x:row r="20" spans="1:10">
       <x:c r="A20" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="D20" s="1" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="E20" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F20" s="1" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="D20" s="1" t="s">
+      <x:c r="G20" s="1" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="E20" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F20" s="1" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="G20" s="1" t="s">
-        <x:v>46</x:v>
-      </x:c>
       <x:c r="H20" s="1">
-        <x:v>366028</x:v>
+        <x:v>418060</x:v>
       </x:c>
       <x:c r="I20" s="1">
         <x:v>2026</x:v>
@@ -1486,28 +1492,28 @@
     </x:row>
     <x:row r="21" spans="1:10">
       <x:c r="A21" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="D21" s="1" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="D21" s="1" t="s">
+      <x:c r="E21" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F21" s="1" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="E21" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F21" s="1" t="s">
-        <x:v>77</x:v>
-      </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H21" s="1">
-        <x:v>430866</x:v>
+        <x:v>366028</x:v>
       </x:c>
       <x:c r="I21" s="1">
         <x:v>2026</x:v>
@@ -1524,16 +1530,16 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="D22" s="1" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="D22" s="1" t="s">
+      <x:c r="E22" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F22" s="1" t="s">
         <x:v>79</x:v>
-      </x:c>
-      <x:c r="E22" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F22" s="1" t="s">
-        <x:v>77</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
         <x:v>40</x:v>
@@ -1550,10 +1556,10 @@
     </x:row>
     <x:row r="23" spans="1:10">
       <x:c r="A23" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
         <x:v>80</x:v>
@@ -1562,16 +1568,16 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F23" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H23" s="1">
-        <x:v>350000</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="I23" s="1">
         <x:v>2026</x:v>
@@ -1582,28 +1588,28 @@
     </x:row>
     <x:row r="24" spans="1:10">
       <x:c r="A24" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="D24" s="1" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="D24" s="1" t="s">
+      <x:c r="E24" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F24" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G24" s="1" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="E24" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F24" s="1" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="G24" s="1" t="s">
-        <x:v>46</x:v>
-      </x:c>
       <x:c r="H24" s="1">
-        <x:v>106348</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I24" s="1">
         <x:v>2026</x:v>
@@ -1620,22 +1626,22 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="D25" s="1" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="D25" s="1" t="s">
+      <x:c r="E25" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F25" s="1" t="s">
         <x:v>87</x:v>
-      </x:c>
-      <x:c r="E25" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F25" s="1" t="s">
-        <x:v>63</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
         <x:v>46</x:v>
       </x:c>
       <x:c r="H25" s="1">
-        <x:v>109274</x:v>
+        <x:v>106348</x:v>
       </x:c>
       <x:c r="I25" s="1">
         <x:v>2026</x:v>
@@ -1661,13 +1667,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F26" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
         <x:v>46</x:v>
       </x:c>
       <x:c r="H26" s="1">
-        <x:v>372060</x:v>
+        <x:v>109274</x:v>
       </x:c>
       <x:c r="I26" s="1">
         <x:v>2026</x:v>
@@ -1678,10 +1684,10 @@
     </x:row>
     <x:row r="27" spans="1:10">
       <x:c r="A27" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
         <x:v>90</x:v>
@@ -1693,13 +1699,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F27" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H27" s="1">
-        <x:v>461943</x:v>
+        <x:v>372060</x:v>
       </x:c>
       <x:c r="I27" s="1">
         <x:v>2026</x:v>
@@ -1710,28 +1716,28 @@
     </x:row>
     <x:row r="28" spans="1:10">
       <x:c r="A28" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D28" s="1" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="D28" s="1" t="s">
+      <x:c r="E28" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F28" s="1" t="s">
         <x:v>94</x:v>
-      </x:c>
-      <x:c r="E28" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F28" s="1" t="s">
-        <x:v>63</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
         <x:v>36</x:v>
       </x:c>
       <x:c r="H28" s="1">
-        <x:v>4715211</x:v>
+        <x:v>461943</x:v>
       </x:c>
       <x:c r="I28" s="1">
         <x:v>2026</x:v>
@@ -1757,13 +1763,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F29" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="H29" s="1">
-        <x:v>228075</x:v>
+        <x:v>4715211</x:v>
       </x:c>
       <x:c r="I29" s="1">
         <x:v>2026</x:v>
@@ -1780,22 +1786,22 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="D30" s="1" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="E30" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F30" s="1" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="D30" s="1" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="E30" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F30" s="1" t="s">
-        <x:v>97</x:v>
-      </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="H30" s="1">
-        <x:v>34890</x:v>
+        <x:v>228075</x:v>
       </x:c>
       <x:c r="I30" s="1">
         <x:v>2026</x:v>
@@ -1806,28 +1812,28 @@
     </x:row>
     <x:row r="31" spans="1:10">
       <x:c r="A31" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="D31" s="1" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="E31" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F31" s="1" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="G31" s="1" t="s">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="D31" s="1" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="E31" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F31" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="G31" s="1" t="s">
-        <x:v>82</x:v>
-      </x:c>
       <x:c r="H31" s="1">
-        <x:v>250000</x:v>
+        <x:v>34890</x:v>
       </x:c>
       <x:c r="I31" s="1">
         <x:v>2026</x:v>
@@ -1838,10 +1844,10 @@
     </x:row>
     <x:row r="32" spans="1:10">
       <x:c r="A32" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
         <x:v>102</x:v>
@@ -1850,16 +1856,16 @@
         <x:v>103</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F32" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="H32" s="1">
-        <x:v>107940</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="I32" s="1">
         <x:v>2026</x:v>
@@ -1870,28 +1876,28 @@
     </x:row>
     <x:row r="33" spans="1:10">
       <x:c r="A33" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="D33" s="1" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="D33" s="1" t="s">
+      <x:c r="E33" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F33" s="1" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="E33" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F33" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H33" s="1">
-        <x:v>12203100</x:v>
+        <x:v>107940</x:v>
       </x:c>
       <x:c r="I33" s="1">
         <x:v>2026</x:v>
@@ -1902,16 +1908,16 @@
     </x:row>
     <x:row r="34" spans="1:10">
       <x:c r="A34" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
         <x:v>25</x:v>
@@ -1920,10 +1926,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="H34" s="1">
-        <x:v>350000</x:v>
+        <x:v>12203100</x:v>
       </x:c>
       <x:c r="I34" s="1">
         <x:v>2026</x:v>
@@ -1934,28 +1940,28 @@
     </x:row>
     <x:row r="35" spans="1:10">
       <x:c r="A35" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="D35" s="1" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="D35" s="1" t="s">
+      <x:c r="E35" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F35" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G35" s="1" t="s">
         <x:v>109</x:v>
       </x:c>
-      <x:c r="E35" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F35" s="1" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="G35" s="1" t="s">
-        <x:v>110</x:v>
-      </x:c>
       <x:c r="H35" s="1">
-        <x:v>80948</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I35" s="1">
         <x:v>2026</x:v>
@@ -1966,28 +1972,28 @@
     </x:row>
     <x:row r="36" spans="1:10">
       <x:c r="A36" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="D36" s="1" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="D36" s="1" t="s">
+      <x:c r="E36" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F36" s="1" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="G36" s="1" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="E36" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F36" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="G36" s="1" t="s">
-        <x:v>21</x:v>
-      </x:c>
       <x:c r="H36" s="1">
-        <x:v>221403</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="I36" s="1">
         <x:v>2026</x:v>
@@ -1998,10 +2004,10 @@
     </x:row>
     <x:row r="37" spans="1:10">
       <x:c r="A37" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
         <x:v>113</x:v>
@@ -2010,16 +2016,16 @@
         <x:v>114</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F37" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="H37" s="1">
-        <x:v>141263</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="I37" s="1">
         <x:v>2026</x:v>
@@ -2030,28 +2036,28 @@
     </x:row>
     <x:row r="38" spans="1:10">
       <x:c r="A38" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="D38" s="1" t="s">
         <x:v>116</x:v>
       </x:c>
-      <x:c r="D38" s="1" t="s">
+      <x:c r="E38" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F38" s="1" t="s">
         <x:v>117</x:v>
-      </x:c>
-      <x:c r="E38" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F38" s="1" t="s">
-        <x:v>26</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
         <x:v>36</x:v>
       </x:c>
       <x:c r="H38" s="1">
-        <x:v>2250000</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="I38" s="1">
         <x:v>2026</x:v>
@@ -2080,10 +2086,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="H39" s="1">
-        <x:v>350000</x:v>
+        <x:v>2250000</x:v>
       </x:c>
       <x:c r="I39" s="1">
         <x:v>2026</x:v>
@@ -2094,16 +2100,16 @@
     </x:row>
     <x:row r="40" spans="1:10">
       <x:c r="A40" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="D40" s="1" t="s">
         <x:v>121</x:v>
-      </x:c>
-      <x:c r="D40" s="1" t="s">
-        <x:v>122</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
         <x:v>25</x:v>
@@ -2112,10 +2118,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="H40" s="1">
-        <x:v>411748</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I40" s="1">
         <x:v>2026</x:v>
@@ -2132,22 +2138,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="D41" s="1" t="s">
         <x:v>124</x:v>
       </x:c>
-      <x:c r="D41" s="1" t="s">
+      <x:c r="E41" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F41" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G41" s="1" t="s">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="E41" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F41" s="1" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="G41" s="1" t="s">
-        <x:v>36</x:v>
-      </x:c>
       <x:c r="H41" s="1">
-        <x:v>426280</x:v>
+        <x:v>411748</x:v>
       </x:c>
       <x:c r="I41" s="1">
         <x:v>2026</x:v>
@@ -2158,28 +2164,28 @@
     </x:row>
     <x:row r="42" spans="1:10">
       <x:c r="A42" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="D42" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
-      <x:c r="D42" s="1" t="s">
+      <x:c r="E42" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F42" s="1" t="s">
         <x:v>128</x:v>
       </x:c>
-      <x:c r="E42" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F42" s="1" t="s">
-        <x:v>129</x:v>
-      </x:c>
       <x:c r="G42" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="H42" s="1">
-        <x:v>111598</x:v>
+        <x:v>426280</x:v>
       </x:c>
       <x:c r="I42" s="1">
         <x:v>2026</x:v>
@@ -2190,28 +2196,28 @@
     </x:row>
     <x:row r="43" spans="1:10">
       <x:c r="A43" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="D43" s="1" t="s">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="D43" s="1" t="s">
+      <x:c r="E43" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F43" s="1" t="s">
         <x:v>131</x:v>
       </x:c>
-      <x:c r="E43" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F43" s="1" t="s">
-        <x:v>132</x:v>
-      </x:c>
       <x:c r="G43" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H43" s="1">
-        <x:v>282975</x:v>
+        <x:v>111598</x:v>
       </x:c>
       <x:c r="I43" s="1">
         <x:v>2026</x:v>
@@ -2222,28 +2228,28 @@
     </x:row>
     <x:row r="44" spans="1:10">
       <x:c r="A44" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="D44" s="1" t="s">
         <x:v>133</x:v>
       </x:c>
-      <x:c r="D44" s="1" t="s">
+      <x:c r="E44" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F44" s="1" t="s">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="E44" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F44" s="1" t="s">
-        <x:v>35</x:v>
-      </x:c>
       <x:c r="G44" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="H44" s="1">
-        <x:v>367531</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="I44" s="1">
         <x:v>2026</x:v>
@@ -2254,10 +2260,10 @@
     </x:row>
     <x:row r="45" spans="1:10">
       <x:c r="A45" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
         <x:v>135</x:v>
@@ -2269,13 +2275,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F45" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H45" s="1">
-        <x:v>771658</x:v>
+        <x:v>367531</x:v>
       </x:c>
       <x:c r="I45" s="1">
         <x:v>2026</x:v>
@@ -2301,13 +2307,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F46" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="H46" s="1">
-        <x:v>487317</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="I46" s="1">
         <x:v>2026</x:v>
@@ -2318,10 +2324,10 @@
     </x:row>
     <x:row r="47" spans="1:10">
       <x:c r="A47" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
         <x:v>139</x:v>
@@ -2333,13 +2339,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F47" s="1" t="s">
-        <x:v>141</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H47" s="1">
-        <x:v>300000</x:v>
+        <x:v>487317</x:v>
       </x:c>
       <x:c r="I47" s="1">
         <x:v>2026</x:v>
@@ -2350,28 +2356,28 @@
     </x:row>
     <x:row r="48" spans="1:10">
       <x:c r="A48" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>139</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>140</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F48" s="1" t="s">
-        <x:v>141</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="H48" s="1">
-        <x:v>463780</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="I48" s="1">
         <x:v>2026</x:v>
@@ -2388,27 +2394,59 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="D49" s="1" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="E49" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F49" s="1" t="s">
         <x:v>143</x:v>
       </x:c>
-      <x:c r="D49" s="1" t="s">
+      <x:c r="G49" s="1" t="s">
         <x:v>144</x:v>
       </x:c>
-      <x:c r="E49" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F49" s="1" t="s">
+      <x:c r="H49" s="1">
+        <x:v>486091</x:v>
+      </x:c>
+      <x:c r="I49" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J49" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:10">
+      <x:c r="A50" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B50" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C50" s="1" t="s">
         <x:v>145</x:v>
       </x:c>
-      <x:c r="G49" s="1" t="s">
+      <x:c r="D50" s="1" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="E50" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F50" s="1" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="G50" s="1" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="H49" s="1">
+      <x:c r="H50" s="1">
         <x:v>476254</x:v>
       </x:c>
-      <x:c r="I49" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J49" s="1" t="s">
+      <x:c r="I50" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J50" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -70,6 +70,27 @@
     <x:t>SUPPORT</x:t>
   </x:si>
   <x:si>
+    <x:t>C00848440</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PROTECT PROGRESS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H4MD05235</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAREEBE, QUINCY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OPPOSE</x:t>
+  </x:si>
+  <x:si>
     <x:t>H0KY06104</x:t>
   </x:si>
   <x:si>
@@ -97,24 +118,12 @@
     <x:t>00</x:t>
   </x:si>
   <x:si>
-    <x:t>C00848440</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PROTECT PROGRESS</x:t>
-  </x:si>
-  <x:si>
     <x:t>H6MD05321</x:t>
   </x:si>
   <x:si>
     <x:t>BOAFO, ADRIAN</x:t>
   </x:si>
   <x:si>
-    <x:t>05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MD</x:t>
-  </x:si>
-  <x:si>
     <x:t>H6TX02244</x:t>
   </x:si>
   <x:si>
@@ -172,9 +181,6 @@
     <x:t>DUNN, HARRY</x:t>
   </x:si>
   <x:si>
-    <x:t>OPPOSE</x:t>
-  </x:si>
-  <x:si>
     <x:t>H0GA14030</x:t>
   </x:si>
   <x:si>
@@ -335,6 +341,15 @@
   </x:si>
   <x:si>
     <x:t>47</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H0UT01205</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOORE, BLAKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UT</x:t>
   </x:si>
   <x:si>
     <x:t>S6AL00476</x:t>
@@ -528,8 +543,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J50" totalsRowShown="0">
-  <x:autoFilter ref="A1:J50"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J52" totalsRowShown="0">
+  <x:autoFilter ref="A1:J52"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -834,7 +849,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J50"/>
+  <x:dimension ref="A1:J52"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -916,60 +931,60 @@
     </x:row>
     <x:row r="3" spans="1:10">
       <x:c r="A3" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F3" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="G3" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="H3" s="1">
-        <x:v>7170138</x:v>
+        <x:v>73841</x:v>
       </x:c>
       <x:c r="I3" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J3" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:10">
       <x:c r="A4" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F4" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G4" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="H4" s="1">
-        <x:v>628597</x:v>
+        <x:v>7170138</x:v>
       </x:c>
       <x:c r="I4" s="1">
         <x:v>2026</x:v>
@@ -980,28 +995,28 @@
     </x:row>
     <x:row r="5" spans="1:10">
       <x:c r="A5" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C5" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="D5" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E5" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F5" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G5" s="1" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C5" s="1" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="D5" s="1" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E5" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F5" s="1" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="G5" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
       <x:c r="H5" s="1">
-        <x:v>5175229</x:v>
+        <x:v>628597</x:v>
       </x:c>
       <x:c r="I5" s="1">
         <x:v>2026</x:v>
@@ -1012,28 +1027,28 @@
     </x:row>
     <x:row r="6" spans="1:10">
       <x:c r="A6" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F6" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="G6" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="H6" s="1">
-        <x:v>348433</x:v>
+        <x:v>5175229</x:v>
       </x:c>
       <x:c r="I6" s="1">
         <x:v>2026</x:v>
@@ -1044,28 +1059,28 @@
     </x:row>
     <x:row r="7" spans="1:10">
       <x:c r="A7" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D7" s="1" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="D7" s="1" t="s">
+      <x:c r="E7" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F7" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="E7" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F7" s="1" t="s">
+      <x:c r="G7" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="G7" s="1" t="s">
-        <x:v>40</x:v>
-      </x:c>
       <x:c r="H7" s="1">
-        <x:v>1281252</x:v>
+        <x:v>348433</x:v>
       </x:c>
       <x:c r="I7" s="1">
         <x:v>2026</x:v>
@@ -1076,28 +1091,28 @@
     </x:row>
     <x:row r="8" spans="1:10">
       <x:c r="A8" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="D8" s="1" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="D8" s="1" t="s">
+      <x:c r="E8" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F8" s="1" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="E8" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F8" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
       <x:c r="G8" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="H8" s="1">
-        <x:v>350000</x:v>
+        <x:v>1281252</x:v>
       </x:c>
       <x:c r="I8" s="1">
         <x:v>2026</x:v>
@@ -1108,28 +1123,28 @@
     </x:row>
     <x:row r="9" spans="1:10">
       <x:c r="A9" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="D9" s="1" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E9" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F9" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G9" s="1" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="D9" s="1" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="E9" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F9" s="1" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="G9" s="1" t="s">
-        <x:v>46</x:v>
-      </x:c>
       <x:c r="H9" s="1">
-        <x:v>107388</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I9" s="1">
         <x:v>2026</x:v>
@@ -1140,28 +1155,28 @@
     </x:row>
     <x:row r="10" spans="1:10">
       <x:c r="A10" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D10" s="1" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="D10" s="1" t="s">
+      <x:c r="E10" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F10" s="1" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="E10" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F10" s="1" t="s">
+      <x:c r="G10" s="1" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="G10" s="1" t="s">
-        <x:v>36</x:v>
-      </x:c>
       <x:c r="H10" s="1">
-        <x:v>616386</x:v>
+        <x:v>107388</x:v>
       </x:c>
       <x:c r="I10" s="1">
         <x:v>2026</x:v>
@@ -1172,10 +1187,10 @@
     </x:row>
     <x:row r="11" spans="1:10">
       <x:c r="A11" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
         <x:v>50</x:v>
@@ -1187,27 +1202,27 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F11" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H11" s="1">
-        <x:v>73841</x:v>
+        <x:v>616386</x:v>
       </x:c>
       <x:c r="I11" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J11" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:10">
       <x:c r="A12" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
         <x:v>53</x:v>
@@ -1219,45 +1234,45 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F12" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="H12" s="1">
-        <x:v>455146</x:v>
+        <x:v>73841</x:v>
       </x:c>
       <x:c r="I12" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J12" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:10">
       <x:c r="A13" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="H13" s="1">
-        <x:v>300000</x:v>
+        <x:v>455146</x:v>
       </x:c>
       <x:c r="I13" s="1">
         <x:v>2026</x:v>
@@ -1268,28 +1283,28 @@
     </x:row>
     <x:row r="14" spans="1:10">
       <x:c r="A14" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="D14" s="1" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="D14" s="1" t="s">
+      <x:c r="E14" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F14" s="1" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="E14" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F14" s="1" t="s">
-        <x:v>58</x:v>
-      </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="H14" s="1">
-        <x:v>708827</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="I14" s="1">
         <x:v>2026</x:v>
@@ -1306,22 +1321,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="D15" s="1" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="D15" s="1" t="s">
+      <x:c r="E15" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F15" s="1" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="E15" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F15" s="1" t="s">
-        <x:v>58</x:v>
-      </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="H15" s="1">
-        <x:v>91656</x:v>
+        <x:v>708827</x:v>
       </x:c>
       <x:c r="I15" s="1">
         <x:v>2026</x:v>
@@ -1332,10 +1347,10 @@
     </x:row>
     <x:row r="16" spans="1:10">
       <x:c r="A16" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
         <x:v>61</x:v>
@@ -1344,16 +1359,16 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F16" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H16" s="1">
-        <x:v>550000</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="I16" s="1">
         <x:v>2026</x:v>
@@ -1364,92 +1379,92 @@
     </x:row>
     <x:row r="17" spans="1:10">
       <x:c r="A17" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="D17" s="1" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="D17" s="1" t="s">
+      <x:c r="E17" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F17" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G17" s="1" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="E17" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F17" s="1" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="G17" s="1" t="s">
-        <x:v>36</x:v>
-      </x:c>
       <x:c r="H17" s="1">
-        <x:v>47162</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="I17" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J17" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:10">
       <x:c r="A18" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="D18" s="1" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="D18" s="1" t="s">
+      <x:c r="E18" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F18" s="1" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="E18" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F18" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H18" s="1">
-        <x:v>735613</x:v>
+        <x:v>47162</x:v>
       </x:c>
       <x:c r="I18" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J18" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:10">
       <x:c r="A19" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F19" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="H19" s="1">
-        <x:v>300000</x:v>
+        <x:v>735613</x:v>
       </x:c>
       <x:c r="I19" s="1">
         <x:v>2026</x:v>
@@ -1460,28 +1475,28 @@
     </x:row>
     <x:row r="20" spans="1:10">
       <x:c r="A20" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="D20" s="1" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="D20" s="1" t="s">
+      <x:c r="E20" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F20" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G20" s="1" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="E20" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F20" s="1" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="G20" s="1" t="s">
-        <x:v>73</x:v>
-      </x:c>
       <x:c r="H20" s="1">
-        <x:v>418060</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="I20" s="1">
         <x:v>2026</x:v>
@@ -1492,28 +1507,28 @@
     </x:row>
     <x:row r="21" spans="1:10">
       <x:c r="A21" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="D21" s="1" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="E21" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F21" s="1" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="D21" s="1" t="s">
+      <x:c r="G21" s="1" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="E21" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F21" s="1" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="G21" s="1" t="s">
-        <x:v>46</x:v>
-      </x:c>
       <x:c r="H21" s="1">
-        <x:v>366028</x:v>
+        <x:v>418060</x:v>
       </x:c>
       <x:c r="I21" s="1">
         <x:v>2026</x:v>
@@ -1524,28 +1539,28 @@
     </x:row>
     <x:row r="22" spans="1:10">
       <x:c r="A22" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="D22" s="1" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="D22" s="1" t="s">
+      <x:c r="E22" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F22" s="1" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="E22" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F22" s="1" t="s">
-        <x:v>79</x:v>
-      </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="H22" s="1">
-        <x:v>430866</x:v>
+        <x:v>366028</x:v>
       </x:c>
       <x:c r="I22" s="1">
         <x:v>2026</x:v>
@@ -1562,19 +1577,19 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="D23" s="1" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="D23" s="1" t="s">
+      <x:c r="E23" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F23" s="1" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="E23" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F23" s="1" t="s">
-        <x:v>79</x:v>
-      </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="H23" s="1">
         <x:v>430866</x:v>
@@ -1588,10 +1603,10 @@
     </x:row>
     <x:row r="24" spans="1:10">
       <x:c r="A24" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
         <x:v>82</x:v>
@@ -1600,16 +1615,16 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F24" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="H24" s="1">
-        <x:v>350000</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="I24" s="1">
         <x:v>2026</x:v>
@@ -1620,28 +1635,28 @@
     </x:row>
     <x:row r="25" spans="1:10">
       <x:c r="A25" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="D25" s="1" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="D25" s="1" t="s">
+      <x:c r="E25" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F25" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G25" s="1" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="E25" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F25" s="1" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="G25" s="1" t="s">
-        <x:v>46</x:v>
-      </x:c>
       <x:c r="H25" s="1">
-        <x:v>106348</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I25" s="1">
         <x:v>2026</x:v>
@@ -1652,28 +1667,28 @@
     </x:row>
     <x:row r="26" spans="1:10">
       <x:c r="A26" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="D26" s="1" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="D26" s="1" t="s">
+      <x:c r="E26" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F26" s="1" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="E26" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F26" s="1" t="s">
-        <x:v>66</x:v>
-      </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="H26" s="1">
-        <x:v>109274</x:v>
+        <x:v>106348</x:v>
       </x:c>
       <x:c r="I26" s="1">
         <x:v>2026</x:v>
@@ -1684,10 +1699,10 @@
     </x:row>
     <x:row r="27" spans="1:10">
       <x:c r="A27" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
         <x:v>90</x:v>
@@ -1699,13 +1714,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F27" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="H27" s="1">
-        <x:v>372060</x:v>
+        <x:v>109274</x:v>
       </x:c>
       <x:c r="I27" s="1">
         <x:v>2026</x:v>
@@ -1716,10 +1731,10 @@
     </x:row>
     <x:row r="28" spans="1:10">
       <x:c r="A28" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
         <x:v>92</x:v>
@@ -1731,13 +1746,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F28" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="H28" s="1">
-        <x:v>461943</x:v>
+        <x:v>372060</x:v>
       </x:c>
       <x:c r="I28" s="1">
         <x:v>2026</x:v>
@@ -1748,28 +1763,28 @@
     </x:row>
     <x:row r="29" spans="1:10">
       <x:c r="A29" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="D29" s="1" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="D29" s="1" t="s">
+      <x:c r="E29" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F29" s="1" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="E29" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F29" s="1" t="s">
-        <x:v>66</x:v>
-      </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H29" s="1">
-        <x:v>4715211</x:v>
+        <x:v>461943</x:v>
       </x:c>
       <x:c r="I29" s="1">
         <x:v>2026</x:v>
@@ -1780,10 +1795,10 @@
     </x:row>
     <x:row r="30" spans="1:10">
       <x:c r="A30" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
         <x:v>97</x:v>
@@ -1795,13 +1810,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F30" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H30" s="1">
-        <x:v>228075</x:v>
+        <x:v>4715211</x:v>
       </x:c>
       <x:c r="I30" s="1">
         <x:v>2026</x:v>
@@ -1812,28 +1827,28 @@
     </x:row>
     <x:row r="31" spans="1:10">
       <x:c r="A31" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D31" s="1" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E31" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F31" s="1" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="D31" s="1" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="E31" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F31" s="1" t="s">
-        <x:v>99</x:v>
-      </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="H31" s="1">
-        <x:v>34890</x:v>
+        <x:v>228075</x:v>
       </x:c>
       <x:c r="I31" s="1">
         <x:v>2026</x:v>
@@ -1844,28 +1859,28 @@
     </x:row>
     <x:row r="32" spans="1:10">
       <x:c r="A32" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="D32" s="1" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E32" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F32" s="1" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="G32" s="1" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="D32" s="1" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="E32" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F32" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="G32" s="1" t="s">
-        <x:v>84</x:v>
-      </x:c>
       <x:c r="H32" s="1">
-        <x:v>250000</x:v>
+        <x:v>34890</x:v>
       </x:c>
       <x:c r="I32" s="1">
         <x:v>2026</x:v>
@@ -1876,10 +1891,10 @@
     </x:row>
     <x:row r="33" spans="1:10">
       <x:c r="A33" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
         <x:v>104</x:v>
@@ -1888,16 +1903,16 @@
         <x:v>105</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F33" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="H33" s="1">
-        <x:v>107940</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="I33" s="1">
         <x:v>2026</x:v>
@@ -1908,28 +1923,28 @@
     </x:row>
     <x:row r="34" spans="1:10">
       <x:c r="A34" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="D34" s="1" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="D34" s="1" t="s">
+      <x:c r="E34" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F34" s="1" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="E34" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F34" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="H34" s="1">
-        <x:v>12203100</x:v>
+        <x:v>107940</x:v>
       </x:c>
       <x:c r="I34" s="1">
         <x:v>2026</x:v>
@@ -1940,28 +1955,28 @@
     </x:row>
     <x:row r="35" spans="1:10">
       <x:c r="A35" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F35" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="H35" s="1">
-        <x:v>350000</x:v>
+        <x:v>400022</x:v>
       </x:c>
       <x:c r="I35" s="1">
         <x:v>2026</x:v>
@@ -1978,22 +1993,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F36" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="H36" s="1">
-        <x:v>80948</x:v>
+        <x:v>12203100</x:v>
       </x:c>
       <x:c r="I36" s="1">
         <x:v>2026</x:v>
@@ -2004,28 +2019,28 @@
     </x:row>
     <x:row r="37" spans="1:10">
       <x:c r="A37" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="D37" s="1" t="s">
         <x:v>113</x:v>
       </x:c>
-      <x:c r="D37" s="1" t="s">
+      <x:c r="E37" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F37" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G37" s="1" t="s">
         <x:v>114</x:v>
       </x:c>
-      <x:c r="E37" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F37" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="G37" s="1" t="s">
-        <x:v>21</x:v>
-      </x:c>
       <x:c r="H37" s="1">
-        <x:v>221403</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I37" s="1">
         <x:v>2026</x:v>
@@ -2051,13 +2066,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F38" s="1" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="G38" s="1" t="s">
         <x:v>117</x:v>
       </x:c>
-      <x:c r="G38" s="1" t="s">
-        <x:v>36</x:v>
-      </x:c>
       <x:c r="H38" s="1">
-        <x:v>141263</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="I38" s="1">
         <x:v>2026</x:v>
@@ -2068,10 +2083,10 @@
     </x:row>
     <x:row r="39" spans="1:10">
       <x:c r="A39" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
         <x:v>118</x:v>
@@ -2080,16 +2095,16 @@
         <x:v>119</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F39" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="H39" s="1">
-        <x:v>2250000</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="I39" s="1">
         <x:v>2026</x:v>
@@ -2100,10 +2115,10 @@
     </x:row>
     <x:row r="40" spans="1:10">
       <x:c r="A40" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
         <x:v>120</x:v>
@@ -2112,16 +2127,16 @@
         <x:v>121</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F40" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H40" s="1">
-        <x:v>350000</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="I40" s="1">
         <x:v>2026</x:v>
@@ -2132,10 +2147,10 @@
     </x:row>
     <x:row r="41" spans="1:10">
       <x:c r="A41" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
         <x:v>123</x:v>
@@ -2144,16 +2159,16 @@
         <x:v>124</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F41" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H41" s="1">
-        <x:v>411748</x:v>
+        <x:v>2250000</x:v>
       </x:c>
       <x:c r="I41" s="1">
         <x:v>2026</x:v>
@@ -2164,28 +2179,28 @@
     </x:row>
     <x:row r="42" spans="1:10">
       <x:c r="A42" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="D42" s="1" t="s">
         <x:v>126</x:v>
       </x:c>
-      <x:c r="D42" s="1" t="s">
+      <x:c r="E42" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F42" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G42" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
-      <x:c r="E42" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F42" s="1" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="G42" s="1" t="s">
-        <x:v>36</x:v>
-      </x:c>
       <x:c r="H42" s="1">
-        <x:v>426280</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I42" s="1">
         <x:v>2026</x:v>
@@ -2196,28 +2211,28 @@
     </x:row>
     <x:row r="43" spans="1:10">
       <x:c r="A43" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="D43" s="1" t="s">
         <x:v>129</x:v>
       </x:c>
-      <x:c r="D43" s="1" t="s">
+      <x:c r="E43" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F43" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G43" s="1" t="s">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="E43" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F43" s="1" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="G43" s="1" t="s">
-        <x:v>46</x:v>
-      </x:c>
       <x:c r="H43" s="1">
-        <x:v>111598</x:v>
+        <x:v>411748</x:v>
       </x:c>
       <x:c r="I43" s="1">
         <x:v>2026</x:v>
@@ -2234,22 +2249,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="D44" s="1" t="s">
         <x:v>132</x:v>
       </x:c>
-      <x:c r="D44" s="1" t="s">
+      <x:c r="E44" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F44" s="1" t="s">
         <x:v>133</x:v>
       </x:c>
-      <x:c r="E44" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F44" s="1" t="s">
-        <x:v>134</x:v>
-      </x:c>
       <x:c r="G44" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H44" s="1">
-        <x:v>282975</x:v>
+        <x:v>426280</x:v>
       </x:c>
       <x:c r="I44" s="1">
         <x:v>2026</x:v>
@@ -2260,28 +2275,28 @@
     </x:row>
     <x:row r="45" spans="1:10">
       <x:c r="A45" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="D45" s="1" t="s">
         <x:v>135</x:v>
       </x:c>
-      <x:c r="D45" s="1" t="s">
+      <x:c r="E45" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F45" s="1" t="s">
         <x:v>136</x:v>
       </x:c>
-      <x:c r="E45" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F45" s="1" t="s">
-        <x:v>35</x:v>
-      </x:c>
       <x:c r="G45" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="H45" s="1">
-        <x:v>367531</x:v>
+        <x:v>111598</x:v>
       </x:c>
       <x:c r="I45" s="1">
         <x:v>2026</x:v>
@@ -2307,13 +2322,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F46" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="H46" s="1">
-        <x:v>771658</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="I46" s="1">
         <x:v>2026</x:v>
@@ -2324,28 +2339,28 @@
     </x:row>
     <x:row r="47" spans="1:10">
       <x:c r="A47" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F47" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="H47" s="1">
-        <x:v>487317</x:v>
+        <x:v>367531</x:v>
       </x:c>
       <x:c r="I47" s="1">
         <x:v>2026</x:v>
@@ -2356,28 +2371,28 @@
     </x:row>
     <x:row r="48" spans="1:10">
       <x:c r="A48" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F48" s="1" t="s">
-        <x:v>143</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
-        <x:v>144</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H48" s="1">
-        <x:v>300000</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="I48" s="1">
         <x:v>2026</x:v>
@@ -2388,28 +2403,28 @@
     </x:row>
     <x:row r="49" spans="1:10">
       <x:c r="A49" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>141</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F49" s="1" t="s">
-        <x:v>143</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
-        <x:v>144</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="H49" s="1">
-        <x:v>486091</x:v>
+        <x:v>487317</x:v>
       </x:c>
       <x:c r="I49" s="1">
         <x:v>2026</x:v>
@@ -2420,33 +2435,97 @@
     </x:row>
     <x:row r="50" spans="1:10">
       <x:c r="A50" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>145</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="E50" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F50" s="1" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="G50" s="1" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="H50" s="1">
+        <x:v>300000</x:v>
+      </x:c>
+      <x:c r="I50" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J50" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:10">
+      <x:c r="A51" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B51" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C51" s="1" t="s">
         <x:v>146</x:v>
       </x:c>
-      <x:c r="E50" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F50" s="1" t="s">
+      <x:c r="D51" s="1" t="s">
         <x:v>147</x:v>
       </x:c>
-      <x:c r="G50" s="1" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="H50" s="1">
+      <x:c r="E51" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F51" s="1" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="G51" s="1" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="H51" s="1">
+        <x:v>1260039</x:v>
+      </x:c>
+      <x:c r="I51" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J51" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:10">
+      <x:c r="A52" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B52" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C52" s="1" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="D52" s="1" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="E52" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F52" s="1" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="G52" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="H52" s="1">
         <x:v>476254</x:v>
       </x:c>
-      <x:c r="I50" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J50" s="1" t="s">
+      <x:c r="I52" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J52" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -952,7 +952,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="H3" s="1">
-        <x:v>73841</x:v>
+        <x:v>98455</x:v>
       </x:c>
       <x:c r="I3" s="1">
         <x:v>2026</x:v>
@@ -1048,7 +1048,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="H6" s="1">
-        <x:v>5175229</x:v>
+        <x:v>5259517</x:v>
       </x:c>
       <x:c r="I6" s="1">
         <x:v>2026</x:v>
@@ -1240,7 +1240,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="H12" s="1">
-        <x:v>73841</x:v>
+        <x:v>172296</x:v>
       </x:c>
       <x:c r="I12" s="1">
         <x:v>2026</x:v>
@@ -2488,7 +2488,7 @@
         <x:v>149</x:v>
       </x:c>
       <x:c r="H51" s="1">
-        <x:v>1260039</x:v>
+        <x:v>1317288</x:v>
       </x:c>
       <x:c r="I51" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -173,6 +173,12 @@
   </x:si>
   <x:si>
     <x:t>35</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H4MD06340</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DELANEY, APRIL MCCLAIN</x:t>
   </x:si>
   <x:si>
     <x:t>H4MD03263</x:t>
@@ -543,8 +549,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J52" totalsRowShown="0">
-  <x:autoFilter ref="A1:J52"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J53" totalsRowShown="0">
+  <x:autoFilter ref="A1:J53"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -849,7 +855,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J52"/>
+  <x:dimension ref="A1:J53"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1234,27 +1240,27 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F12" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="H12" s="1">
-        <x:v>172296</x:v>
+        <x:v>516368</x:v>
       </x:c>
       <x:c r="I12" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J12" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:10">
       <x:c r="A13" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
         <x:v>55</x:v>
@@ -1266,45 +1272,45 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="H13" s="1">
-        <x:v>455146</x:v>
+        <x:v>172296</x:v>
       </x:c>
       <x:c r="I13" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J13" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:10">
       <x:c r="A14" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F14" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
         <x:v>43</x:v>
       </x:c>
       <x:c r="H14" s="1">
-        <x:v>300000</x:v>
+        <x:v>455146</x:v>
       </x:c>
       <x:c r="I14" s="1">
         <x:v>2026</x:v>
@@ -1315,28 +1321,28 @@
     </x:row>
     <x:row r="15" spans="1:10">
       <x:c r="A15" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="D15" s="1" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="D15" s="1" t="s">
+      <x:c r="E15" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F15" s="1" t="s">
         <x:v>59</x:v>
-      </x:c>
-      <x:c r="E15" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F15" s="1" t="s">
-        <x:v>60</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
         <x:v>43</x:v>
       </x:c>
       <x:c r="H15" s="1">
-        <x:v>708827</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="I15" s="1">
         <x:v>2026</x:v>
@@ -1353,22 +1359,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="D16" s="1" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="D16" s="1" t="s">
+      <x:c r="E16" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F16" s="1" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="E16" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F16" s="1" t="s">
-        <x:v>60</x:v>
-      </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="H16" s="1">
-        <x:v>91656</x:v>
+        <x:v>708827</x:v>
       </x:c>
       <x:c r="I16" s="1">
         <x:v>2026</x:v>
@@ -1379,10 +1385,10 @@
     </x:row>
     <x:row r="17" spans="1:10">
       <x:c r="A17" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
         <x:v>63</x:v>
@@ -1391,16 +1397,16 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F17" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H17" s="1">
-        <x:v>550000</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="I17" s="1">
         <x:v>2026</x:v>
@@ -1411,80 +1417,80 @@
     </x:row>
     <x:row r="18" spans="1:10">
       <x:c r="A18" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="D18" s="1" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="D18" s="1" t="s">
+      <x:c r="E18" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F18" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G18" s="1" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="E18" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F18" s="1" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="G18" s="1" t="s">
-        <x:v>39</x:v>
-      </x:c>
       <x:c r="H18" s="1">
-        <x:v>47162</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="I18" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J18" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:10">
       <x:c r="A19" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="D19" s="1" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="D19" s="1" t="s">
+      <x:c r="E19" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F19" s="1" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="E19" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="F19" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H19" s="1">
-        <x:v>735613</x:v>
+        <x:v>47162</x:v>
       </x:c>
       <x:c r="I19" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J19" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:10">
       <x:c r="A20" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
         <x:v>32</x:v>
@@ -1493,10 +1499,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="H20" s="1">
-        <x:v>300000</x:v>
+        <x:v>735613</x:v>
       </x:c>
       <x:c r="I20" s="1">
         <x:v>2026</x:v>
@@ -1507,28 +1513,28 @@
     </x:row>
     <x:row r="21" spans="1:10">
       <x:c r="A21" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="D21" s="1" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="D21" s="1" t="s">
+      <x:c r="E21" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F21" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G21" s="1" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="E21" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F21" s="1" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="G21" s="1" t="s">
-        <x:v>75</x:v>
-      </x:c>
       <x:c r="H21" s="1">
-        <x:v>418060</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="I21" s="1">
         <x:v>2026</x:v>
@@ -1539,28 +1545,28 @@
     </x:row>
     <x:row r="22" spans="1:10">
       <x:c r="A22" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="D22" s="1" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="E22" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F22" s="1" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="D22" s="1" t="s">
+      <x:c r="G22" s="1" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="E22" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F22" s="1" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="G22" s="1" t="s">
-        <x:v>49</x:v>
-      </x:c>
       <x:c r="H22" s="1">
-        <x:v>366028</x:v>
+        <x:v>418060</x:v>
       </x:c>
       <x:c r="I22" s="1">
         <x:v>2026</x:v>
@@ -1571,28 +1577,28 @@
     </x:row>
     <x:row r="23" spans="1:10">
       <x:c r="A23" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="D23" s="1" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="D23" s="1" t="s">
+      <x:c r="E23" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F23" s="1" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="E23" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F23" s="1" t="s">
-        <x:v>81</x:v>
-      </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="H23" s="1">
-        <x:v>430866</x:v>
+        <x:v>366028</x:v>
       </x:c>
       <x:c r="I23" s="1">
         <x:v>2026</x:v>
@@ -1609,16 +1615,16 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="D24" s="1" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="D24" s="1" t="s">
+      <x:c r="E24" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F24" s="1" t="s">
         <x:v>83</x:v>
-      </x:c>
-      <x:c r="E24" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F24" s="1" t="s">
-        <x:v>81</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
         <x:v>43</x:v>
@@ -1635,10 +1641,10 @@
     </x:row>
     <x:row r="25" spans="1:10">
       <x:c r="A25" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
         <x:v>84</x:v>
@@ -1647,16 +1653,16 @@
         <x:v>85</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F25" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="H25" s="1">
-        <x:v>350000</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="I25" s="1">
         <x:v>2026</x:v>
@@ -1667,28 +1673,28 @@
     </x:row>
     <x:row r="26" spans="1:10">
       <x:c r="A26" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="D26" s="1" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="D26" s="1" t="s">
+      <x:c r="E26" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F26" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G26" s="1" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="E26" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F26" s="1" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="G26" s="1" t="s">
-        <x:v>49</x:v>
-      </x:c>
       <x:c r="H26" s="1">
-        <x:v>106348</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I26" s="1">
         <x:v>2026</x:v>
@@ -1705,22 +1711,22 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D27" s="1" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="D27" s="1" t="s">
+      <x:c r="E27" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F27" s="1" t="s">
         <x:v>91</x:v>
-      </x:c>
-      <x:c r="E27" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F27" s="1" t="s">
-        <x:v>68</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="H27" s="1">
-        <x:v>109274</x:v>
+        <x:v>106348</x:v>
       </x:c>
       <x:c r="I27" s="1">
         <x:v>2026</x:v>
@@ -1746,13 +1752,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F28" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="H28" s="1">
-        <x:v>372060</x:v>
+        <x:v>109274</x:v>
       </x:c>
       <x:c r="I28" s="1">
         <x:v>2026</x:v>
@@ -1763,10 +1769,10 @@
     </x:row>
     <x:row r="29" spans="1:10">
       <x:c r="A29" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
         <x:v>94</x:v>
@@ -1778,13 +1784,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F29" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="H29" s="1">
-        <x:v>461943</x:v>
+        <x:v>372060</x:v>
       </x:c>
       <x:c r="I29" s="1">
         <x:v>2026</x:v>
@@ -1795,28 +1801,28 @@
     </x:row>
     <x:row r="30" spans="1:10">
       <x:c r="A30" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D30" s="1" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="D30" s="1" t="s">
+      <x:c r="E30" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F30" s="1" t="s">
         <x:v>98</x:v>
-      </x:c>
-      <x:c r="E30" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F30" s="1" t="s">
-        <x:v>68</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="H30" s="1">
-        <x:v>4715211</x:v>
+        <x:v>461943</x:v>
       </x:c>
       <x:c r="I30" s="1">
         <x:v>2026</x:v>
@@ -1842,13 +1848,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F31" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H31" s="1">
-        <x:v>228075</x:v>
+        <x:v>4715211</x:v>
       </x:c>
       <x:c r="I31" s="1">
         <x:v>2026</x:v>
@@ -1865,22 +1871,22 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="D32" s="1" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="E32" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F32" s="1" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="D32" s="1" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E32" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F32" s="1" t="s">
-        <x:v>101</x:v>
-      </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="H32" s="1">
-        <x:v>34890</x:v>
+        <x:v>228075</x:v>
       </x:c>
       <x:c r="I32" s="1">
         <x:v>2026</x:v>
@@ -1891,28 +1897,28 @@
     </x:row>
     <x:row r="33" spans="1:10">
       <x:c r="A33" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="D33" s="1" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="E33" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F33" s="1" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="G33" s="1" t="s">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="D33" s="1" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="E33" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="F33" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="G33" s="1" t="s">
-        <x:v>86</x:v>
-      </x:c>
       <x:c r="H33" s="1">
-        <x:v>250000</x:v>
+        <x:v>34890</x:v>
       </x:c>
       <x:c r="I33" s="1">
         <x:v>2026</x:v>
@@ -1923,10 +1929,10 @@
     </x:row>
     <x:row r="34" spans="1:10">
       <x:c r="A34" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
         <x:v>106</x:v>
@@ -1935,16 +1941,16 @@
         <x:v>107</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F34" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="H34" s="1">
-        <x:v>107940</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="I34" s="1">
         <x:v>2026</x:v>
@@ -1955,28 +1961,28 @@
     </x:row>
     <x:row r="35" spans="1:10">
       <x:c r="A35" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="D35" s="1" t="s">
         <x:v>109</x:v>
       </x:c>
-      <x:c r="D35" s="1" t="s">
+      <x:c r="E35" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F35" s="1" t="s">
         <x:v>110</x:v>
       </x:c>
-      <x:c r="E35" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F35" s="1" t="s">
-        <x:v>81</x:v>
-      </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="H35" s="1">
-        <x:v>400022</x:v>
+        <x:v>107940</x:v>
       </x:c>
       <x:c r="I35" s="1">
         <x:v>2026</x:v>
@@ -1993,22 +1999,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="D36" s="1" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="D36" s="1" t="s">
+      <x:c r="E36" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F36" s="1" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="G36" s="1" t="s">
         <x:v>113</x:v>
       </x:c>
-      <x:c r="E36" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="F36" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="G36" s="1" t="s">
-        <x:v>114</x:v>
-      </x:c>
       <x:c r="H36" s="1">
-        <x:v>12203100</x:v>
+        <x:v>400022</x:v>
       </x:c>
       <x:c r="I36" s="1">
         <x:v>2026</x:v>
@@ -2019,16 +2025,16 @@
     </x:row>
     <x:row r="37" spans="1:10">
       <x:c r="A37" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
         <x:v>32</x:v>
@@ -2037,10 +2043,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H37" s="1">
-        <x:v>350000</x:v>
+        <x:v>12203100</x:v>
       </x:c>
       <x:c r="I37" s="1">
         <x:v>2026</x:v>
@@ -2051,28 +2057,28 @@
     </x:row>
     <x:row r="38" spans="1:10">
       <x:c r="A38" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="D38" s="1" t="s">
         <x:v>115</x:v>
       </x:c>
-      <x:c r="D38" s="1" t="s">
+      <x:c r="E38" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F38" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G38" s="1" t="s">
         <x:v>116</x:v>
       </x:c>
-      <x:c r="E38" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F38" s="1" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="G38" s="1" t="s">
-        <x:v>117</x:v>
-      </x:c>
       <x:c r="H38" s="1">
-        <x:v>80948</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I38" s="1">
         <x:v>2026</x:v>
@@ -2083,28 +2089,28 @@
     </x:row>
     <x:row r="39" spans="1:10">
       <x:c r="A39" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="D39" s="1" t="s">
         <x:v>118</x:v>
       </x:c>
-      <x:c r="D39" s="1" t="s">
+      <x:c r="E39" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F39" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="G39" s="1" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="E39" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="F39" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="G39" s="1" t="s">
-        <x:v>28</x:v>
-      </x:c>
       <x:c r="H39" s="1">
-        <x:v>221403</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="I39" s="1">
         <x:v>2026</x:v>
@@ -2115,10 +2121,10 @@
     </x:row>
     <x:row r="40" spans="1:10">
       <x:c r="A40" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
         <x:v>120</x:v>
@@ -2127,16 +2133,16 @@
         <x:v>121</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F40" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="H40" s="1">
-        <x:v>141263</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="I40" s="1">
         <x:v>2026</x:v>
@@ -2147,28 +2153,28 @@
     </x:row>
     <x:row r="41" spans="1:10">
       <x:c r="A41" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="D41" s="1" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="D41" s="1" t="s">
+      <x:c r="E41" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F41" s="1" t="s">
         <x:v>124</x:v>
-      </x:c>
-      <x:c r="E41" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="F41" s="1" t="s">
-        <x:v>33</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="H41" s="1">
-        <x:v>2250000</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="I41" s="1">
         <x:v>2026</x:v>
@@ -2197,10 +2203,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H42" s="1">
-        <x:v>350000</x:v>
+        <x:v>2250000</x:v>
       </x:c>
       <x:c r="I42" s="1">
         <x:v>2026</x:v>
@@ -2211,16 +2217,16 @@
     </x:row>
     <x:row r="43" spans="1:10">
       <x:c r="A43" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="D43" s="1" t="s">
         <x:v>128</x:v>
-      </x:c>
-      <x:c r="D43" s="1" t="s">
-        <x:v>129</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
         <x:v>32</x:v>
@@ -2229,10 +2235,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="H43" s="1">
-        <x:v>411748</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I43" s="1">
         <x:v>2026</x:v>
@@ -2249,22 +2255,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="D44" s="1" t="s">
         <x:v>131</x:v>
       </x:c>
-      <x:c r="D44" s="1" t="s">
+      <x:c r="E44" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F44" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G44" s="1" t="s">
         <x:v>132</x:v>
       </x:c>
-      <x:c r="E44" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F44" s="1" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="G44" s="1" t="s">
-        <x:v>39</x:v>
-      </x:c>
       <x:c r="H44" s="1">
-        <x:v>426280</x:v>
+        <x:v>411748</x:v>
       </x:c>
       <x:c r="I44" s="1">
         <x:v>2026</x:v>
@@ -2275,28 +2281,28 @@
     </x:row>
     <x:row r="45" spans="1:10">
       <x:c r="A45" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="D45" s="1" t="s">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="D45" s="1" t="s">
+      <x:c r="E45" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F45" s="1" t="s">
         <x:v>135</x:v>
       </x:c>
-      <x:c r="E45" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F45" s="1" t="s">
-        <x:v>136</x:v>
-      </x:c>
       <x:c r="G45" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H45" s="1">
-        <x:v>111598</x:v>
+        <x:v>426280</x:v>
       </x:c>
       <x:c r="I45" s="1">
         <x:v>2026</x:v>
@@ -2307,28 +2313,28 @@
     </x:row>
     <x:row r="46" spans="1:10">
       <x:c r="A46" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="D46" s="1" t="s">
         <x:v>137</x:v>
       </x:c>
-      <x:c r="D46" s="1" t="s">
+      <x:c r="E46" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F46" s="1" t="s">
         <x:v>138</x:v>
       </x:c>
-      <x:c r="E46" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F46" s="1" t="s">
-        <x:v>139</x:v>
-      </x:c>
       <x:c r="G46" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="H46" s="1">
-        <x:v>282975</x:v>
+        <x:v>111598</x:v>
       </x:c>
       <x:c r="I46" s="1">
         <x:v>2026</x:v>
@@ -2339,28 +2345,28 @@
     </x:row>
     <x:row r="47" spans="1:10">
       <x:c r="A47" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="D47" s="1" t="s">
         <x:v>140</x:v>
       </x:c>
-      <x:c r="D47" s="1" t="s">
+      <x:c r="E47" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F47" s="1" t="s">
         <x:v>141</x:v>
       </x:c>
-      <x:c r="E47" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F47" s="1" t="s">
-        <x:v>38</x:v>
-      </x:c>
       <x:c r="G47" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="H47" s="1">
-        <x:v>367531</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="I47" s="1">
         <x:v>2026</x:v>
@@ -2371,10 +2377,10 @@
     </x:row>
     <x:row r="48" spans="1:10">
       <x:c r="A48" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
         <x:v>142</x:v>
@@ -2386,13 +2392,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F48" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="H48" s="1">
-        <x:v>771658</x:v>
+        <x:v>367531</x:v>
       </x:c>
       <x:c r="I48" s="1">
         <x:v>2026</x:v>
@@ -2418,13 +2424,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F49" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H49" s="1">
-        <x:v>487317</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="I49" s="1">
         <x:v>2026</x:v>
@@ -2435,10 +2441,10 @@
     </x:row>
     <x:row r="50" spans="1:10">
       <x:c r="A50" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
         <x:v>146</x:v>
@@ -2450,13 +2456,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F50" s="1" t="s">
-        <x:v>148</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
-        <x:v>149</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H50" s="1">
-        <x:v>300000</x:v>
+        <x:v>487317</x:v>
       </x:c>
       <x:c r="I50" s="1">
         <x:v>2026</x:v>
@@ -2467,28 +2473,28 @@
     </x:row>
     <x:row r="51" spans="1:10">
       <x:c r="A51" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>147</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F51" s="1" t="s">
-        <x:v>148</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
-        <x:v>149</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="H51" s="1">
-        <x:v>1317288</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="I51" s="1">
         <x:v>2026</x:v>
@@ -2505,27 +2511,59 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="D52" s="1" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="E52" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F52" s="1" t="s">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="D52" s="1" t="s">
+      <x:c r="G52" s="1" t="s">
         <x:v>151</x:v>
       </x:c>
-      <x:c r="E52" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F52" s="1" t="s">
+      <x:c r="H52" s="1">
+        <x:v>1317288</x:v>
+      </x:c>
+      <x:c r="I52" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J52" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:10">
+      <x:c r="A53" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B53" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C53" s="1" t="s">
         <x:v>152</x:v>
       </x:c>
-      <x:c r="G52" s="1" t="s">
+      <x:c r="D53" s="1" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="E53" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F53" s="1" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="G53" s="1" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="H52" s="1">
+      <x:c r="H53" s="1">
         <x:v>476254</x:v>
       </x:c>
-      <x:c r="I52" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J52" s="1" t="s">
+      <x:c r="I53" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J53" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -446,6 +446,15 @@
   </x:si>
   <x:si>
     <x:t>SOLIS, HILDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H8AZ09040</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STANTON, GREG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AZ</x:t>
   </x:si>
   <x:si>
     <x:t>H6TX08209</x:t>
@@ -549,8 +558,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J53" totalsRowShown="0">
-  <x:autoFilter ref="A1:J53"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J54" totalsRowShown="0">
+  <x:autoFilter ref="A1:J54"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -855,7 +864,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J53"/>
+  <x:dimension ref="A1:J54"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2409,10 +2418,10 @@
     </x:row>
     <x:row r="49" spans="1:10">
       <x:c r="A49" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
         <x:v>144</x:v>
@@ -2424,13 +2433,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F49" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="H49" s="1">
-        <x:v>771658</x:v>
+        <x:v>52520</x:v>
       </x:c>
       <x:c r="I49" s="1">
         <x:v>2026</x:v>
@@ -2447,22 +2456,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>147</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F50" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H50" s="1">
-        <x:v>487317</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="I50" s="1">
         <x:v>2026</x:v>
@@ -2473,28 +2482,28 @@
     </x:row>
     <x:row r="51" spans="1:10">
       <x:c r="A51" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>148</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F51" s="1" t="s">
-        <x:v>150</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H51" s="1">
-        <x:v>300000</x:v>
+        <x:v>487317</x:v>
       </x:c>
       <x:c r="I51" s="1">
         <x:v>2026</x:v>
@@ -2505,28 +2514,28 @@
     </x:row>
     <x:row r="52" spans="1:10">
       <x:c r="A52" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>148</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>149</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F52" s="1" t="s">
-        <x:v>150</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="G52" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="H52" s="1">
-        <x:v>1317288</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="I52" s="1">
         <x:v>2026</x:v>
@@ -2543,27 +2552,59 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="D53" s="1" t="s">
         <x:v>152</x:v>
       </x:c>
-      <x:c r="D53" s="1" t="s">
+      <x:c r="E53" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F53" s="1" t="s">
         <x:v>153</x:v>
       </x:c>
-      <x:c r="E53" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F53" s="1" t="s">
+      <x:c r="G53" s="1" t="s">
         <x:v>154</x:v>
       </x:c>
-      <x:c r="G53" s="1" t="s">
+      <x:c r="H53" s="1">
+        <x:v>1317288</x:v>
+      </x:c>
+      <x:c r="I53" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J53" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:10">
+      <x:c r="A54" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B54" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C54" s="1" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="D54" s="1" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="E54" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F54" s="1" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="G54" s="1" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="H53" s="1">
+      <x:c r="H54" s="1">
         <x:v>476254</x:v>
       </x:c>
-      <x:c r="I53" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J53" s="1" t="s">
+      <x:c r="I54" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J54" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -136,36 +136,15 @@
     <x:t>TX</x:t>
   </x:si>
   <x:si>
-    <x:t>H6GA13070</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CLARK, JASMINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13</x:t>
+    <x:t>S6GA00390</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COLLINS, MICHAEL A JR</x:t>
   </x:si>
   <x:si>
     <x:t>GA</x:t>
   </x:si>
   <x:si>
-    <x:t>S6GA00390</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COLLINS, MICHAEL A JR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6CA46116</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CORREA, LOU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>46</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CA</x:t>
-  </x:si>
-  <x:si>
     <x:t>H6TX35087</x:t>
   </x:si>
   <x:si>
@@ -220,15 +199,6 @@
     <x:t>SC</x:t>
   </x:si>
   <x:si>
-    <x:t>H4TX09095</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GREEN, ALEXANDER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18</x:t>
-  </x:si>
-  <x:si>
     <x:t>S6OK04247</x:t>
   </x:si>
   <x:si>
@@ -250,15 +220,6 @@
     <x:t>AR</x:t>
   </x:si>
   <x:si>
-    <x:t>H6CA26266</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IRWIN, JACQUI V</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26</x:t>
-  </x:si>
-  <x:si>
     <x:t>H2GA01157</x:t>
   </x:si>
   <x:si>
@@ -283,27 +244,6 @@
     <x:t>LA</x:t>
   </x:si>
   <x:si>
-    <x:t>H4CA33119</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LIEU, TED</x:t>
-  </x:si>
-  <x:si>
-    <x:t>36</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H4CA16049</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LOFGREN, ZOE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6CA01269</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MCGUIRE, MIKE</x:t>
-  </x:si>
-  <x:si>
     <x:t>H6TX09140</x:t>
   </x:si>
   <x:si>
@@ -313,13 +253,7 @@
     <x:t>09</x:t>
   </x:si>
   <x:si>
-    <x:t>H6TX18232</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MENEFEE, CHRISTIAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H2NJ08232</x:t>
+    <x:t>H2NJ13075</x:t>
   </x:si>
   <x:si>
     <x:t>MENENDEZ, ROBERT</x:t>
@@ -331,24 +265,12 @@
     <x:t>NJ</x:t>
   </x:si>
   <x:si>
-    <x:t>H2NJ13075</x:t>
-  </x:si>
-  <x:si>
     <x:t>S6LA00540</x:t>
   </x:si>
   <x:si>
     <x:t>MIGUEZ, BLAKE</x:t>
   </x:si>
   <x:si>
-    <x:t>H4CA47085</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIN, DAVE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>47</x:t>
-  </x:si>
-  <x:si>
     <x:t>H0UT01205</x:t>
   </x:si>
   <x:si>
@@ -424,15 +346,6 @@
     <x:t>19</x:t>
   </x:si>
   <x:si>
-    <x:t>H4CA12154</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SIMON, LATEEFAH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12</x:t>
-  </x:si>
-  <x:si>
     <x:t>H6NE03115</x:t>
   </x:si>
   <x:si>
@@ -442,12 +355,6 @@
     <x:t>03</x:t>
   </x:si>
   <x:si>
-    <x:t>H6CA38139</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SOLIS, HILDA</x:t>
-  </x:si>
-  <x:si>
     <x:t>H8AZ09040</x:t>
   </x:si>
   <x:si>
@@ -479,15 +386,6 @@
   </x:si>
   <x:si>
     <x:t>NY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H4CA27111</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WHITESIDES, GEORGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -558,8 +456,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J54" totalsRowShown="0">
-  <x:autoFilter ref="A1:J54"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J41" totalsRowShown="0">
+  <x:autoFilter ref="A1:J41"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -864,7 +762,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J54"/>
+  <x:dimension ref="A1:J41"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1063,7 +961,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="H6" s="1">
-        <x:v>5259517</x:v>
+        <x:v>1965632</x:v>
       </x:c>
       <x:c r="I6" s="1">
         <x:v>2026</x:v>
@@ -1106,10 +1004,10 @@
     </x:row>
     <x:row r="8" spans="1:10">
       <x:c r="A8" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
         <x:v>40</x:v>
@@ -1118,16 +1016,16 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F8" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G8" s="1" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="G8" s="1" t="s">
-        <x:v>43</x:v>
-      </x:c>
       <x:c r="H8" s="1">
-        <x:v>1281252</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I8" s="1">
         <x:v>2026</x:v>
@@ -1138,28 +1036,28 @@
     </x:row>
     <x:row r="9" spans="1:10">
       <x:c r="A9" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="D9" s="1" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="D9" s="1" t="s">
+      <x:c r="E9" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F9" s="1" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="E9" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="F9" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
       <x:c r="G9" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H9" s="1">
-        <x:v>350000</x:v>
+        <x:v>616386</x:v>
       </x:c>
       <x:c r="I9" s="1">
         <x:v>2026</x:v>
@@ -1185,13 +1083,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F10" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="H10" s="1">
-        <x:v>107388</x:v>
+        <x:v>516368</x:v>
       </x:c>
       <x:c r="I10" s="1">
         <x:v>2026</x:v>
@@ -1202,60 +1100,60 @@
     </x:row>
     <x:row r="11" spans="1:10">
       <x:c r="A11" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F11" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="H11" s="1">
-        <x:v>616386</x:v>
+        <x:v>172296</x:v>
       </x:c>
       <x:c r="I11" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J11" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:10">
       <x:c r="A12" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F12" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H12" s="1">
-        <x:v>516368</x:v>
+        <x:v>455146</x:v>
       </x:c>
       <x:c r="I12" s="1">
         <x:v>2026</x:v>
@@ -1266,34 +1164,34 @@
     </x:row>
     <x:row r="13" spans="1:10">
       <x:c r="A13" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H13" s="1">
-        <x:v>172296</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="I13" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J13" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:10">
@@ -1304,22 +1202,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F14" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H14" s="1">
-        <x:v>455146</x:v>
+        <x:v>708827</x:v>
       </x:c>
       <x:c r="I14" s="1">
         <x:v>2026</x:v>
@@ -1330,28 +1228,28 @@
     </x:row>
     <x:row r="15" spans="1:10">
       <x:c r="A15" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="D15" s="1" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="D15" s="1" t="s">
-        <x:v>58</x:v>
-      </x:c>
       <x:c r="E15" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F15" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H15" s="1">
-        <x:v>300000</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="I15" s="1">
         <x:v>2026</x:v>
@@ -1362,28 +1260,28 @@
     </x:row>
     <x:row r="16" spans="1:10">
       <x:c r="A16" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="D16" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="E16" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F16" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G16" s="1" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="D16" s="1" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="E16" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F16" s="1" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="G16" s="1" t="s">
-        <x:v>43</x:v>
-      </x:c>
       <x:c r="H16" s="1">
-        <x:v>708827</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="I16" s="1">
         <x:v>2026</x:v>
@@ -1400,22 +1298,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="D17" s="1" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="E17" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F17" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G17" s="1" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="D17" s="1" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="E17" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F17" s="1" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="G17" s="1" t="s">
-        <x:v>39</x:v>
-      </x:c>
       <x:c r="H17" s="1">
-        <x:v>91656</x:v>
+        <x:v>735613</x:v>
       </x:c>
       <x:c r="I17" s="1">
         <x:v>2026</x:v>
@@ -1432,10 +1330,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
         <x:v>32</x:v>
@@ -1444,10 +1342,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H18" s="1">
-        <x:v>550000</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="I18" s="1">
         <x:v>2026</x:v>
@@ -1458,34 +1356,34 @@
     </x:row>
     <x:row r="19" spans="1:10">
       <x:c r="A19" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F19" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H19" s="1">
-        <x:v>47162</x:v>
+        <x:v>418060</x:v>
       </x:c>
       <x:c r="I19" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J19" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:10">
@@ -1496,22 +1394,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F20" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H20" s="1">
-        <x:v>735613</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="I20" s="1">
         <x:v>2026</x:v>
@@ -1522,10 +1420,10 @@
     </x:row>
     <x:row r="21" spans="1:10">
       <x:c r="A21" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
         <x:v>71</x:v>
@@ -1534,16 +1432,16 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F21" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H21" s="1">
-        <x:v>300000</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="I21" s="1">
         <x:v>2026</x:v>
@@ -1554,28 +1452,28 @@
     </x:row>
     <x:row r="22" spans="1:10">
       <x:c r="A22" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="D22" s="1" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="D22" s="1" t="s">
+      <x:c r="E22" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F22" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G22" s="1" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="E22" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F22" s="1" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="G22" s="1" t="s">
-        <x:v>77</x:v>
-      </x:c>
       <x:c r="H22" s="1">
-        <x:v>418060</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I22" s="1">
         <x:v>2026</x:v>
@@ -1586,28 +1484,28 @@
     </x:row>
     <x:row r="23" spans="1:10">
       <x:c r="A23" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="D23" s="1" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="E23" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F23" s="1" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="D23" s="1" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="E23" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F23" s="1" t="s">
-        <x:v>80</x:v>
-      </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H23" s="1">
-        <x:v>366028</x:v>
+        <x:v>461943</x:v>
       </x:c>
       <x:c r="I23" s="1">
         <x:v>2026</x:v>
@@ -1618,28 +1516,28 @@
     </x:row>
     <x:row r="24" spans="1:10">
       <x:c r="A24" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="D24" s="1" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="E24" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F24" s="1" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="D24" s="1" t="s">
+      <x:c r="G24" s="1" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="E24" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F24" s="1" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="G24" s="1" t="s">
-        <x:v>43</x:v>
-      </x:c>
       <x:c r="H24" s="1">
-        <x:v>430866</x:v>
+        <x:v>34890</x:v>
       </x:c>
       <x:c r="I24" s="1">
         <x:v>2026</x:v>
@@ -1650,28 +1548,28 @@
     </x:row>
     <x:row r="25" spans="1:10">
       <x:c r="A25" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="D25" s="1" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="D25" s="1" t="s">
-        <x:v>85</x:v>
-      </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F25" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="H25" s="1">
-        <x:v>430866</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="I25" s="1">
         <x:v>2026</x:v>
@@ -1682,28 +1580,28 @@
     </x:row>
     <x:row r="26" spans="1:10">
       <x:c r="A26" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="D26" s="1" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="D26" s="1" t="s">
+      <x:c r="E26" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F26" s="1" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="G26" s="1" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="E26" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="F26" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="G26" s="1" t="s">
-        <x:v>88</x:v>
-      </x:c>
       <x:c r="H26" s="1">
-        <x:v>350000</x:v>
+        <x:v>400022</x:v>
       </x:c>
       <x:c r="I26" s="1">
         <x:v>2026</x:v>
@@ -1714,28 +1612,28 @@
     </x:row>
     <x:row r="27" spans="1:10">
       <x:c r="A27" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="D27" s="1" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="D27" s="1" t="s">
+      <x:c r="E27" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F27" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G27" s="1" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="E27" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F27" s="1" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="G27" s="1" t="s">
-        <x:v>49</x:v>
-      </x:c>
       <x:c r="H27" s="1">
-        <x:v>106348</x:v>
+        <x:v>12203100</x:v>
       </x:c>
       <x:c r="I27" s="1">
         <x:v>2026</x:v>
@@ -1746,28 +1644,28 @@
     </x:row>
     <x:row r="28" spans="1:10">
       <x:c r="A28" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F28" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H28" s="1">
-        <x:v>109274</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I28" s="1">
         <x:v>2026</x:v>
@@ -1778,28 +1676,28 @@
     </x:row>
     <x:row r="29" spans="1:10">
       <x:c r="A29" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F29" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="H29" s="1">
-        <x:v>372060</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="I29" s="1">
         <x:v>2026</x:v>
@@ -1810,28 +1708,28 @@
     </x:row>
     <x:row r="30" spans="1:10">
       <x:c r="A30" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F30" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="H30" s="1">
-        <x:v>461943</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="I30" s="1">
         <x:v>2026</x:v>
@@ -1842,28 +1740,28 @@
     </x:row>
     <x:row r="31" spans="1:10">
       <x:c r="A31" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F31" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="H31" s="1">
-        <x:v>4715211</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="I31" s="1">
         <x:v>2026</x:v>
@@ -1874,28 +1772,28 @@
     </x:row>
     <x:row r="32" spans="1:10">
       <x:c r="A32" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F32" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H32" s="1">
-        <x:v>228075</x:v>
+        <x:v>2250000</x:v>
       </x:c>
       <x:c r="I32" s="1">
         <x:v>2026</x:v>
@@ -1906,28 +1804,28 @@
     </x:row>
     <x:row r="33" spans="1:10">
       <x:c r="A33" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
         <x:v>102</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F33" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G33" s="1" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="G33" s="1" t="s">
-        <x:v>104</x:v>
-      </x:c>
       <x:c r="H33" s="1">
-        <x:v>34890</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I33" s="1">
         <x:v>2026</x:v>
@@ -1938,16 +1836,16 @@
     </x:row>
     <x:row r="34" spans="1:10">
       <x:c r="A34" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
         <x:v>32</x:v>
@@ -1956,10 +1854,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="H34" s="1">
-        <x:v>250000</x:v>
+        <x:v>411748</x:v>
       </x:c>
       <x:c r="I34" s="1">
         <x:v>2026</x:v>
@@ -1970,28 +1868,28 @@
     </x:row>
     <x:row r="35" spans="1:10">
       <x:c r="A35" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="D35" s="1" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="D35" s="1" t="s">
+      <x:c r="E35" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F35" s="1" t="s">
         <x:v>109</x:v>
       </x:c>
-      <x:c r="E35" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F35" s="1" t="s">
-        <x:v>110</x:v>
-      </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H35" s="1">
-        <x:v>107940</x:v>
+        <x:v>426280</x:v>
       </x:c>
       <x:c r="I35" s="1">
         <x:v>2026</x:v>
@@ -2008,22 +1906,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="D36" s="1" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="D36" s="1" t="s">
+      <x:c r="E36" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F36" s="1" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="E36" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F36" s="1" t="s">
-        <x:v>83</x:v>
-      </x:c>
       <x:c r="G36" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="H36" s="1">
-        <x:v>400022</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="I36" s="1">
         <x:v>2026</x:v>
@@ -2034,28 +1932,28 @@
     </x:row>
     <x:row r="37" spans="1:10">
       <x:c r="A37" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="D37" s="1" t="s">
         <x:v>114</x:v>
       </x:c>
-      <x:c r="D37" s="1" t="s">
+      <x:c r="E37" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F37" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G37" s="1" t="s">
         <x:v>115</x:v>
       </x:c>
-      <x:c r="E37" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="F37" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="G37" s="1" t="s">
-        <x:v>116</x:v>
-      </x:c>
       <x:c r="H37" s="1">
-        <x:v>12203100</x:v>
+        <x:v>52520</x:v>
       </x:c>
       <x:c r="I37" s="1">
         <x:v>2026</x:v>
@@ -2066,28 +1964,28 @@
     </x:row>
     <x:row r="38" spans="1:10">
       <x:c r="A38" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F38" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H38" s="1">
-        <x:v>350000</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="I38" s="1">
         <x:v>2026</x:v>
@@ -2104,22 +2002,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F39" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H39" s="1">
-        <x:v>80948</x:v>
+        <x:v>487317</x:v>
       </x:c>
       <x:c r="I39" s="1">
         <x:v>2026</x:v>
@@ -2142,16 +2040,16 @@
         <x:v>121</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F40" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H40" s="1">
-        <x:v>221403</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="I40" s="1">
         <x:v>2026</x:v>
@@ -2162,449 +2060,33 @@
     </x:row>
     <x:row r="41" spans="1:10">
       <x:c r="A41" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="D41" s="1" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="E41" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F41" s="1" t="s">
         <x:v>122</x:v>
       </x:c>
-      <x:c r="D41" s="1" t="s">
+      <x:c r="G41" s="1" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="E41" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F41" s="1" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="G41" s="1" t="s">
-        <x:v>39</x:v>
-      </x:c>
       <x:c r="H41" s="1">
-        <x:v>141263</x:v>
+        <x:v>1012628</x:v>
       </x:c>
       <x:c r="I41" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J41" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" spans="1:10">
-      <x:c r="A42" s="1" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="B42" s="1" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C42" s="1" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="D42" s="1" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="E42" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="F42" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="G42" s="1" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="H42" s="1">
-        <x:v>2250000</x:v>
-      </x:c>
-      <x:c r="I42" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J42" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" spans="1:10">
-      <x:c r="A43" s="1" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="B43" s="1" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C43" s="1" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="D43" s="1" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="E43" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="F43" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="G43" s="1" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="H43" s="1">
-        <x:v>350000</x:v>
-      </x:c>
-      <x:c r="I43" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J43" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" spans="1:10">
-      <x:c r="A44" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B44" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C44" s="1" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="D44" s="1" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="E44" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="F44" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="G44" s="1" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="H44" s="1">
-        <x:v>411748</x:v>
-      </x:c>
-      <x:c r="I44" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J44" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" spans="1:10">
-      <x:c r="A45" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B45" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C45" s="1" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="D45" s="1" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="E45" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F45" s="1" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="G45" s="1" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="H45" s="1">
-        <x:v>426280</x:v>
-      </x:c>
-      <x:c r="I45" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J45" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" spans="1:10">
-      <x:c r="A46" s="1" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="B46" s="1" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C46" s="1" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="D46" s="1" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="E46" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F46" s="1" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="G46" s="1" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="H46" s="1">
-        <x:v>111598</x:v>
-      </x:c>
-      <x:c r="I46" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J46" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" spans="1:10">
-      <x:c r="A47" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B47" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C47" s="1" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="D47" s="1" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="E47" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F47" s="1" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="G47" s="1" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="H47" s="1">
-        <x:v>282975</x:v>
-      </x:c>
-      <x:c r="I47" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J47" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48" spans="1:10">
-      <x:c r="A48" s="1" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="B48" s="1" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C48" s="1" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="D48" s="1" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="E48" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F48" s="1" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="G48" s="1" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="H48" s="1">
-        <x:v>367531</x:v>
-      </x:c>
-      <x:c r="I48" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J48" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" spans="1:10">
-      <x:c r="A49" s="1" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="B49" s="1" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C49" s="1" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="D49" s="1" t="s">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="E49" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F49" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G49" s="1" t="s">
-        <x:v>146</x:v>
-      </x:c>
-      <x:c r="H49" s="1">
-        <x:v>52520</x:v>
-      </x:c>
-      <x:c r="I49" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J49" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50" spans="1:10">
-      <x:c r="A50" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B50" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C50" s="1" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="D50" s="1" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="E50" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F50" s="1" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="G50" s="1" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="H50" s="1">
-        <x:v>771658</x:v>
-      </x:c>
-      <x:c r="I50" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J50" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51" spans="1:10">
-      <x:c r="A51" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B51" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C51" s="1" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="D51" s="1" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="E51" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F51" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G51" s="1" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="H51" s="1">
-        <x:v>487317</x:v>
-      </x:c>
-      <x:c r="I51" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J51" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="52" spans="1:10">
-      <x:c r="A52" s="1" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="B52" s="1" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C52" s="1" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="D52" s="1" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="E52" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F52" s="1" t="s">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c r="G52" s="1" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="H52" s="1">
-        <x:v>300000</x:v>
-      </x:c>
-      <x:c r="I52" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J52" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="53" spans="1:10">
-      <x:c r="A53" s="1" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="B53" s="1" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C53" s="1" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="D53" s="1" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="E53" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F53" s="1" t="s">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c r="G53" s="1" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="H53" s="1">
-        <x:v>1317288</x:v>
-      </x:c>
-      <x:c r="I53" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J53" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="54" spans="1:10">
-      <x:c r="A54" s="1" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="B54" s="1" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C54" s="1" t="s">
-        <x:v>155</x:v>
-      </x:c>
-      <x:c r="D54" s="1" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="E54" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F54" s="1" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="G54" s="1" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="H54" s="1">
-        <x:v>476254</x:v>
-      </x:c>
-      <x:c r="I54" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J54" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -1953,7 +1953,7 @@
         <x:v>115</x:v>
       </x:c>
       <x:c r="H37" s="1">
-        <x:v>52520</x:v>
+        <x:v>105040</x:v>
       </x:c>
       <x:c r="I37" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -160,6 +160,18 @@
     <x:t>DELANEY, APRIL MCCLAIN</x:t>
   </x:si>
   <x:si>
+    <x:t>H0WA08046</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DELBENE, SUZAN K</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WA</x:t>
+  </x:si>
+  <x:si>
     <x:t>H4MD03263</x:t>
   </x:si>
   <x:si>
@@ -226,9 +238,6 @@
     <x:t>KINGSTON, JACK REP.</x:t>
   </x:si>
   <x:si>
-    <x:t>01</x:t>
-  </x:si>
-  <x:si>
     <x:t>H6GA01109</x:t>
   </x:si>
   <x:si>
@@ -244,6 +253,12 @@
     <x:t>LA</x:t>
   </x:si>
   <x:si>
+    <x:t>H6WA04216</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCKINNEY, AMANDA</x:t>
+  </x:si>
+  <x:si>
     <x:t>H6TX09140</x:t>
   </x:si>
   <x:si>
@@ -337,6 +352,12 @@
     <x:t>SD</x:t>
   </x:si>
   <x:si>
+    <x:t>H8WA08189</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SCHRIER, KIM DR.</x:t>
+  </x:si>
+  <x:si>
     <x:t>H6TX19206</x:t>
   </x:si>
   <x:si>
@@ -368,6 +389,12 @@
   </x:si>
   <x:si>
     <x:t>STEINMANN, JESSICA HART</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H0WA10034</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STRICKLAND, MARILYN</x:t>
   </x:si>
   <x:si>
     <x:t>H8SC04250</x:t>
@@ -456,8 +483,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J41" totalsRowShown="0">
-  <x:autoFilter ref="A1:J41"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J45" totalsRowShown="0">
+  <x:autoFilter ref="A1:J45"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -762,7 +789,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J41"/>
+  <x:dimension ref="A1:J45"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1115,77 +1142,77 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F11" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H11" s="1">
-        <x:v>172296</x:v>
+        <x:v>56560</x:v>
       </x:c>
       <x:c r="I11" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J11" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:10">
       <x:c r="A12" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F12" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="H12" s="1">
-        <x:v>455146</x:v>
+        <x:v>172296</x:v>
       </x:c>
       <x:c r="I12" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J12" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:10">
       <x:c r="A13" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
         <x:v>42</x:v>
       </x:c>
       <x:c r="H13" s="1">
-        <x:v>300000</x:v>
+        <x:v>455146</x:v>
       </x:c>
       <x:c r="I13" s="1">
         <x:v>2026</x:v>
@@ -1196,28 +1223,28 @@
     </x:row>
     <x:row r="14" spans="1:10">
       <x:c r="A14" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F14" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
         <x:v>42</x:v>
       </x:c>
       <x:c r="H14" s="1">
-        <x:v>708827</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="I14" s="1">
         <x:v>2026</x:v>
@@ -1234,22 +1261,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F15" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H15" s="1">
-        <x:v>91656</x:v>
+        <x:v>708827</x:v>
       </x:c>
       <x:c r="I15" s="1">
         <x:v>2026</x:v>
@@ -1260,28 +1287,28 @@
     </x:row>
     <x:row r="16" spans="1:10">
       <x:c r="A16" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E16" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F16" s="1" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="E16" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="F16" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H16" s="1">
-        <x:v>550000</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="I16" s="1">
         <x:v>2026</x:v>
@@ -1292,16 +1319,16 @@
     </x:row>
     <x:row r="17" spans="1:10">
       <x:c r="A17" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
         <x:v>32</x:v>
@@ -1310,10 +1337,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="H17" s="1">
-        <x:v>735613</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="I17" s="1">
         <x:v>2026</x:v>
@@ -1324,16 +1351,16 @@
     </x:row>
     <x:row r="18" spans="1:10">
       <x:c r="A18" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
         <x:v>32</x:v>
@@ -1342,10 +1369,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H18" s="1">
-        <x:v>300000</x:v>
+        <x:v>735613</x:v>
       </x:c>
       <x:c r="I18" s="1">
         <x:v>2026</x:v>
@@ -1356,28 +1383,28 @@
     </x:row>
     <x:row r="19" spans="1:10">
       <x:c r="A19" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F19" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
         <x:v>67</x:v>
       </x:c>
       <x:c r="H19" s="1">
-        <x:v>418060</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="I19" s="1">
         <x:v>2026</x:v>
@@ -1406,10 +1433,10 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="H20" s="1">
-        <x:v>430866</x:v>
+        <x:v>418060</x:v>
       </x:c>
       <x:c r="I20" s="1">
         <x:v>2026</x:v>
@@ -1426,16 +1453,16 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F21" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
         <x:v>42</x:v>
@@ -1452,28 +1479,28 @@
     </x:row>
     <x:row r="22" spans="1:10">
       <x:c r="A22" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F22" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H22" s="1">
-        <x:v>350000</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="I22" s="1">
         <x:v>2026</x:v>
@@ -1484,10 +1511,10 @@
     </x:row>
     <x:row r="23" spans="1:10">
       <x:c r="A23" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
         <x:v>76</x:v>
@@ -1496,16 +1523,16 @@
         <x:v>77</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F23" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G23" s="1" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="G23" s="1" t="s">
-        <x:v>39</x:v>
-      </x:c>
       <x:c r="H23" s="1">
-        <x:v>461943</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I23" s="1">
         <x:v>2026</x:v>
@@ -1516,10 +1543,10 @@
     </x:row>
     <x:row r="24" spans="1:10">
       <x:c r="A24" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
         <x:v>79</x:v>
@@ -1531,13 +1558,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F24" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H24" s="1">
-        <x:v>34890</x:v>
+        <x:v>65340</x:v>
       </x:c>
       <x:c r="I24" s="1">
         <x:v>2026</x:v>
@@ -1548,28 +1575,28 @@
     </x:row>
     <x:row r="25" spans="1:10">
       <x:c r="A25" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="D25" s="1" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="E25" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F25" s="1" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="D25" s="1" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="E25" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="F25" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H25" s="1">
-        <x:v>250000</x:v>
+        <x:v>461943</x:v>
       </x:c>
       <x:c r="I25" s="1">
         <x:v>2026</x:v>
@@ -1580,28 +1607,28 @@
     </x:row>
     <x:row r="26" spans="1:10">
       <x:c r="A26" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="D26" s="1" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="D26" s="1" t="s">
+      <x:c r="E26" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F26" s="1" t="s">
         <x:v>86</x:v>
-      </x:c>
-      <x:c r="E26" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F26" s="1" t="s">
-        <x:v>70</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
         <x:v>87</x:v>
       </x:c>
       <x:c r="H26" s="1">
-        <x:v>400022</x:v>
+        <x:v>34890</x:v>
       </x:c>
       <x:c r="I26" s="1">
         <x:v>2026</x:v>
@@ -1612,10 +1639,10 @@
     </x:row>
     <x:row r="27" spans="1:10">
       <x:c r="A27" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
         <x:v>88</x:v>
@@ -1630,10 +1657,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="H27" s="1">
-        <x:v>12203100</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="I27" s="1">
         <x:v>2026</x:v>
@@ -1644,28 +1671,28 @@
     </x:row>
     <x:row r="28" spans="1:10">
       <x:c r="A28" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F28" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="H28" s="1">
-        <x:v>350000</x:v>
+        <x:v>400022</x:v>
       </x:c>
       <x:c r="I28" s="1">
         <x:v>2026</x:v>
@@ -1682,22 +1709,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F29" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="H29" s="1">
-        <x:v>80948</x:v>
+        <x:v>12203100</x:v>
       </x:c>
       <x:c r="I29" s="1">
         <x:v>2026</x:v>
@@ -1714,10 +1741,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="D30" s="1" t="s">
         <x:v>94</x:v>
-      </x:c>
-      <x:c r="D30" s="1" t="s">
-        <x:v>95</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
         <x:v>32</x:v>
@@ -1726,10 +1753,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="H30" s="1">
-        <x:v>221403</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I30" s="1">
         <x:v>2026</x:v>
@@ -1755,13 +1782,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F31" s="1" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="G31" s="1" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="G31" s="1" t="s">
-        <x:v>39</x:v>
-      </x:c>
       <x:c r="H31" s="1">
-        <x:v>141263</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="I31" s="1">
         <x:v>2026</x:v>
@@ -1790,10 +1817,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="H32" s="1">
-        <x:v>2250000</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="I32" s="1">
         <x:v>2026</x:v>
@@ -1804,10 +1831,10 @@
     </x:row>
     <x:row r="33" spans="1:10">
       <x:c r="A33" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
         <x:v>101</x:v>
@@ -1816,16 +1843,16 @@
         <x:v>102</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F33" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H33" s="1">
-        <x:v>350000</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="I33" s="1">
         <x:v>2026</x:v>
@@ -1836,10 +1863,10 @@
     </x:row>
     <x:row r="34" spans="1:10">
       <x:c r="A34" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
         <x:v>104</x:v>
@@ -1854,10 +1881,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H34" s="1">
-        <x:v>411748</x:v>
+        <x:v>2250000</x:v>
       </x:c>
       <x:c r="I34" s="1">
         <x:v>2026</x:v>
@@ -1868,28 +1895,28 @@
     </x:row>
     <x:row r="35" spans="1:10">
       <x:c r="A35" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="D35" s="1" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="D35" s="1" t="s">
+      <x:c r="E35" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F35" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G35" s="1" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="E35" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F35" s="1" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="G35" s="1" t="s">
-        <x:v>39</x:v>
-      </x:c>
       <x:c r="H35" s="1">
-        <x:v>426280</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I35" s="1">
         <x:v>2026</x:v>
@@ -1906,22 +1933,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="D36" s="1" t="s">
         <x:v>110</x:v>
       </x:c>
-      <x:c r="D36" s="1" t="s">
+      <x:c r="E36" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F36" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G36" s="1" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="E36" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F36" s="1" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="G36" s="1" t="s">
-        <x:v>103</x:v>
-      </x:c>
       <x:c r="H36" s="1">
-        <x:v>282975</x:v>
+        <x:v>411748</x:v>
       </x:c>
       <x:c r="I36" s="1">
         <x:v>2026</x:v>
@@ -1938,22 +1965,22 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="D37" s="1" t="s">
         <x:v>113</x:v>
       </x:c>
-      <x:c r="D37" s="1" t="s">
-        <x:v>114</x:v>
-      </x:c>
       <x:c r="E37" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F37" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H37" s="1">
-        <x:v>105040</x:v>
+        <x:v>52520</x:v>
       </x:c>
       <x:c r="I37" s="1">
         <x:v>2026</x:v>
@@ -1970,22 +1997,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="D38" s="1" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="E38" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F38" s="1" t="s">
         <x:v>116</x:v>
-      </x:c>
-      <x:c r="D38" s="1" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="E38" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F38" s="1" t="s">
-        <x:v>81</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="H38" s="1">
-        <x:v>771658</x:v>
+        <x:v>426280</x:v>
       </x:c>
       <x:c r="I38" s="1">
         <x:v>2026</x:v>
@@ -2002,22 +2029,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="D39" s="1" t="s">
         <x:v>118</x:v>
       </x:c>
-      <x:c r="D39" s="1" t="s">
+      <x:c r="E39" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F39" s="1" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="E39" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F39" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
       <x:c r="G39" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="H39" s="1">
-        <x:v>487317</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="I39" s="1">
         <x:v>2026</x:v>
@@ -2028,10 +2055,10 @@
     </x:row>
     <x:row r="40" spans="1:10">
       <x:c r="A40" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
         <x:v>120</x:v>
@@ -2043,13 +2070,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F40" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G40" s="1" t="s">
         <x:v>122</x:v>
       </x:c>
-      <x:c r="G40" s="1" t="s">
-        <x:v>123</x:v>
-      </x:c>
       <x:c r="H40" s="1">
-        <x:v>300000</x:v>
+        <x:v>157560</x:v>
       </x:c>
       <x:c r="I40" s="1">
         <x:v>2026</x:v>
@@ -2060,33 +2087,161 @@
     </x:row>
     <x:row r="41" spans="1:10">
       <x:c r="A41" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B41" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C41" s="1" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="D41" s="1" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="E41" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F41" s="1" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="G41" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="H41" s="1">
+        <x:v>771658</x:v>
+      </x:c>
+      <x:c r="I41" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J41" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:10">
+      <x:c r="A42" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="B41" s="1" t="s">
+      <x:c r="B42" s="1" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="C41" s="1" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="D41" s="1" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="E41" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F41" s="1" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="G41" s="1" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="H41" s="1">
+      <x:c r="C42" s="1" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="D42" s="1" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="E42" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F42" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="G42" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="H42" s="1">
+        <x:v>51510</x:v>
+      </x:c>
+      <x:c r="I42" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J42" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:10">
+      <x:c r="A43" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B43" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C43" s="1" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="D43" s="1" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="E43" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F43" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G43" s="1" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="H43" s="1">
+        <x:v>487317</x:v>
+      </x:c>
+      <x:c r="I43" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J43" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:10">
+      <x:c r="A44" s="1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B44" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C44" s="1" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="D44" s="1" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="E44" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F44" s="1" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="G44" s="1" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="H44" s="1">
+        <x:v>300000</x:v>
+      </x:c>
+      <x:c r="I44" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J44" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:10">
+      <x:c r="A45" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B45" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C45" s="1" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="D45" s="1" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="E45" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F45" s="1" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="G45" s="1" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="H45" s="1">
         <x:v>1012628</x:v>
       </x:c>
-      <x:c r="I41" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J41" s="1" t="s">
+      <x:c r="I45" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J45" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -257,6 +257,18 @@
   </x:si>
   <x:si>
     <x:t>MCKINNEY, AMANDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H6MI13254</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCKINNEY, DONAVAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MI</x:t>
   </x:si>
   <x:si>
     <x:t>H6TX09140</x:t>
@@ -483,8 +495,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J45" totalsRowShown="0">
-  <x:autoFilter ref="A1:J45"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J46" totalsRowShown="0">
+  <x:autoFilter ref="A1:J46"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -789,7 +801,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J45"/>
+  <x:dimension ref="A1:J46"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1575,10 +1587,10 @@
     </x:row>
     <x:row r="25" spans="1:10">
       <x:c r="A25" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
         <x:v>81</x:v>
@@ -1593,42 +1605,42 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="H25" s="1">
-        <x:v>461943</x:v>
+        <x:v>54570</x:v>
       </x:c>
       <x:c r="I25" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J25" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:10">
       <x:c r="A26" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F26" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H26" s="1">
-        <x:v>34890</x:v>
+        <x:v>461943</x:v>
       </x:c>
       <x:c r="I26" s="1">
         <x:v>2026</x:v>
@@ -1639,10 +1651,10 @@
     </x:row>
     <x:row r="27" spans="1:10">
       <x:c r="A27" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
         <x:v>88</x:v>
@@ -1651,16 +1663,16 @@
         <x:v>89</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F27" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="H27" s="1">
-        <x:v>250000</x:v>
+        <x:v>34890</x:v>
       </x:c>
       <x:c r="I27" s="1">
         <x:v>2026</x:v>
@@ -1671,28 +1683,28 @@
     </x:row>
     <x:row r="28" spans="1:10">
       <x:c r="A28" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F28" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="H28" s="1">
-        <x:v>400022</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="I28" s="1">
         <x:v>2026</x:v>
@@ -1709,22 +1721,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F29" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="H29" s="1">
-        <x:v>12203100</x:v>
+        <x:v>400022</x:v>
       </x:c>
       <x:c r="I29" s="1">
         <x:v>2026</x:v>
@@ -1735,16 +1747,16 @@
     </x:row>
     <x:row r="30" spans="1:10">
       <x:c r="A30" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
         <x:v>32</x:v>
@@ -1753,10 +1765,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="H30" s="1">
-        <x:v>350000</x:v>
+        <x:v>12203100</x:v>
       </x:c>
       <x:c r="I30" s="1">
         <x:v>2026</x:v>
@@ -1767,28 +1779,28 @@
     </x:row>
     <x:row r="31" spans="1:10">
       <x:c r="A31" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F31" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="H31" s="1">
-        <x:v>80948</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I31" s="1">
         <x:v>2026</x:v>
@@ -1799,28 +1811,28 @@
     </x:row>
     <x:row r="32" spans="1:10">
       <x:c r="A32" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F32" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="H32" s="1">
-        <x:v>221403</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="I32" s="1">
         <x:v>2026</x:v>
@@ -1831,28 +1843,28 @@
     </x:row>
     <x:row r="33" spans="1:10">
       <x:c r="A33" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F33" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="H33" s="1">
-        <x:v>141263</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="I33" s="1">
         <x:v>2026</x:v>
@@ -1863,28 +1875,28 @@
     </x:row>
     <x:row r="34" spans="1:10">
       <x:c r="A34" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F34" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="H34" s="1">
-        <x:v>2250000</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="I34" s="1">
         <x:v>2026</x:v>
@@ -1901,10 +1913,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
         <x:v>32</x:v>
@@ -1913,10 +1925,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H35" s="1">
-        <x:v>350000</x:v>
+        <x:v>2250000</x:v>
       </x:c>
       <x:c r="I35" s="1">
         <x:v>2026</x:v>
@@ -1927,16 +1939,16 @@
     </x:row>
     <x:row r="36" spans="1:10">
       <x:c r="A36" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
         <x:v>32</x:v>
@@ -1945,10 +1957,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="H36" s="1">
-        <x:v>411748</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I36" s="1">
         <x:v>2026</x:v>
@@ -1959,28 +1971,28 @@
     </x:row>
     <x:row r="37" spans="1:10">
       <x:c r="A37" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F37" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="H37" s="1">
-        <x:v>52520</x:v>
+        <x:v>411748</x:v>
       </x:c>
       <x:c r="I37" s="1">
         <x:v>2026</x:v>
@@ -1991,28 +2003,28 @@
     </x:row>
     <x:row r="38" spans="1:10">
       <x:c r="A38" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F38" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H38" s="1">
-        <x:v>426280</x:v>
+        <x:v>52520</x:v>
       </x:c>
       <x:c r="I38" s="1">
         <x:v>2026</x:v>
@@ -2029,22 +2041,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F39" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H39" s="1">
-        <x:v>282975</x:v>
+        <x:v>426280</x:v>
       </x:c>
       <x:c r="I39" s="1">
         <x:v>2026</x:v>
@@ -2055,28 +2067,28 @@
     </x:row>
     <x:row r="40" spans="1:10">
       <x:c r="A40" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F40" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="H40" s="1">
-        <x:v>157560</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="I40" s="1">
         <x:v>2026</x:v>
@@ -2087,28 +2099,28 @@
     </x:row>
     <x:row r="41" spans="1:10">
       <x:c r="A41" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F41" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="H41" s="1">
-        <x:v>771658</x:v>
+        <x:v>157560</x:v>
       </x:c>
       <x:c r="I41" s="1">
         <x:v>2026</x:v>
@@ -2119,28 +2131,28 @@
     </x:row>
     <x:row r="42" spans="1:10">
       <x:c r="A42" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F42" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H42" s="1">
-        <x:v>51510</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="I42" s="1">
         <x:v>2026</x:v>
@@ -2151,28 +2163,28 @@
     </x:row>
     <x:row r="43" spans="1:10">
       <x:c r="A43" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F43" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H43" s="1">
-        <x:v>487317</x:v>
+        <x:v>51510</x:v>
       </x:c>
       <x:c r="I43" s="1">
         <x:v>2026</x:v>
@@ -2183,28 +2195,28 @@
     </x:row>
     <x:row r="44" spans="1:10">
       <x:c r="A44" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F44" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="H44" s="1">
-        <x:v>300000</x:v>
+        <x:v>487317</x:v>
       </x:c>
       <x:c r="I44" s="1">
         <x:v>2026</x:v>
@@ -2215,33 +2227,65 @@
     </x:row>
     <x:row r="45" spans="1:10">
       <x:c r="A45" s="1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B45" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C45" s="1" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="D45" s="1" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="E45" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F45" s="1" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="G45" s="1" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="H45" s="1">
+        <x:v>300000</x:v>
+      </x:c>
+      <x:c r="I45" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J45" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:10">
+      <x:c r="A46" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="B45" s="1" t="s">
+      <x:c r="B46" s="1" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="C45" s="1" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="D45" s="1" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="E45" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F45" s="1" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="G45" s="1" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="H45" s="1">
+      <x:c r="C46" s="1" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="D46" s="1" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="E46" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F46" s="1" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="G46" s="1" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="H46" s="1">
         <x:v>1012628</x:v>
       </x:c>
-      <x:c r="I45" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J45" s="1" t="s">
+      <x:c r="I46" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J46" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -407,6 +407,12 @@
   </x:si>
   <x:si>
     <x:t>STRICKLAND, MARILYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H2MI13204</x:t>
+  </x:si>
+  <x:si>
+    <x:t>THANEDAR, SHRI</x:t>
   </x:si>
   <x:si>
     <x:t>H8SC04250</x:t>
@@ -495,8 +501,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J46" totalsRowShown="0">
-  <x:autoFilter ref="A1:J46"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J47" totalsRowShown="0">
+  <x:autoFilter ref="A1:J47"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -801,7 +807,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J46"/>
+  <x:dimension ref="A1:J47"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2195,10 +2201,10 @@
     </x:row>
     <x:row r="44" spans="1:10">
       <x:c r="A44" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
         <x:v>131</x:v>
@@ -2210,13 +2216,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F44" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="H44" s="1">
-        <x:v>487317</x:v>
+        <x:v>877913</x:v>
       </x:c>
       <x:c r="I44" s="1">
         <x:v>2026</x:v>
@@ -2227,10 +2233,10 @@
     </x:row>
     <x:row r="45" spans="1:10">
       <x:c r="A45" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
         <x:v>133</x:v>
@@ -2242,13 +2248,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F45" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="H45" s="1">
-        <x:v>300000</x:v>
+        <x:v>487317</x:v>
       </x:c>
       <x:c r="I45" s="1">
         <x:v>2026</x:v>
@@ -2259,33 +2265,65 @@
     </x:row>
     <x:row r="46" spans="1:10">
       <x:c r="A46" s="1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B46" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C46" s="1" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="D46" s="1" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="E46" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F46" s="1" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="G46" s="1" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="H46" s="1">
+        <x:v>300000</x:v>
+      </x:c>
+      <x:c r="I46" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J46" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:10">
+      <x:c r="A47" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="B46" s="1" t="s">
+      <x:c r="B47" s="1" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="C46" s="1" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="D46" s="1" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="E46" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F46" s="1" t="s">
+      <x:c r="C47" s="1" t="s">
         <x:v>135</x:v>
       </x:c>
-      <x:c r="G46" s="1" t="s">
+      <x:c r="D47" s="1" t="s">
         <x:v>136</x:v>
       </x:c>
-      <x:c r="H46" s="1">
+      <x:c r="E47" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F47" s="1" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="G47" s="1" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="H47" s="1">
         <x:v>1012628</x:v>
       </x:c>
-      <x:c r="I46" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J46" s="1" t="s">
+      <x:c r="I47" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J47" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -1614,7 +1614,7 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="H25" s="1">
-        <x:v>54570</x:v>
+        <x:v>108100</x:v>
       </x:c>
       <x:c r="I25" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -1166,7 +1166,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="H11" s="1">
-        <x:v>56560</x:v>
+        <x:v>113120</x:v>
       </x:c>
       <x:c r="I11" s="1">
         <x:v>2026</x:v>
@@ -1582,7 +1582,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="H24" s="1">
-        <x:v>65340</x:v>
+        <x:v>441577</x:v>
       </x:c>
       <x:c r="I24" s="1">
         <x:v>2026</x:v>
@@ -2030,7 +2030,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="H38" s="1">
-        <x:v>52520</x:v>
+        <x:v>105040</x:v>
       </x:c>
       <x:c r="I38" s="1">
         <x:v>2026</x:v>
@@ -2190,7 +2190,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="H43" s="1">
-        <x:v>51510</x:v>
+        <x:v>103020</x:v>
       </x:c>
       <x:c r="I43" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -1614,7 +1614,7 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="H25" s="1">
-        <x:v>108100</x:v>
+        <x:v>161630</x:v>
       </x:c>
       <x:c r="I25" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -232,6 +232,15 @@
     <x:t>AR</x:t>
   </x:si>
   <x:si>
+    <x:t>H0MI02094</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HUIZENGA, WILLIAM P</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MI</x:t>
+  </x:si>
+  <x:si>
     <x:t>H2GA01157</x:t>
   </x:si>
   <x:si>
@@ -266,9 +275,6 @@
   </x:si>
   <x:si>
     <x:t>13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MI</x:t>
   </x:si>
   <x:si>
     <x:t>H6TX09140</x:t>
@@ -501,8 +507,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J47" totalsRowShown="0">
-  <x:autoFilter ref="A1:J47"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J48" totalsRowShown="0">
+  <x:autoFilter ref="A1:J48"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -807,7 +813,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J47"/>
+  <x:dimension ref="A1:J48"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1480,13 +1486,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F21" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="H21" s="1">
-        <x:v>430866</x:v>
+        <x:v>511996</x:v>
       </x:c>
       <x:c r="I21" s="1">
         <x:v>2026</x:v>
@@ -1503,10 +1509,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
         <x:v>14</x:v>
@@ -1529,28 +1535,28 @@
     </x:row>
     <x:row r="23" spans="1:10">
       <x:c r="A23" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F23" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H23" s="1">
-        <x:v>350000</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="I23" s="1">
         <x:v>2026</x:v>
@@ -1561,10 +1567,10 @@
     </x:row>
     <x:row r="24" spans="1:10">
       <x:c r="A24" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
         <x:v>79</x:v>
@@ -1573,16 +1579,16 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F24" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="H24" s="1">
-        <x:v>441577</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I24" s="1">
         <x:v>2026</x:v>
@@ -1593,92 +1599,92 @@
     </x:row>
     <x:row r="25" spans="1:10">
       <x:c r="A25" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F25" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H25" s="1">
-        <x:v>161630</x:v>
+        <x:v>441577</x:v>
       </x:c>
       <x:c r="I25" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J25" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:10">
       <x:c r="A26" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="D26" s="1" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="D26" s="1" t="s">
+      <x:c r="E26" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F26" s="1" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="E26" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F26" s="1" t="s">
-        <x:v>87</x:v>
-      </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="H26" s="1">
-        <x:v>461943</x:v>
+        <x:v>215160</x:v>
       </x:c>
       <x:c r="I26" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J26" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:10">
       <x:c r="A27" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="D27" s="1" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="D27" s="1" t="s">
+      <x:c r="E27" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F27" s="1" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="E27" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F27" s="1" t="s">
-        <x:v>90</x:v>
-      </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H27" s="1">
-        <x:v>34890</x:v>
+        <x:v>461943</x:v>
       </x:c>
       <x:c r="I27" s="1">
         <x:v>2026</x:v>
@@ -1689,28 +1695,28 @@
     </x:row>
     <x:row r="28" spans="1:10">
       <x:c r="A28" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D28" s="1" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="E28" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F28" s="1" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="D28" s="1" t="s">
+      <x:c r="G28" s="1" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="E28" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="F28" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="G28" s="1" t="s">
-        <x:v>78</x:v>
-      </x:c>
       <x:c r="H28" s="1">
-        <x:v>250000</x:v>
+        <x:v>34890</x:v>
       </x:c>
       <x:c r="I28" s="1">
         <x:v>2026</x:v>
@@ -1721,10 +1727,10 @@
     </x:row>
     <x:row r="29" spans="1:10">
       <x:c r="A29" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
         <x:v>94</x:v>
@@ -1733,16 +1739,16 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F29" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="H29" s="1">
-        <x:v>400022</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="I29" s="1">
         <x:v>2026</x:v>
@@ -1759,22 +1765,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D30" s="1" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="D30" s="1" t="s">
+      <x:c r="E30" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F30" s="1" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="G30" s="1" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="E30" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="F30" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="G30" s="1" t="s">
-        <x:v>99</x:v>
-      </x:c>
       <x:c r="H30" s="1">
-        <x:v>12203100</x:v>
+        <x:v>400022</x:v>
       </x:c>
       <x:c r="I30" s="1">
         <x:v>2026</x:v>
@@ -1785,16 +1791,16 @@
     </x:row>
     <x:row r="31" spans="1:10">
       <x:c r="A31" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
         <x:v>32</x:v>
@@ -1803,10 +1809,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="H31" s="1">
-        <x:v>350000</x:v>
+        <x:v>12203100</x:v>
       </x:c>
       <x:c r="I31" s="1">
         <x:v>2026</x:v>
@@ -1817,28 +1823,28 @@
     </x:row>
     <x:row r="32" spans="1:10">
       <x:c r="A32" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D32" s="1" t="s">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="D32" s="1" t="s">
+      <x:c r="E32" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F32" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G32" s="1" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="E32" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F32" s="1" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="G32" s="1" t="s">
-        <x:v>102</x:v>
-      </x:c>
       <x:c r="H32" s="1">
-        <x:v>80948</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I32" s="1">
         <x:v>2026</x:v>
@@ -1849,28 +1855,28 @@
     </x:row>
     <x:row r="33" spans="1:10">
       <x:c r="A33" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="D33" s="1" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="D33" s="1" t="s">
+      <x:c r="E33" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F33" s="1" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="G33" s="1" t="s">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="E33" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="F33" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="G33" s="1" t="s">
-        <x:v>28</x:v>
-      </x:c>
       <x:c r="H33" s="1">
-        <x:v>221403</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="I33" s="1">
         <x:v>2026</x:v>
@@ -1881,10 +1887,10 @@
     </x:row>
     <x:row r="34" spans="1:10">
       <x:c r="A34" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
         <x:v>105</x:v>
@@ -1893,16 +1899,16 @@
         <x:v>106</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F34" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="H34" s="1">
-        <x:v>141263</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="I34" s="1">
         <x:v>2026</x:v>
@@ -1913,28 +1919,28 @@
     </x:row>
     <x:row r="35" spans="1:10">
       <x:c r="A35" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="D35" s="1" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="D35" s="1" t="s">
+      <x:c r="E35" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F35" s="1" t="s">
         <x:v>109</x:v>
-      </x:c>
-      <x:c r="E35" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="F35" s="1" t="s">
-        <x:v>33</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="H35" s="1">
-        <x:v>2250000</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="I35" s="1">
         <x:v>2026</x:v>
@@ -1963,10 +1969,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H36" s="1">
-        <x:v>350000</x:v>
+        <x:v>2250000</x:v>
       </x:c>
       <x:c r="I36" s="1">
         <x:v>2026</x:v>
@@ -1977,16 +1983,16 @@
     </x:row>
     <x:row r="37" spans="1:10">
       <x:c r="A37" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="D37" s="1" t="s">
         <x:v>113</x:v>
-      </x:c>
-      <x:c r="D37" s="1" t="s">
-        <x:v>114</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
         <x:v>32</x:v>
@@ -1995,10 +2001,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="H37" s="1">
-        <x:v>411748</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I37" s="1">
         <x:v>2026</x:v>
@@ -2009,28 +2015,28 @@
     </x:row>
     <x:row r="38" spans="1:10">
       <x:c r="A38" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="D38" s="1" t="s">
         <x:v>116</x:v>
       </x:c>
-      <x:c r="D38" s="1" t="s">
+      <x:c r="E38" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F38" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G38" s="1" t="s">
         <x:v>117</x:v>
       </x:c>
-      <x:c r="E38" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F38" s="1" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="G38" s="1" t="s">
-        <x:v>51</x:v>
-      </x:c>
       <x:c r="H38" s="1">
-        <x:v>105040</x:v>
+        <x:v>411748</x:v>
       </x:c>
       <x:c r="I38" s="1">
         <x:v>2026</x:v>
@@ -2041,10 +2047,10 @@
     </x:row>
     <x:row r="39" spans="1:10">
       <x:c r="A39" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
         <x:v>118</x:v>
@@ -2056,13 +2062,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F39" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H39" s="1">
-        <x:v>426280</x:v>
+        <x:v>105040</x:v>
       </x:c>
       <x:c r="I39" s="1">
         <x:v>2026</x:v>
@@ -2079,22 +2085,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="D40" s="1" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="D40" s="1" t="s">
+      <x:c r="E40" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F40" s="1" t="s">
         <x:v>122</x:v>
       </x:c>
-      <x:c r="E40" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F40" s="1" t="s">
-        <x:v>123</x:v>
-      </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H40" s="1">
-        <x:v>282975</x:v>
+        <x:v>426280</x:v>
       </x:c>
       <x:c r="I40" s="1">
         <x:v>2026</x:v>
@@ -2105,28 +2111,28 @@
     </x:row>
     <x:row r="41" spans="1:10">
       <x:c r="A41" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="D41" s="1" t="s">
         <x:v>124</x:v>
       </x:c>
-      <x:c r="D41" s="1" t="s">
+      <x:c r="E41" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F41" s="1" t="s">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="E41" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F41" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
       <x:c r="G41" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="H41" s="1">
-        <x:v>157560</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="I41" s="1">
         <x:v>2026</x:v>
@@ -2137,28 +2143,28 @@
     </x:row>
     <x:row r="42" spans="1:10">
       <x:c r="A42" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="D42" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
-      <x:c r="D42" s="1" t="s">
+      <x:c r="E42" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F42" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G42" s="1" t="s">
         <x:v>128</x:v>
       </x:c>
-      <x:c r="E42" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F42" s="1" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="G42" s="1" t="s">
-        <x:v>39</x:v>
-      </x:c>
       <x:c r="H42" s="1">
-        <x:v>771658</x:v>
+        <x:v>157560</x:v>
       </x:c>
       <x:c r="I42" s="1">
         <x:v>2026</x:v>
@@ -2169,10 +2175,10 @@
     </x:row>
     <x:row r="43" spans="1:10">
       <x:c r="A43" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
         <x:v>129</x:v>
@@ -2184,13 +2190,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F43" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H43" s="1">
-        <x:v>103020</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="I43" s="1">
         <x:v>2026</x:v>
@@ -2216,13 +2222,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F44" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H44" s="1">
-        <x:v>877913</x:v>
+        <x:v>103020</x:v>
       </x:c>
       <x:c r="I44" s="1">
         <x:v>2026</x:v>
@@ -2233,10 +2239,10 @@
     </x:row>
     <x:row r="45" spans="1:10">
       <x:c r="A45" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
         <x:v>133</x:v>
@@ -2248,13 +2254,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F45" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="H45" s="1">
-        <x:v>487317</x:v>
+        <x:v>877913</x:v>
       </x:c>
       <x:c r="I45" s="1">
         <x:v>2026</x:v>
@@ -2265,10 +2271,10 @@
     </x:row>
     <x:row r="46" spans="1:10">
       <x:c r="A46" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
         <x:v>135</x:v>
@@ -2280,13 +2286,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F46" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
-        <x:v>138</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="H46" s="1">
-        <x:v>300000</x:v>
+        <x:v>487317</x:v>
       </x:c>
       <x:c r="I46" s="1">
         <x:v>2026</x:v>
@@ -2297,33 +2303,65 @@
     </x:row>
     <x:row r="47" spans="1:10">
       <x:c r="A47" s="1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B47" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C47" s="1" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="D47" s="1" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="E47" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F47" s="1" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="G47" s="1" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="H47" s="1">
+        <x:v>300000</x:v>
+      </x:c>
+      <x:c r="I47" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J47" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:10">
+      <x:c r="A48" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="B47" s="1" t="s">
+      <x:c r="B48" s="1" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="C47" s="1" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="D47" s="1" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="E47" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F47" s="1" t="s">
+      <x:c r="C48" s="1" t="s">
         <x:v>137</x:v>
       </x:c>
-      <x:c r="G47" s="1" t="s">
+      <x:c r="D48" s="1" t="s">
         <x:v>138</x:v>
       </x:c>
-      <x:c r="H47" s="1">
+      <x:c r="E48" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F48" s="1" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="G48" s="1" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="H48" s="1">
         <x:v>1012628</x:v>
       </x:c>
-      <x:c r="I47" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J47" s="1" t="s">
+      <x:c r="I48" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J48" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -437,6 +437,15 @@
   </x:si>
   <x:si>
     <x:t>NY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>S6VA00093</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WARNER, MARK ROBERT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VA</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -507,8 +516,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J48" totalsRowShown="0">
-  <x:autoFilter ref="A1:J48"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J49" totalsRowShown="0">
+  <x:autoFilter ref="A1:J49"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -813,7 +822,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J48"/>
+  <x:dimension ref="A1:J49"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2365,6 +2374,38 @@
         <x:v>17</x:v>
       </x:c>
     </x:row>
+    <x:row r="49" spans="1:10">
+      <x:c r="A49" s="1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B49" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C49" s="1" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="D49" s="1" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="E49" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F49" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G49" s="1" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="H49" s="1">
+        <x:v>150000</x:v>
+      </x:c>
+      <x:c r="I49" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J49" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -136,6 +136,18 @@
     <x:t>TX</x:t>
   </x:si>
   <x:si>
+    <x:t>H0AL01055</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CARL, JERRY LEE, JR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AL</x:t>
+  </x:si>
+  <x:si>
     <x:t>S6GA00390</x:t>
   </x:si>
   <x:si>
@@ -166,9 +178,6 @@
     <x:t>DELBENE, SUZAN K</x:t>
   </x:si>
   <x:si>
-    <x:t>01</x:t>
-  </x:si>
-  <x:si>
     <x:t>WA</x:t>
   </x:si>
   <x:si>
@@ -317,9 +326,6 @@
   </x:si>
   <x:si>
     <x:t>MOORE, FELIX BARRY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AL</x:t>
   </x:si>
   <x:si>
     <x:t>H4NC14015</x:t>
@@ -516,8 +522,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J49" totalsRowShown="0">
-  <x:autoFilter ref="A1:J49"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J50" totalsRowShown="0">
+  <x:autoFilter ref="A1:J50"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -822,7 +828,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J49"/>
+  <x:dimension ref="A1:J50"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1064,10 +1070,10 @@
     </x:row>
     <x:row r="8" spans="1:10">
       <x:c r="A8" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
         <x:v>40</x:v>
@@ -1076,16 +1082,16 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F8" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="H8" s="1">
-        <x:v>350000</x:v>
+        <x:v>511942</x:v>
       </x:c>
       <x:c r="I8" s="1">
         <x:v>2026</x:v>
@@ -1096,28 +1102,28 @@
     </x:row>
     <x:row r="9" spans="1:10">
       <x:c r="A9" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F9" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H9" s="1">
-        <x:v>616386</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I9" s="1">
         <x:v>2026</x:v>
@@ -1128,28 +1134,28 @@
     </x:row>
     <x:row r="10" spans="1:10">
       <x:c r="A10" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F10" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H10" s="1">
-        <x:v>516368</x:v>
+        <x:v>616386</x:v>
       </x:c>
       <x:c r="I10" s="1">
         <x:v>2026</x:v>
@@ -1166,22 +1172,22 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F11" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="H11" s="1">
-        <x:v>113120</x:v>
+        <x:v>516368</x:v>
       </x:c>
       <x:c r="I11" s="1">
         <x:v>2026</x:v>
@@ -1207,77 +1213,77 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F12" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="H12" s="1">
-        <x:v>172296</x:v>
+        <x:v>113120</x:v>
       </x:c>
       <x:c r="I12" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J12" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:10">
       <x:c r="A13" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="H13" s="1">
-        <x:v>455146</x:v>
+        <x:v>172296</x:v>
       </x:c>
       <x:c r="I13" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J13" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:10">
       <x:c r="A14" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F14" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H14" s="1">
-        <x:v>300000</x:v>
+        <x:v>455146</x:v>
       </x:c>
       <x:c r="I14" s="1">
         <x:v>2026</x:v>
@@ -1288,10 +1294,10 @@
     </x:row>
     <x:row r="15" spans="1:10">
       <x:c r="A15" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
         <x:v>57</x:v>
@@ -1306,10 +1312,10 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H15" s="1">
-        <x:v>708827</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="I15" s="1">
         <x:v>2026</x:v>
@@ -1335,13 +1341,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F16" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H16" s="1">
-        <x:v>91656</x:v>
+        <x:v>708827</x:v>
       </x:c>
       <x:c r="I16" s="1">
         <x:v>2026</x:v>
@@ -1352,28 +1358,28 @@
     </x:row>
     <x:row r="17" spans="1:10">
       <x:c r="A17" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="D17" s="1" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="E17" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F17" s="1" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="D17" s="1" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="E17" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="F17" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H17" s="1">
-        <x:v>550000</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="I17" s="1">
         <x:v>2026</x:v>
@@ -1384,10 +1390,10 @@
     </x:row>
     <x:row r="18" spans="1:10">
       <x:c r="A18" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
         <x:v>65</x:v>
@@ -1405,7 +1411,7 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="H18" s="1">
-        <x:v>735613</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="I18" s="1">
         <x:v>2026</x:v>
@@ -1416,16 +1422,16 @@
     </x:row>
     <x:row r="19" spans="1:10">
       <x:c r="A19" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
         <x:v>32</x:v>
@@ -1434,10 +1440,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="H19" s="1">
-        <x:v>300000</x:v>
+        <x:v>735613</x:v>
       </x:c>
       <x:c r="I19" s="1">
         <x:v>2026</x:v>
@@ -1448,10 +1454,10 @@
     </x:row>
     <x:row r="20" spans="1:10">
       <x:c r="A20" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
         <x:v>68</x:v>
@@ -1460,16 +1466,16 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F20" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G20" s="1" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="G20" s="1" t="s">
-        <x:v>71</x:v>
-      </x:c>
       <x:c r="H20" s="1">
-        <x:v>418060</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="I20" s="1">
         <x:v>2026</x:v>
@@ -1486,22 +1492,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="D21" s="1" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="D21" s="1" t="s">
+      <x:c r="E21" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F21" s="1" t="s">
         <x:v>73</x:v>
-      </x:c>
-      <x:c r="E21" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F21" s="1" t="s">
-        <x:v>15</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
         <x:v>74</x:v>
       </x:c>
       <x:c r="H21" s="1">
-        <x:v>511996</x:v>
+        <x:v>418060</x:v>
       </x:c>
       <x:c r="I21" s="1">
         <x:v>2026</x:v>
@@ -1527,13 +1533,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F22" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="H22" s="1">
-        <x:v>430866</x:v>
+        <x:v>511996</x:v>
       </x:c>
       <x:c r="I22" s="1">
         <x:v>2026</x:v>
@@ -1550,19 +1556,19 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F23" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H23" s="1">
         <x:v>430866</x:v>
@@ -1576,28 +1582,28 @@
     </x:row>
     <x:row r="24" spans="1:10">
       <x:c r="A24" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F24" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H24" s="1">
-        <x:v>350000</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="I24" s="1">
         <x:v>2026</x:v>
@@ -1608,10 +1614,10 @@
     </x:row>
     <x:row r="25" spans="1:10">
       <x:c r="A25" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
         <x:v>82</x:v>
@@ -1620,16 +1626,16 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F25" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="H25" s="1">
-        <x:v>441577</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I25" s="1">
         <x:v>2026</x:v>
@@ -1640,42 +1646,42 @@
     </x:row>
     <x:row r="26" spans="1:10">
       <x:c r="A26" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F26" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="H26" s="1">
-        <x:v>215160</x:v>
+        <x:v>506917</x:v>
       </x:c>
       <x:c r="I26" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J26" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:10">
       <x:c r="A27" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
         <x:v>87</x:v>
@@ -1690,24 +1696,24 @@
         <x:v>89</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="H27" s="1">
-        <x:v>461943</x:v>
+        <x:v>215160</x:v>
       </x:c>
       <x:c r="I27" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J27" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:10">
       <x:c r="A28" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
         <x:v>90</x:v>
@@ -1722,10 +1728,10 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H28" s="1">
-        <x:v>34890</x:v>
+        <x:v>461943</x:v>
       </x:c>
       <x:c r="I28" s="1">
         <x:v>2026</x:v>
@@ -1736,28 +1742,28 @@
     </x:row>
     <x:row r="29" spans="1:10">
       <x:c r="A29" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="D29" s="1" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="D29" s="1" t="s">
+      <x:c r="E29" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F29" s="1" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="E29" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="F29" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="H29" s="1">
-        <x:v>250000</x:v>
+        <x:v>34890</x:v>
       </x:c>
       <x:c r="I29" s="1">
         <x:v>2026</x:v>
@@ -1768,28 +1774,28 @@
     </x:row>
     <x:row r="30" spans="1:10">
       <x:c r="A30" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F30" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="H30" s="1">
-        <x:v>400022</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="I30" s="1">
         <x:v>2026</x:v>
@@ -1812,16 +1818,16 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F31" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
         <x:v>101</x:v>
       </x:c>
       <x:c r="H31" s="1">
-        <x:v>12203100</x:v>
+        <x:v>400022</x:v>
       </x:c>
       <x:c r="I31" s="1">
         <x:v>2026</x:v>
@@ -1832,16 +1838,16 @@
     </x:row>
     <x:row r="32" spans="1:10">
       <x:c r="A32" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
         <x:v>32</x:v>
@@ -1850,10 +1856,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="H32" s="1">
-        <x:v>350000</x:v>
+        <x:v>12203100</x:v>
       </x:c>
       <x:c r="I32" s="1">
         <x:v>2026</x:v>
@@ -1864,10 +1870,10 @@
     </x:row>
     <x:row r="33" spans="1:10">
       <x:c r="A33" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
         <x:v>102</x:v>
@@ -1876,16 +1882,16 @@
         <x:v>103</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F33" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="H33" s="1">
-        <x:v>80948</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I33" s="1">
         <x:v>2026</x:v>
@@ -1896,28 +1902,28 @@
     </x:row>
     <x:row r="34" spans="1:10">
       <x:c r="A34" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="D34" s="1" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="D34" s="1" t="s">
+      <x:c r="E34" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F34" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="G34" s="1" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="E34" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="F34" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="G34" s="1" t="s">
-        <x:v>28</x:v>
-      </x:c>
       <x:c r="H34" s="1">
-        <x:v>221403</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="I34" s="1">
         <x:v>2026</x:v>
@@ -1928,10 +1934,10 @@
     </x:row>
     <x:row r="35" spans="1:10">
       <x:c r="A35" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
         <x:v>107</x:v>
@@ -1940,16 +1946,16 @@
         <x:v>108</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F35" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="H35" s="1">
-        <x:v>141263</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="I35" s="1">
         <x:v>2026</x:v>
@@ -1960,28 +1966,28 @@
     </x:row>
     <x:row r="36" spans="1:10">
       <x:c r="A36" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="D36" s="1" t="s">
         <x:v>110</x:v>
       </x:c>
-      <x:c r="D36" s="1" t="s">
+      <x:c r="E36" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F36" s="1" t="s">
         <x:v>111</x:v>
-      </x:c>
-      <x:c r="E36" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="F36" s="1" t="s">
-        <x:v>33</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="H36" s="1">
-        <x:v>2250000</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="I36" s="1">
         <x:v>2026</x:v>
@@ -2010,10 +2016,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H37" s="1">
-        <x:v>350000</x:v>
+        <x:v>2250000</x:v>
       </x:c>
       <x:c r="I37" s="1">
         <x:v>2026</x:v>
@@ -2024,16 +2030,16 @@
     </x:row>
     <x:row r="38" spans="1:10">
       <x:c r="A38" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="D38" s="1" t="s">
         <x:v>115</x:v>
-      </x:c>
-      <x:c r="D38" s="1" t="s">
-        <x:v>116</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
         <x:v>32</x:v>
@@ -2042,10 +2048,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H38" s="1">
-        <x:v>411748</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I38" s="1">
         <x:v>2026</x:v>
@@ -2056,28 +2062,28 @@
     </x:row>
     <x:row r="39" spans="1:10">
       <x:c r="A39" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="D39" s="1" t="s">
         <x:v>118</x:v>
       </x:c>
-      <x:c r="D39" s="1" t="s">
+      <x:c r="E39" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F39" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G39" s="1" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="E39" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F39" s="1" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="G39" s="1" t="s">
-        <x:v>51</x:v>
-      </x:c>
       <x:c r="H39" s="1">
-        <x:v>105040</x:v>
+        <x:v>411748</x:v>
       </x:c>
       <x:c r="I39" s="1">
         <x:v>2026</x:v>
@@ -2088,10 +2094,10 @@
     </x:row>
     <x:row r="40" spans="1:10">
       <x:c r="A40" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
         <x:v>120</x:v>
@@ -2103,13 +2109,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F40" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="H40" s="1">
-        <x:v>426280</x:v>
+        <x:v>105040</x:v>
       </x:c>
       <x:c r="I40" s="1">
         <x:v>2026</x:v>
@@ -2126,22 +2132,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="D41" s="1" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="D41" s="1" t="s">
+      <x:c r="E41" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F41" s="1" t="s">
         <x:v>124</x:v>
       </x:c>
-      <x:c r="E41" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F41" s="1" t="s">
-        <x:v>125</x:v>
-      </x:c>
       <x:c r="G41" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H41" s="1">
-        <x:v>282975</x:v>
+        <x:v>426280</x:v>
       </x:c>
       <x:c r="I41" s="1">
         <x:v>2026</x:v>
@@ -2152,28 +2158,28 @@
     </x:row>
     <x:row r="42" spans="1:10">
       <x:c r="A42" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="D42" s="1" t="s">
         <x:v>126</x:v>
       </x:c>
-      <x:c r="D42" s="1" t="s">
+      <x:c r="E42" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F42" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
-      <x:c r="E42" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F42" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
       <x:c r="G42" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H42" s="1">
-        <x:v>157560</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="I42" s="1">
         <x:v>2026</x:v>
@@ -2184,28 +2190,28 @@
     </x:row>
     <x:row r="43" spans="1:10">
       <x:c r="A43" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="D43" s="1" t="s">
         <x:v>129</x:v>
       </x:c>
-      <x:c r="D43" s="1" t="s">
+      <x:c r="E43" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F43" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G43" s="1" t="s">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="E43" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F43" s="1" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="G43" s="1" t="s">
-        <x:v>39</x:v>
-      </x:c>
       <x:c r="H43" s="1">
-        <x:v>771658</x:v>
+        <x:v>157560</x:v>
       </x:c>
       <x:c r="I43" s="1">
         <x:v>2026</x:v>
@@ -2216,10 +2222,10 @@
     </x:row>
     <x:row r="44" spans="1:10">
       <x:c r="A44" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
         <x:v>131</x:v>
@@ -2231,13 +2237,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F44" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H44" s="1">
-        <x:v>103020</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="I44" s="1">
         <x:v>2026</x:v>
@@ -2263,13 +2269,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F45" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="H45" s="1">
-        <x:v>877913</x:v>
+        <x:v>103020</x:v>
       </x:c>
       <x:c r="I45" s="1">
         <x:v>2026</x:v>
@@ -2280,10 +2286,10 @@
     </x:row>
     <x:row r="46" spans="1:10">
       <x:c r="A46" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
         <x:v>135</x:v>
@@ -2295,13 +2301,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F46" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="H46" s="1">
-        <x:v>487317</x:v>
+        <x:v>1762153</x:v>
       </x:c>
       <x:c r="I46" s="1">
         <x:v>2026</x:v>
@@ -2312,10 +2318,10 @@
     </x:row>
     <x:row r="47" spans="1:10">
       <x:c r="A47" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
         <x:v>137</x:v>
@@ -2327,13 +2333,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F47" s="1" t="s">
-        <x:v>139</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
-        <x:v>140</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H47" s="1">
-        <x:v>300000</x:v>
+        <x:v>487317</x:v>
       </x:c>
       <x:c r="I47" s="1">
         <x:v>2026</x:v>
@@ -2344,28 +2350,28 @@
     </x:row>
     <x:row r="48" spans="1:10">
       <x:c r="A48" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>138</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F48" s="1" t="s">
-        <x:v>139</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
-        <x:v>140</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="H48" s="1">
-        <x:v>1012628</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="I48" s="1">
         <x:v>2026</x:v>
@@ -2376,33 +2382,65 @@
     </x:row>
     <x:row r="49" spans="1:10">
       <x:c r="A49" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B49" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C49" s="1" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="D49" s="1" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="E49" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F49" s="1" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="G49" s="1" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="H49" s="1">
+        <x:v>1012628</x:v>
+      </x:c>
+      <x:c r="I49" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J49" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:10">
+      <x:c r="A50" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="B49" s="1" t="s">
+      <x:c r="B50" s="1" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="C49" s="1" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="D49" s="1" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="E49" s="1" t="s">
+      <x:c r="C50" s="1" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="D50" s="1" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="E50" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="F49" s="1" t="s">
+      <x:c r="F50" s="1" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="G49" s="1" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="H49" s="1">
+      <x:c r="G50" s="1" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="H50" s="1">
         <x:v>150000</x:v>
       </x:c>
-      <x:c r="I49" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J49" s="1" t="s">
+      <x:c r="I50" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J50" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -1699,7 +1699,7 @@
         <x:v>77</x:v>
       </x:c>
       <x:c r="H27" s="1">
-        <x:v>215160</x:v>
+        <x:v>268690</x:v>
       </x:c>
       <x:c r="I27" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -187,6 +187,18 @@
     <x:t>DUNN, HARRY</x:t>
   </x:si>
   <x:si>
+    <x:t>H2FL14053</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FRANKEL, LOIS J.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FL</x:t>
+  </x:si>
+  <x:si>
     <x:t>H0GA14030</x:t>
   </x:si>
   <x:si>
@@ -347,9 +359,6 @@
   </x:si>
   <x:si>
     <x:t>NEHLS, TREVER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22</x:t>
   </x:si>
   <x:si>
     <x:t>S6TX00388</x:t>
@@ -522,8 +531,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J50" totalsRowShown="0">
-  <x:autoFilter ref="A1:J50"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J51" totalsRowShown="0">
+  <x:autoFilter ref="A1:J51"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -828,7 +837,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J50"/>
+  <x:dimension ref="A1:J51"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1262,10 +1271,10 @@
     </x:row>
     <x:row r="14" spans="1:10">
       <x:c r="A14" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
         <x:v>57</x:v>
@@ -1280,10 +1289,10 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H14" s="1">
-        <x:v>455146</x:v>
+        <x:v>50571</x:v>
       </x:c>
       <x:c r="I14" s="1">
         <x:v>2026</x:v>
@@ -1294,28 +1303,28 @@
     </x:row>
     <x:row r="15" spans="1:10">
       <x:c r="A15" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F15" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
         <x:v>46</x:v>
       </x:c>
       <x:c r="H15" s="1">
-        <x:v>300000</x:v>
+        <x:v>455146</x:v>
       </x:c>
       <x:c r="I15" s="1">
         <x:v>2026</x:v>
@@ -1326,28 +1335,28 @@
     </x:row>
     <x:row r="16" spans="1:10">
       <x:c r="A16" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F16" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
         <x:v>46</x:v>
       </x:c>
       <x:c r="H16" s="1">
-        <x:v>708827</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="I16" s="1">
         <x:v>2026</x:v>
@@ -1364,22 +1373,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F17" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H17" s="1">
-        <x:v>91656</x:v>
+        <x:v>708827</x:v>
       </x:c>
       <x:c r="I17" s="1">
         <x:v>2026</x:v>
@@ -1390,28 +1399,28 @@
     </x:row>
     <x:row r="18" spans="1:10">
       <x:c r="A18" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="E18" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F18" s="1" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="E18" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="F18" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H18" s="1">
-        <x:v>550000</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="I18" s="1">
         <x:v>2026</x:v>
@@ -1422,16 +1431,16 @@
     </x:row>
     <x:row r="19" spans="1:10">
       <x:c r="A19" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
         <x:v>32</x:v>
@@ -1440,10 +1449,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="H19" s="1">
-        <x:v>735613</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="I19" s="1">
         <x:v>2026</x:v>
@@ -1454,16 +1463,16 @@
     </x:row>
     <x:row r="20" spans="1:10">
       <x:c r="A20" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
         <x:v>32</x:v>
@@ -1472,10 +1481,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="H20" s="1">
-        <x:v>300000</x:v>
+        <x:v>735613</x:v>
       </x:c>
       <x:c r="I20" s="1">
         <x:v>2026</x:v>
@@ -1486,28 +1495,28 @@
     </x:row>
     <x:row r="21" spans="1:10">
       <x:c r="A21" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F21" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
         <x:v>74</x:v>
       </x:c>
       <x:c r="H21" s="1">
-        <x:v>418060</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="I21" s="1">
         <x:v>2026</x:v>
@@ -1533,13 +1542,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F22" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="H22" s="1">
-        <x:v>511996</x:v>
+        <x:v>418060</x:v>
       </x:c>
       <x:c r="I22" s="1">
         <x:v>2026</x:v>
@@ -1556,22 +1565,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F23" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="H23" s="1">
-        <x:v>430866</x:v>
+        <x:v>511996</x:v>
       </x:c>
       <x:c r="I23" s="1">
         <x:v>2026</x:v>
@@ -1588,10 +1597,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
         <x:v>14</x:v>
@@ -1614,28 +1623,28 @@
     </x:row>
     <x:row r="25" spans="1:10">
       <x:c r="A25" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F25" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H25" s="1">
-        <x:v>350000</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="I25" s="1">
         <x:v>2026</x:v>
@@ -1646,28 +1655,28 @@
     </x:row>
     <x:row r="26" spans="1:10">
       <x:c r="A26" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F26" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="H26" s="1">
-        <x:v>506917</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I26" s="1">
         <x:v>2026</x:v>
@@ -1678,92 +1687,92 @@
     </x:row>
     <x:row r="27" spans="1:10">
       <x:c r="A27" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F27" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="H27" s="1">
-        <x:v>268690</x:v>
+        <x:v>506917</x:v>
       </x:c>
       <x:c r="I27" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J27" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:10">
       <x:c r="A28" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F28" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="H28" s="1">
-        <x:v>461943</x:v>
+        <x:v>268690</x:v>
       </x:c>
       <x:c r="I28" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J28" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:10">
       <x:c r="A29" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F29" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H29" s="1">
-        <x:v>34890</x:v>
+        <x:v>461943</x:v>
       </x:c>
       <x:c r="I29" s="1">
         <x:v>2026</x:v>
@@ -1774,10 +1783,10 @@
     </x:row>
     <x:row r="30" spans="1:10">
       <x:c r="A30" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
         <x:v>97</x:v>
@@ -1786,16 +1795,16 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F30" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="H30" s="1">
-        <x:v>250000</x:v>
+        <x:v>34890</x:v>
       </x:c>
       <x:c r="I30" s="1">
         <x:v>2026</x:v>
@@ -1806,28 +1815,28 @@
     </x:row>
     <x:row r="31" spans="1:10">
       <x:c r="A31" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F31" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="H31" s="1">
-        <x:v>400022</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="I31" s="1">
         <x:v>2026</x:v>
@@ -1844,22 +1853,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F32" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="H32" s="1">
-        <x:v>12203100</x:v>
+        <x:v>400022</x:v>
       </x:c>
       <x:c r="I32" s="1">
         <x:v>2026</x:v>
@@ -1870,16 +1879,16 @@
     </x:row>
     <x:row r="33" spans="1:10">
       <x:c r="A33" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
         <x:v>32</x:v>
@@ -1891,7 +1900,7 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="H33" s="1">
-        <x:v>350000</x:v>
+        <x:v>12203100</x:v>
       </x:c>
       <x:c r="I33" s="1">
         <x:v>2026</x:v>
@@ -1902,28 +1911,28 @@
     </x:row>
     <x:row r="34" spans="1:10">
       <x:c r="A34" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F34" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="H34" s="1">
-        <x:v>80948</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I34" s="1">
         <x:v>2026</x:v>
@@ -1934,28 +1943,28 @@
     </x:row>
     <x:row r="35" spans="1:10">
       <x:c r="A35" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F35" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="H35" s="1">
-        <x:v>221403</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="I35" s="1">
         <x:v>2026</x:v>
@@ -1966,28 +1975,28 @@
     </x:row>
     <x:row r="36" spans="1:10">
       <x:c r="A36" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F36" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="H36" s="1">
-        <x:v>141263</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="I36" s="1">
         <x:v>2026</x:v>
@@ -1998,28 +2007,28 @@
     </x:row>
     <x:row r="37" spans="1:10">
       <x:c r="A37" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F37" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="H37" s="1">
-        <x:v>2250000</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="I37" s="1">
         <x:v>2026</x:v>
@@ -2036,10 +2045,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
         <x:v>32</x:v>
@@ -2048,10 +2057,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H38" s="1">
-        <x:v>350000</x:v>
+        <x:v>2250000</x:v>
       </x:c>
       <x:c r="I38" s="1">
         <x:v>2026</x:v>
@@ -2062,10 +2071,10 @@
     </x:row>
     <x:row r="39" spans="1:10">
       <x:c r="A39" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
         <x:v>117</x:v>
@@ -2083,7 +2092,7 @@
         <x:v>119</x:v>
       </x:c>
       <x:c r="H39" s="1">
-        <x:v>411748</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I39" s="1">
         <x:v>2026</x:v>
@@ -2094,10 +2103,10 @@
     </x:row>
     <x:row r="40" spans="1:10">
       <x:c r="A40" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
         <x:v>120</x:v>
@@ -2106,16 +2115,16 @@
         <x:v>121</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F40" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="H40" s="1">
-        <x:v>105040</x:v>
+        <x:v>411748</x:v>
       </x:c>
       <x:c r="I40" s="1">
         <x:v>2026</x:v>
@@ -2126,28 +2135,28 @@
     </x:row>
     <x:row r="41" spans="1:10">
       <x:c r="A41" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F41" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="H41" s="1">
-        <x:v>426280</x:v>
+        <x:v>105040</x:v>
       </x:c>
       <x:c r="I41" s="1">
         <x:v>2026</x:v>
@@ -2176,10 +2185,10 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H42" s="1">
-        <x:v>282975</x:v>
+        <x:v>426280</x:v>
       </x:c>
       <x:c r="I42" s="1">
         <x:v>2026</x:v>
@@ -2190,10 +2199,10 @@
     </x:row>
     <x:row r="43" spans="1:10">
       <x:c r="A43" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
         <x:v>128</x:v>
@@ -2205,13 +2214,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F43" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="H43" s="1">
-        <x:v>157560</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="I43" s="1">
         <x:v>2026</x:v>
@@ -2222,10 +2231,10 @@
     </x:row>
     <x:row r="44" spans="1:10">
       <x:c r="A44" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
         <x:v>131</x:v>
@@ -2237,13 +2246,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F44" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="H44" s="1">
-        <x:v>771658</x:v>
+        <x:v>157560</x:v>
       </x:c>
       <x:c r="I44" s="1">
         <x:v>2026</x:v>
@@ -2254,28 +2263,28 @@
     </x:row>
     <x:row r="45" spans="1:10">
       <x:c r="A45" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F45" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H45" s="1">
-        <x:v>103020</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="I45" s="1">
         <x:v>2026</x:v>
@@ -2292,22 +2301,22 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F46" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="H46" s="1">
-        <x:v>1762153</x:v>
+        <x:v>103020</x:v>
       </x:c>
       <x:c r="I46" s="1">
         <x:v>2026</x:v>
@@ -2318,28 +2327,28 @@
     </x:row>
     <x:row r="47" spans="1:10">
       <x:c r="A47" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>138</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F47" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="H47" s="1">
-        <x:v>487317</x:v>
+        <x:v>1762153</x:v>
       </x:c>
       <x:c r="I47" s="1">
         <x:v>2026</x:v>
@@ -2350,28 +2359,28 @@
     </x:row>
     <x:row r="48" spans="1:10">
       <x:c r="A48" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F48" s="1" t="s">
-        <x:v>141</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="H48" s="1">
-        <x:v>300000</x:v>
+        <x:v>487317</x:v>
       </x:c>
       <x:c r="I48" s="1">
         <x:v>2026</x:v>
@@ -2382,28 +2391,28 @@
     </x:row>
     <x:row r="49" spans="1:10">
       <x:c r="A49" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>139</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>140</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F49" s="1" t="s">
-        <x:v>141</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="H49" s="1">
-        <x:v>1012628</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="I49" s="1">
         <x:v>2026</x:v>
@@ -2414,33 +2423,65 @@
     </x:row>
     <x:row r="50" spans="1:10">
       <x:c r="A50" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="D50" s="1" t="s">
         <x:v>143</x:v>
       </x:c>
-      <x:c r="D50" s="1" t="s">
+      <x:c r="E50" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F50" s="1" t="s">
         <x:v>144</x:v>
-      </x:c>
-      <x:c r="E50" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="F50" s="1" t="s">
-        <x:v>33</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
         <x:v>145</x:v>
       </x:c>
       <x:c r="H50" s="1">
+        <x:v>1012628</x:v>
+      </x:c>
+      <x:c r="I50" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J50" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:10">
+      <x:c r="A51" s="1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B51" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C51" s="1" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="D51" s="1" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="E51" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F51" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G51" s="1" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="H51" s="1">
         <x:v>150000</x:v>
       </x:c>
-      <x:c r="I50" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J50" s="1" t="s">
+      <x:c r="I51" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J51" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -118,6 +118,15 @@
     <x:t>00</x:t>
   </x:si>
   <x:si>
+    <x:t>H2AK01083</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BEGICH, NICHOLAS III</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AK</x:t>
+  </x:si>
+  <x:si>
     <x:t>H6MD05321</x:t>
   </x:si>
   <x:si>
@@ -230,6 +239,15 @@
   </x:si>
   <x:si>
     <x:t>SC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>S6WY00209</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HAGEMAN, HARRIET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WY</x:t>
   </x:si>
   <x:si>
     <x:t>S6OK04247</x:t>
@@ -531,8 +549,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J51" totalsRowShown="0">
-  <x:autoFilter ref="A1:J51"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J53" totalsRowShown="0">
+  <x:autoFilter ref="A1:J53"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -837,7 +855,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J51"/>
+  <x:dimension ref="A1:J53"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1015,10 +1033,10 @@
     </x:row>
     <x:row r="6" spans="1:10">
       <x:c r="A6" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
         <x:v>34</x:v>
@@ -1030,13 +1048,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F6" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G6" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="H6" s="1">
-        <x:v>1965632</x:v>
+        <x:v>508142</x:v>
       </x:c>
       <x:c r="I6" s="1">
         <x:v>2026</x:v>
@@ -1047,28 +1065,28 @@
     </x:row>
     <x:row r="7" spans="1:10">
       <x:c r="A7" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F7" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="H7" s="1">
-        <x:v>348433</x:v>
+        <x:v>1965632</x:v>
       </x:c>
       <x:c r="I7" s="1">
         <x:v>2026</x:v>
@@ -1085,22 +1103,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D8" s="1" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D8" s="1" t="s">
+      <x:c r="E8" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F8" s="1" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="E8" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F8" s="1" t="s">
+      <x:c r="G8" s="1" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="G8" s="1" t="s">
-        <x:v>43</x:v>
-      </x:c>
       <x:c r="H8" s="1">
-        <x:v>511942</x:v>
+        <x:v>348433</x:v>
       </x:c>
       <x:c r="I8" s="1">
         <x:v>2026</x:v>
@@ -1111,28 +1129,28 @@
     </x:row>
     <x:row r="9" spans="1:10">
       <x:c r="A9" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="D9" s="1" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="D9" s="1" t="s">
+      <x:c r="E9" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F9" s="1" t="s">
         <x:v>45</x:v>
-      </x:c>
-      <x:c r="E9" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="F9" s="1" t="s">
-        <x:v>33</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
         <x:v>46</x:v>
       </x:c>
       <x:c r="H9" s="1">
-        <x:v>350000</x:v>
+        <x:v>547042</x:v>
       </x:c>
       <x:c r="I9" s="1">
         <x:v>2026</x:v>
@@ -1143,10 +1161,10 @@
     </x:row>
     <x:row r="10" spans="1:10">
       <x:c r="A10" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
         <x:v>47</x:v>
@@ -1155,16 +1173,16 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F10" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G10" s="1" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="G10" s="1" t="s">
-        <x:v>39</x:v>
-      </x:c>
       <x:c r="H10" s="1">
-        <x:v>616386</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I10" s="1">
         <x:v>2026</x:v>
@@ -1175,10 +1193,10 @@
     </x:row>
     <x:row r="11" spans="1:10">
       <x:c r="A11" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
         <x:v>50</x:v>
@@ -1190,13 +1208,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F11" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H11" s="1">
-        <x:v>516368</x:v>
+        <x:v>616386</x:v>
       </x:c>
       <x:c r="I11" s="1">
         <x:v>2026</x:v>
@@ -1213,22 +1231,22 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F12" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="H12" s="1">
-        <x:v>113120</x:v>
+        <x:v>516368</x:v>
       </x:c>
       <x:c r="I12" s="1">
         <x:v>2026</x:v>
@@ -1254,19 +1272,19 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H13" s="1">
-        <x:v>172296</x:v>
+        <x:v>113120</x:v>
       </x:c>
       <x:c r="I13" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J13" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:10">
@@ -1277,54 +1295,54 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F14" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="H14" s="1">
-        <x:v>50571</x:v>
+        <x:v>172296</x:v>
       </x:c>
       <x:c r="I14" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J14" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:10">
       <x:c r="A15" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="D15" s="1" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="D15" s="1" t="s">
+      <x:c r="E15" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F15" s="1" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="E15" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F15" s="1" t="s">
+      <x:c r="G15" s="1" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="G15" s="1" t="s">
-        <x:v>46</x:v>
-      </x:c>
       <x:c r="H15" s="1">
-        <x:v>455146</x:v>
+        <x:v>50571</x:v>
       </x:c>
       <x:c r="I15" s="1">
         <x:v>2026</x:v>
@@ -1335,28 +1353,28 @@
     </x:row>
     <x:row r="16" spans="1:10">
       <x:c r="A16" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F16" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="H16" s="1">
-        <x:v>300000</x:v>
+        <x:v>455146</x:v>
       </x:c>
       <x:c r="I16" s="1">
         <x:v>2026</x:v>
@@ -1367,10 +1385,10 @@
     </x:row>
     <x:row r="17" spans="1:10">
       <x:c r="A17" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
         <x:v>64</x:v>
@@ -1385,10 +1403,10 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="H17" s="1">
-        <x:v>708827</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="I17" s="1">
         <x:v>2026</x:v>
@@ -1414,13 +1432,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F18" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="H18" s="1">
-        <x:v>91656</x:v>
+        <x:v>708827</x:v>
       </x:c>
       <x:c r="I18" s="1">
         <x:v>2026</x:v>
@@ -1431,28 +1449,28 @@
     </x:row>
     <x:row r="19" spans="1:10">
       <x:c r="A19" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="D19" s="1" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="E19" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F19" s="1" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="D19" s="1" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="E19" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="F19" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H19" s="1">
-        <x:v>550000</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="I19" s="1">
         <x:v>2026</x:v>
@@ -1463,10 +1481,10 @@
     </x:row>
     <x:row r="20" spans="1:10">
       <x:c r="A20" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
         <x:v>72</x:v>
@@ -1484,7 +1502,7 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="H20" s="1">
-        <x:v>735613</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="I20" s="1">
         <x:v>2026</x:v>
@@ -1495,16 +1513,16 @@
     </x:row>
     <x:row r="21" spans="1:10">
       <x:c r="A21" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
         <x:v>32</x:v>
@@ -1513,10 +1531,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="H21" s="1">
-        <x:v>300000</x:v>
+        <x:v>515838</x:v>
       </x:c>
       <x:c r="I21" s="1">
         <x:v>2026</x:v>
@@ -1533,22 +1551,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F22" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="H22" s="1">
-        <x:v>418060</x:v>
+        <x:v>735613</x:v>
       </x:c>
       <x:c r="I22" s="1">
         <x:v>2026</x:v>
@@ -1559,28 +1577,28 @@
     </x:row>
     <x:row r="23" spans="1:10">
       <x:c r="A23" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="D23" s="1" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="D23" s="1" t="s">
+      <x:c r="E23" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F23" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G23" s="1" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="E23" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F23" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G23" s="1" t="s">
-        <x:v>81</x:v>
-      </x:c>
       <x:c r="H23" s="1">
-        <x:v>511996</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="I23" s="1">
         <x:v>2026</x:v>
@@ -1597,22 +1615,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="D24" s="1" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="D24" s="1" t="s">
+      <x:c r="E24" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F24" s="1" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="E24" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F24" s="1" t="s">
-        <x:v>42</x:v>
-      </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="H24" s="1">
-        <x:v>430866</x:v>
+        <x:v>418060</x:v>
       </x:c>
       <x:c r="I24" s="1">
         <x:v>2026</x:v>
@@ -1629,22 +1647,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F25" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="H25" s="1">
-        <x:v>430866</x:v>
+        <x:v>511996</x:v>
       </x:c>
       <x:c r="I25" s="1">
         <x:v>2026</x:v>
@@ -1655,28 +1673,28 @@
     </x:row>
     <x:row r="26" spans="1:10">
       <x:c r="A26" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F26" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="H26" s="1">
-        <x:v>350000</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="I26" s="1">
         <x:v>2026</x:v>
@@ -1693,22 +1711,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F27" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="H27" s="1">
-        <x:v>506917</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="I27" s="1">
         <x:v>2026</x:v>
@@ -1719,34 +1737,34 @@
     </x:row>
     <x:row r="28" spans="1:10">
       <x:c r="A28" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F28" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="H28" s="1">
-        <x:v>268690</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I28" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J28" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:10">
@@ -1757,22 +1775,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F29" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H29" s="1">
-        <x:v>461943</x:v>
+        <x:v>506917</x:v>
       </x:c>
       <x:c r="I29" s="1">
         <x:v>2026</x:v>
@@ -1801,42 +1819,42 @@
         <x:v>99</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="H30" s="1">
-        <x:v>34890</x:v>
+        <x:v>268690</x:v>
       </x:c>
       <x:c r="I30" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J30" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:10">
       <x:c r="A31" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D31" s="1" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="D31" s="1" t="s">
+      <x:c r="E31" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F31" s="1" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="E31" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="F31" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H31" s="1">
-        <x:v>250000</x:v>
+        <x:v>461943</x:v>
       </x:c>
       <x:c r="I31" s="1">
         <x:v>2026</x:v>
@@ -1847,10 +1865,10 @@
     </x:row>
     <x:row r="32" spans="1:10">
       <x:c r="A32" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
         <x:v>103</x:v>
@@ -1862,13 +1880,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F32" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="H32" s="1">
-        <x:v>400022</x:v>
+        <x:v>34890</x:v>
       </x:c>
       <x:c r="I32" s="1">
         <x:v>2026</x:v>
@@ -1879,16 +1897,16 @@
     </x:row>
     <x:row r="33" spans="1:10">
       <x:c r="A33" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
         <x:v>32</x:v>
@@ -1897,10 +1915,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="H33" s="1">
-        <x:v>12203100</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="I33" s="1">
         <x:v>2026</x:v>
@@ -1911,28 +1929,28 @@
     </x:row>
     <x:row r="34" spans="1:10">
       <x:c r="A34" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F34" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="H34" s="1">
-        <x:v>350000</x:v>
+        <x:v>400022</x:v>
       </x:c>
       <x:c r="I34" s="1">
         <x:v>2026</x:v>
@@ -1949,22 +1967,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F35" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H35" s="1">
-        <x:v>80948</x:v>
+        <x:v>12203100</x:v>
       </x:c>
       <x:c r="I35" s="1">
         <x:v>2026</x:v>
@@ -1981,10 +1999,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
         <x:v>32</x:v>
@@ -1993,10 +2011,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H36" s="1">
-        <x:v>221403</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I36" s="1">
         <x:v>2026</x:v>
@@ -2013,22 +2031,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F37" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H37" s="1">
-        <x:v>141263</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="I37" s="1">
         <x:v>2026</x:v>
@@ -2045,10 +2063,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
         <x:v>32</x:v>
@@ -2057,10 +2075,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="H38" s="1">
-        <x:v>2250000</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="I38" s="1">
         <x:v>2026</x:v>
@@ -2071,28 +2089,28 @@
     </x:row>
     <x:row r="39" spans="1:10">
       <x:c r="A39" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F39" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H39" s="1">
-        <x:v>350000</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="I39" s="1">
         <x:v>2026</x:v>
@@ -2103,16 +2121,16 @@
     </x:row>
     <x:row r="40" spans="1:10">
       <x:c r="A40" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
         <x:v>32</x:v>
@@ -2121,10 +2139,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H40" s="1">
-        <x:v>411748</x:v>
+        <x:v>2250000</x:v>
       </x:c>
       <x:c r="I40" s="1">
         <x:v>2026</x:v>
@@ -2135,10 +2153,10 @@
     </x:row>
     <x:row r="41" spans="1:10">
       <x:c r="A41" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
         <x:v>123</x:v>
@@ -2147,16 +2165,16 @@
         <x:v>124</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F41" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="H41" s="1">
-        <x:v>105040</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I41" s="1">
         <x:v>2026</x:v>
@@ -2173,22 +2191,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F42" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="H42" s="1">
-        <x:v>426280</x:v>
+        <x:v>411748</x:v>
       </x:c>
       <x:c r="I42" s="1">
         <x:v>2026</x:v>
@@ -2199,28 +2217,28 @@
     </x:row>
     <x:row r="43" spans="1:10">
       <x:c r="A43" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F43" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H43" s="1">
-        <x:v>282975</x:v>
+        <x:v>105040</x:v>
       </x:c>
       <x:c r="I43" s="1">
         <x:v>2026</x:v>
@@ -2231,10 +2249,10 @@
     </x:row>
     <x:row r="44" spans="1:10">
       <x:c r="A44" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
         <x:v>131</x:v>
@@ -2246,13 +2264,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F44" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H44" s="1">
-        <x:v>157560</x:v>
+        <x:v>426280</x:v>
       </x:c>
       <x:c r="I44" s="1">
         <x:v>2026</x:v>
@@ -2278,13 +2296,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F45" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="H45" s="1">
-        <x:v>771658</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="I45" s="1">
         <x:v>2026</x:v>
@@ -2301,22 +2319,22 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F46" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="H46" s="1">
-        <x:v>103020</x:v>
+        <x:v>157560</x:v>
       </x:c>
       <x:c r="I46" s="1">
         <x:v>2026</x:v>
@@ -2327,28 +2345,28 @@
     </x:row>
     <x:row r="47" spans="1:10">
       <x:c r="A47" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>138</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>139</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F47" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H47" s="1">
-        <x:v>1762153</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="I47" s="1">
         <x:v>2026</x:v>
@@ -2359,28 +2377,28 @@
     </x:row>
     <x:row r="48" spans="1:10">
       <x:c r="A48" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>140</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>141</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F48" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H48" s="1">
-        <x:v>487317</x:v>
+        <x:v>103020</x:v>
       </x:c>
       <x:c r="I48" s="1">
         <x:v>2026</x:v>
@@ -2391,28 +2409,28 @@
     </x:row>
     <x:row r="49" spans="1:10">
       <x:c r="A49" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>143</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F49" s="1" t="s">
-        <x:v>144</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
-        <x:v>145</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="H49" s="1">
-        <x:v>300000</x:v>
+        <x:v>1762153</x:v>
       </x:c>
       <x:c r="I49" s="1">
         <x:v>2026</x:v>
@@ -2423,28 +2441,28 @@
     </x:row>
     <x:row r="50" spans="1:10">
       <x:c r="A50" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>143</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F50" s="1" t="s">
-        <x:v>144</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
-        <x:v>145</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="H50" s="1">
-        <x:v>1012628</x:v>
+        <x:v>487317</x:v>
       </x:c>
       <x:c r="I50" s="1">
         <x:v>2026</x:v>
@@ -2461,27 +2479,91 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>147</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F51" s="1" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="G51" s="1" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="H51" s="1">
+        <x:v>300000</x:v>
+      </x:c>
+      <x:c r="I51" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J51" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:10">
+      <x:c r="A52" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B52" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C52" s="1" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="D52" s="1" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="E52" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F52" s="1" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="G52" s="1" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="H52" s="1">
+        <x:v>1012628</x:v>
+      </x:c>
+      <x:c r="I52" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J52" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:10">
+      <x:c r="A53" s="1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B53" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C53" s="1" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="D53" s="1" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="E53" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="F51" s="1" t="s">
+      <x:c r="F53" s="1" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="G51" s="1" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="H51" s="1">
+      <x:c r="G53" s="1" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="H53" s="1">
         <x:v>150000</x:v>
       </x:c>
-      <x:c r="I51" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J51" s="1" t="s">
+      <x:c r="I53" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J53" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -1342,7 +1342,7 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="H15" s="1">
-        <x:v>50571</x:v>
+        <x:v>101142</x:v>
       </x:c>
       <x:c r="I15" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -1342,7 +1342,7 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="H15" s="1">
-        <x:v>101142</x:v>
+        <x:v>151713</x:v>
       </x:c>
       <x:c r="I15" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -46,6 +46,30 @@
     <x:t>expenditure_description</x:t>
   </x:si>
   <x:si>
+    <x:t>C00848440</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PROTECT PROGRESS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H0MA04192</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AUCHINCLOSS, JAKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>House</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUPPORT</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00836221</x:t>
   </x:si>
   <x:si>
@@ -58,22 +82,7 @@
     <x:t>BAIRD, JAMES R DR.</x:t>
   </x:si>
   <x:si>
-    <x:t>House</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04</x:t>
-  </x:si>
-  <x:si>
     <x:t>IN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SUPPORT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00848440</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PROTECT PROGRESS</x:t>
   </x:si>
   <x:si>
     <x:t>H4MD05235</x:t>
@@ -549,8 +558,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J53" totalsRowShown="0">
-  <x:autoFilter ref="A1:J53"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J54" totalsRowShown="0">
+  <x:autoFilter ref="A1:J54"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -855,7 +864,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J53"/>
+  <x:dimension ref="A1:J54"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -926,7 +935,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="H2" s="1">
-        <x:v>513868</x:v>
+        <x:v>47382</x:v>
       </x:c>
       <x:c r="I2" s="1">
         <x:v>2026</x:v>
@@ -952,19 +961,19 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F3" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G3" s="1" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="G3" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
       <x:c r="H3" s="1">
-        <x:v>98455</x:v>
+        <x:v>513868</x:v>
       </x:c>
       <x:c r="I3" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J3" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:10">
@@ -975,54 +984,54 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="D4" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E4" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F4" s="1" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="D4" s="1" t="s">
+      <x:c r="G4" s="1" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="E4" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F4" s="1" t="s">
+      <x:c r="H4" s="1">
+        <x:v>98455</x:v>
+      </x:c>
+      <x:c r="I4" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J4" s="1" t="s">
         <x:v>27</x:v>
-      </x:c>
-      <x:c r="G4" s="1" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="H4" s="1">
-        <x:v>7170138</x:v>
-      </x:c>
-      <x:c r="I4" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J4" s="1" t="s">
-        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:10">
       <x:c r="A5" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B5" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C5" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D5" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="B5" s="1" t="s">
+      <x:c r="E5" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F5" s="1" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="C5" s="1" t="s">
+      <x:c r="G5" s="1" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="D5" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E5" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="F5" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="G5" s="1" t="s">
-        <x:v>28</x:v>
-      </x:c>
       <x:c r="H5" s="1">
-        <x:v>628597</x:v>
+        <x:v>7170138</x:v>
       </x:c>
       <x:c r="I5" s="1">
         <x:v>2026</x:v>
@@ -1033,28 +1042,28 @@
     </x:row>
     <x:row r="6" spans="1:10">
       <x:c r="A6" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
         <x:v>34</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E6" s="1" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="E6" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
       <x:c r="F6" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="G6" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="H6" s="1">
-        <x:v>508142</x:v>
+        <x:v>628597</x:v>
       </x:c>
       <x:c r="I6" s="1">
         <x:v>2026</x:v>
@@ -1080,13 +1089,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F7" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H7" s="1">
-        <x:v>1965632</x:v>
+        <x:v>508142</x:v>
       </x:c>
       <x:c r="I7" s="1">
         <x:v>2026</x:v>
@@ -1103,22 +1112,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F8" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H8" s="1">
-        <x:v>348433</x:v>
+        <x:v>1965632</x:v>
       </x:c>
       <x:c r="I8" s="1">
         <x:v>2026</x:v>
@@ -1129,28 +1138,28 @@
     </x:row>
     <x:row r="9" spans="1:10">
       <x:c r="A9" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D9" s="1" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="D9" s="1" t="s">
+      <x:c r="E9" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F9" s="1" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="E9" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F9" s="1" t="s">
+      <x:c r="G9" s="1" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="G9" s="1" t="s">
-        <x:v>46</x:v>
-      </x:c>
       <x:c r="H9" s="1">
-        <x:v>547042</x:v>
+        <x:v>348433</x:v>
       </x:c>
       <x:c r="I9" s="1">
         <x:v>2026</x:v>
@@ -1161,28 +1170,28 @@
     </x:row>
     <x:row r="10" spans="1:10">
       <x:c r="A10" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D10" s="1" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="D10" s="1" t="s">
+      <x:c r="E10" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F10" s="1" t="s">
         <x:v>48</x:v>
-      </x:c>
-      <x:c r="E10" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="F10" s="1" t="s">
-        <x:v>33</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="H10" s="1">
-        <x:v>350000</x:v>
+        <x:v>547042</x:v>
       </x:c>
       <x:c r="I10" s="1">
         <x:v>2026</x:v>
@@ -1193,10 +1202,10 @@
     </x:row>
     <x:row r="11" spans="1:10">
       <x:c r="A11" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
         <x:v>50</x:v>
@@ -1205,16 +1214,16 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F11" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G11" s="1" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="G11" s="1" t="s">
-        <x:v>42</x:v>
-      </x:c>
       <x:c r="H11" s="1">
-        <x:v>616386</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I11" s="1">
         <x:v>2026</x:v>
@@ -1240,13 +1249,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F12" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="H12" s="1">
-        <x:v>516368</x:v>
+        <x:v>616386</x:v>
       </x:c>
       <x:c r="I12" s="1">
         <x:v>2026</x:v>
@@ -1257,28 +1266,28 @@
     </x:row>
     <x:row r="13" spans="1:10">
       <x:c r="A13" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H13" s="1">
-        <x:v>113120</x:v>
+        <x:v>516368</x:v>
       </x:c>
       <x:c r="I13" s="1">
         <x:v>2026</x:v>
@@ -1289,10 +1298,10 @@
     </x:row>
     <x:row r="14" spans="1:10">
       <x:c r="A14" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
         <x:v>58</x:v>
@@ -1304,51 +1313,51 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F14" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H14" s="1">
-        <x:v>172296</x:v>
+        <x:v>113120</x:v>
       </x:c>
       <x:c r="I14" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J14" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:10">
       <x:c r="A15" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F15" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H15" s="1">
-        <x:v>151713</x:v>
+        <x:v>172296</x:v>
       </x:c>
       <x:c r="I15" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J15" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:10">
@@ -1359,22 +1368,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="D16" s="1" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="D16" s="1" t="s">
+      <x:c r="E16" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F16" s="1" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="E16" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F16" s="1" t="s">
+      <x:c r="G16" s="1" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="G16" s="1" t="s">
-        <x:v>49</x:v>
-      </x:c>
       <x:c r="H16" s="1">
-        <x:v>455146</x:v>
+        <x:v>151713</x:v>
       </x:c>
       <x:c r="I16" s="1">
         <x:v>2026</x:v>
@@ -1385,28 +1394,28 @@
     </x:row>
     <x:row r="17" spans="1:10">
       <x:c r="A17" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F17" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="H17" s="1">
-        <x:v>300000</x:v>
+        <x:v>455146</x:v>
       </x:c>
       <x:c r="I17" s="1">
         <x:v>2026</x:v>
@@ -1417,10 +1426,10 @@
     </x:row>
     <x:row r="18" spans="1:10">
       <x:c r="A18" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
         <x:v>67</x:v>
@@ -1435,10 +1444,10 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="H18" s="1">
-        <x:v>708827</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="I18" s="1">
         <x:v>2026</x:v>
@@ -1449,10 +1458,10 @@
     </x:row>
     <x:row r="19" spans="1:10">
       <x:c r="A19" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
         <x:v>70</x:v>
@@ -1464,13 +1473,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F19" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="H19" s="1">
-        <x:v>91656</x:v>
+        <x:v>708827</x:v>
       </x:c>
       <x:c r="I19" s="1">
         <x:v>2026</x:v>
@@ -1481,28 +1490,28 @@
     </x:row>
     <x:row r="20" spans="1:10">
       <x:c r="A20" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="D20" s="1" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="E20" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F20" s="1" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="D20" s="1" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="E20" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="F20" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="H20" s="1">
-        <x:v>550000</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="I20" s="1">
         <x:v>2026</x:v>
@@ -1513,10 +1522,10 @@
     </x:row>
     <x:row r="21" spans="1:10">
       <x:c r="A21" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
         <x:v>75</x:v>
@@ -1525,16 +1534,16 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F21" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
         <x:v>77</x:v>
       </x:c>
       <x:c r="H21" s="1">
-        <x:v>515838</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="I21" s="1">
         <x:v>2026</x:v>
@@ -1545,10 +1554,10 @@
     </x:row>
     <x:row r="22" spans="1:10">
       <x:c r="A22" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
         <x:v>78</x:v>
@@ -1557,16 +1566,16 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F22" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
         <x:v>80</x:v>
       </x:c>
       <x:c r="H22" s="1">
-        <x:v>735613</x:v>
+        <x:v>515838</x:v>
       </x:c>
       <x:c r="I22" s="1">
         <x:v>2026</x:v>
@@ -1577,28 +1586,28 @@
     </x:row>
     <x:row r="23" spans="1:10">
       <x:c r="A23" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F23" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="H23" s="1">
-        <x:v>300000</x:v>
+        <x:v>735613</x:v>
       </x:c>
       <x:c r="I23" s="1">
         <x:v>2026</x:v>
@@ -1609,10 +1618,10 @@
     </x:row>
     <x:row r="24" spans="1:10">
       <x:c r="A24" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
         <x:v>81</x:v>
@@ -1621,16 +1630,16 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F24" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G24" s="1" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="G24" s="1" t="s">
-        <x:v>84</x:v>
-      </x:c>
       <x:c r="H24" s="1">
-        <x:v>418060</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="I24" s="1">
         <x:v>2026</x:v>
@@ -1641,28 +1650,28 @@
     </x:row>
     <x:row r="25" spans="1:10">
       <x:c r="A25" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="D25" s="1" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="D25" s="1" t="s">
+      <x:c r="E25" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F25" s="1" t="s">
         <x:v>86</x:v>
-      </x:c>
-      <x:c r="E25" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F25" s="1" t="s">
-        <x:v>15</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
         <x:v>87</x:v>
       </x:c>
       <x:c r="H25" s="1">
-        <x:v>511996</x:v>
+        <x:v>418060</x:v>
       </x:c>
       <x:c r="I25" s="1">
         <x:v>2026</x:v>
@@ -1673,10 +1682,10 @@
     </x:row>
     <x:row r="26" spans="1:10">
       <x:c r="A26" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
         <x:v>88</x:v>
@@ -1688,13 +1697,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F26" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H26" s="1">
-        <x:v>430866</x:v>
+        <x:v>511996</x:v>
       </x:c>
       <x:c r="I26" s="1">
         <x:v>2026</x:v>
@@ -1705,25 +1714,25 @@
     </x:row>
     <x:row r="27" spans="1:10">
       <x:c r="A27" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F27" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="H27" s="1">
         <x:v>430866</x:v>
@@ -1737,28 +1746,28 @@
     </x:row>
     <x:row r="28" spans="1:10">
       <x:c r="A28" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F28" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="H28" s="1">
-        <x:v>350000</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="I28" s="1">
         <x:v>2026</x:v>
@@ -1769,10 +1778,10 @@
     </x:row>
     <x:row r="29" spans="1:10">
       <x:c r="A29" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
         <x:v>95</x:v>
@@ -1781,16 +1790,16 @@
         <x:v>96</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F29" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H29" s="1">
-        <x:v>506917</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I29" s="1">
         <x:v>2026</x:v>
@@ -1807,28 +1816,28 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F30" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H30" s="1">
-        <x:v>268690</x:v>
+        <x:v>506917</x:v>
       </x:c>
       <x:c r="I30" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J30" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:10">
@@ -1851,16 +1860,16 @@
         <x:v>102</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H31" s="1">
-        <x:v>461943</x:v>
+        <x:v>268690</x:v>
       </x:c>
       <x:c r="I31" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J31" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:10">
@@ -1883,10 +1892,10 @@
         <x:v>105</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="H32" s="1">
-        <x:v>34890</x:v>
+        <x:v>461943</x:v>
       </x:c>
       <x:c r="I32" s="1">
         <x:v>2026</x:v>
@@ -1897,28 +1906,28 @@
     </x:row>
     <x:row r="33" spans="1:10">
       <x:c r="A33" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="D33" s="1" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="D33" s="1" t="s">
+      <x:c r="E33" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F33" s="1" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="E33" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="F33" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="H33" s="1">
-        <x:v>250000</x:v>
+        <x:v>34890</x:v>
       </x:c>
       <x:c r="I33" s="1">
         <x:v>2026</x:v>
@@ -1929,28 +1938,28 @@
     </x:row>
     <x:row r="34" spans="1:10">
       <x:c r="A34" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F34" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H34" s="1">
-        <x:v>400022</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="I34" s="1">
         <x:v>2026</x:v>
@@ -1961,10 +1970,10 @@
     </x:row>
     <x:row r="35" spans="1:10">
       <x:c r="A35" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
         <x:v>112</x:v>
@@ -1973,16 +1982,16 @@
         <x:v>113</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F35" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="H35" s="1">
-        <x:v>12203100</x:v>
+        <x:v>400022</x:v>
       </x:c>
       <x:c r="I35" s="1">
         <x:v>2026</x:v>
@@ -1993,28 +2002,28 @@
     </x:row>
     <x:row r="36" spans="1:10">
       <x:c r="A36" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F36" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="H36" s="1">
-        <x:v>350000</x:v>
+        <x:v>12203100</x:v>
       </x:c>
       <x:c r="I36" s="1">
         <x:v>2026</x:v>
@@ -2025,28 +2034,28 @@
     </x:row>
     <x:row r="37" spans="1:10">
       <x:c r="A37" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F37" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="H37" s="1">
-        <x:v>80948</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I37" s="1">
         <x:v>2026</x:v>
@@ -2057,10 +2066,10 @@
     </x:row>
     <x:row r="38" spans="1:10">
       <x:c r="A38" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
         <x:v>117</x:v>
@@ -2069,16 +2078,16 @@
         <x:v>118</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F38" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="H38" s="1">
-        <x:v>221403</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="I38" s="1">
         <x:v>2026</x:v>
@@ -2089,28 +2098,28 @@
     </x:row>
     <x:row r="39" spans="1:10">
       <x:c r="A39" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F39" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="H39" s="1">
-        <x:v>141263</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="I39" s="1">
         <x:v>2026</x:v>
@@ -2121,28 +2130,28 @@
     </x:row>
     <x:row r="40" spans="1:10">
       <x:c r="A40" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F40" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="H40" s="1">
-        <x:v>2250000</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="I40" s="1">
         <x:v>2026</x:v>
@@ -2153,28 +2162,28 @@
     </x:row>
     <x:row r="41" spans="1:10">
       <x:c r="A41" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F41" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="H41" s="1">
-        <x:v>350000</x:v>
+        <x:v>2250000</x:v>
       </x:c>
       <x:c r="I41" s="1">
         <x:v>2026</x:v>
@@ -2185,10 +2194,10 @@
     </x:row>
     <x:row r="42" spans="1:10">
       <x:c r="A42" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
         <x:v>126</x:v>
@@ -2197,16 +2206,16 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F42" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
         <x:v>128</x:v>
       </x:c>
       <x:c r="H42" s="1">
-        <x:v>411748</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I42" s="1">
         <x:v>2026</x:v>
@@ -2229,16 +2238,16 @@
         <x:v>130</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F43" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="H43" s="1">
-        <x:v>105040</x:v>
+        <x:v>411748</x:v>
       </x:c>
       <x:c r="I43" s="1">
         <x:v>2026</x:v>
@@ -2255,22 +2264,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F44" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H44" s="1">
-        <x:v>426280</x:v>
+        <x:v>105040</x:v>
       </x:c>
       <x:c r="I44" s="1">
         <x:v>2026</x:v>
@@ -2281,10 +2290,10 @@
     </x:row>
     <x:row r="45" spans="1:10">
       <x:c r="A45" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
         <x:v>134</x:v>
@@ -2299,10 +2308,10 @@
         <x:v>136</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="H45" s="1">
-        <x:v>282975</x:v>
+        <x:v>426280</x:v>
       </x:c>
       <x:c r="I45" s="1">
         <x:v>2026</x:v>
@@ -2328,13 +2337,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F46" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
-        <x:v>139</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="H46" s="1">
-        <x:v>157560</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="I46" s="1">
         <x:v>2026</x:v>
@@ -2360,13 +2369,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F47" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="H47" s="1">
-        <x:v>771658</x:v>
+        <x:v>157560</x:v>
       </x:c>
       <x:c r="I47" s="1">
         <x:v>2026</x:v>
@@ -2383,22 +2392,22 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>143</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F48" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="H48" s="1">
-        <x:v>103020</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="I48" s="1">
         <x:v>2026</x:v>
@@ -2409,28 +2418,28 @@
     </x:row>
     <x:row r="49" spans="1:10">
       <x:c r="A49" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>144</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>145</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F49" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H49" s="1">
-        <x:v>1762153</x:v>
+        <x:v>103020</x:v>
       </x:c>
       <x:c r="I49" s="1">
         <x:v>2026</x:v>
@@ -2447,22 +2456,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>147</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F50" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H50" s="1">
-        <x:v>487317</x:v>
+        <x:v>1762153</x:v>
       </x:c>
       <x:c r="I50" s="1">
         <x:v>2026</x:v>
@@ -2473,28 +2482,28 @@
     </x:row>
     <x:row r="51" spans="1:10">
       <x:c r="A51" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>148</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F51" s="1" t="s">
-        <x:v>150</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="H51" s="1">
-        <x:v>300000</x:v>
+        <x:v>487317</x:v>
       </x:c>
       <x:c r="I51" s="1">
         <x:v>2026</x:v>
@@ -2505,28 +2514,28 @@
     </x:row>
     <x:row r="52" spans="1:10">
       <x:c r="A52" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>148</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>149</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F52" s="1" t="s">
-        <x:v>150</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="G52" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="H52" s="1">
-        <x:v>1012628</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="I52" s="1">
         <x:v>2026</x:v>
@@ -2537,33 +2546,65 @@
     </x:row>
     <x:row r="53" spans="1:10">
       <x:c r="A53" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="D53" s="1" t="s">
         <x:v>152</x:v>
       </x:c>
-      <x:c r="D53" s="1" t="s">
+      <x:c r="E53" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F53" s="1" t="s">
         <x:v>153</x:v>
-      </x:c>
-      <x:c r="E53" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="F53" s="1" t="s">
-        <x:v>33</x:v>
       </x:c>
       <x:c r="G53" s="1" t="s">
         <x:v>154</x:v>
       </x:c>
       <x:c r="H53" s="1">
+        <x:v>1012628</x:v>
+      </x:c>
+      <x:c r="I53" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J53" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:10">
+      <x:c r="A54" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B54" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C54" s="1" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="D54" s="1" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="E54" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="F54" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G54" s="1" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="H54" s="1">
         <x:v>150000</x:v>
       </x:c>
-      <x:c r="I53" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J53" s="1" t="s">
+      <x:c r="I54" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J54" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -85,244 +85,214 @@
     <x:t>IN</x:t>
   </x:si>
   <x:si>
-    <x:t>H4MD05235</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAREEBE, QUINCY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MD</x:t>
+    <x:t>H0KY06104</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BARR, GARLAND ANDY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00915181</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FELLOWSHIP PAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>S6KY00286</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Senate</x:t>
+  </x:si>
+  <x:si>
+    <x:t>00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H2AK01083</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BEGICH, NICHOLAS III</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H6TX02244</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BONCK, JON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>38</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TX</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H0AL01055</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CARL, JERRY LEE, JR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>S6GA00390</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COLLINS, MICHAEL A JR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H6TX35087</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DE LA CRUZ, CARLOS JR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H0WA08046</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DELBENE, SUZAN K</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H2FL14053</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FRANKEL, LOIS J.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H0GA14030</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FULLER, CLAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H6GA10175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GAINES, HOUSTON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H6TX10221</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOBER, CHRIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>S0SC00149</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRAHAM, LINDSEY O.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>S6WY00209</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HAGEMAN, HARRIET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>S6OK04247</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HERN, KEVIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H4AR02141</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HILL, JAMES FRENCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H0MI02094</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HUIZENGA, WILLIAM P</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H2GA01157</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KINGSTON, JACK REP.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H6GA01109</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KINGSTON, JAMES MORRIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>S6LA00664</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LETLOW, JULIA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H6WA04216</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCKINNEY, AMANDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H6MI13254</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCKINNEY, DONAVAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13</x:t>
   </x:si>
   <x:si>
     <x:t>OPPOSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H0KY06104</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BARR, GARLAND ANDY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00915181</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FELLOWSHIP PAC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>S6KY00286</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Senate</x:t>
-  </x:si>
-  <x:si>
-    <x:t>00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H2AK01083</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BEGICH, NICHOLAS III</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6MD05321</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOAFO, ADRIAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6TX02244</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BONCK, JON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>38</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TX</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H0AL01055</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CARL, JERRY LEE, JR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>S6GA00390</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COLLINS, MICHAEL A JR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6TX35087</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DE LA CRUZ, CARLOS JR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>35</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H4MD06340</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DELANEY, APRIL MCCLAIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H0WA08046</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DELBENE, SUZAN K</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H4MD03263</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DUNN, HARRY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H2FL14053</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FRANKEL, LOIS J.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H0GA14030</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FULLER, CLAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6GA10175</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GAINES, HOUSTON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6TX10221</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOBER, CHRIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>S0SC00149</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRAHAM, LINDSEY O.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>S6WY00209</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HAGEMAN, HARRIET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>S6OK04247</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HERN, KEVIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H4AR02141</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HILL, JAMES FRENCH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H0MI02094</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HUIZENGA, WILLIAM P</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H2GA01157</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KINGSTON, JACK REP.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6GA01109</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KINGSTON, JAMES MORRIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>S6LA00664</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LETLOW, JULIA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6WA04216</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MCKINNEY, AMANDA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6MI13254</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MCKINNEY, DONAVAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13</x:t>
   </x:si>
   <x:si>
     <x:t>H6TX09140</x:t>
@@ -558,8 +528,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J54" totalsRowShown="0">
-  <x:autoFilter ref="A1:J54"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J49" totalsRowShown="0">
+  <x:autoFilter ref="A1:J49"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -864,7 +834,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J54"/>
+  <x:dimension ref="A1:J49"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -978,10 +948,10 @@
     </x:row>
     <x:row r="4" spans="1:10">
       <x:c r="A4" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
         <x:v>23</x:v>
@@ -999,39 +969,39 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="H4" s="1">
-        <x:v>98455</x:v>
+        <x:v>7170138</x:v>
       </x:c>
       <x:c r="I4" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J4" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:10">
       <x:c r="A5" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F5" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="G5" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H5" s="1">
-        <x:v>7170138</x:v>
+        <x:v>628597</x:v>
       </x:c>
       <x:c r="I5" s="1">
         <x:v>2026</x:v>
@@ -1042,28 +1012,28 @@
     </x:row>
     <x:row r="6" spans="1:10">
       <x:c r="A6" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B6" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C6" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="B6" s="1" t="s">
+      <x:c r="D6" s="1" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C6" s="1" t="s">
+      <x:c r="E6" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F6" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="G6" s="1" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="D6" s="1" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E6" s="1" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="F6" s="1" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="G6" s="1" t="s">
-        <x:v>31</x:v>
-      </x:c>
       <x:c r="H6" s="1">
-        <x:v>628597</x:v>
+        <x:v>508142</x:v>
       </x:c>
       <x:c r="I6" s="1">
         <x:v>2026</x:v>
@@ -1080,22 +1050,22 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D7" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E7" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F7" s="1" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="D7" s="1" t="s">
+      <x:c r="G7" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="E7" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F7" s="1" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="G7" s="1" t="s">
-        <x:v>39</x:v>
-      </x:c>
       <x:c r="H7" s="1">
-        <x:v>508142</x:v>
+        <x:v>348433</x:v>
       </x:c>
       <x:c r="I7" s="1">
         <x:v>2026</x:v>
@@ -1106,28 +1076,28 @@
     </x:row>
     <x:row r="8" spans="1:10">
       <x:c r="A8" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D8" s="1" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D8" s="1" t="s">
+      <x:c r="E8" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F8" s="1" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="E8" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F8" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
       <x:c r="G8" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H8" s="1">
-        <x:v>1965632</x:v>
+        <x:v>547042</x:v>
       </x:c>
       <x:c r="I8" s="1">
         <x:v>2026</x:v>
@@ -1138,28 +1108,28 @@
     </x:row>
     <x:row r="9" spans="1:10">
       <x:c r="A9" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F9" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
         <x:v>45</x:v>
       </x:c>
       <x:c r="H9" s="1">
-        <x:v>348433</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I9" s="1">
         <x:v>2026</x:v>
@@ -1188,10 +1158,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H10" s="1">
-        <x:v>547042</x:v>
+        <x:v>616386</x:v>
       </x:c>
       <x:c r="I10" s="1">
         <x:v>2026</x:v>
@@ -1202,28 +1172,28 @@
     </x:row>
     <x:row r="11" spans="1:10">
       <x:c r="A11" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D11" s="1" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="D11" s="1" t="s">
+      <x:c r="E11" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F11" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="G11" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="E11" s="1" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="F11" s="1" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="G11" s="1" t="s">
-        <x:v>52</x:v>
-      </x:c>
       <x:c r="H11" s="1">
-        <x:v>350000</x:v>
+        <x:v>113120</x:v>
       </x:c>
       <x:c r="I11" s="1">
         <x:v>2026</x:v>
@@ -1234,28 +1204,28 @@
     </x:row>
     <x:row r="12" spans="1:10">
       <x:c r="A12" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="D12" s="1" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="D12" s="1" t="s">
+      <x:c r="E12" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F12" s="1" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="E12" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F12" s="1" t="s">
+      <x:c r="G12" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="G12" s="1" t="s">
-        <x:v>45</x:v>
-      </x:c>
       <x:c r="H12" s="1">
-        <x:v>616386</x:v>
+        <x:v>151713</x:v>
       </x:c>
       <x:c r="I12" s="1">
         <x:v>2026</x:v>
@@ -1266,10 +1236,10 @@
     </x:row>
     <x:row r="13" spans="1:10">
       <x:c r="A13" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
         <x:v>56</x:v>
@@ -1281,13 +1251,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="H13" s="1">
-        <x:v>516368</x:v>
+        <x:v>455146</x:v>
       </x:c>
       <x:c r="I13" s="1">
         <x:v>2026</x:v>
@@ -1298,28 +1268,28 @@
     </x:row>
     <x:row r="14" spans="1:10">
       <x:c r="A14" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="D14" s="1" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E14" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F14" s="1" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="D14" s="1" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="E14" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F14" s="1" t="s">
-        <x:v>48</x:v>
-      </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="H14" s="1">
-        <x:v>113120</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="I14" s="1">
         <x:v>2026</x:v>
@@ -1330,60 +1300,60 @@
     </x:row>
     <x:row r="15" spans="1:10">
       <x:c r="A15" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="D15" s="1" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E15" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F15" s="1" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="D15" s="1" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="E15" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F15" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="H15" s="1">
-        <x:v>172296</x:v>
+        <x:v>708827</x:v>
       </x:c>
       <x:c r="I15" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J15" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:10">
       <x:c r="A16" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="D16" s="1" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="D16" s="1" t="s">
-        <x:v>64</x:v>
-      </x:c>
       <x:c r="E16" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F16" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H16" s="1">
-        <x:v>151713</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="I16" s="1">
         <x:v>2026</x:v>
@@ -1394,28 +1364,28 @@
     </x:row>
     <x:row r="17" spans="1:10">
       <x:c r="A17" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F17" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="H17" s="1">
-        <x:v>455146</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="I17" s="1">
         <x:v>2026</x:v>
@@ -1426,10 +1396,10 @@
     </x:row>
     <x:row r="18" spans="1:10">
       <x:c r="A18" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
         <x:v>67</x:v>
@@ -1438,16 +1408,16 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F18" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="G18" s="1" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="G18" s="1" t="s">
-        <x:v>52</x:v>
-      </x:c>
       <x:c r="H18" s="1">
-        <x:v>300000</x:v>
+        <x:v>515838</x:v>
       </x:c>
       <x:c r="I18" s="1">
         <x:v>2026</x:v>
@@ -1470,16 +1440,16 @@
         <x:v>71</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F19" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="G19" s="1" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="G19" s="1" t="s">
-        <x:v>52</x:v>
-      </x:c>
       <x:c r="H19" s="1">
-        <x:v>708827</x:v>
+        <x:v>735613</x:v>
       </x:c>
       <x:c r="I19" s="1">
         <x:v>2026</x:v>
@@ -1490,28 +1460,28 @@
     </x:row>
     <x:row r="20" spans="1:10">
       <x:c r="A20" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F20" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="G20" s="1" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="G20" s="1" t="s">
-        <x:v>45</x:v>
-      </x:c>
       <x:c r="H20" s="1">
-        <x:v>91656</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="I20" s="1">
         <x:v>2026</x:v>
@@ -1522,28 +1492,28 @@
     </x:row>
     <x:row r="21" spans="1:10">
       <x:c r="A21" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="D21" s="1" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="E21" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F21" s="1" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="D21" s="1" t="s">
+      <x:c r="G21" s="1" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="E21" s="1" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="F21" s="1" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="G21" s="1" t="s">
-        <x:v>77</x:v>
-      </x:c>
       <x:c r="H21" s="1">
-        <x:v>550000</x:v>
+        <x:v>418060</x:v>
       </x:c>
       <x:c r="I21" s="1">
         <x:v>2026</x:v>
@@ -1560,22 +1530,22 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="D22" s="1" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="D22" s="1" t="s">
+      <x:c r="E22" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F22" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G22" s="1" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="E22" s="1" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="F22" s="1" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="G22" s="1" t="s">
-        <x:v>80</x:v>
-      </x:c>
       <x:c r="H22" s="1">
-        <x:v>515838</x:v>
+        <x:v>511996</x:v>
       </x:c>
       <x:c r="I22" s="1">
         <x:v>2026</x:v>
@@ -1592,22 +1562,22 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D23" s="1" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="D23" s="1" t="s">
-        <x:v>82</x:v>
-      </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F23" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="H23" s="1">
-        <x:v>735613</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="I23" s="1">
         <x:v>2026</x:v>
@@ -1618,28 +1588,28 @@
     </x:row>
     <x:row r="24" spans="1:10">
       <x:c r="A24" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F24" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="H24" s="1">
-        <x:v>300000</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="I24" s="1">
         <x:v>2026</x:v>
@@ -1650,10 +1620,10 @@
     </x:row>
     <x:row r="25" spans="1:10">
       <x:c r="A25" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
         <x:v>84</x:v>
@@ -1662,16 +1632,16 @@
         <x:v>85</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F25" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="G25" s="1" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="G25" s="1" t="s">
-        <x:v>87</x:v>
-      </x:c>
       <x:c r="H25" s="1">
-        <x:v>418060</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I25" s="1">
         <x:v>2026</x:v>
@@ -1688,10 +1658,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="D26" s="1" t="s">
         <x:v>88</x:v>
-      </x:c>
-      <x:c r="D26" s="1" t="s">
-        <x:v>89</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
         <x:v>14</x:v>
@@ -1700,10 +1670,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H26" s="1">
-        <x:v>511996</x:v>
+        <x:v>506917</x:v>
       </x:c>
       <x:c r="I26" s="1">
         <x:v>2026</x:v>
@@ -1714,34 +1684,34 @@
     </x:row>
     <x:row r="27" spans="1:10">
       <x:c r="A27" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D27" s="1" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="E27" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F27" s="1" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="D27" s="1" t="s">
+      <x:c r="G27" s="1" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="H27" s="1">
+        <x:v>268690</x:v>
+      </x:c>
+      <x:c r="I27" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J27" s="1" t="s">
         <x:v>92</x:v>
-      </x:c>
-      <x:c r="E27" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F27" s="1" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="G27" s="1" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="H27" s="1">
-        <x:v>430866</x:v>
-      </x:c>
-      <x:c r="I27" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J27" s="1" t="s">
-        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:10">
@@ -1761,13 +1731,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F28" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H28" s="1">
-        <x:v>430866</x:v>
+        <x:v>461943</x:v>
       </x:c>
       <x:c r="I28" s="1">
         <x:v>2026</x:v>
@@ -1778,28 +1748,28 @@
     </x:row>
     <x:row r="29" spans="1:10">
       <x:c r="A29" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F29" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="H29" s="1">
-        <x:v>350000</x:v>
+        <x:v>34890</x:v>
       </x:c>
       <x:c r="I29" s="1">
         <x:v>2026</x:v>
@@ -1810,28 +1780,28 @@
     </x:row>
     <x:row r="30" spans="1:10">
       <x:c r="A30" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F30" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="H30" s="1">
-        <x:v>506917</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="I30" s="1">
         <x:v>2026</x:v>
@@ -1842,34 +1812,34 @@
     </x:row>
     <x:row r="31" spans="1:10">
       <x:c r="A31" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F31" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="H31" s="1">
-        <x:v>268690</x:v>
+        <x:v>400022</x:v>
       </x:c>
       <x:c r="I31" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J31" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:10">
@@ -1880,22 +1850,22 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F32" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H32" s="1">
-        <x:v>461943</x:v>
+        <x:v>12203100</x:v>
       </x:c>
       <x:c r="I32" s="1">
         <x:v>2026</x:v>
@@ -1906,28 +1876,28 @@
     </x:row>
     <x:row r="33" spans="1:10">
       <x:c r="A33" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="D33" s="1" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="D33" s="1" t="s">
-        <x:v>107</x:v>
-      </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F33" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H33" s="1">
-        <x:v>34890</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I33" s="1">
         <x:v>2026</x:v>
@@ -1938,28 +1908,28 @@
     </x:row>
     <x:row r="34" spans="1:10">
       <x:c r="A34" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F34" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="H34" s="1">
-        <x:v>250000</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="I34" s="1">
         <x:v>2026</x:v>
@@ -1970,28 +1940,28 @@
     </x:row>
     <x:row r="35" spans="1:10">
       <x:c r="A35" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F35" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H35" s="1">
-        <x:v>400022</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="I35" s="1">
         <x:v>2026</x:v>
@@ -2008,22 +1978,22 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F36" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H36" s="1">
-        <x:v>12203100</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="I36" s="1">
         <x:v>2026</x:v>
@@ -2034,28 +2004,28 @@
     </x:row>
     <x:row r="37" spans="1:10">
       <x:c r="A37" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="D37" s="1" t="s">
         <x:v>115</x:v>
       </x:c>
-      <x:c r="D37" s="1" t="s">
-        <x:v>116</x:v>
-      </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F37" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H37" s="1">
-        <x:v>350000</x:v>
+        <x:v>2250000</x:v>
       </x:c>
       <x:c r="I37" s="1">
         <x:v>2026</x:v>
@@ -2066,28 +2036,28 @@
     </x:row>
     <x:row r="38" spans="1:10">
       <x:c r="A38" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="D38" s="1" t="s">
         <x:v>117</x:v>
       </x:c>
-      <x:c r="D38" s="1" t="s">
+      <x:c r="E38" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="F38" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="G38" s="1" t="s">
         <x:v>118</x:v>
       </x:c>
-      <x:c r="E38" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F38" s="1" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="G38" s="1" t="s">
-        <x:v>119</x:v>
-      </x:c>
       <x:c r="H38" s="1">
-        <x:v>80948</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I38" s="1">
         <x:v>2026</x:v>
@@ -2098,28 +2068,28 @@
     </x:row>
     <x:row r="39" spans="1:10">
       <x:c r="A39" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="D39" s="1" t="s">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="D39" s="1" t="s">
+      <x:c r="E39" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="F39" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="G39" s="1" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="E39" s="1" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="F39" s="1" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="G39" s="1" t="s">
-        <x:v>31</x:v>
-      </x:c>
       <x:c r="H39" s="1">
-        <x:v>221403</x:v>
+        <x:v>411748</x:v>
       </x:c>
       <x:c r="I39" s="1">
         <x:v>2026</x:v>
@@ -2130,10 +2100,10 @@
     </x:row>
     <x:row r="40" spans="1:10">
       <x:c r="A40" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
         <x:v>122</x:v>
@@ -2145,13 +2115,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F40" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H40" s="1">
-        <x:v>141263</x:v>
+        <x:v>105040</x:v>
       </x:c>
       <x:c r="I40" s="1">
         <x:v>2026</x:v>
@@ -2162,10 +2132,10 @@
     </x:row>
     <x:row r="41" spans="1:10">
       <x:c r="A41" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
         <x:v>124</x:v>
@@ -2174,16 +2144,16 @@
         <x:v>125</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F41" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H41" s="1">
-        <x:v>2250000</x:v>
+        <x:v>426280</x:v>
       </x:c>
       <x:c r="I41" s="1">
         <x:v>2026</x:v>
@@ -2194,28 +2164,28 @@
     </x:row>
     <x:row r="42" spans="1:10">
       <x:c r="A42" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F42" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="H42" s="1">
-        <x:v>350000</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="I42" s="1">
         <x:v>2026</x:v>
@@ -2226,28 +2196,28 @@
     </x:row>
     <x:row r="43" spans="1:10">
       <x:c r="A43" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F43" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="H43" s="1">
-        <x:v>411748</x:v>
+        <x:v>157560</x:v>
       </x:c>
       <x:c r="I43" s="1">
         <x:v>2026</x:v>
@@ -2258,28 +2228,28 @@
     </x:row>
     <x:row r="44" spans="1:10">
       <x:c r="A44" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F44" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H44" s="1">
-        <x:v>105040</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="I44" s="1">
         <x:v>2026</x:v>
@@ -2290,28 +2260,28 @@
     </x:row>
     <x:row r="45" spans="1:10">
       <x:c r="A45" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F45" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H45" s="1">
-        <x:v>426280</x:v>
+        <x:v>103020</x:v>
       </x:c>
       <x:c r="I45" s="1">
         <x:v>2026</x:v>
@@ -2322,10 +2292,10 @@
     </x:row>
     <x:row r="46" spans="1:10">
       <x:c r="A46" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
         <x:v>137</x:v>
@@ -2337,13 +2307,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F46" s="1" t="s">
-        <x:v>139</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="H46" s="1">
-        <x:v>282975</x:v>
+        <x:v>1762153</x:v>
       </x:c>
       <x:c r="I46" s="1">
         <x:v>2026</x:v>
@@ -2354,16 +2324,16 @@
     </x:row>
     <x:row r="47" spans="1:10">
       <x:c r="A47" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="D47" s="1" t="s">
         <x:v>140</x:v>
-      </x:c>
-      <x:c r="D47" s="1" t="s">
-        <x:v>141</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
         <x:v>14</x:v>
@@ -2372,10 +2342,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="H47" s="1">
-        <x:v>157560</x:v>
+        <x:v>487317</x:v>
       </x:c>
       <x:c r="I47" s="1">
         <x:v>2026</x:v>
@@ -2386,28 +2356,28 @@
     </x:row>
     <x:row r="48" spans="1:10">
       <x:c r="A48" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="D48" s="1" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="E48" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F48" s="1" t="s">
         <x:v>143</x:v>
       </x:c>
-      <x:c r="D48" s="1" t="s">
+      <x:c r="G48" s="1" t="s">
         <x:v>144</x:v>
       </x:c>
-      <x:c r="E48" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F48" s="1" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="G48" s="1" t="s">
-        <x:v>45</x:v>
-      </x:c>
       <x:c r="H48" s="1">
-        <x:v>771658</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="I48" s="1">
         <x:v>2026</x:v>
@@ -2418,10 +2388,10 @@
     </x:row>
     <x:row r="49" spans="1:10">
       <x:c r="A49" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
         <x:v>145</x:v>
@@ -2430,181 +2400,21 @@
         <x:v>146</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F49" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="H49" s="1">
-        <x:v>103020</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="I49" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J49" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50" spans="1:10">
-      <x:c r="A50" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B50" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C50" s="1" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="D50" s="1" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="E50" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F50" s="1" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="G50" s="1" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="H50" s="1">
-        <x:v>1762153</x:v>
-      </x:c>
-      <x:c r="I50" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J50" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51" spans="1:10">
-      <x:c r="A51" s="1" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="B51" s="1" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C51" s="1" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="D51" s="1" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="E51" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F51" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G51" s="1" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="H51" s="1">
-        <x:v>487317</x:v>
-      </x:c>
-      <x:c r="I51" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J51" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="52" spans="1:10">
-      <x:c r="A52" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="B52" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C52" s="1" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="D52" s="1" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="E52" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F52" s="1" t="s">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c r="G52" s="1" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="H52" s="1">
-        <x:v>300000</x:v>
-      </x:c>
-      <x:c r="I52" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J52" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="53" spans="1:10">
-      <x:c r="A53" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B53" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C53" s="1" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="D53" s="1" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="E53" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F53" s="1" t="s">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c r="G53" s="1" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="H53" s="1">
-        <x:v>1012628</x:v>
-      </x:c>
-      <x:c r="I53" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J53" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="54" spans="1:10">
-      <x:c r="A54" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="B54" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C54" s="1" t="s">
-        <x:v>155</x:v>
-      </x:c>
-      <x:c r="D54" s="1" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="E54" s="1" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="F54" s="1" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="G54" s="1" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="H54" s="1">
-        <x:v>150000</x:v>
-      </x:c>
-      <x:c r="I54" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J54" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -905,7 +905,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="H2" s="1">
-        <x:v>47382</x:v>
+        <x:v>94764</x:v>
       </x:c>
       <x:c r="I2" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -905,7 +905,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="H2" s="1">
-        <x:v>94764</x:v>
+        <x:v>142146</x:v>
       </x:c>
       <x:c r="I2" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -905,7 +905,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="H2" s="1">
-        <x:v>142146</x:v>
+        <x:v>189528</x:v>
       </x:c>
       <x:c r="I2" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -208,6 +208,18 @@
     <x:t>GOBER, CHRIS</x:t>
   </x:si>
   <x:si>
+    <x:t>H4NH02399</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOODLANDER, MAGGIE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NH</x:t>
+  </x:si>
+  <x:si>
     <x:t>S0SC00149</x:t>
   </x:si>
   <x:si>
@@ -239,9 +251,6 @@
   </x:si>
   <x:si>
     <x:t>HILL, JAMES FRENCH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02</x:t>
   </x:si>
   <x:si>
     <x:t>AR</x:t>
@@ -528,8 +537,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J49" totalsRowShown="0">
-  <x:autoFilter ref="A1:J49"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J50" totalsRowShown="0">
+  <x:autoFilter ref="A1:J50"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -834,7 +843,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J49"/>
+  <x:dimension ref="A1:J50"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1376,16 +1385,16 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F17" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H17" s="1">
-        <x:v>550000</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="I17" s="1">
         <x:v>2026</x:v>
@@ -1396,16 +1405,16 @@
     </x:row>
     <x:row r="18" spans="1:10">
       <x:c r="A18" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
         <x:v>30</x:v>
@@ -1414,10 +1423,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="H18" s="1">
-        <x:v>515838</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="I18" s="1">
         <x:v>2026</x:v>
@@ -1434,10 +1443,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
         <x:v>30</x:v>
@@ -1446,10 +1455,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="H19" s="1">
-        <x:v>735613</x:v>
+        <x:v>515838</x:v>
       </x:c>
       <x:c r="I19" s="1">
         <x:v>2026</x:v>
@@ -1460,16 +1469,16 @@
     </x:row>
     <x:row r="20" spans="1:10">
       <x:c r="A20" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
         <x:v>30</x:v>
@@ -1478,10 +1487,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="H20" s="1">
-        <x:v>300000</x:v>
+        <x:v>735613</x:v>
       </x:c>
       <x:c r="I20" s="1">
         <x:v>2026</x:v>
@@ -1492,28 +1501,28 @@
     </x:row>
     <x:row r="21" spans="1:10">
       <x:c r="A21" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F21" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
         <x:v>76</x:v>
       </x:c>
       <x:c r="H21" s="1">
-        <x:v>418060</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="I21" s="1">
         <x:v>2026</x:v>
@@ -1539,13 +1548,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F22" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
         <x:v>79</x:v>
       </x:c>
       <x:c r="H22" s="1">
-        <x:v>511996</x:v>
+        <x:v>418060</x:v>
       </x:c>
       <x:c r="I22" s="1">
         <x:v>2026</x:v>
@@ -1571,13 +1580,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F23" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="H23" s="1">
-        <x:v>430866</x:v>
+        <x:v>511996</x:v>
       </x:c>
       <x:c r="I23" s="1">
         <x:v>2026</x:v>
@@ -1594,10 +1603,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
         <x:v>14</x:v>
@@ -1620,28 +1629,28 @@
     </x:row>
     <x:row r="25" spans="1:10">
       <x:c r="A25" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F25" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="H25" s="1">
-        <x:v>350000</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="I25" s="1">
         <x:v>2026</x:v>
@@ -1652,10 +1661,10 @@
     </x:row>
     <x:row r="26" spans="1:10">
       <x:c r="A26" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
         <x:v>87</x:v>
@@ -1664,16 +1673,16 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F26" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="H26" s="1">
-        <x:v>506917</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I26" s="1">
         <x:v>2026</x:v>
@@ -1684,74 +1693,74 @@
     </x:row>
     <x:row r="27" spans="1:10">
       <x:c r="A27" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F27" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H27" s="1">
-        <x:v>268690</x:v>
+        <x:v>506917</x:v>
       </x:c>
       <x:c r="I27" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J27" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:10">
       <x:c r="A28" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D28" s="1" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="D28" s="1" t="s">
+      <x:c r="E28" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F28" s="1" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="E28" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F28" s="1" t="s">
+      <x:c r="G28" s="1" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="H28" s="1">
+        <x:v>268690</x:v>
+      </x:c>
+      <x:c r="I28" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J28" s="1" t="s">
         <x:v>95</x:v>
-      </x:c>
-      <x:c r="G28" s="1" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="H28" s="1">
-        <x:v>461943</x:v>
-      </x:c>
-      <x:c r="I28" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J28" s="1" t="s">
-        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:10">
       <x:c r="A29" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
         <x:v>96</x:v>
@@ -1766,10 +1775,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H29" s="1">
-        <x:v>34890</x:v>
+        <x:v>461943</x:v>
       </x:c>
       <x:c r="I29" s="1">
         <x:v>2026</x:v>
@@ -1780,28 +1789,28 @@
     </x:row>
     <x:row r="30" spans="1:10">
       <x:c r="A30" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D30" s="1" t="s">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="D30" s="1" t="s">
+      <x:c r="E30" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F30" s="1" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="E30" s="1" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="F30" s="1" t="s">
-        <x:v>31</x:v>
-      </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="H30" s="1">
-        <x:v>250000</x:v>
+        <x:v>34890</x:v>
       </x:c>
       <x:c r="I30" s="1">
         <x:v>2026</x:v>
@@ -1812,28 +1821,28 @@
     </x:row>
     <x:row r="31" spans="1:10">
       <x:c r="A31" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F31" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="H31" s="1">
-        <x:v>400022</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="I31" s="1">
         <x:v>2026</x:v>
@@ -1856,16 +1865,16 @@
         <x:v>106</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F32" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="H32" s="1">
-        <x:v>12203100</x:v>
+        <x:v>400022</x:v>
       </x:c>
       <x:c r="I32" s="1">
         <x:v>2026</x:v>
@@ -1876,16 +1885,16 @@
     </x:row>
     <x:row r="33" spans="1:10">
       <x:c r="A33" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
         <x:v>30</x:v>
@@ -1897,7 +1906,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="H33" s="1">
-        <x:v>350000</x:v>
+        <x:v>12203100</x:v>
       </x:c>
       <x:c r="I33" s="1">
         <x:v>2026</x:v>
@@ -1908,28 +1917,28 @@
     </x:row>
     <x:row r="34" spans="1:10">
       <x:c r="A34" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F34" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H34" s="1">
-        <x:v>80948</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I34" s="1">
         <x:v>2026</x:v>
@@ -1940,10 +1949,10 @@
     </x:row>
     <x:row r="35" spans="1:10">
       <x:c r="A35" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
         <x:v>110</x:v>
@@ -1952,16 +1961,16 @@
         <x:v>111</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F35" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="H35" s="1">
-        <x:v>221403</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="I35" s="1">
         <x:v>2026</x:v>
@@ -1972,28 +1981,28 @@
     </x:row>
     <x:row r="36" spans="1:10">
       <x:c r="A36" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F36" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H36" s="1">
-        <x:v>141263</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="I36" s="1">
         <x:v>2026</x:v>
@@ -2004,28 +2013,28 @@
     </x:row>
     <x:row r="37" spans="1:10">
       <x:c r="A37" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F37" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="H37" s="1">
-        <x:v>2250000</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="I37" s="1">
         <x:v>2026</x:v>
@@ -2042,10 +2051,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
         <x:v>30</x:v>
@@ -2054,10 +2063,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H38" s="1">
-        <x:v>350000</x:v>
+        <x:v>2250000</x:v>
       </x:c>
       <x:c r="I38" s="1">
         <x:v>2026</x:v>
@@ -2068,10 +2077,10 @@
     </x:row>
     <x:row r="39" spans="1:10">
       <x:c r="A39" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
         <x:v>119</x:v>
@@ -2089,7 +2098,7 @@
         <x:v>121</x:v>
       </x:c>
       <x:c r="H39" s="1">
-        <x:v>411748</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I39" s="1">
         <x:v>2026</x:v>
@@ -2100,10 +2109,10 @@
     </x:row>
     <x:row r="40" spans="1:10">
       <x:c r="A40" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
         <x:v>122</x:v>
@@ -2112,16 +2121,16 @@
         <x:v>123</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F40" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="H40" s="1">
-        <x:v>105040</x:v>
+        <x:v>411748</x:v>
       </x:c>
       <x:c r="I40" s="1">
         <x:v>2026</x:v>
@@ -2132,28 +2141,28 @@
     </x:row>
     <x:row r="41" spans="1:10">
       <x:c r="A41" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F41" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H41" s="1">
-        <x:v>426280</x:v>
+        <x:v>105040</x:v>
       </x:c>
       <x:c r="I41" s="1">
         <x:v>2026</x:v>
@@ -2182,10 +2191,10 @@
         <x:v>129</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H42" s="1">
-        <x:v>282975</x:v>
+        <x:v>426280</x:v>
       </x:c>
       <x:c r="I42" s="1">
         <x:v>2026</x:v>
@@ -2196,10 +2205,10 @@
     </x:row>
     <x:row r="43" spans="1:10">
       <x:c r="A43" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
         <x:v>130</x:v>
@@ -2211,13 +2220,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F43" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="H43" s="1">
-        <x:v>157560</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="I43" s="1">
         <x:v>2026</x:v>
@@ -2228,10 +2237,10 @@
     </x:row>
     <x:row r="44" spans="1:10">
       <x:c r="A44" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
         <x:v>133</x:v>
@@ -2243,13 +2252,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F44" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="H44" s="1">
-        <x:v>771658</x:v>
+        <x:v>157560</x:v>
       </x:c>
       <x:c r="I44" s="1">
         <x:v>2026</x:v>
@@ -2260,28 +2269,28 @@
     </x:row>
     <x:row r="45" spans="1:10">
       <x:c r="A45" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F45" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H45" s="1">
-        <x:v>103020</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="I45" s="1">
         <x:v>2026</x:v>
@@ -2298,22 +2307,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>138</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F46" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H46" s="1">
-        <x:v>1762153</x:v>
+        <x:v>103020</x:v>
       </x:c>
       <x:c r="I46" s="1">
         <x:v>2026</x:v>
@@ -2324,28 +2333,28 @@
     </x:row>
     <x:row r="47" spans="1:10">
       <x:c r="A47" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F47" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="H47" s="1">
-        <x:v>487317</x:v>
+        <x:v>1762153</x:v>
       </x:c>
       <x:c r="I47" s="1">
         <x:v>2026</x:v>
@@ -2356,28 +2365,28 @@
     </x:row>
     <x:row r="48" spans="1:10">
       <x:c r="A48" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F48" s="1" t="s">
-        <x:v>143</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
-        <x:v>144</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="H48" s="1">
-        <x:v>300000</x:v>
+        <x:v>487317</x:v>
       </x:c>
       <x:c r="I48" s="1">
         <x:v>2026</x:v>
@@ -2394,27 +2403,59 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="D49" s="1" t="s">
         <x:v>145</x:v>
       </x:c>
-      <x:c r="D49" s="1" t="s">
+      <x:c r="E49" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F49" s="1" t="s">
         <x:v>146</x:v>
-      </x:c>
-      <x:c r="E49" s="1" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="F49" s="1" t="s">
-        <x:v>31</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
         <x:v>147</x:v>
       </x:c>
       <x:c r="H49" s="1">
+        <x:v>300000</x:v>
+      </x:c>
+      <x:c r="I49" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J49" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:10">
+      <x:c r="A50" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B50" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C50" s="1" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="D50" s="1" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="E50" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="F50" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="G50" s="1" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="H50" s="1">
         <x:v>150000</x:v>
       </x:c>
-      <x:c r="I49" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J49" s="1" t="s">
+      <x:c r="I50" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J50" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>
